--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6540F8EC-BBE5-4F7B-9FFC-523292C4CA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2DBBA0-0E83-4949-A983-BA907A393A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4189,7 +4189,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>0.94020000000000004</v>
+        <v>1.0598962000000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4211,7 +4211,7 @@
         <v>280</v>
       </c>
       <c r="C19" s="255">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="5"/>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C20" s="258">
         <f>C129</f>
-        <v>27.658966981315359</v>
+        <v>26.736896573077772</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>-5.7047688184643786E-2</v>
+        <v>-2.7445446695169684E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
-        <v>179630775.93084043</v>
+        <v>177569627.47223881</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>157793721.93084043</v>
+        <v>155732573.47223881</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-1008965448.0596488</v>
+        <v>-1008450160.9449984</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>3157349439.9308405</v>
+        <v>3155288291.4722385</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>2880261779.7072697</v>
+        <v>2878715918.3633184</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C125</f>
-        <v>3.6256932844595753E-2</v>
+        <v>4.0850840664093072E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>4.2738405022151121E-2</v>
+        <v>3.7911871371768754E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>24.813338415520217</v>
+        <v>27.957294079488697</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.19669426116300168</v>
+        <v>0.22173526905815044</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="C91" s="191">
         <f>Valuation_Model!C8</f>
-        <v>12742567110.786873</v>
+        <v>12802649228.826981</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>8.7821359080650598</v>
+        <v>9.9468635221318582</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.899020717592468</v>
+        <v>2.1407837080382155</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
-        <v>35.297800780014747</v>
+        <v>39.823206040600617</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="E107" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>53.68 HKD</v>
+        <v>60.54 HKD</v>
       </c>
       <c r="F107" s="265">
         <f>Valuation_Model!F74</f>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>40.6 HKD</v>
+        <v>45.8 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F75</f>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>38.66 HKD</v>
+        <v>43.61 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>36.9 HKD</v>
+        <v>41.63 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F77</f>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="E111" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>35.3 HKD</v>
+        <v>39.82 HKD</v>
       </c>
       <c r="F111" s="252">
         <f>Valuation_Model!F78</f>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="C113" s="247">
         <f>Scenarios!C60</f>
-        <v>39.277358206848447</v>
+        <v>44.30699034342598</v>
       </c>
       <c r="D113" s="242" t="str">
         <f>Market_currency</f>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="C123" s="256">
         <f>C19</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C124" s="243">
         <f>Scenarios!C77</f>
-        <v>2.339927674962774</v>
+        <v>2.0756749576043392</v>
       </c>
       <c r="D124" s="242" t="str">
         <f>Market_currency</f>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C127" s="246">
         <f>Scenarios!C81</f>
-        <v>4.9290143153151025</v>
+        <v>4.0517175172436701</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>22.729952666000258</v>
+        <v>22.685179055834102</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>27.658966981315359</v>
+        <v>26.736896573077772</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.29580378508010985</v>
+        <v>0.39655353780885183</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5845,23 +5845,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.339927674962774</v>
+        <v>2.0756749576043392</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>2.1272069772388851</v>
+        <v>1.8869772341857627</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.3826845352052755</v>
+        <v>1.2265352022207456</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.169963837481387</v>
+        <v>1.0378374788021696</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.79770261646458196</v>
+        <v>0.70761646281966095</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7183,23 +7183,23 @@
       </c>
       <c r="C65" s="75">
         <f t="shared" ref="C65:M65" si="33">IF(C$4="","",C25)</f>
-        <v>2.339927674962774</v>
+        <v>2.0756749576043392</v>
       </c>
       <c r="D65" s="75">
         <f t="shared" si="33"/>
-        <v>2.1272069772388851</v>
+        <v>1.8869772341857627</v>
       </c>
       <c r="E65" s="75">
         <f t="shared" si="33"/>
-        <v>1.3826845352052755</v>
+        <v>1.2265352022207456</v>
       </c>
       <c r="F65" s="75">
         <f t="shared" si="33"/>
-        <v>1.169963837481387</v>
+        <v>1.0378374788021696</v>
       </c>
       <c r="G65" s="75">
         <f t="shared" si="33"/>
-        <v>0.79770261646458196</v>
+        <v>0.70761646281966095</v>
       </c>
       <c r="H65" s="75" t="str">
         <f t="shared" si="33"/>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D72" s="94">
         <f t="shared" ref="D72:M72" si="38">IF(E$36="","",D65/E65-1)</f>
-        <v>0.53846153846153832</v>
+        <v>0.53846153846153855</v>
       </c>
       <c r="E72" s="94">
         <f t="shared" si="38"/>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="F72" s="94">
         <f t="shared" si="38"/>
-        <v>0.46666666666666679</v>
+        <v>0.46666666666666701</v>
       </c>
       <c r="G72" s="94" t="str">
         <f t="shared" si="38"/>
@@ -8538,11 +8538,11 @@
       </c>
       <c r="C47" s="151">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>20.02832272632898</v>
+        <v>22.578114390565549</v>
       </c>
       <c r="D47" s="151">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.1685753266721788</v>
+        <v>1.3173458287104882</v>
       </c>
       <c r="F47" s="289"/>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>12742567110.786873</v>
+        <v>12802649228.826981</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8800,11 +8800,11 @@
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2570179946.0280437</v>
+        <v>-2540138887.0079894</v>
       </c>
       <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2618102892.606564</v>
+        <v>-2588061833.5865102</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>365</v>
@@ -8816,11 +8816,11 @@
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
-        <v>6.9951416918431715</v>
+        <v>7.077870028271195</v>
       </c>
       <c r="D74" s="295">
         <f>-$C$66/D73</f>
-        <v>6.8670994355384041</v>
+        <v>6.9468096405893043</v>
       </c>
       <c r="F74" s="289" t="s">
         <v>332</v>
@@ -8833,7 +8833,7 @@
       <c r="C75" s="299"/>
       <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5236205785.2131281</v>
+        <v>5176123667.1730204</v>
       </c>
       <c r="F75" s="289" t="s">
         <v>366</v>
@@ -8948,11 +8948,11 @@
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-268329679.29660001</v>
+        <v>-302490541.83544463</v>
       </c>
       <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-0.19669426116300168</v>
+        <v>-0.22173526905815044</v>
       </c>
       <c r="E86" s="275" t="str">
         <f>Market_currency</f>
@@ -8965,11 +8965,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>11980561597.561819</v>
+        <v>13569479267.566648</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>8.7821359080650598</v>
+        <v>9.9468635221318582</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8982,11 +8982,11 @@
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2590637963.2851</v>
+        <v>2920450258.3084631</v>
       </c>
       <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
-        <v>1.899020717592468</v>
+        <v>2.1407837080382155</v>
       </c>
       <c r="E88" s="275" t="str">
         <f>Market_currency</f>
@@ -8999,11 +8999,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>14302869881.55032</v>
+        <v>16187438984.039665</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>10.484462364494526</v>
+        <v>11.865911961111923</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -9583,28 +9583,28 @@
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>157793721.93084043</v>
+        <v>155732573.47223881</v>
       </c>
       <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>157793721.93084043</v>
+        <v>155732573.47223881</v>
       </c>
       <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>131048271.41837943</v>
+        <v>129356045.64964005</v>
       </c>
       <c r="I12" s="197">
         <f t="shared" si="6"/>
-        <v>124635798.39910661</v>
+        <v>123099684.33648068</v>
       </c>
       <c r="J12" s="197">
         <f t="shared" si="6"/>
-        <v>69245239.208049491</v>
+        <v>68190394.199992597</v>
       </c>
       <c r="K12" s="197">
         <f t="shared" si="6"/>
-        <v>138957604.02296314</v>
+        <v>137206383.68971309</v>
       </c>
       <c r="L12" s="197" t="str">
         <f t="shared" si="6"/>
@@ -9638,28 +9638,28 @@
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>4035861792.238595</v>
+        <v>4033800643.7799935</v>
       </c>
       <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4693858581.9308405</v>
+        <v>4691797433.4722385</v>
       </c>
       <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4551716063.4183798</v>
+        <v>4550023837.6496401</v>
       </c>
       <c r="I13" s="187">
         <f t="shared" si="7"/>
-        <v>3871589006.3991065</v>
+        <v>3870052892.3364806</v>
       </c>
       <c r="J13" s="187">
         <f t="shared" si="7"/>
-        <v>3026336239.2080493</v>
+        <v>3025281394.1999927</v>
       </c>
       <c r="K13" s="187">
         <f t="shared" si="7"/>
-        <v>2473017476.022963</v>
+        <v>2471266255.689713</v>
       </c>
       <c r="L13" s="187" t="str">
         <f t="shared" si="7"/>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008965448.0596488</v>
+        <v>-1008450160.9449984</v>
       </c>
       <c r="E14" s="308"/>
       <c r="G14" s="197">
@@ -9805,30 +9805,30 @@
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>2880261779.7072697</v>
+        <v>2878715918.3633184</v>
       </c>
       <c r="D16" s="62"/>
       <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3157349439.9308405</v>
+        <v>3155288291.4722385</v>
       </c>
       <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3073160167.4183798</v>
+        <v>3071467941.6496401</v>
       </c>
       <c r="I16" s="187">
         <f t="shared" si="8"/>
-        <v>2576076313.3991065</v>
+        <v>2574540199.3364806</v>
       </c>
       <c r="J16" s="187">
         <f t="shared" si="8"/>
-        <v>1702816584.2080493</v>
+        <v>1701761739.1999927</v>
       </c>
       <c r="K16" s="187">
         <f t="shared" si="8"/>
-        <v>1434791708.022963</v>
+        <v>1433040487.689713</v>
       </c>
       <c r="L16" s="187" t="str">
         <f t="shared" si="8"/>
@@ -9913,30 +9913,30 @@
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>2880261779.7072697</v>
+        <v>2878715918.3633184</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3157349439.9308405</v>
+        <v>3155288291.4722385</v>
       </c>
       <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3073160167.4183798</v>
+        <v>3071467941.6496401</v>
       </c>
       <c r="I19" s="189">
         <f t="shared" si="9"/>
-        <v>2576076313.3991065</v>
+        <v>2574540199.3364806</v>
       </c>
       <c r="J19" s="189">
         <f t="shared" si="9"/>
-        <v>1702816584.2080493</v>
+        <v>1701761739.1999927</v>
       </c>
       <c r="K19" s="189">
         <f t="shared" si="9"/>
-        <v>1434791708.022963</v>
+        <v>1433040487.689713</v>
       </c>
       <c r="L19" s="189" t="str">
         <f t="shared" si="9"/>
@@ -10774,23 +10774,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29607119382542918</v>
+        <v>0.29620126054153162</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30718268857700515</v>
+        <v>0.30729693467326064</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31031697993104346</v>
+        <v>0.31044015196253882</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.4040303186271107</v>
+        <v>0.40417119456860967</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36901498992541948</v>
+        <v>0.36927648605200786</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10912,28 +10912,28 @@
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>179630775.93084043</v>
+        <v>177569627.47223881</v>
       </c>
       <c r="E48" s="308"/>
       <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>179630775.93084043</v>
+        <v>177569627.47223881</v>
       </c>
       <c r="H48" s="334">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>147478861.41837943</v>
+        <v>145786635.64964005</v>
       </c>
       <c r="I48" s="334">
         <f t="shared" si="19"/>
-        <v>133873598.39910661</v>
+        <v>132337484.33648068</v>
       </c>
       <c r="J48" s="334">
         <f t="shared" si="19"/>
-        <v>91930606.208049491</v>
+        <v>90875761.199992597</v>
       </c>
       <c r="K48" s="334">
         <f t="shared" si="19"/>
-        <v>152620286.02296314</v>
+        <v>150869065.68971309</v>
       </c>
       <c r="L48" s="334" t="str">
         <f t="shared" si="19"/>
@@ -11024,28 +11024,28 @@
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>157793721.93084043</v>
+        <v>155732573.47223881</v>
       </c>
       <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>157793721.93084043</v>
+        <v>155732573.47223881</v>
       </c>
       <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>131048271.41837943</v>
+        <v>129356045.64964005</v>
       </c>
       <c r="I50" s="187">
         <f t="shared" si="20"/>
-        <v>124635798.39910661</v>
+        <v>123099684.33648068</v>
       </c>
       <c r="J50" s="187">
         <f t="shared" si="20"/>
-        <v>69245239.208049491</v>
+        <v>68190394.199992597</v>
       </c>
       <c r="K50" s="187">
         <f t="shared" si="20"/>
-        <v>138957604.02296314</v>
+        <v>137206383.68971309</v>
       </c>
       <c r="L50" s="187" t="str">
         <f t="shared" si="20"/>
@@ -12111,30 +12111,30 @@
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>4.9152051976243168E-3</v>
+        <v>4.8510013275791302E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.9099059079546091E-3</v>
+        <v>4.8457712588049102E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8615703918320143E-3</v>
+        <v>3.811705949866222E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8740980111371471E-3</v>
+        <v>3.8263504417282157E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2954117395819432E-3</v>
+        <v>2.2604446625290602E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>5.0057295046546813E-3</v>
+        <v>4.9426445417774263E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12168,30 +12168,30 @@
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>0.12571532387580636</v>
+        <v>0.12565112000576117</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14605399822324178</v>
+        <v>0.14598986357409208</v>
       </c>
       <c r="H81" s="66">
         <f t="shared" si="32"/>
-        <v>0.13412440921412608</v>
+        <v>0.13407454477216027</v>
       </c>
       <c r="I81" s="66">
         <f t="shared" si="32"/>
-        <v>0.12034195200966222</v>
+        <v>0.12029420444025328</v>
       </c>
       <c r="J81" s="66">
         <f t="shared" si="32"/>
-        <v>0.10032007703127263</v>
+        <v>0.10028510995421976</v>
       </c>
       <c r="K81" s="66">
         <f t="shared" si="32"/>
-        <v>8.9086571636692091E-2</v>
+        <v>8.9023486673814836E-2</v>
       </c>
       <c r="L81" s="66" t="str">
         <f t="shared" si="32"/>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>3.142883096895159E-2</v>
+        <v>3.1412780001440294E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="305"/>
@@ -12340,30 +12340,30 @@
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>8.9718890567400122E-2</v>
+        <v>8.9670737664866232E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8244014266854821E-2</v>
+        <v>9.8179879617705107E-2</v>
       </c>
       <c r="H84" s="66">
         <f t="shared" si="35"/>
-        <v>9.0556130068846996E-2</v>
+        <v>9.0506265626881188E-2</v>
       </c>
       <c r="I84" s="66">
         <f t="shared" si="35"/>
-        <v>8.007307892648384E-2</v>
+        <v>8.0025331357074916E-2</v>
       </c>
       <c r="J84" s="66">
         <f t="shared" si="35"/>
-        <v>5.6446699043125173E-2</v>
+        <v>5.6411731966072298E-2</v>
       </c>
       <c r="K84" s="66">
         <f t="shared" si="35"/>
-        <v>5.168611848472543E-2</v>
+        <v>5.1623033521848175E-2</v>
       </c>
       <c r="L84" s="66" t="str">
         <f t="shared" si="35"/>
@@ -12447,30 +12447,30 @@
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>8.9718890567400122E-2</v>
+        <v>8.9670737664866232E-2</v>
       </c>
       <c r="D87" s="77"/>
       <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8244014266854821E-2</v>
+        <v>9.8179879617705107E-2</v>
       </c>
       <c r="H87" s="66">
         <f t="shared" si="36"/>
-        <v>9.0556130068846996E-2</v>
+        <v>9.0506265626881188E-2</v>
       </c>
       <c r="I87" s="66">
         <f t="shared" si="36"/>
-        <v>8.007307892648384E-2</v>
+        <v>8.0025331357074916E-2</v>
       </c>
       <c r="J87" s="66">
         <f t="shared" si="36"/>
-        <v>5.6446699043125173E-2</v>
+        <v>5.6411731966072298E-2</v>
       </c>
       <c r="K87" s="66">
         <f t="shared" si="36"/>
-        <v>5.168611848472543E-2</v>
+        <v>5.1623033521848175E-2</v>
       </c>
       <c r="L87" s="66" t="str">
         <f t="shared" si="36"/>
@@ -12516,28 +12516,28 @@
       </c>
       <c r="C90" s="117">
         <f>G90</f>
-        <v>2.339927674962774</v>
+        <v>2.0756749576043392</v>
       </c>
       <c r="E90" s="308"/>
       <c r="G90" s="116">
         <f>Data!C65</f>
-        <v>2.339927674962774</v>
+        <v>2.0756749576043392</v>
       </c>
       <c r="H90" s="116">
         <f>Data!D65</f>
-        <v>2.1272069772388851</v>
+        <v>1.8869772341857627</v>
       </c>
       <c r="I90" s="116">
         <f>Data!E65</f>
-        <v>1.3826845352052755</v>
+        <v>1.2265352022207456</v>
       </c>
       <c r="J90" s="116">
         <f>Data!F65</f>
-        <v>1.169963837481387</v>
+        <v>1.0378374788021696</v>
       </c>
       <c r="K90" s="116">
         <f>Data!G65</f>
-        <v>0.79770261646458196</v>
+        <v>0.70761646281966095</v>
       </c>
       <c r="L90" s="116" t="str">
         <f>Data!H65</f>
@@ -12572,28 +12572,28 @@
       </c>
       <c r="C91" s="76">
         <f>C90*Common_Shares/$C$3</f>
-        <v>3192121818.3365245</v>
+        <v>2831629110.0958757</v>
       </c>
       <c r="E91" s="308"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>3192121818.3365245</v>
+        <v>2831629110.0958757</v>
       </c>
       <c r="H91" s="76">
         <f t="shared" si="37"/>
-        <v>2901928925.7604761</v>
+        <v>2574208281.9053411</v>
       </c>
       <c r="I91" s="76">
         <f t="shared" si="37"/>
-        <v>1886253801.7443097</v>
+        <v>1673235383.2384717</v>
       </c>
       <c r="J91" s="76">
         <f t="shared" si="37"/>
-        <v>1596060909.1682622</v>
+        <v>1415814555.0479379</v>
       </c>
       <c r="K91" s="76">
         <f t="shared" si="37"/>
-        <v>1088223347.1601787</v>
+        <v>965328105.71450293</v>
       </c>
       <c r="L91" s="76" t="str">
         <f t="shared" si="37"/>
@@ -12627,28 +12627,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>1.1082748939094522</v>
+        <v>0.98364312089043715</v>
       </c>
       <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>1.011013154884258</v>
+        <v>0.89742326168701825</v>
       </c>
       <c r="H92" s="174">
         <f t="shared" si="38"/>
-        <v>0.94428170601932959</v>
+        <v>0.83810358135230023</v>
       </c>
       <c r="I92" s="174">
         <f t="shared" si="38"/>
-        <v>0.73221969082717786</v>
+        <v>0.64991620005378192</v>
       </c>
       <c r="J92" s="174">
         <f t="shared" si="38"/>
-        <v>0.93730641571744067</v>
+        <v>0.83196990650026015</v>
       </c>
       <c r="K92" s="174">
         <f t="shared" si="38"/>
-        <v>0.75845388642485956</v>
+        <v>0.67362235331589548</v>
       </c>
       <c r="L92" s="174" t="str">
         <f t="shared" si="38"/>
@@ -12682,28 +12682,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.2738405022151121E-2</v>
+        <v>3.7911871371768754E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.2738405022151121E-2</v>
+        <v>3.7911871371768754E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.8853095474682832E-2</v>
+        <v>3.4465337610698865E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.5254512058543843E-2</v>
+        <v>2.240246944695426E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>2.1369202511075561E-2</v>
+        <v>1.8955935685884377E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4569910803006063E-2</v>
+        <v>1.2924501604012073E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12819,26 +12819,26 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>-0.14018249127172799</v>
+        <v>-0.14024407469042932</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="305"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1228335979663457E-2</v>
+        <v>3.1158868806241857E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17567129566055018</v>
+        <v>0.17570068529545035</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27929902706787413</v>
+        <v>0.27923732970958226</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.22374235869732617</v>
+        <v>0.22418269874188756</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13430,23 +13430,23 @@
       <c r="E114" s="308"/>
       <c r="G114" s="340">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6325912700093497</v>
+        <v>1.6336577376880088</v>
       </c>
       <c r="H114" s="340">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90381463662315598</v>
+        <v>0.90431259344618442</v>
       </c>
       <c r="I114" s="340">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8938768609546783</v>
+        <v>1.8950068533625437</v>
       </c>
       <c r="J114" s="340">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5488915899950242</v>
+        <v>3.5510913871179755</v>
       </c>
       <c r="K114" s="340">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.4523633878714355</v>
+        <v>3.456582283997919</v>
       </c>
       <c r="L114" s="340" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13538,28 +13538,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12571532387580636</v>
+        <v>0.12565112000576117</v>
       </c>
       <c r="E117" s="308"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14605399822324178</v>
+        <v>0.14598986357409208</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13412440921412608</v>
+        <v>0.13407454477216027</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12034195200966222</v>
+        <v>0.12029420444025328</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10032007703127263</v>
+        <v>0.10028510995421976</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.9086571636692091E-2</v>
+        <v>8.9023486673814836E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13824,30 +13824,30 @@
       </c>
       <c r="C124" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.9850670732416174</v>
+        <v>2.2365835263590959</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="305"/>
       <c r="F124" s="27"/>
       <c r="G124" s="181">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.1760349896256876</v>
+        <v>2.4514630876230434</v>
       </c>
       <c r="H124" s="181">
         <f t="shared" si="49"/>
-        <v>2.1180120161716438</v>
+        <v>2.3863398802961231</v>
       </c>
       <c r="I124" s="181">
         <f t="shared" si="49"/>
-        <v>1.7754234368259192</v>
+        <v>2.0002578792349266</v>
       </c>
       <c r="J124" s="181">
         <f t="shared" si="49"/>
-        <v>1.1735756648566511</v>
+        <v>1.3221632073535297</v>
       </c>
       <c r="K124" s="181">
         <f t="shared" si="49"/>
-        <v>0.98885378982668426</v>
+        <v>1.1133834800881188</v>
       </c>
       <c r="L124" s="181" t="str">
         <f t="shared" si="49"/>
@@ -13881,30 +13881,30 @@
       </c>
       <c r="C125" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.6256932844595753E-2</v>
+        <v>4.0850840664093072E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="305"/>
       <c r="F125" s="27"/>
       <c r="G125" s="79">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.974493131736416E-2</v>
+        <v>4.4775581509096683E-2</v>
       </c>
       <c r="H125" s="79">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>3.8685150980303999E-2</v>
+        <v>4.3586116535089009E-2</v>
       </c>
       <c r="I125" s="79">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.2427825330153773E-2</v>
+        <v>3.6534390488309164E-2</v>
       </c>
       <c r="J125" s="79">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.1435171960852074E-2</v>
+        <v>2.414909967769004E-2</v>
       </c>
       <c r="K125" s="79">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.8061256435190579E-2</v>
+        <v>2.0335771325810388E-2</v>
       </c>
       <c r="L125" s="79" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>2880261779.7072697</v>
+        <v>2878715918.3633184</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>36003272246.340874</v>
+        <v>35983948979.541481</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>12742567110.786873</v>
+        <v>12802649228.826981</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>51215854549.627747</v>
+        <v>51256613400.868462</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14836,7 +14836,7 @@
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
-        <v>0.94020000000000004</v>
+        <v>1.0598962000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>35.297800780014747</v>
+        <v>39.823206040600617</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>39.279947779882377</v>
+        <v>44.309908026393003</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>3014409600.2267666</v>
+        <v>3012791740.5903068</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2791120000.2099686</v>
+        <v>2789621982.0280614</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3154805338.1671443</v>
+        <v>3153112126.9269981</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14972,7 +14972,7 @@
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>2704737086.9059877</v>
+        <v>2703285431.1788392</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>3301739989.4756131</v>
+        <v>3299967917.1405673</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>2621027655.1113372</v>
+        <v>2619620926.9583578</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>3455518103.1980524</v>
+        <v>3453663496.822794</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15016,7 +15016,7 @@
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>2539908962.7291441</v>
+        <v>2538545771.6781425</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>3616458412.7128344</v>
+        <v>3614517428.2850966</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>2461300828.4637127</v>
+        <v>2459979827.0764904</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>3784894496.3642764</v>
+        <v>3782863110.8374166</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>2385125552.5657921</v>
+        <v>2383845435.1062751</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>3961175468.8650155</v>
+        <v>3959049471.8195148</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>2311307840.0307164</v>
+        <v>2310067341.1743112</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -15092,7 +15092,7 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>4145666704.9003539</v>
+        <v>4143441689.8169465</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>2239774726.1734958</v>
+        <v>2238572619.7563829</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>4338750596.4343901</v>
+        <v>4336421951.5607433</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>2170455504.5073056</v>
+        <v>2169290602.3144479</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>4540827345.2875767</v>
+        <v>4538390244.0795918</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>2103281656.8540695</v>
+        <v>2102152807.4447277</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -15598,7 +15598,7 @@
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>37680120002.834579</v>
+        <v>37659896757.37883</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>17453186215.562431</v>
+        <v>17443818939.959389</v>
       </c>
       <c r="H51" s="124"/>
     </row>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>41781226029.11396</v>
+        <v>41758801684.67543</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -15642,7 +15642,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>41781226029.11396</v>
+        <v>41758801684.67543</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
@@ -15672,19 +15672,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>36003272246.340866</v>
+        <v>35983948979.541473</v>
       </c>
       <c r="C56" s="127">
-        <v>37164926276.482529</v>
+        <v>37144979539.944077</v>
       </c>
       <c r="D56" s="127">
-        <v>38361371337.901474</v>
+        <v>38340782458.977325</v>
       </c>
       <c r="E56" s="127">
-        <v>39594134173.441559</v>
+        <v>39572883660.069077</v>
       </c>
       <c r="F56" s="127">
-        <v>42174957251.040771</v>
+        <v>42152321587.658882</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -15693,19 +15693,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>36003272246.340858</v>
+        <v>35983948979.541466</v>
       </c>
       <c r="C57" s="127">
-        <v>38327650006.415695</v>
+        <v>38307079226.021072</v>
       </c>
       <c r="D57" s="127">
-        <v>40884993352.983871</v>
+        <v>40863050024.354027</v>
       </c>
       <c r="E57" s="127">
-        <v>43703183161.819977</v>
+        <v>43679727286.408424</v>
       </c>
       <c r="F57" s="127">
-        <v>50249520558.23806</v>
+        <v>50222551207.07341</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -15714,19 +15714,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>36003272246.340858</v>
+        <v>35983948979.541458</v>
       </c>
       <c r="C58" s="127">
-        <v>39766843015.28804</v>
+        <v>39745499807.590248</v>
       </c>
       <c r="D58" s="127">
-        <v>44174854683.123947</v>
+        <v>44151145657.537994</v>
       </c>
       <c r="E58" s="127">
-        <v>49355338577.140076</v>
+        <v>49328849141.158401</v>
       </c>
       <c r="F58" s="127">
-        <v>62677173149.138901</v>
+        <v>62643533769.620674</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -15735,19 +15735,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>36003272246.340858</v>
+        <v>35983948979.541466</v>
       </c>
       <c r="C59" s="127">
-        <v>41233149891.481445</v>
+        <v>41211019704.234009</v>
       </c>
       <c r="D59" s="127">
-        <v>47715818149.870476</v>
+        <v>47690208658.645538</v>
       </c>
       <c r="E59" s="127">
-        <v>55802911570.760323</v>
+        <v>55772961666.732529</v>
       </c>
       <c r="F59" s="127">
-        <v>78733556730.096573</v>
+        <v>78691299750.998917</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -15756,19 +15756,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>36003272246.340858</v>
+        <v>35983948979.541458</v>
       </c>
       <c r="C60" s="127">
-        <v>42596896651.723969</v>
+        <v>42574034529.825851</v>
       </c>
       <c r="D60" s="127">
-        <v>51203787625.648758</v>
+        <v>51176306111.116959</v>
       </c>
       <c r="E60" s="127">
-        <v>62559772030.275948</v>
+        <v>62526195660.950989</v>
       </c>
       <c r="F60" s="127">
-        <v>97989687322.006714</v>
+        <v>97937095411.505997</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -15777,19 +15777,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>36003272246.340851</v>
+        <v>35983948979.541458</v>
       </c>
       <c r="C61" s="127">
-        <v>43799911002.586906</v>
+        <v>43776403212.508789</v>
       </c>
       <c r="D61" s="127">
-        <v>54470301950.884308</v>
+        <v>54441067269.935341</v>
       </c>
       <c r="E61" s="127">
-        <v>69315773825.086578</v>
+        <v>69278571451.3172</v>
       </c>
       <c r="F61" s="127">
-        <v>120223757450.11841</v>
+        <v>120159232322.37616</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -15839,23 +15839,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>35.297800780014747</v>
+        <v>39.823206040600617</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>35.297800780014747</v>
+        <v>39.823206040600617</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>35.297800780014747</v>
+        <v>39.823206040600617</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>35.297800780014747</v>
+        <v>39.823206040600617</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>35.297800780014747</v>
+        <v>39.823206040600617</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15866,23 +15866,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>35.29780078001474</v>
+        <v>39.82320604060061</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>36.098408968471482</v>
+        <v>40.725254696541732</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>36.922995022801132</v>
+        <v>41.654319316090039</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>37.772611169217967</v>
+        <v>42.611585447002952</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>39.551306060529186</v>
+        <v>44.615648556986109</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15893,23 +15893,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>35.297800780014732</v>
+        <v>39.823206040600603</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>36.899754390553774</v>
+        <v>41.628133996748822</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>38.662267127421032</v>
+        <v>43.613964604395775</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>40.604554399737722</v>
+        <v>45.802347946842012</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>45.1162688930226</v>
+        <v>50.885715883038856</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15920,23 +15920,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>35.297800780014732</v>
+        <v>39.823206040600603</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>37.891641542645338</v>
+        <v>42.745697475726132</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>40.929628881829224</v>
+        <v>46.168610750394684</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>44.500001572923672</v>
+        <v>50.191364868634132</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>53.68136673575772</v>
+        <v>60.536048103517679</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15947,23 +15947,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>35.297800780014732</v>
+        <v>39.823206040600603</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>38.902215484120589</v>
+        <v>43.884315439894159</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>43.370049414057512</v>
+        <v>48.918242958467637</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>48.94364796025247</v>
+        <v>55.198040179929784</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>64.747374203014999</v>
+        <v>73.004165849996383</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15974,23 +15974,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>35.297800780014732</v>
+        <v>39.823206040600603</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>39.842105326450302</v>
+        <v>44.943293328492196</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>45.773946659655444</v>
+        <v>51.626724223931625</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>53.600454265558469</v>
+        <v>60.444883678716089</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>78.018636928282405</v>
+        <v>87.956954088453926</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16000,23 +16000,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>35.297800780014732</v>
+        <v>39.823206040600603</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>40.671218913749946</v>
+        <v>45.877459138721804</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>48.025217734035408</v>
+        <v>54.163240932208176</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>58.256668781935815</v>
+        <v>65.691060406395891</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>93.342285919640815</v>
+        <v>105.22217467458466</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>53.68136673575772</v>
+        <v>60.536048103517679</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>40.604554399737722</v>
+        <v>45.802347946842012</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>38.662267127421032</v>
+        <v>43.613964604395775</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>36.899754390553774</v>
+        <v>41.628133996748822</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>35.297800780014732</v>
+        <v>39.823206040600603</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -16263,7 +16263,7 @@
       </c>
       <c r="I4" s="270">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.339927674962774</v>
+        <v>2.0756749576043392</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="I5" s="270">
         <f t="shared" si="0"/>
-        <v>2.339927674962774</v>
+        <v>2.0756749576043392</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16292,7 +16292,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>41.61728588181122</v>
+        <v>46.382665301030322</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>3157349439.9308405</v>
+        <v>3155288291.4722385</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16348,7 +16348,7 @@
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>2880261779.7072697</v>
+        <v>2878715918.3633184</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16432,7 +16432,7 @@
       </c>
       <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.22852762417856032</v>
+        <v>0.22851396292762693</v>
       </c>
       <c r="E14" s="351"/>
       <c r="F14" s="351"/>
@@ -16498,7 +16498,7 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>35.297800780014747</v>
+        <v>39.823206040600617</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>38.662267127421032</v>
+        <v>43.613964604395775</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
@@ -16603,7 +16603,7 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>36.899754390553774</v>
+        <v>41.628133996748822</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16661,7 +16661,7 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>40.604554399737722</v>
+        <v>45.802347946842012</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>38.69822203451092</v>
+        <v>43.654475151355633</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16762,7 +16762,7 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>35.297800780014732</v>
+        <v>39.823206040600603</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16820,7 +16820,7 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>53.68136673575772</v>
+        <v>60.536048103517679</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>39.277358206848447</v>
+        <v>44.30699034342598</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>39.279947779882377</v>
+        <v>44.309908026393003</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16970,7 +16970,7 @@
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>0.26693400073598744</v>
+        <v>0.26781128370802371</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
-        <v>2.339927674962774</v>
+        <v>2.0756749576043392</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17021,7 +17021,7 @@
       </c>
       <c r="C80" s="171">
         <f>Thesis!C123</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.9290143153151025</v>
+        <v>4.0517175172436701</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>22.729952666000258</v>
+        <v>22.685179055834102</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>27.658966981315359</v>
+        <v>26.736896573077772</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17063,7 +17063,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.29580378508010985</v>
+        <v>0.39655353780885183</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17093,7 +17093,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-5.7047688184643786E-2</v>
+        <v>-2.7445446695169684E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2DBBA0-0E83-4949-A983-BA907A393A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64573709-9F61-4BB3-B47F-8C125E1E5FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="416">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1422,10 +1422,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3716,29 +3712,29 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4048,10 +4044,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4080,13 +4076,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C5" s="339" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4113,7 +4109,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -4149,24 +4145,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="343" t="s">
-        <v>376</v>
-      </c>
-      <c r="C12" s="343"/>
-      <c r="D12" s="343"/>
-      <c r="E12" s="343"/>
-      <c r="F12" s="343"/>
+      <c r="B12" s="341" t="s">
+        <v>375</v>
+      </c>
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4176,10 +4172,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4202,7 +4198,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4225,7 +4221,7 @@
         <v>26.736896573077772</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E20" s="336">
         <v>3</v>
@@ -4233,7 +4229,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
@@ -4248,7 +4244,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4257,22 +4253,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="343" t="s">
-        <v>377</v>
-      </c>
-      <c r="C25" s="343"/>
-      <c r="D25" s="343"/>
-      <c r="E25" s="343"/>
-      <c r="F25" s="343"/>
+      <c r="B25" s="341" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="341"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="341"/>
+      <c r="F25" s="341"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="346" t="s">
-        <v>353</v>
-      </c>
-      <c r="C26" s="346"/>
-      <c r="D26" s="346"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="B26" s="343" t="s">
+        <v>352</v>
+      </c>
+      <c r="C26" s="343"/>
+      <c r="D26" s="343"/>
+      <c r="E26" s="343"/>
+      <c r="F26" s="343"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4284,13 +4280,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="344" t="s">
+      <c r="B29" s="342" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="344"/>
-      <c r="D29" s="344"/>
-      <c r="E29" s="344"/>
-      <c r="F29" s="344"/>
+      <c r="C29" s="342"/>
+      <c r="D29" s="342"/>
+      <c r="E29" s="342"/>
+      <c r="F29" s="342"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4310,13 +4306,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="344" t="s">
+      <c r="B32" s="342" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="344"/>
-      <c r="D32" s="344"/>
-      <c r="E32" s="344"/>
-      <c r="F32" s="344"/>
+      <c r="C32" s="342"/>
+      <c r="D32" s="342"/>
+      <c r="E32" s="342"/>
+      <c r="F32" s="342"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4345,13 +4341,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="344" t="s">
+      <c r="B36" s="342" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="344"/>
-      <c r="D36" s="344"/>
-      <c r="E36" s="344"/>
-      <c r="F36" s="344"/>
+      <c r="C36" s="342"/>
+      <c r="D36" s="342"/>
+      <c r="E36" s="342"/>
+      <c r="F36" s="342"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4367,17 +4363,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="344" t="s">
+      <c r="B39" s="342" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="344"/>
-      <c r="D39" s="344"/>
-      <c r="E39" s="344"/>
-      <c r="F39" s="344"/>
+      <c r="C39" s="342"/>
+      <c r="D39" s="342"/>
+      <c r="E39" s="342"/>
+      <c r="F39" s="342"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
@@ -4392,7 +4388,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
@@ -4437,13 +4433,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="344" t="s">
+      <c r="B47" s="342" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="344"/>
-      <c r="D47" s="344"/>
-      <c r="E47" s="344"/>
-      <c r="F47" s="344"/>
+      <c r="C47" s="342"/>
+      <c r="D47" s="342"/>
+      <c r="E47" s="342"/>
+      <c r="F47" s="342"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4459,8 +4455,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="344" t="s">
-        <v>352</v>
+      <c r="B50" s="342" t="s">
+        <v>351</v>
       </c>
       <c r="C50" s="345"/>
       <c r="D50" s="345"/>
@@ -4481,22 +4477,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="343" t="s">
-        <v>357</v>
-      </c>
-      <c r="C53" s="343"/>
-      <c r="D53" s="343"/>
-      <c r="E53" s="343"/>
-      <c r="F53" s="343"/>
+      <c r="B53" s="341" t="s">
+        <v>356</v>
+      </c>
+      <c r="C53" s="341"/>
+      <c r="D53" s="341"/>
+      <c r="E53" s="341"/>
+      <c r="F53" s="341"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="343" t="s">
-        <v>378</v>
-      </c>
-      <c r="C54" s="343"/>
-      <c r="D54" s="343"/>
-      <c r="E54" s="343"/>
-      <c r="F54" s="343"/>
+      <c r="B54" s="341" t="s">
+        <v>377</v>
+      </c>
+      <c r="C54" s="341"/>
+      <c r="D54" s="341"/>
+      <c r="E54" s="341"/>
+      <c r="F54" s="341"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4526,7 +4522,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C125</f>
@@ -4535,7 +4531,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4544,7 +4540,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4557,22 +4553,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="343" t="s">
-        <v>379</v>
-      </c>
-      <c r="C63" s="343"/>
-      <c r="D63" s="343"/>
-      <c r="E63" s="343"/>
-      <c r="F63" s="343"/>
+      <c r="B63" s="341" t="s">
+        <v>378</v>
+      </c>
+      <c r="C63" s="341"/>
+      <c r="D63" s="341"/>
+      <c r="E63" s="341"/>
+      <c r="F63" s="341"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="343" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="343"/>
+      <c r="D64" s="343"/>
+      <c r="E64" s="343"/>
+      <c r="F64" s="343"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4581,7 +4577,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C67" s="317">
         <v>0.08</v>
@@ -4589,26 +4585,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="292" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4625,27 +4621,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="338" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="343" t="s">
+      <c r="B73" s="341" t="s">
+        <v>379</v>
+      </c>
+      <c r="C73" s="341"/>
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="341" t="s">
         <v>380</v>
       </c>
-      <c r="C73" s="343"/>
-      <c r="D73" s="343"/>
-      <c r="E73" s="343"/>
-      <c r="F73" s="343"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="343" t="s">
-        <v>381</v>
-      </c>
-      <c r="C74" s="343"/>
-      <c r="D74" s="343"/>
-      <c r="E74" s="343"/>
-      <c r="F74" s="343"/>
+      <c r="C74" s="341"/>
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4670,7 +4666,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="253" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4682,13 +4678,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="343" t="s">
-        <v>382</v>
-      </c>
-      <c r="C81" s="343"/>
-      <c r="D81" s="343"/>
-      <c r="E81" s="343"/>
-      <c r="F81" s="343"/>
+      <c r="B81" s="341" t="s">
+        <v>381</v>
+      </c>
+      <c r="C81" s="341"/>
+      <c r="D81" s="341"/>
+      <c r="E81" s="341"/>
+      <c r="F81" s="341"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4701,13 +4697,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="343" t="s">
-        <v>358</v>
-      </c>
-      <c r="C85" s="343"/>
-      <c r="D85" s="343"/>
-      <c r="E85" s="343"/>
-      <c r="F85" s="343"/>
+      <c r="B85" s="341" t="s">
+        <v>357</v>
+      </c>
+      <c r="C85" s="341"/>
+      <c r="D85" s="341"/>
+      <c r="E85" s="341"/>
+      <c r="F85" s="341"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4811,13 +4807,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="343" t="s">
-        <v>383</v>
-      </c>
-      <c r="C98" s="343"/>
-      <c r="D98" s="343"/>
-      <c r="E98" s="343"/>
-      <c r="F98" s="343"/>
+      <c r="B98" s="341" t="s">
+        <v>382</v>
+      </c>
+      <c r="C98" s="341"/>
+      <c r="D98" s="341"/>
+      <c r="E98" s="341"/>
+      <c r="F98" s="341"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4834,7 +4830,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="253" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4843,13 +4839,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="344" t="s">
-        <v>384</v>
-      </c>
-      <c r="C104" s="344"/>
-      <c r="D104" s="344"/>
-      <c r="E104" s="344"/>
-      <c r="F104" s="344"/>
+      <c r="B104" s="342" t="s">
+        <v>383</v>
+      </c>
+      <c r="C104" s="342"/>
+      <c r="D104" s="342"/>
+      <c r="E104" s="342"/>
+      <c r="F104" s="342"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="266" t="s">
@@ -4992,17 +4988,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="347" t="s">
-        <v>387</v>
-      </c>
-      <c r="C115" s="347"/>
-      <c r="D115" s="347"/>
-      <c r="E115" s="347"/>
-      <c r="F115" s="347"/>
+      <c r="B115" s="346" t="s">
+        <v>386</v>
+      </c>
+      <c r="C115" s="346"/>
+      <c r="D115" s="346"/>
+      <c r="E115" s="346"/>
+      <c r="F115" s="346"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -5011,22 +5007,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="348" t="s">
+      <c r="B119" s="344" t="s">
+        <v>384</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
+    </row>
+    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="341" t="s">
         <v>385</v>
       </c>
-      <c r="C119" s="348"/>
-      <c r="D119" s="348"/>
-      <c r="E119" s="348"/>
-      <c r="F119" s="348"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="343" t="s">
-        <v>386</v>
-      </c>
-      <c r="C120" s="343"/>
-      <c r="D120" s="343"/>
-      <c r="E120" s="343"/>
-      <c r="F120" s="343"/>
+      <c r="C120" s="341"/>
+      <c r="D120" s="341"/>
+      <c r="E120" s="341"/>
+      <c r="F120" s="341"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -5113,7 +5109,7 @@
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="253" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5122,22 +5118,22 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="342" t="s">
-        <v>393</v>
-      </c>
-      <c r="C134" s="343"/>
-      <c r="D134" s="343"/>
-      <c r="E134" s="343"/>
-      <c r="F134" s="343"/>
+      <c r="B134" s="348" t="s">
+        <v>392</v>
+      </c>
+      <c r="C134" s="341"/>
+      <c r="D134" s="341"/>
+      <c r="E134" s="341"/>
+      <c r="F134" s="341"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="240" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B137" s="345" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C137" s="345"/>
       <c r="D137" s="345"/>
@@ -5146,78 +5142,89 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="244" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="244" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="244" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="344" t="s">
-        <v>398</v>
-      </c>
-      <c r="C143" s="344"/>
-      <c r="D143" s="344"/>
-      <c r="E143" s="344"/>
-      <c r="F143" s="344"/>
+      <c r="B143" s="342" t="s">
+        <v>397</v>
+      </c>
+      <c r="C143" s="342"/>
+      <c r="D143" s="342"/>
+      <c r="E143" s="342"/>
+      <c r="F143" s="342"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="341" t="s">
+      <c r="B146" s="347" t="s">
+        <v>398</v>
+      </c>
+      <c r="C146" s="347"/>
+      <c r="D146" s="347"/>
+      <c r="E146" s="347"/>
+      <c r="F146" s="347"/>
+    </row>
+    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="347" t="s">
         <v>399</v>
       </c>
-      <c r="C146" s="341"/>
-      <c r="D146" s="341"/>
-      <c r="E146" s="341"/>
-      <c r="F146" s="341"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="341" t="s">
-        <v>400</v>
-      </c>
-      <c r="C147" s="341"/>
-      <c r="D147" s="341"/>
-      <c r="E147" s="341"/>
-      <c r="F147" s="341"/>
+      <c r="C147" s="347"/>
+      <c r="D147" s="347"/>
+      <c r="E147" s="347"/>
+      <c r="F147" s="347"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="244" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="244" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="244" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5234,17 +5241,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5762,7 +5758,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C22" s="184">
         <v>5154661132</v>
@@ -5788,7 +5784,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C23" s="184">
         <v>-7421783375</v>
@@ -5814,7 +5810,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C24" s="184">
         <v>-2983143705</v>
@@ -5875,7 +5871,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="100" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7130,7 +7126,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C64" s="186">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8717,7 +8713,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F65" s="293" t="s">
         <v>60</v>
@@ -8784,7 +8780,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C72" s="267" t="s">
         <v>97</v>
@@ -8796,7 +8792,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8807,12 +8803,12 @@
         <v>-2588061833.5865102</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
@@ -8823,12 +8819,12 @@
         <v>6.9468096405893043</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
@@ -8836,12 +8832,12 @@
         <v>5176123667.1730204</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
@@ -8849,7 +8845,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8925,7 +8921,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8936,15 +8932,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="276" t="s">
         <v>300</v>
-      </c>
-      <c r="D85" s="276" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8961,7 +8957,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8995,7 +8991,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
@@ -9866,7 +9862,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9891,7 +9887,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -10219,7 +10215,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10279,7 +10275,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10403,7 +10399,7 @@
         <v>-1522888768.25</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -10461,7 +10457,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -10769,7 +10765,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10908,7 +10904,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10963,7 +10959,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
@@ -11096,7 +11092,7 @@
         <v>3.430552260533988E-2</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11123,7 +11119,7 @@
         <v>7.6514823945754068E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11438,7 +11434,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -11999,7 +11995,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12678,7 +12674,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13372,7 +13368,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C113" s="173"/>
       <c r="E113" s="308"/>
@@ -13424,7 +13420,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C114" s="173"/>
       <c r="E114" s="308"/>
@@ -13933,7 +13929,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C126" s="173"/>
       <c r="G126" s="23">
@@ -16158,7 +16154,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C80" s="159" t="s">
         <v>107</v>
@@ -16230,7 +16226,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I2" s="284"/>
     </row>
@@ -16451,7 +16447,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16462,7 +16458,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="351" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="352"/>
     </row>
@@ -16472,7 +16468,7 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E20" s="352"/>
       <c r="F20" s="352"/>
@@ -16784,7 +16780,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E54" s="163" t="s">
         <v>151</v>
@@ -16853,7 +16849,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F60" s="318">
         <f>Thesis!E20</f>
@@ -16862,7 +16858,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16871,10 +16867,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16886,7 +16882,7 @@
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16898,7 +16894,7 @@
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16914,20 +16910,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16937,19 +16933,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16959,14 +16955,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
@@ -16989,7 +16985,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -17012,12 +17008,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C80" s="171">
         <f>Thesis!C123</f>
@@ -17071,12 +17067,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -17089,7 +17085,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17101,7 +17097,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -17109,30 +17105,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
+        <v>338</v>
+      </c>
+      <c r="F90" s="324" t="s">
         <v>339</v>
-      </c>
-      <c r="F90" s="324" t="s">
-        <v>340</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F92" s="325" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C266B897-D225-4181-A1DA-8AFBDB8BBC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F70612D-CE2E-46E9-9B16-E376E4FA7424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1553,10 +1553,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Always use 10yrs to identify the HGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Use Excel Goal Seek to find the HGR</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2331,6 +2327,10 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4029,10 +4029,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4061,13 +4061,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>59.8</v>
+        <v>58.35</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>81578.967922399999</v>
+        <v>79600.882579800003</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="338" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C12" s="338"/>
       <c r="D12" s="338"/>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4157,10 +4157,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0562040500000001</v>
+        <v>1.0614312000000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4183,7 +4183,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>26.67162630902984</v>
+        <v>44.071651534145857</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>318</v>
@@ -4214,11 +4214,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>-5.7617735553175065E-2</v>
+        <v>0.13479424997108347</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4229,7 +4229,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="338" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C25" s="338"/>
       <c r="D25" s="338"/>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="341" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C26" s="341"/>
       <c r="D26" s="341"/>
@@ -4358,11 +4358,11 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177626222.81127352</v>
+        <v>177546214.0073584</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4373,7 +4373,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155789168.81127352</v>
+        <v>155709160.0073584</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008464309.779757</v>
+        <v>-1008444307.5787783</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4441,7 +4441,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="339" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C50" s="340"/>
       <c r="D50" s="340"/>
@@ -4463,7 +4463,7 @@
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="338" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C53" s="338"/>
       <c r="D53" s="338"/>
@@ -4472,7 +4472,7 @@
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="338" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C54" s="338"/>
       <c r="D54" s="338"/>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3155344886.8112736</v>
+        <v>3155264878.0073586</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878758364.8675942</v>
+        <v>2878698358.264658</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4507,11 +4507,11 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.72713252126061E-2</v>
+        <v>3.8385758471807176E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.4831619570918029E-2</v>
+        <v>3.5521391571982669E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4539,7 +4539,7 @@
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
       <c r="B63" s="338" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="338"/>
@@ -4577,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4606,13 +4606,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="338" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C73" s="338"/>
       <c r="D73" s="338"/>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="338" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C74" s="338"/>
       <c r="D74" s="338"/>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>27.860315596423053</v>
+        <v>27.997612585374359</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="338" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C81" s="338"/>
       <c r="D81" s="338"/>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="338" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C85" s="338"/>
       <c r="D85" s="338"/>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.22096285391631576</v>
+        <v>0.22205639827627979</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12800999484.566097</v>
+        <v>12803331727.244209</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>9.9109363242736404</v>
+        <v>9.9618001440763511</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.1333262847852277</v>
+        <v>2.1438841088056102</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B98" s="338" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C98" s="338"/>
       <c r="D98" s="338"/>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>39.683615351565606</v>
+        <v>39.881240439980047</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4815,7 +4815,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="339" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C104" s="339"/>
       <c r="D104" s="339"/>
@@ -4856,15 +4856,15 @@
       </c>
       <c r="C107" s="256">
         <f>Valuation_Model!C74</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D107" s="257">
         <f>Valuation_Model!D74</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>60.32 HKD</v>
+        <v>139.01 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4878,19 +4878,19 @@
       </c>
       <c r="C108" s="243">
         <f>Valuation_Model!C75</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="D108" s="244">
         <f>Valuation_Model!D75</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>45.64 HKD</v>
+        <v>105.37 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -4900,19 +4900,19 @@
       </c>
       <c r="C109" s="243">
         <f>Valuation_Model!C76</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D109" s="244">
         <f>Valuation_Model!D76</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>43.46 HKD</v>
+        <v>82.08 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
-        <v>0.53999999999999992</v>
+        <v>0.42499999999999999</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -4922,19 +4922,19 @@
       </c>
       <c r="C110" s="243">
         <f>Valuation_Model!C77</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D110" s="244">
         <f>Valuation_Model!D77</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>41.48 HKD</v>
+        <v>54.24 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
-        <v>0.18</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -4944,19 +4944,19 @@
       </c>
       <c r="C111" s="243">
         <f>Valuation_Model!C78</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D111" s="244">
         <f>Valuation_Model!D78</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>39.68 HKD</v>
+        <v>45.94 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>44.151846267899231</v>
+        <v>78.175377834395093</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4974,7 +4974,7 @@
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="342" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C115" s="342"/>
       <c r="D115" s="342"/>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4993,7 +4993,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="343" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C119" s="343"/>
       <c r="D119" s="343"/>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B120" s="338" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C120" s="338"/>
       <c r="D120" s="338"/>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0829308503408979</v>
+        <v>2.0726731982251887</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>4.0658810198654329</v>
+        <v>4.0458580829355686</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>22.605745289164407</v>
+        <v>40.025793451210291</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>26.67162630902984</v>
+        <v>44.071651534145857</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5089,12 +5089,12 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.39591141563605348</v>
+        <v>0.43624638914433878</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="247" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5104,7 +5104,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B134" s="337" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C134" s="338"/>
       <c r="D134" s="338"/>
@@ -5113,12 +5113,12 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B137" s="340" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C137" s="340"/>
       <c r="D137" s="340"/>
@@ -5127,27 +5127,27 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="238" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="238" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="238" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B143" s="339" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C143" s="339"/>
       <c r="D143" s="339"/>
@@ -5156,12 +5156,12 @@
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B146" s="336" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C146" s="336"/>
       <c r="D146" s="336"/>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B147" s="336" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C147" s="336"/>
       <c r="D147" s="336"/>
@@ -5179,22 +5179,22 @@
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="238" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="238" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="238" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -5743,7 +5743,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C22" s="181">
         <v>5154661132</v>
@@ -5769,7 +5769,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C23" s="181">
         <v>-7421783375</v>
@@ -5795,7 +5795,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C24" s="181">
         <v>-2983143705</v>
@@ -5826,23 +5826,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0829308503408979</v>
+        <v>2.0726731982251887</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8935735003099068</v>
+        <v>1.8842483620228987</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2308227752014396</v>
+        <v>1.2247614353148841</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0414654251704489</v>
+        <v>1.0363365991125943</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.7100900626162151</v>
+        <v>0.70659313575858695</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -5856,7 +5856,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7111,7 +7111,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0829308503408979</v>
+        <v>2.0726731982251887</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8935735003099068</v>
+        <v>1.8842483620228987</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2308227752014396</v>
+        <v>1.2247614353148841</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0414654251704489</v>
+        <v>1.0363365991125943</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.7100900626162151</v>
+        <v>0.70659313575858695</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8517,11 +8517,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.499463495273041</v>
+        <v>22.610813258237229</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3127568525433189</v>
+        <v>1.3192536814295288</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12800999484.566097</v>
+        <v>12803331727.244209</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8763,7 +8763,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8775,52 +8775,52 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2540963759.1384301</v>
+        <v>-2539797637.7993741</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2588886705.7169509</v>
+        <v>-2587720584.3778949</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.0755723419274981</v>
+        <v>7.0788210164561916</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.944596245288789</v>
+        <v>6.9477257338130327</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5177773411.4339018</v>
+        <v>5175441168.7557898</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8828,7 +8828,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8927,11 +8927,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-301436815.57995117</v>
+        <v>-302928625.28334963</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-0.22096285391631576</v>
+        <v>-0.22205639827627979</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8944,11 +8944,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13520467499.646626</v>
+        <v>13589855759.246895</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>9.9109363242736404</v>
+        <v>9.9618001440763511</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8961,11 +8961,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2910276865.459981</v>
+        <v>2924679815.0768561</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>2.1333262847852277</v>
+        <v>2.1438841088056102</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8978,11 +8978,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16129307549.526657</v>
+        <v>16211606949.040401</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>11.823299755142553</v>
+        <v>11.883627854605681</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9562,28 +9562,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155789168.81127352</v>
+        <v>155709160.0073584</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155789168.81127352</v>
+        <v>155709160.0073584</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129402511.05134627</v>
+        <v>129336822.93502155</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>123141863.19837074</v>
+        <v>123082234.96134833</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68219358.300375998</v>
+        <v>68178411.765419602</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>137254468.97346407</v>
+        <v>137186490.83066195</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9617,28 +9617,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033857239.1190281</v>
+        <v>4033777230.3151131</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691854028.8112736</v>
+        <v>4691774020.0073586</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4550070303.0513458</v>
+        <v>4550004614.9350214</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3870095071.1983709</v>
+        <v>3870035442.9613485</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025310358.3003759</v>
+        <v>3025269411.7654195</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2471314340.973464</v>
+        <v>2471246362.8306618</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008464309.779757</v>
+        <v>-1008444307.5787783</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9784,30 +9784,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878758364.8675942</v>
+        <v>2878698358.264658</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3155344886.8112736</v>
+        <v>3155264878.0073586</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071514407.0513458</v>
+        <v>3071448718.9350214</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574582378.1983709</v>
+        <v>2574522749.9613485</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701790703.3003759</v>
+        <v>1701749756.7654195</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1433088572.973464</v>
+        <v>1433020594.8306618</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -9892,30 +9892,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878758364.8675942</v>
+        <v>2878698358.264658</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3155344886.8112736</v>
+        <v>3155264878.0073586</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071514407.0513458</v>
+        <v>3071448718.9350214</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574582378.1983709</v>
+        <v>2574522749.9613485</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701790703.3003759</v>
+        <v>1701749756.7654195</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1433088572.973464</v>
+        <v>1433020594.8306618</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10382,7 +10382,7 @@
         <v>-1522888768.25</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10748,28 +10748,28 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29619768762330784</v>
+        <v>0.29620273868131025</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30729379655130612</v>
+        <v>0.30729823293156544</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31043676857994645</v>
+        <v>0.31044155168787663</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.40416732506311603</v>
+        <v>0.4041727954028615</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36926930090185517</v>
+        <v>0.36927945862697992</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10887,32 +10887,32 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177626222.81127352</v>
+        <v>177546214.0073584</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>177626222.81127352</v>
+        <v>177546214.0073584</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>145833101.05134627</v>
+        <v>145767412.93502155</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132379663.19837074</v>
+        <v>132320034.96134833</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90904725.300375998</v>
+        <v>90863778.765419602</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150917150.97346407</v>
+        <v>150849172.83066195</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -10942,7 +10942,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11003,28 +11003,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155789168.81127352</v>
+        <v>155709160.0073584</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155789168.81127352</v>
+        <v>155709160.0073584</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129402511.05134627</v>
+        <v>129336822.93502155</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>123141863.19837074</v>
+        <v>123082234.96134833</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68219358.300375998</v>
+        <v>68178411.765419602</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>137254468.97346407</v>
+        <v>137186490.83066195</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -11075,7 +11075,7 @@
         <v>3.430552260533988E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11102,7 +11102,7 @@
         <v>7.6514823945754068E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11417,7 +11417,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12090,30 +12090,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8527642475557986E-3</v>
+        <v>4.8502720084220279E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8475322781033267E-3</v>
+        <v>4.845042725957498E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8130751355680346E-3</v>
+        <v>3.8111395183916363E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8276615020099258E-3</v>
+        <v>3.8258080567123202E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2614047940385596E-3</v>
+        <v>2.2600474565795652E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.9443767386248344E-3</v>
+        <v>4.9419279327643081E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12147,30 +12147,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12565288292573784</v>
+        <v>0.12565039068660408</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14599162459339052</v>
+        <v>0.14598913504124469</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13407591395786209</v>
+        <v>0.13407397834068568</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12029551550053499</v>
+        <v>0.12029366205523739</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10028607008572925</v>
+        <v>0.10028471274827025</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.902521887066224E-2</v>
+        <v>8.9022770064801707E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.141322073143446E-2</v>
+        <v>3.141259767165102E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12319,30 +12319,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.9672059854848732E-2</v>
+        <v>8.9670190675498404E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8181640637003534E-2</v>
+        <v>9.817915108485771E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.050763481258299E-2</v>
+        <v>9.0505699195406603E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.002664241735663E-2</v>
+        <v>8.002478897205903E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.6412692097581797E-2</v>
+        <v>5.6411334760122799E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1624765718695585E-2</v>
+        <v>5.1622316912835052E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12426,30 +12426,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.9672059854848732E-2</v>
+        <v>8.9670190675498404E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8181640637003534E-2</v>
+        <v>9.817915108485771E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.050763481258299E-2</v>
+        <v>9.0505699195406603E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.002664241735663E-2</v>
+        <v>8.002478897205903E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.6412692097581797E-2</v>
+        <v>5.6411334760122799E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1624765718695585E-2</v>
+        <v>5.1622316912835052E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12495,28 +12495,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0829308503408979</v>
+        <v>2.0726731982251887</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0829308503408979</v>
+        <v>2.0726731982251887</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8935735003099068</v>
+        <v>1.8842483620228987</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2308227752014396</v>
+        <v>1.2247614353148841</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0414654251704489</v>
+        <v>1.0363365991125943</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.7100900626162151</v>
+        <v>0.70659313575858695</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12551,28 +12551,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>2841527575.6611614</v>
+        <v>2827534119.5924897</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>2841527575.6611614</v>
+        <v>2827534119.5924897</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2583206886.9646916</v>
+        <v>2570485563.2658997</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1679084476.52705</v>
+        <v>1670815616.1228347</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1420763787.8305807</v>
+        <v>1413767059.7962449</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>968702582.61175954</v>
+        <v>963932086.22471225</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12606,28 +12606,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.98706706694775148</v>
+        <v>0.98222660650593097</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.90054421231041737</v>
+        <v>0.89613209315667963</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.84102059916579408</v>
+        <v>0.83689678665941614</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.65217741360524328</v>
+        <v>0.64898071541528179</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.83486399653918408</v>
+        <v>0.83077259401725767</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.67595443916061182</v>
+        <v>0.67265752474312412</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12661,28 +12661,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.4831619570918029E-2</v>
+        <v>3.5521391571982669E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.4831619570918029E-2</v>
+        <v>3.5521391571982669E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.1665108700834561E-2</v>
+        <v>3.2292174156347879E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.0582320655542469E-2</v>
+        <v>2.0989913201626121E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.7415809785459015E-2</v>
+        <v>1.7760695785991334E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.1874415762812961E-2</v>
+        <v>1.2109565308630454E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12798,26 +12798,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14024238300076763</v>
+        <v>-0.14024477455357354</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1160776936753232E-2</v>
+        <v>3.1158079402159311E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17569987799871312</v>
+        <v>0.17570101927887283</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27923902437983128</v>
+        <v>0.27923662861581611</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.2241705994829819</v>
+        <v>0.22418770433723911</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13351,7 +13351,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13403,29 +13403,29 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6336284358472124</v>
+        <v>1.6336698601530146</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90429891314313082</v>
+        <v>0.90431825310209957</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8949758078488999</v>
+        <v>1.8950196971742608</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5510309483300517</v>
+        <v>3.5511163912174561</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.4564663032113372</v>
+        <v>3.4566302674703286</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13517,28 +13517,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12565288292573784</v>
+        <v>0.12565039068660408</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14599162459339052</v>
+        <v>0.14598913504124469</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13407591395786209</v>
+        <v>0.13407397834068568</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12029551550053499</v>
+        <v>0.12029366205523739</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10028607008572925</v>
+        <v>0.10028471274827025</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.902521887066224E-2</v>
+        <v>8.9022770064801707E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13803,30 +13803,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2288252477138446</v>
+        <v>2.2398090068299488</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4429672301771022</v>
+        <v>2.4549952142104035</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.3780630367244204</v>
+        <v>2.3897809525392777</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.9933226341182027</v>
+        <v>2.0031411860491599</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3175798747579266</v>
+        <v>1.3240687137750595</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1095422362065357</v>
+        <v>1.1149804654105542</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13860,30 +13860,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.72713252126061E-2</v>
+        <v>3.8385758471807176E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.0852294819015089E-2</v>
+        <v>4.2073611211832104E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>3.976694041345185E-2</v>
+        <v>4.095597176588308E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3333154416692351E-2</v>
+        <v>3.4329754688074719E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.2033108273543923E-2</v>
+        <v>2.2691837425450893E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.8554217996764811E-2</v>
+        <v>1.9108491266676162E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13912,28 +13912,28 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5060474536435582E-2</v>
+        <v>5.6428729687726609E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3300489510189911E-2</v>
+        <v>5.4625008958172343E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6638509592560044E-2</v>
+        <v>4.7797478554157502E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9915237381985789E-2</v>
+        <v>4.0907132741092547E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8524126551998947E-2</v>
+        <v>2.9232952318929507E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878758364.8675942</v>
+        <v>2878698358.264658</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35984479560.844925</v>
+        <v>35983729478.308228</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12800999484.566097</v>
+        <v>12803331727.244209</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14801,7 +14801,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51255494237.911026</v>
+        <v>51257076398.052437</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14815,7 +14815,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0562040500000001</v>
+        <v>1.0614312000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>39.683615351565606</v>
+        <v>39.881240439980047</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H17" s="121"/>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>44.154753829984472</v>
+        <v>78.180177221530386</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14917,11 +14917,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3012836164.0350389</v>
+        <v>3096939513.8249445</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2789663114.8472581</v>
+        <v>2867536586.8749485</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14939,11 +14939,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3153158619.3879333</v>
+        <v>3331726064.5787039</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14951,7 +14951,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2703325290.9704499</v>
+        <v>2856418093.7746086</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14961,11 +14961,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3300016574.9818678</v>
+        <v>3584312357.3580232</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2619659553.1215606</v>
+        <v>2845342711.1578064</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14983,11 +14983,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3453714420.896771</v>
+        <v>3856047834.0928574</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2538583202.3927412</v>
+        <v>2834310271.8693552</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15005,11 +15005,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3614570724.1412439</v>
+        <v>4148384241.2027254</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15017,7 +15017,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2460016099.3406558</v>
+        <v>2823320609.4021907</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15027,11 +15027,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3782918888.9411836</v>
+        <v>4462883385.5500097</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2383880584.7731137</v>
+        <v>2812373557.894856</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15049,11 +15049,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3959107847.7812629</v>
+        <v>4801225478.3910179</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2310101402.9873052</v>
+        <v>2801468952.1290026</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15071,11 +15071,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4143502784.6315756</v>
+        <v>5165218111.9023666</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2238605627.3837314</v>
+        <v>2790606627.5268931</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15093,11 +15093,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4336485891.8584766</v>
+        <v>5556805916.2397518</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2169322588.3823471</v>
+        <v>2779786420.1489167</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15115,11 +15115,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4538457162.3884363</v>
+        <v>5978080948.7219524</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2102183803.569618</v>
+        <v>2769008166.6911197</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15137,19 +15137,19 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6431293870.6442394</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.42888285933767062</v>
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2758271704.4827366</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15159,19 +15159,19 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6918865971.4333248</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.39711375864599124</v>
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2747576871.4837351</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15181,19 +15181,19 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7443402104.3828726</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.36769792467221413</v>
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2736923506.2823734</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15203,19 +15203,19 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8007704603.078722</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.34046104136316119</v>
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2726311448.092761</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15225,19 +15225,19 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8614788252.8623104</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.31524170496588994</v>
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2715740536.7524347</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15247,19 +15247,19 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9267896397.3172989</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.29189046756100923</v>
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2705210612.7199392</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15269,19 +15269,19 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9970518265.8283291</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27026895144537894</v>
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2694721517.0724206</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15291,19 +15291,19 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10726407614.784309</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.25024902911609154</v>
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2684273091.5032248</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15313,19 +15313,19 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11539602782.016891</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.23171206399638106</v>
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2673865178.3195148</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15335,19 +15335,19 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12414448261.614908</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.21454820740405653</v>
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2663497620.4398842</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15357,19 +15357,19 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13355617914.378208</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E41" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.19865574759634863</v>
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2653170261.3919892</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15379,19 +15379,19 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14368139937.912706</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E42" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.18394050703365611</v>
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2642882945.3101873</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15401,19 +15401,19 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15457423729.769335</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E43" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.17031528429042234</v>
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2632635516.9331846</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15423,19 +15423,19 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16629288787.143198</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E44" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1576993373059466</v>
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2622427821.6016908</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15445,19 +15445,19 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17889995797.529522</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E45" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1460179049129135</v>
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2612259705.2560878</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15467,19 +15467,19 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>19246280086.438183</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E46" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.13520176380825324</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2602131014.434103</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15489,19 +15489,19 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20705387600.861214</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E47" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.12518681834097523</v>
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2592041596.2684937</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15511,19 +15511,19 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22275113620.734867</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E48" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.11591372068608817</v>
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2581991298.4847393</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15533,19 +15533,19 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>23963844405.212189</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E49" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.10732751915378534</v>
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2571979969.3987427</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15555,19 +15555,19 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25780601996.241318</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="E50" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.9377332549801231E-2</v>
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2562007457.9145427</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>37660452050.437988</v>
+        <v>38711743922.811806</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15585,11 +15585,11 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>9.9377332549801231E-2</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>17444076148.088371</v>
+        <v>3847069849.4000158</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>41759417415.857147</v>
+        <v>85207161521.012482</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15621,27 +15621,27 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>41759417415.857147</v>
+        <v>85207161521.012482</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C55" s="132">
         <f>C77</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D55" s="132">
         <f>C76</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="E55" s="132">
         <f>C75</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="F55" s="132">
         <f>C74</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H55" s="121"/>
     </row>
@@ -15651,19 +15651,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>35984479560.844925</v>
+        <v>37144752956.452003</v>
       </c>
       <c r="C56" s="124">
-        <v>37145527240.57782</v>
+        <v>38340548581.115875</v>
       </c>
       <c r="D56" s="124">
-        <v>38341347791.657852</v>
+        <v>40842607172.831581</v>
       </c>
       <c r="E56" s="124">
-        <v>39573467160.012497</v>
+        <v>42152064459.499367</v>
       </c>
       <c r="F56" s="124">
-        <v>42152943121.269424</v>
+        <v>43502684036.579926</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15672,19 +15672,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>35984479560.84491</v>
+        <v>38306845553.748535</v>
       </c>
       <c r="C57" s="124">
-        <v>38307644061.749313</v>
+        <v>40862800760.720398</v>
       </c>
       <c r="D57" s="124">
-        <v>40863652547.727921</v>
+        <v>46787807087.708107</v>
       </c>
       <c r="E57" s="124">
-        <v>43680371341.530075</v>
+        <v>50222244850.705086</v>
       </c>
       <c r="F57" s="124">
-        <v>50223291735.765717</v>
+        <v>54020937906.700729</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15693,19 +15693,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>35984479560.84491</v>
+        <v>39745257360.986374</v>
       </c>
       <c r="C58" s="124">
-        <v>39746085852.749054</v>
+        <v>44150876336.599182</v>
       </c>
       <c r="D58" s="124">
-        <v>44151796663.697029</v>
+        <v>55431533384.284958</v>
       </c>
       <c r="E58" s="124">
-        <v>49329576492.264023</v>
+        <v>62643151645.554031</v>
       </c>
       <c r="F58" s="124">
-        <v>62644457445.002136</v>
+        <v>71182373232.479904</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15714,19 +15714,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>35984479560.84491</v>
+        <v>41210768317.993607</v>
       </c>
       <c r="C59" s="124">
-        <v>41211627358.401245</v>
+        <v>47689917749.506561</v>
       </c>
       <c r="D59" s="124">
-        <v>47690911848.089432</v>
+        <v>65911831392.999359</v>
       </c>
       <c r="E59" s="124">
-        <v>55773784035.914818</v>
+        <v>78690819735.941315</v>
       </c>
       <c r="F59" s="124">
-        <v>78692460049.787003</v>
+        <v>94859823623.012939</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15735,19 +15735,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>35984479560.844902</v>
+        <v>42573774829.227417</v>
       </c>
       <c r="C60" s="124">
-        <v>42574662281.570023</v>
+        <v>51175993936.866402</v>
       </c>
       <c r="D60" s="124">
-        <v>51177060702.871681</v>
+        <v>77642069249.142105</v>
       </c>
       <c r="E60" s="124">
-        <v>62527117606.188622</v>
+        <v>97936497997.552444</v>
       </c>
       <c r="F60" s="124">
-        <v>97938539488.46846</v>
+        <v>125364540550.09386</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15756,19 +15756,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>35984479560.844902</v>
+        <v>43776136177.489975</v>
       </c>
       <c r="C61" s="124">
-        <v>43777048693.111542</v>
+        <v>54440735180.719337</v>
       </c>
       <c r="D61" s="124">
-        <v>54441870000.409698</v>
+        <v>90222995162.747513</v>
       </c>
       <c r="E61" s="124">
-        <v>69279592959.956009</v>
+        <v>120158499353.91579</v>
       </c>
       <c r="F61" s="124">
-        <v>120161004063.49727</v>
+        <v>163385484403.4957</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15792,23 +15792,23 @@
     <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B64" s="133">
         <f>B55</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C64" s="133">
         <f>C55</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D64" s="133">
         <f>D55</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="E64" s="133">
         <f>E55</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="F64" s="133">
         <f>F55</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -15818,23 +15818,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>39.683615351565606</v>
+        <v>39.881240439980047</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>39.683615351565606</v>
+        <v>39.881240439980047</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>39.683615351565606</v>
+        <v>39.881240439980047</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>39.683615351565606</v>
+        <v>39.881240439980047</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>39.683615351565606</v>
+        <v>39.881240439980047</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15845,23 +15845,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>39.683615351565606</v>
+        <v>40.784589981977589</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>40.582534973986675</v>
+        <v>41.714994448552041</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>41.508376846826472</v>
+        <v>43.661753946035269</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>42.462322405404947</v>
+        <v>44.680594359209245</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>44.459433805404231</v>
+        <v>45.731461632211584</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15872,23 +15872,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>39.683615351565599</v>
+        <v>41.688771366151599</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>41.482282359328302</v>
+        <v>43.67746583189637</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>43.461224502039883</v>
+        <v>48.287494700885432</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>45.64201676302045</v>
+        <v>50.959704039134664</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>50.707751472270687</v>
+        <v>53.915326984683723</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15899,23 +15899,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>39.683615351565599</v>
+        <v>42.807946535072041</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>42.595969225261008</v>
+        <v>46.235796151169708</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>46.007009071260143</v>
+        <v>55.012859293553809</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>50.015809028162529</v>
+        <v>60.62395344971506</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>60.324608543932861</v>
+        <v>67.268006782639816</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15926,23 +15926,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>39.683615351565599</v>
+        <v>43.94820655282934</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>43.730637542419466</v>
+        <v>48.989393730928839</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>48.74710333335846</v>
+        <v>63.167192590332789</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>55.00511714449604</v>
+        <v>73.110052045031111</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>72.749476784851424</v>
+        <v>85.690557548067886</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15953,23 +15953,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>39.683615351565585</v>
+        <v>45.008711642382977</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>44.785942040132674</v>
+        <v>51.701781022402784</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>51.446189397563344</v>
+        <v>72.294057976216578</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>60.233760351009849</v>
+        <v>88.08440439047574</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>87.650396673072933</v>
+        <v>109.42515257012555</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15979,23 +15979,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>39.683615351565585</v>
+        <v>45.944224656301571</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>45.716867408603136</v>
+        <v>54.241955758653752</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>53.973907416598379</v>
+        <v>82.082812360521189</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>65.461739099318052</v>
+        <v>105.37452394915512</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>104.85572752533042</v>
+        <v>139.00784651460719</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16022,15 +16022,15 @@
       </c>
       <c r="C74" s="143">
         <f>Scenarios!C56</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D74" s="146">
         <f>Scenarios!C55</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>60.324608543932861</v>
+        <v>139.00784651460719</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16044,19 +16044,19 @@
       </c>
       <c r="C75" s="143">
         <f>Scenarios!C38</f>
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="D75" s="146">
         <f>Scenarios!C37</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>45.64201676302045</v>
+        <v>105.37452394915512</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H75" s="121"/>
     </row>
@@ -16067,19 +16067,19 @@
       </c>
       <c r="C76" s="143">
         <f>Scenarios!C26</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D76" s="146">
         <f>Scenarios!C25</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>43.461224502039883</v>
+        <v>82.082812360521189</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
-        <v>0.53999999999999992</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="H76" s="121"/>
     </row>
@@ -16090,19 +16090,19 @@
       </c>
       <c r="C77" s="143">
         <f>Scenarios!C32</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D77" s="146">
         <f>Scenarios!C31</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>41.482282359328302</v>
+        <v>54.241955758653752</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
-        <v>0.18</v>
+        <v>0.255</v>
       </c>
       <c r="H77" s="121"/>
     </row>
@@ -16113,19 +16113,19 @@
       </c>
       <c r="C78" s="143">
         <f>Scenarios!C50</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D78" s="146">
         <f>Scenarios!C49</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>39.683615351565599</v>
+        <v>45.944224656301571</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
@@ -16222,7 +16222,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-59.8</v>
+        <v>-58.35</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0829308503408979</v>
+        <v>2.0726731982251887</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0829308503408979</v>
+        <v>2.0726731982251887</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>46.234777118240132</v>
+        <v>80.248051032620282</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16288,7 +16288,7 @@
       </c>
       <c r="E7" s="346" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 青島啤酒股份(0168.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+        <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 青島啤酒股份(0168.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
       <c r="F7" s="346"/>
       <c r="H7" s="276">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3155344886.8112736</v>
+        <v>3155264878.0073586</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878758364.8675942</v>
+        <v>2878698358.264658</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16411,7 +16411,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.22851433827059342</v>
+        <v>0.22851380764461693</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16430,7 +16430,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16438,10 +16438,10 @@
         <v>135</v>
       </c>
       <c r="C18" s="151">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>59.8</v>
+        <v>58.35</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>39.683615351565606</v>
+        <v>39.881240439980047</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="C25" s="167">
         <f>C18</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D25" s="164"/>
       <c r="E25" s="345"/>
@@ -16512,7 +16512,7 @@
         <v>136</v>
       </c>
       <c r="C26" s="165">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D26" s="165"/>
       <c r="E26" s="345"/>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>43.461224502039883</v>
+        <v>82.082812360521189</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16538,7 +16538,7 @@
         <v>149</v>
       </c>
       <c r="C28" s="166">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
       <c r="E28" s="345"/>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="C31" s="167">
         <f>C18</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D31" s="164"/>
       <c r="E31" s="345"/>
@@ -16570,7 +16570,7 @@
         <v>136</v>
       </c>
       <c r="C32" s="165">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D32" s="165"/>
       <c r="E32" s="345"/>
@@ -16582,7 +16582,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>41.482282359328302</v>
+        <v>54.241955758653752</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16596,7 +16596,7 @@
         <v>149</v>
       </c>
       <c r="C34" s="166">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D34" s="166"/>
       <c r="E34" s="345"/>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="C37" s="167">
         <f>C18</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D37" s="164"/>
       <c r="E37" s="345"/>
@@ -16628,7 +16628,7 @@
         <v>136</v>
       </c>
       <c r="C38" s="165">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="D38" s="165"/>
       <c r="E38" s="345"/>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>45.64201676302045</v>
+        <v>105.37452394915512</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>43.501594525693683</v>
+        <v>78.388897697687739</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16693,7 +16693,7 @@
         <v>135</v>
       </c>
       <c r="C46" s="151">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="C49" s="167">
         <f>C46</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D49" s="164"/>
       <c r="E49" s="345"/>
@@ -16729,7 +16729,7 @@
         <v>136</v>
       </c>
       <c r="C50" s="165">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D50" s="165"/>
       <c r="E50" s="345"/>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>39.683615351565599</v>
+        <v>45.944224656301571</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16755,7 +16755,7 @@
         <v>149</v>
       </c>
       <c r="C52" s="166">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D52" s="166"/>
       <c r="E52" s="345"/>
@@ -16763,7 +16763,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="C55" s="167">
         <f>C46</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D55" s="164"/>
       <c r="E55" s="345"/>
@@ -16787,7 +16787,7 @@
         <v>136</v>
       </c>
       <c r="C56" s="165">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D56" s="165"/>
       <c r="E56" s="345"/>
@@ -16799,7 +16799,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>60.324608543932861</v>
+        <v>139.00784651460719</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>44.151846267899231</v>
+        <v>78.175377834395093</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16841,7 +16841,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16861,11 +16861,12 @@
         <v>135</v>
       </c>
       <c r="C64" s="167">
-        <v>10</v>
+        <f>C18</f>
+        <v>30</v>
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>323</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16873,11 +16874,11 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>4.6574870890079501E-2</v>
+        <v>7.5812443125109957E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16886,22 +16887,22 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>44.154753829984472</v>
+        <v>78.180177221530386</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
@@ -16945,11 +16946,11 @@
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.26778721060502353</v>
+        <v>0.15201241341973021</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16982,7 +16983,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0829308503408979</v>
+        <v>2.0726731982251887</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17009,7 +17010,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.0658810198654329</v>
+        <v>4.0458580829355686</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17021,7 +17022,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>22.605745289164407</v>
+        <v>40.025793451210291</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17031,7 +17032,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>26.67162630902984</v>
+        <v>44.071651534145857</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17042,7 +17043,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.39591141563605348</v>
+        <v>0.43624638914433878</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17059,7 +17060,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>59.8</v>
+        <v>58.35</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17072,7 +17073,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-5.7617735553175065E-2</v>
+        <v>0.13479424997108347</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -17080,7 +17081,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="320" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F89" s="317"/>
       <c r="G89" s="2"/>
@@ -17088,30 +17089,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="313" t="s">
+        <v>337</v>
+      </c>
+      <c r="F90" s="318" t="s">
         <v>338</v>
-      </c>
-      <c r="F90" s="318" t="s">
-        <v>339</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="316"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="314" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F91" s="318" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="316"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="315" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F92" s="319" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="316"/>

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F70612D-CE2E-46E9-9B16-E376E4FA7424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1E4B87-AF50-4743-ADB2-1387FF571905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2322,15 +2322,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>CNS_03</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>58.35</v>
+        <v>59.9</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>79600.882579800003</v>
+        <v>81715.387601199996</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0614312000000001</v>
+        <v>1.0624809</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4183,7 +4183,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>44.071651534145857</v>
+        <v>44.107282041660923</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>318</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13479424997108347</v>
+        <v>0.12493740306462042</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177546214.0073584</v>
+        <v>177530241.80848101</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155709160.0073584</v>
+        <v>155693187.80848101</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008444307.5787783</v>
+        <v>-1008440314.5290589</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3155264878.0073586</v>
+        <v>3155248905.8084812</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878698358.264658</v>
+        <v>2878686379.1155</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.8385758471807176E-2</v>
+        <v>3.7429294343278158E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5521391571982669E-2</v>
+        <v>3.456803769335158E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>27.997612585374359</v>
+        <v>28.025184139529522</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.22205639827627979</v>
+        <v>0.22227600045235163</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12803331727.244209</v>
+        <v>12803797314.055439</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>9.9618001440763511</v>
+        <v>9.9720144581187835</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.1438841088056102</v>
+        <v>2.1460042981772935</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>39.881240439980047</v>
+        <v>39.920926895373249</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>139.01 HKD</v>
+        <v>139.15 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>105.37 HKD</v>
+        <v>105.48 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>82.08 HKD</v>
+        <v>82.16 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>54.24 HKD</v>
+        <v>54.3 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>45.94 HKD</v>
+        <v>45.99 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>78.175377834395093</v>
+        <v>78.252775679635405</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0726731982251887</v>
+        <v>2.0706254578317598</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>4.0458580829355686</v>
+        <v>4.0418608936875957</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>40.025793451210291</v>
+        <v>40.065421147973325</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>44.071651534145857</v>
+        <v>44.107282041660923</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.43624638914433878</v>
+        <v>0.43634865781330423</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,6 +5199,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5215,17 +5226,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5826,23 +5826,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0726731982251887</v>
+        <v>2.0706254578317598</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8842483620228987</v>
+        <v>1.8823867798470544</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2247614353148841</v>
+        <v>1.2235514069005853</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0363365991125943</v>
+        <v>1.0353127289158799</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.70659313575858695</v>
+        <v>0.70589504244264534</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -5856,7 +5856,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7164,23 +7164,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0726731982251887</v>
+        <v>2.0706254578317598</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8842483620228987</v>
+        <v>1.8823867798470544</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2247614353148841</v>
+        <v>1.2235514069005853</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0363365991125943</v>
+        <v>1.0353127289158799</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.70659313575858695</v>
+        <v>0.70589504244264534</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8517,11 +8517,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.610813258237229</v>
+        <v>22.633174171198114</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3192536814295288</v>
+        <v>1.3205583543931616</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12803331727.244209</v>
+        <v>12803797314.055439</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8779,11 +8779,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2539797637.7993741</v>
+        <v>-2539564844.3937597</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2587720584.3778949</v>
+        <v>-2587487790.97228</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>363</v>
@@ -8795,11 +8795,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.0788210164561916</v>
+        <v>7.0794699082755104</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.9477257338130327</v>
+        <v>6.948350812988477</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>330</v>
@@ -8812,7 +8812,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5175441168.7557898</v>
+        <v>5174975581.9445601</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>364</v>
@@ -8927,11 +8927,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-302928625.28334963</v>
+        <v>-303228205.86658466</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-0.22205639827627979</v>
+        <v>-0.22227600045235163</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8944,11 +8944,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13589855759.246895</v>
+        <v>13603790093.655205</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>9.9618001440763511</v>
+        <v>9.9720144581187835</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8961,11 +8961,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2924679815.0768561</v>
+        <v>2927572170.6076579</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>2.1438841088056102</v>
+        <v>2.1460042981772935</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8978,11 +8978,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16211606949.040401</v>
+        <v>16228134058.396278</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>11.883627854605681</v>
+        <v>11.895742755843726</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9562,28 +9562,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155709160.0073584</v>
+        <v>155693187.80848101</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155709160.0073584</v>
+        <v>155693187.80848101</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129336822.93502155</v>
+        <v>129323709.58240932</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>123082234.96134833</v>
+        <v>123070331.34557323</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68178411.765419602</v>
+        <v>68170237.587483406</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>137186490.83066195</v>
+        <v>137172920.3188805</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9617,28 +9617,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033777230.3151131</v>
+        <v>4033761258.1162357</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691774020.0073586</v>
+        <v>4691758047.8084812</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4550004614.9350214</v>
+        <v>4549991501.5824089</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3870035442.9613485</v>
+        <v>3870023539.3455734</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025269411.7654195</v>
+        <v>3025261237.5874834</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2471246362.8306618</v>
+        <v>2471232792.3188806</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008444307.5787783</v>
+        <v>-1008440314.5290589</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9784,30 +9784,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878698358.264658</v>
+        <v>2878686379.1155</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3155264878.0073586</v>
+        <v>3155248905.8084812</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071448718.9350214</v>
+        <v>3071435605.5824089</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574522749.9613485</v>
+        <v>2574510846.3455734</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701749756.7654195</v>
+        <v>1701741582.5874834</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1433020594.8306618</v>
+        <v>1433007024.3188806</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -9892,30 +9892,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878698358.264658</v>
+        <v>2878686379.1155</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3155264878.0073586</v>
+        <v>3155248905.8084812</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071448718.9350214</v>
+        <v>3071435605.5824089</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574522749.9613485</v>
+        <v>2574510846.3455734</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701749756.7654195</v>
+        <v>1701741582.5874834</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1433020594.8306618</v>
+        <v>1433007024.3188806</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10753,23 +10753,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29620273868131025</v>
+        <v>0.29620374704725794</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30729823293156544</v>
+        <v>0.30729911858378794</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31044155168787663</v>
+        <v>0.31044250655983396</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.4041727954028615</v>
+        <v>0.40417388746734356</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36927945862697992</v>
+        <v>0.36928148648581194</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10891,28 +10891,28 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177546214.0073584</v>
+        <v>177530241.80848101</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
-        <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>177546214.0073584</v>
+        <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
+        <v>177530241.80848101</v>
       </c>
       <c r="H48" s="328">
-        <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>145767412.93502155</v>
+        <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
+        <v>145754299.58240932</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132320034.96134833</v>
+        <v>132308131.34557323</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90863778.765419602</v>
+        <v>90855604.587483406</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150849172.83066195</v>
+        <v>150835602.3188805</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -11003,28 +11003,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155709160.0073584</v>
+        <v>155693187.80848101</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155709160.0073584</v>
+        <v>155693187.80848101</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129336822.93502155</v>
+        <v>129323709.58240932</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>123082234.96134833</v>
+        <v>123070331.34557323</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68178411.765419602</v>
+        <v>68170237.587483406</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>137186490.83066195</v>
+        <v>137172920.3188805</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -11194,7 +11194,7 @@
         <v>169</v>
       </c>
       <c r="C58" s="191">
-        <f>BS!$C79*C66</f>
+        <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="302"/>
@@ -11304,7 +11304,7 @@
         <v>160</v>
       </c>
       <c r="C60" s="191">
-        <f>BS!$C81*C68</f>
+        <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="302"/>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="E68" s="302"/>
       <c r="G68" s="23">
-        <f>IFERROR(G60/BS!$C$81,0)</f>
+        <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
       </c>
       <c r="H68" s="176"/>
@@ -12090,30 +12090,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8502720084220279E-3</v>
+        <v>4.8497744814356624E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.845042725957498E-3</v>
+        <v>4.8445457353759238E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8111395183916363E-3</v>
+        <v>3.8107531101343049E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8258080567123202E-3</v>
+        <v>3.8254380524696228E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2600474565795652E-3</v>
+        <v>2.2597764906010986E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.9419279327643081E-3</v>
+        <v>4.941439076384729E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12147,30 +12147,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12565039068660408</v>
+        <v>0.12564989315961772</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14598913504124469</v>
+        <v>0.14598863805066312</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13407397834068568</v>
+        <v>0.13407359193242835</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12029366205523739</v>
+        <v>0.12029329205099469</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10028471274827025</v>
+        <v>0.10028444178229179</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.9022770064801707E-2</v>
+        <v>8.9022281208422135E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.141259767165102E-2</v>
+        <v>3.141247328990443E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12319,30 +12319,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.9670190675498404E-2</v>
+        <v>8.9669817530258628E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.817915108485771E-2</v>
+        <v>9.8178654094276147E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0505699195406603E-2</v>
+        <v>9.0505312787149253E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.002478897205903E-2</v>
+        <v>8.0024418967816327E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.6411334760122799E-2</v>
+        <v>5.6411063794144338E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1622316912835052E-2</v>
+        <v>5.1621828056455481E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12426,30 +12426,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.9670190675498404E-2</v>
+        <v>8.9669817530258628E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.817915108485771E-2</v>
+        <v>9.8178654094276147E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0505699195406603E-2</v>
+        <v>9.0505312787149253E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.002478897205903E-2</v>
+        <v>8.0024418967816327E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.6411334760122799E-2</v>
+        <v>5.6411063794144338E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1622316912835052E-2</v>
+        <v>5.1621828056455481E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12495,28 +12495,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0726731982251887</v>
+        <v>2.0706254578317598</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0726731982251887</v>
+        <v>2.0706254578317598</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8842483620228987</v>
+        <v>1.8823867798470544</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2247614353148841</v>
+        <v>1.2235514069005853</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0363365991125943</v>
+        <v>1.0353127289158799</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.70659313575858695</v>
+        <v>0.70589504244264534</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12551,28 +12551,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>2827534119.5924897</v>
+        <v>2824740598.7251163</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>2827534119.5924897</v>
+        <v>2824740598.7251163</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2570485563.2658997</v>
+        <v>2567945998.8410149</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1670815616.1228347</v>
+        <v>1669164899.2466595</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1413767059.7962449</v>
+        <v>1412370299.3625581</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>963932086.22471225</v>
+        <v>962979749.56538045</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12606,28 +12606,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.98222660650593097</v>
+        <v>0.98126027872235277</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.89613209315667963</v>
+        <v>0.89525127273638105</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.83689678665941614</v>
+        <v>0.83607352671620738</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.64898071541528179</v>
+        <v>0.64834253917243334</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.83077259401725767</v>
+        <v>0.82995580164119942</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.67265752474312412</v>
+        <v>0.67199932255956119</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12661,28 +12661,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5521391571982669E-2</v>
+        <v>3.456803769335158E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5521391571982669E-2</v>
+        <v>3.456803769335158E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.2292174156347879E-2</v>
+        <v>3.1425488812137803E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.0989913201626121E-2</v>
+        <v>2.0426567727889571E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.7760695785991334E-2</v>
+        <v>1.728401884667579E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2109565308630454E-2</v>
+        <v>1.1784558304551676E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12798,26 +12798,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14024477455357354</v>
+        <v>-0.14024525199026316</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1158079402159311E-2</v>
+        <v>3.1157540882607915E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17570101927887283</v>
+        <v>0.17570124711743196</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27923662861581611</v>
+        <v>0.27923615034044191</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.22418770433723911</v>
+        <v>0.22419111910081546</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13409,23 +13409,23 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6336698601530146</v>
+        <v>1.6336781299601471</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90431825310209957</v>
+        <v>0.90432211404715901</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8950196971742608</v>
+        <v>1.8950284590664057</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5511163912174561</v>
+        <v>3.5511334487175787</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.4566302674703286</v>
+        <v>3.4566630016028013</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13517,28 +13517,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12565039068660408</v>
+        <v>0.12564989315961772</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14598913504124469</v>
+        <v>0.14598863805066312</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13407397834068568</v>
+        <v>0.13407359193242835</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12029366205523739</v>
+        <v>0.12029329205099469</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10028471274827025</v>
+        <v>0.10028444178229179</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.9022770064801707E-2</v>
+        <v>8.9022281208422135E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13803,30 +13803,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2398090068299488</v>
+        <v>2.2420147311623619</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4549952142104035</v>
+        <v>2.4574106365418373</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.3897809525392777</v>
+        <v>2.3921341079357847</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0031411860491599</v>
+        <v>2.0051129170999094</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3240687137750595</v>
+        <v>1.3253717822380429</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1149804654105542</v>
+        <v>1.1160725536795841</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13860,30 +13860,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.8385758471807176E-2</v>
+        <v>3.7429294343278158E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.2073611211832104E-2</v>
+        <v>4.1025219307877087E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.095597176588308E-2</v>
+        <v>3.9935460900430465E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.4329754688074719E-2</v>
+        <v>3.3474339183637888E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.2691837425450893E-2</v>
+        <v>2.212640704904913E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.9108491266676162E-2</v>
+        <v>1.8632262999659168E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13917,23 +13917,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6428729687726609E-2</v>
+        <v>5.496855387777709E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4625008958172343E-2</v>
+        <v>5.3211507056917469E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7797478554157502E-2</v>
+        <v>4.6560648975544079E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0907132741092547E-2</v>
+        <v>3.9848600925588486E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9232952318929507E-2</v>
+        <v>2.8476506975117478E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878698358.264658</v>
+        <v>2878686379.1155</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35983729478.308228</v>
+        <v>35983579738.943748</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12803331727.244209</v>
+        <v>12803797314.055439</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14801,7 +14801,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51257076398.052437</v>
+        <v>51257392245.499191</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14815,7 +14815,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0614312000000001</v>
+        <v>1.0624809</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>39.881240439980047</v>
+        <v>39.920926895373249</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>78.180177221530386</v>
+        <v>78.25757979312236</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14917,11 +14917,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3096939513.8249445</v>
+        <v>3096926626.5072227</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2867536586.8749485</v>
+        <v>2867524654.1733541</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14939,11 +14939,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3331726064.5787039</v>
+        <v>3331712200.24194</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14951,7 +14951,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2856418093.7746086</v>
+        <v>2856406207.3404832</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14961,11 +14961,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3584312357.3580232</v>
+        <v>3584297441.9320173</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2845342711.1578064</v>
+        <v>2845330870.8117547</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14983,11 +14983,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3856047834.0928574</v>
+        <v>3856031787.8919654</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2834310271.8693552</v>
+        <v>2834298477.4326758</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15005,11 +15005,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>4148384241.2027254</v>
+        <v>4148366978.5001411</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15017,7 +15017,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2823320609.4021907</v>
+        <v>2823308860.696876</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15027,11 +15027,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4462883385.5500097</v>
+        <v>4462864814.1197672</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2812373557.894856</v>
+        <v>2812361854.7435894</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15049,11 +15049,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4801225478.3910179</v>
+        <v>4801205499.0152769</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2801468952.1290026</v>
+        <v>2801457294.3551545</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15071,11 +15071,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>5165218111.9023666</v>
+        <v>5165196617.8413382</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2790606627.5268931</v>
+        <v>2790595014.9545178</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15093,11 +15093,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>5556805916.2397518</v>
+        <v>5556782792.6614447</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2779786420.1489167</v>
+        <v>2779774852.6027522</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15115,11 +15115,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5978080948.7219524</v>
+        <v>5978056072.0886803</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2769008166.6911197</v>
+        <v>2768996643.9965825</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15137,11 +15137,11 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>6431293870.6442394</v>
+        <v>6431267108.0526218</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2758271704.4827366</v>
+        <v>2758260226.4659204</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15159,11 +15159,11 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>6918865971.4333248</v>
+        <v>6918837179.9042521</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2747576871.4837351</v>
+        <v>2747565437.9714079</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15181,11 +15181,11 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>7443402104.3828726</v>
+        <v>7443371130.09764</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2736923506.2823734</v>
+        <v>2736912117.1019754</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15203,11 +15203,11 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>8007704603.078722</v>
+        <v>8007671280.557251</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
@@ -15215,7 +15215,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2726311448.092761</v>
+        <v>2726300103.0724001</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15225,11 +15225,11 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>8614788252.8623104</v>
+        <v>8614752404.0790749</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2715740536.7524347</v>
+        <v>2715729235.7208867</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15247,11 +15247,11 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>9267896397.3172989</v>
+        <v>9267857830.7502251</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
@@ -15259,7 +15259,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2705210612.7199392</v>
+        <v>2705199355.5066438</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15269,11 +15269,11 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>9970518265.8283291</v>
+        <v>9970476775.4355812</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2694721517.0724206</v>
+        <v>2694710303.5074773</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15291,11 +15291,11 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>10726407614.784309</v>
+        <v>10726362978.903521</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2684273091.5032248</v>
+        <v>2684261921.4173937</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15313,11 +15313,11 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>11539602782.016891</v>
+        <v>11539554762.180931</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2673865178.3195148</v>
+        <v>2673854051.5442119</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15335,11 +15335,11 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>12414448261.614908</v>
+        <v>12414396601.277864</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2663497620.4398842</v>
+        <v>2663486536.8071775</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15357,11 +15357,11 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>13355617914.378208</v>
+        <v>13355562337.544802</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E41" s="125">
         <f t="shared" si="0"/>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>2653170261.3919892</v>
+        <v>2653159220.7346001</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15379,11 +15379,11 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>14368139937.912706</v>
+        <v>14368080147.663776</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E42" s="125">
         <f t="shared" si="0"/>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>2642882945.3101873</v>
+        <v>2642871947.4614835</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15401,11 +15401,11 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>15457423729.769335</v>
+        <v>15457359406.675558</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E43" s="125">
         <f t="shared" si="0"/>
@@ -15413,7 +15413,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>2632635516.9331846</v>
+        <v>2632624561.7271814</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15423,11 +15423,11 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>16629288787.143198</v>
+        <v>16629219587.558533</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E44" s="125">
         <f t="shared" si="0"/>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>2622427821.6016908</v>
+        <v>2622416908.8730474</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15445,11 +15445,11 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>17889995797.529522</v>
+        <v>17889921351.75528</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E45" s="125">
         <f t="shared" si="0"/>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>2612259705.2560878</v>
+        <v>2612248834.8401031</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15467,11 +15467,11 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>19246280086.438183</v>
+        <v>19246199996.747917</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E46" s="125">
         <f t="shared" si="0"/>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>2602131014.434103</v>
+        <v>2602120186.1667161</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15489,11 +15489,11 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>20705387600.861214</v>
+        <v>20705301439.375858</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E47" s="125">
         <f t="shared" si="0"/>
@@ -15501,7 +15501,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>2592041596.2684937</v>
+        <v>2592030809.9862785</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15511,11 +15511,11 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>22275113620.734867</v>
+        <v>22275020927.136803</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E48" s="125">
         <f t="shared" si="0"/>
@@ -15523,7 +15523,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>2581991298.4847393</v>
+        <v>2581980554.0249043</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15533,11 +15533,11 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>23963844405.212189</v>
+        <v>23963744684.285995</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E49" s="125">
         <f t="shared" si="0"/>
@@ -15545,7 +15545,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>2571979969.3987427</v>
+        <v>2571969266.5991268</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15555,11 +15555,11 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>25780601996.241318</v>
+        <v>25780494715.228077</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="E50" s="125">
         <f t="shared" si="0"/>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>2562007457.9145427</v>
+        <v>2561996796.6136136</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38711743922.811806</v>
+        <v>38711582831.340279</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3847069849.4000158</v>
+        <v>3847053840.559279</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>85207161521.012482</v>
+        <v>85206806947.80957</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15621,7 +15621,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>85207161521.012482</v>
+        <v>85206806947.80957</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15651,19 +15651,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37144752956.452003</v>
+        <v>37144598385.711792</v>
       </c>
       <c r="C56" s="124">
-        <v>38340548581.115875</v>
+        <v>38340389034.302322</v>
       </c>
       <c r="D56" s="124">
-        <v>40842607172.831581</v>
+        <v>40842437214.182762</v>
       </c>
       <c r="E56" s="124">
-        <v>42152064459.499367</v>
+        <v>42151889051.796074</v>
       </c>
       <c r="F56" s="124">
-        <v>43502684036.579926</v>
+        <v>43502503008.533218</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15672,19 +15672,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>38306845553.748535</v>
+        <v>38306686147.183655</v>
       </c>
       <c r="C57" s="124">
-        <v>40862800760.720398</v>
+        <v>40862630718.039856</v>
       </c>
       <c r="D57" s="124">
-        <v>46787807087.708107</v>
+        <v>46787612389.254112</v>
       </c>
       <c r="E57" s="124">
-        <v>50222244850.705086</v>
+        <v>50222035860.499359</v>
       </c>
       <c r="F57" s="124">
-        <v>54020937906.700729</v>
+        <v>54020713108.964981</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15693,19 +15693,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>39745257360.986374</v>
+        <v>39745091968.747597</v>
       </c>
       <c r="C58" s="124">
-        <v>44150876336.599182</v>
+        <v>44150692611.224976</v>
       </c>
       <c r="D58" s="124">
-        <v>55431533384.284958</v>
+        <v>55431302716.627647</v>
       </c>
       <c r="E58" s="124">
-        <v>62643151645.554031</v>
+        <v>62642890968.13533</v>
       </c>
       <c r="F58" s="124">
-        <v>71182373232.479904</v>
+        <v>71182077020.7341</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15714,19 +15714,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>41210768317.993607</v>
+        <v>41210596827.313049</v>
       </c>
       <c r="C59" s="124">
-        <v>47689917749.506561</v>
+        <v>47689719297.092667</v>
       </c>
       <c r="D59" s="124">
-        <v>65911831392.999359</v>
+        <v>65911557113.599037</v>
       </c>
       <c r="E59" s="124">
-        <v>78690819735.941315</v>
+        <v>78690492279.240524</v>
       </c>
       <c r="F59" s="124">
-        <v>94859823623.012939</v>
+        <v>94859428882.114502</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15735,19 +15735,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>42573774829.227417</v>
+        <v>42573597666.657608</v>
       </c>
       <c r="C60" s="124">
-        <v>51175993936.866402</v>
+        <v>51175780977.817421</v>
       </c>
       <c r="D60" s="124">
-        <v>77642069249.142105</v>
+        <v>77641746156.614624</v>
       </c>
       <c r="E60" s="124">
-        <v>97936497997.552444</v>
+        <v>97936090453.665756</v>
       </c>
       <c r="F60" s="124">
-        <v>125364540550.09386</v>
+        <v>125364018869.68709</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15756,19 +15756,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>43776136177.489975</v>
+        <v>43775954011.524841</v>
       </c>
       <c r="C61" s="124">
-        <v>54440735180.719337</v>
+        <v>54440508636.078033</v>
       </c>
       <c r="D61" s="124">
-        <v>90222995162.747513</v>
+        <v>90222619717.118225</v>
       </c>
       <c r="E61" s="124">
-        <v>120158499353.91579</v>
+        <v>120157999337.44751</v>
       </c>
       <c r="F61" s="124">
-        <v>163385484403.4957</v>
+        <v>163384804506.24893</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15818,23 +15818,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>39.881240439980047</v>
+        <v>39.920926895373249</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>39.881240439980047</v>
+        <v>39.920926895373249</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>39.881240439980047</v>
+        <v>39.920926895373249</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>39.881240439980047</v>
+        <v>39.920926895373249</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>39.881240439980047</v>
+        <v>39.920926895373249</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15845,23 +15845,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>40.784589981977589</v>
+        <v>40.82516604003753</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>41.714994448552041</v>
+        <v>41.756486752490382</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>43.661753946035269</v>
+        <v>43.70516338432742</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>44.680594359209245</v>
+        <v>44.725007133537339</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>45.731461632211584</v>
+        <v>45.776909282061254</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15872,23 +15872,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>41.688771366151599</v>
+        <v>41.730237846061762</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>43.67746583189637</v>
+        <v>43.720890742976081</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>48.287494700885432</v>
+        <v>48.335459486935939</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>50.959704039134664</v>
+        <v>51.010300369723417</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>53.915326984683723</v>
+        <v>53.968833960523284</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15899,23 +15899,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>42.807946535072041</v>
+        <v>42.850515158912692</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>46.235796151169708</v>
+        <v>46.281740460742036</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>55.012859293553809</v>
+        <v>55.067447099817734</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>60.62395344971506</v>
+        <v>60.684066962355708</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>67.268006782639816</v>
+        <v>67.33466324160203</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15926,23 +15926,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>43.94820655282934</v>
+        <v>43.991898084587035</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>48.989393730928839</v>
+        <v>49.038049734741534</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>63.167192590332789</v>
+        <v>63.229810639940013</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>73.110052045031111</v>
+        <v>73.182461646938577</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>85.690557548067886</v>
+        <v>85.775356209496707</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15953,23 +15953,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.008711642382977</v>
+        <v>45.053447540813693</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>51.701781022402784</v>
+        <v>51.753108137292152</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>72.294057976216578</v>
+        <v>72.36566400158371</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.08440439047574</v>
+        <v>88.171560469975589</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>109.42515257012555</v>
+        <v>109.53332464134081</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15979,23 +15979,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>45.944224656301571</v>
+        <v>45.989881831417854</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>54.241955758653752</v>
+        <v>54.295784392738383</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>82.082812360521189</v>
+        <v>82.164058178238278</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>105.37452394915512</v>
+        <v>105.47870703287926</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>139.00784651460719</v>
+        <v>139.14515110009165</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>139.00784651460719</v>
+        <v>139.14515110009165</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>105.37452394915512</v>
+        <v>105.47870703287926</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16075,7 +16075,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>82.082812360521189</v>
+        <v>82.164058178238278</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>54.241955758653752</v>
+        <v>54.295784392738383</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>45.944224656301571</v>
+        <v>45.989881831417854</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-58.35</v>
+        <v>-59.9</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0726731982251887</v>
+        <v>2.0706254578317598</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0726731982251887</v>
+        <v>2.0706254578317598</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>80.248051032620282</v>
+        <v>80.323401137467158</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3155264878.0073586</v>
+        <v>3155248905.8084812</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878698358.264658</v>
+        <v>2878686379.1155</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16411,7 +16411,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.22851380764461693</v>
+        <v>0.2285137017123664</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>58.35</v>
+        <v>59.9</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>39.881240439980047</v>
+        <v>39.920926895373249</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>82.082812360521189</v>
+        <v>82.164058178238278</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16582,7 +16582,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>54.241955758653752</v>
+        <v>54.295784392738383</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>105.37452394915512</v>
+        <v>105.47870703287926</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>78.388897697687739</v>
+        <v>78.466505813516505</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>45.944224656301571</v>
+        <v>45.989881831417854</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16799,7 +16799,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>139.00784651460719</v>
+        <v>139.14515110009165</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>78.175377834395093</v>
+        <v>78.252775679635405</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16874,7 +16874,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>7.5812443125109957E-2</v>
+        <v>7.5812443125109999E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>78.180177221530386</v>
+        <v>78.25757979312236</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.15201241341973021</v>
+        <v>0.15201687930591179</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0726731982251887</v>
+        <v>2.0706254578317598</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.0458580829355686</v>
+        <v>4.0418608936875957</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>40.025793451210291</v>
+        <v>40.065421147973325</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>44.071651534145857</v>
+        <v>44.107282041660923</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.43624638914433878</v>
+        <v>0.43634865781330423</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>58.35</v>
+        <v>59.9</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13479424997108347</v>
+        <v>0.12493740306462042</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1E4B87-AF50-4743-ADB2-1387FF571905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DD9309-0D51-48CC-80F7-A3A61B40EBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>59.9</v>
+        <v>58.45</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>81715.387601199996</v>
+        <v>79737.302258600001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0624809</v>
+        <v>1.0653656200000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>44.107282041660923</v>
+        <v>44.205240144973352</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>318</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12493740306462042</v>
+        <v>0.13533159592642741</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177530241.80848101</v>
+        <v>177486510.10960329</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155693187.80848101</v>
+        <v>155649456.10960329</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008440314.5290589</v>
+        <v>-1008429381.6043395</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3155248905.8084812</v>
+        <v>3155205174.1096029</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878686379.1155</v>
+        <v>2878653580.3413415</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.7429294343278158E-2</v>
+        <v>3.8461528914527629E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.456803769335158E-2</v>
+        <v>3.5329662411002084E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>28.025184139529522</v>
+        <v>28.100954563176753</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.22227600045235163</v>
+        <v>0.22287949744135632</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12803797314.055439</v>
+        <v>12805072085.449562</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>9.9720144581187835</v>
+        <v>10.000084798220231</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.1460042981772935</v>
+        <v>2.1518308702305307</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>39.920926895373249</v>
+        <v>40.029990734186157</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>139.15 HKD</v>
+        <v>139.52 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>105.48 HKD</v>
+        <v>105.77 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>82.16 HKD</v>
+        <v>82.39 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>54.3 HKD</v>
+        <v>54.44 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>45.99 HKD</v>
+        <v>46.12 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>78.252775679635405</v>
+        <v>78.465475605444368</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0706254578317598</v>
+        <v>2.065018767923072</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>4.0418608936875957</v>
+        <v>4.0309166349858367</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>40.065421147973325</v>
+        <v>40.174323509987516</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>44.107282041660923</v>
+        <v>44.205240144973352</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.43634865781330423</v>
+        <v>0.43662815010190104</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,17 +5199,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5226,6 +5215,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5826,23 +5826,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0706254578317598</v>
+        <v>2.065018767923072</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8823867798470544</v>
+        <v>1.8772897890209745</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2235514069005853</v>
+        <v>1.2202383628636335</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0353127289158799</v>
+        <v>1.032509383961536</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.70589504244264534</v>
+        <v>0.70398367088286551</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0706254578317598</v>
+        <v>2.065018767923072</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8823867798470544</v>
+        <v>1.8772897890209745</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2235514069005853</v>
+        <v>1.2202383628636335</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0353127289158799</v>
+        <v>1.032509383961536</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.70589504244264534</v>
+        <v>0.70398367088286551</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8517,11 +8517,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.633174171198114</v>
+        <v>22.694625036051445</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3205583543931616</v>
+        <v>1.3241437751721001</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12803797314.055439</v>
+        <v>12805072085.449562</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8779,11 +8779,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2539564844.3937597</v>
+        <v>-2538927458.6966977</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2587487790.97228</v>
+        <v>-2586850405.2752185</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>363</v>
@@ -8795,11 +8795,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.0794699082755104</v>
+        <v>7.0812471756199784</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.948350812988477</v>
+        <v>6.9500628483722524</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>330</v>
@@ -8812,7 +8812,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5174975581.9445601</v>
+        <v>5173700810.550437</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>364</v>
@@ -8927,11 +8927,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-303228205.86658466</v>
+        <v>-304051494.52055252</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-0.22227600045235163</v>
+        <v>-0.22287949744135632</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8944,11 +8944,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13603790093.655205</v>
+        <v>13642083561.459667</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>9.9720144581187835</v>
+        <v>10.000084798220231</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8961,11 +8961,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2927572170.6076579</v>
+        <v>2935520761.4877348</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>2.1460042981772935</v>
+        <v>2.1518308702305307</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8978,11 +8978,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16228134058.396278</v>
+        <v>16273552828.426849</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>11.895742755843726</v>
+        <v>11.929036171009404</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9562,28 +9562,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155693187.80848101</v>
+        <v>155649456.10960329</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155693187.80848101</v>
+        <v>155649456.10960329</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129323709.58240932</v>
+        <v>129287805.3720926</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>123070331.34557323</v>
+        <v>123037739.38095842</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68170237.587483406</v>
+        <v>68147856.781257391</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>137172920.3188805</v>
+        <v>137135764.41195753</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9617,28 +9617,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033761258.1162357</v>
+        <v>4033717526.4173579</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691758047.8084812</v>
+        <v>4691714316.1096029</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4549991501.5824089</v>
+        <v>4549955597.3720922</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3870023539.3455734</v>
+        <v>3869990947.3809586</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025261237.5874834</v>
+        <v>3025238856.7812576</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2471232792.3188806</v>
+        <v>2471195636.4119577</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008440314.5290589</v>
+        <v>-1008429381.6043395</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9784,30 +9784,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878686379.1155</v>
+        <v>2878653580.3413415</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3155248905.8084812</v>
+        <v>3155205174.1096029</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071435605.5824089</v>
+        <v>3071399701.3720922</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574510846.3455734</v>
+        <v>2574478254.3809586</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701741582.5874834</v>
+        <v>1701719201.7812576</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1433007024.3188806</v>
+        <v>1432969868.4119577</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -9892,30 +9892,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878686379.1155</v>
+        <v>2878653580.3413415</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3155248905.8084812</v>
+        <v>3155205174.1096029</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071435605.5824089</v>
+        <v>3071399701.3720922</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574510846.3455734</v>
+        <v>2574478254.3809586</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701741582.5874834</v>
+        <v>1701719201.7812576</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1433007024.3188806</v>
+        <v>1432969868.4119577</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10753,23 +10753,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29620374704725794</v>
+        <v>0.29620650797688824</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30729911858378794</v>
+        <v>0.30730154351562466</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31044250655983396</v>
+        <v>0.31044512101845317</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.40417388746734356</v>
+        <v>0.40417687755767528</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36928148648581194</v>
+        <v>0.36928703885420316</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10891,28 +10891,28 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177530241.80848101</v>
+        <v>177486510.10960329</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>177530241.80848101</v>
+        <v>177486510.10960329</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>145754299.58240932</v>
+        <v>145718395.3720926</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132308131.34557323</v>
+        <v>132275539.38095842</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90855604.587483406</v>
+        <v>90833223.781257391</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150835602.3188805</v>
+        <v>150798446.41195753</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -11003,28 +11003,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155693187.80848101</v>
+        <v>155649456.10960329</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155693187.80848101</v>
+        <v>155649456.10960329</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129323709.58240932</v>
+        <v>129287805.3720926</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>123070331.34557323</v>
+        <v>123037739.38095842</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68170237.587483406</v>
+        <v>68147856.781257391</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>137172920.3188805</v>
+        <v>137135764.41195753</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -12090,30 +12090,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8497744814356624E-3</v>
+        <v>4.8484122582052678E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8445457353759238E-3</v>
+        <v>4.8431849808157476E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8107531101343049E-3</v>
+        <v>3.8096951287202772E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8254380524696228E-3</v>
+        <v>3.8244249850611007E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2597764906010986E-3</v>
+        <v>2.259034588833698E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.941439076384729E-3</v>
+        <v>4.940100593177104E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12147,30 +12147,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12564989315961772</v>
+        <v>0.12564853093638731</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14598863805066312</v>
+        <v>0.14598727729610292</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13407359193242835</v>
+        <v>0.13407253395101432</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12029329205099469</v>
+        <v>0.12029227898358617</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10028444178229179</v>
+        <v>0.10028369988052439</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.9022281208422135E-2</v>
+        <v>8.9020942725214519E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.141247328990443E-2</v>
+        <v>3.1412132734096827E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12319,30 +12319,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.9669817530258628E-2</v>
+        <v>8.9668795862835826E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8178654094276147E-2</v>
+        <v>9.8177293339715949E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0505312787149253E-2</v>
+        <v>9.0504254805735235E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.0024418967816327E-2</v>
+        <v>8.002340590040781E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.6411063794144338E-2</v>
+        <v>5.6410321892376943E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1621828056455481E-2</v>
+        <v>5.1620489573247864E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12426,30 +12426,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.9669817530258628E-2</v>
+        <v>8.9668795862835826E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8178654094276147E-2</v>
+        <v>9.8177293339715949E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0505312787149253E-2</v>
+        <v>9.0504254805735235E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.0024418967816327E-2</v>
+        <v>8.002340590040781E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.6411063794144338E-2</v>
+        <v>5.6410321892376943E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1621828056455481E-2</v>
+        <v>5.1620489573247864E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12495,28 +12495,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0706254578317598</v>
+        <v>2.065018767923072</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0706254578317598</v>
+        <v>2.065018767923072</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8823867798470544</v>
+        <v>1.8772897890209745</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2235514069005853</v>
+        <v>1.2202383628636335</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0353127289158799</v>
+        <v>1.032509383961536</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.70589504244264534</v>
+        <v>0.70398367088286551</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12551,28 +12551,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>2824740598.7251163</v>
+        <v>2817091970.3603725</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>2824740598.7251163</v>
+        <v>2817091970.3603725</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2567945998.8410149</v>
+        <v>2560992700.327611</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1669164899.2466595</v>
+        <v>1664645255.2129474</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1412370299.3625581</v>
+        <v>1408545985.1801863</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>962979749.56538045</v>
+        <v>960372262.62285423</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12606,28 +12606,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.98126027872235277</v>
+        <v>0.97861444308499612</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.89525127273638105</v>
+        <v>0.89283955080840471</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.83607352671620738</v>
+        <v>0.83381941438085505</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.64834253917243334</v>
+        <v>0.64659518967784668</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82995580164119942</v>
+        <v>0.82771939324995847</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.67199932255956119</v>
+        <v>0.67019710867134674</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12661,28 +12661,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.456803769335158E-2</v>
+        <v>3.5329662411002084E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.456803769335158E-2</v>
+        <v>3.5329662411002084E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.1425488812137803E-2</v>
+        <v>3.2117874919092806E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.0426567727889571E-2</v>
+        <v>2.0876618697410323E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.728401884667579E-2</v>
+        <v>1.7664831205501042E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.1784558304551676E-2</v>
+        <v>1.2044203094659802E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12798,26 +12798,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14024525199026316</v>
+        <v>-0.14024655922312423</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1157540882607915E-2</v>
+        <v>3.1156066406315297E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17570124711743196</v>
+        <v>0.17570187094398859</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27923615034044191</v>
+        <v>0.27923484081468075</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.22419111910081546</v>
+        <v>0.22420046887657219</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13409,23 +13409,23 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6336781299601471</v>
+        <v>1.6337007730264776</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90432211404715901</v>
+        <v>0.90433268543953171</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8950284590664057</v>
+        <v>1.8950524494420777</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5511334487175787</v>
+        <v>3.5511801527974964</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.4566630016028013</v>
+        <v>3.4567526304579377</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13517,28 +13517,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12564989315961772</v>
+        <v>0.12564853093638731</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14598863805066312</v>
+        <v>0.14598727729610292</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13407359193242835</v>
+        <v>0.13407253395101432</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12029329205099469</v>
+        <v>0.12029227898358617</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10028444178229179</v>
+        <v>0.10028369988052439</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.9022281208422135E-2</v>
+        <v>8.9020942725214519E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13803,30 +13803,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2420147311623619</v>
+        <v>2.2480763650541404</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4574106365418373</v>
+        <v>2.4640485493816349</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.3921341079357847</v>
+        <v>2.3986009026727704</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0051129170999094</v>
+        <v>2.0105315052648312</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3253717822380429</v>
+        <v>1.3289527936284766</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1160725536795841</v>
+        <v>1.11907376247394</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13860,30 +13860,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.7429294343278158E-2</v>
+        <v>3.8461528914527629E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.1025219307877087E-2</v>
+        <v>4.2156519236640461E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>3.9935460900430465E-2</v>
+        <v>4.1036799019209071E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.3474339183637888E-2</v>
+        <v>3.439745945705442E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.212640704904913E-2</v>
+        <v>2.2736574741291302E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.8632262999659168E-2</v>
+        <v>1.9145829982445507E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13917,23 +13917,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.496855387777709E-2</v>
+        <v>5.6332187806310476E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3211507056917469E-2</v>
+        <v>5.4531552997593775E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6560648975544079E-2</v>
+        <v>4.7715703569462621E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9848600925588486E-2</v>
+        <v>4.083714620090248E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8476506975117478E-2</v>
+        <v>2.9182938713593443E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878686379.1155</v>
+        <v>2878653580.3413415</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35983579738.943748</v>
+        <v>35983169754.266769</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12803797314.055439</v>
+        <v>12805072085.449562</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14801,7 +14801,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51257392245.499191</v>
+        <v>51258257032.216331</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14815,7 +14815,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0624809</v>
+        <v>1.0653656200000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>39.920926895373249</v>
+        <v>40.029990734186157</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>78.25757979312236</v>
+        <v>78.470292707595817</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14917,7 +14917,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3096926626.5072227</v>
+        <v>3096891341.1778636</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2867524654.1733541</v>
+        <v>2867491982.5720954</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3331712200.24194</v>
+        <v>3331674239.8455558</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14951,7 +14951,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2856406207.3404832</v>
+        <v>2856373662.4190292</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3584297441.9320173</v>
+        <v>3584256603.6652412</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2845330870.8117547</v>
+        <v>2845298452.0789204</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3856031787.8919654</v>
+        <v>3855987853.5764122</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2834298477.4326758</v>
+        <v>2834266184.3991823</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15005,7 +15005,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>4148366978.5001411</v>
+        <v>4148319713.4167886</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15017,7 +15017,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2823308860.696876</v>
+        <v>2823276692.87534</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15027,7 +15027,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4462864814.1197672</v>
+        <v>4462813965.7549715</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2812361854.7435894</v>
+        <v>2812329811.6485186</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4801205499.0152769</v>
+        <v>4801150795.7117167</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2801457294.3551545</v>
+        <v>2801425375.5029383</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>5165196617.8413382</v>
+        <v>5165137767.3466883</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2790595014.9545178</v>
+        <v>2790563219.863421</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>5556782792.6614447</v>
+        <v>5556719480.5670166</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2779774852.6027522</v>
+        <v>2779743180.7929077</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5978056072.0886803</v>
+        <v>5977987960.1496935</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2768996643.9965825</v>
+        <v>2768965094.9899831</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15137,7 +15137,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>6431267108.0526218</v>
+        <v>6431193832.381135</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2758260226.4659204</v>
+        <v>2758228799.7864132</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15159,7 +15159,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>6918837179.9042521</v>
+        <v>6918758349.0250883</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2747565437.9714079</v>
+        <v>2747534133.1446857</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15181,7 +15181,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>7443371130.09764</v>
+        <v>7443286322.8569326</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2736912117.1019754</v>
+        <v>2736880933.65557</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15203,7 +15203,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>8007671280.557251</v>
+        <v>8007580043.8724318</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15215,7 +15215,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2726300103.0724001</v>
+        <v>2726269040.535676</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>8614752404.0790749</v>
+        <v>8614654250.5182762</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2715729235.7208867</v>
+        <v>2715698293.6250319</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>9267857830.7502251</v>
+        <v>9267752235.9281807</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15259,7 +15259,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2705199355.5066438</v>
+        <v>2705168533.3846655</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>9970476775.4355812</v>
+        <v>9970363175.2120972</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2694710303.5074773</v>
+        <v>2694679600.8941922</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>10726362978.903521</v>
+        <v>10726240766.369555</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2684261921.4173937</v>
+        <v>2684231337.8494225</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>11539554762.180931</v>
+        <v>11539423284.416183</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2673854051.5442119</v>
+        <v>2673823586.5599723</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>12414396601.277864</v>
+        <v>12414255155.862555</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2663486536.8071775</v>
+        <v>2663456189.9468775</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>13355562337.544802</v>
+        <v>13355410168.806988</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>2653159220.7346001</v>
+        <v>2653128991.5402288</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>14368080147.663776</v>
+        <v>14367916442.642181</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>2642871947.4614835</v>
+        <v>2642841835.4768076</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>15457359406.675558</v>
+        <v>15457183290.776325</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
@@ -15413,7 +15413,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>2632624561.7271814</v>
+        <v>2632594566.4977355</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>16629219587.558533</v>
+        <v>16629030119.882706</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>2622416908.8730474</v>
+        <v>2622387029.9461284</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>17889921351.75528</v>
+        <v>17889717520.072056</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>2612248834.8401031</v>
+        <v>2612219071.7647643</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>19246199996.747917</v>
+        <v>19245980712.0868</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>2602120186.1667161</v>
+        <v>2602090538.4937572</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>20705301439.375858</v>
+        <v>20705065530.208843</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
@@ -15501,7 +15501,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>2592030809.9862785</v>
+        <v>2592001277.2682424</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>22275020927.136803</v>
+        <v>22274767133.11948</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
@@ -15523,7 +15523,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>2581980554.0249043</v>
+        <v>2581951135.8160682</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>23963744684.285995</v>
+        <v>23963471649.52417</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
@@ -15545,7 +15545,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>2571969266.5991268</v>
+        <v>2571939962.4554973</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>25780494715.228077</v>
+        <v>25780200981.033901</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>2561996796.6136136</v>
+        <v>2561967606.0929179</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38711582831.340279</v>
+        <v>38711141764.723297</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3847053840.559279</v>
+        <v>3847010008.5354066</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>85206806947.80957</v>
+        <v>85205836130.412384</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15621,7 +15621,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>85206806947.80957</v>
+        <v>85205836130.412384</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15651,19 +15651,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37144598385.711792</v>
+        <v>37144175172.782967</v>
       </c>
       <c r="C56" s="124">
-        <v>38340389034.302322</v>
+        <v>38339952196.941292</v>
       </c>
       <c r="D56" s="124">
-        <v>40842437214.182762</v>
+        <v>40841971869.335205</v>
       </c>
       <c r="E56" s="124">
-        <v>42151889051.796074</v>
+        <v>42151408787.499352</v>
       </c>
       <c r="F56" s="124">
-        <v>43502503008.533218</v>
+        <v>43502007355.800133</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15672,19 +15672,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>38306686147.183655</v>
+        <v>38306249693.821854</v>
       </c>
       <c r="C57" s="124">
-        <v>40862630718.039856</v>
+        <v>40862165143.114365</v>
       </c>
       <c r="D57" s="124">
-        <v>46787612389.254112</v>
+        <v>46787079307.101334</v>
       </c>
       <c r="E57" s="124">
-        <v>50222035860.499359</v>
+        <v>50221463647.692871</v>
       </c>
       <c r="F57" s="124">
-        <v>54020713108.964981</v>
+        <v>54020097615.321075</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15693,19 +15693,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>39745091968.747597</v>
+        <v>39744639126.678787</v>
       </c>
       <c r="C58" s="124">
-        <v>44150692611.224976</v>
+        <v>44150189573.239868</v>
       </c>
       <c r="D58" s="124">
-        <v>55431302716.627647</v>
+        <v>55430671151.205193</v>
       </c>
       <c r="E58" s="124">
-        <v>62642890968.13533</v>
+        <v>62642177236.327507</v>
       </c>
       <c r="F58" s="124">
-        <v>71182077020.7341</v>
+        <v>71181265996.342804</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15714,19 +15714,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>41210596827.313049</v>
+        <v>41210127287.779991</v>
       </c>
       <c r="C59" s="124">
-        <v>47689719297.092667</v>
+        <v>47689175936.640396</v>
       </c>
       <c r="D59" s="124">
-        <v>65911557113.599037</v>
+        <v>65910806139.720123</v>
       </c>
       <c r="E59" s="124">
-        <v>78690492279.240524</v>
+        <v>78689595706.517838</v>
       </c>
       <c r="F59" s="124">
-        <v>94859428882.114502</v>
+        <v>94858348086.02388</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15735,19 +15735,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>42573597666.657608</v>
+        <v>42573112597.556252</v>
       </c>
       <c r="C60" s="124">
-        <v>51175780977.817421</v>
+        <v>51175197898.363251</v>
       </c>
       <c r="D60" s="124">
-        <v>77641746156.614624</v>
+        <v>77640861532.948776</v>
       </c>
       <c r="E60" s="124">
-        <v>97936090453.665756</v>
+        <v>97934974603.138916</v>
       </c>
       <c r="F60" s="124">
-        <v>125364018869.68709</v>
+        <v>125362590514.66646</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15756,19 +15756,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>43775954011.524841</v>
+        <v>43775455243.183952</v>
       </c>
       <c r="C61" s="124">
-        <v>54440508636.078033</v>
+        <v>54439888359.426582</v>
       </c>
       <c r="D61" s="124">
-        <v>90222619717.118225</v>
+        <v>90221591751.255188</v>
       </c>
       <c r="E61" s="124">
-        <v>120157999337.44751</v>
+        <v>120156630298.0439</v>
       </c>
       <c r="F61" s="124">
-        <v>163384804506.24893</v>
+        <v>163382942955.31973</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15818,23 +15818,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>39.920926895373249</v>
+        <v>40.029990734186157</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>39.920926895373249</v>
+        <v>40.029990734186157</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>39.920926895373249</v>
+        <v>40.029990734186157</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>39.920926895373249</v>
+        <v>40.029990734186157</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>39.920926895373249</v>
+        <v>40.029990734186157</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15845,23 +15845,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>40.82516604003753</v>
+        <v>40.936674629355146</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>41.756486752490382</v>
+        <v>41.870513311523482</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>43.70516338432742</v>
+        <v>43.82445849229174</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>44.725007133537339</v>
+        <v>44.847059546950462</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>45.776909282061254</v>
+        <v>45.901805675768408</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15872,23 +15872,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>41.730237846061762</v>
+        <v>41.844193437112963</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>43.720890742976081</v>
+        <v>43.840228372289118</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>48.335459486935939</v>
+        <v>48.467273317188045</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>51.010300369723417</v>
+        <v>51.149346046370127</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>53.968833960523284</v>
+        <v>54.115878490716625</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15899,23 +15899,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>42.850515158912692</v>
+        <v>42.96749959309922</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>46.281740460742036</v>
+        <v>46.408001743689113</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>55.067447099817734</v>
+        <v>55.217461900699547</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>60.684066962355708</v>
+        <v>60.849267164494158</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>67.33466324160203</v>
+        <v>67.517844360300259</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15926,23 +15926,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>43.991898084587035</v>
+        <v>44.11196842420032</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>49.038049734741534</v>
+        <v>49.171763126490248</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>63.229810639940013</v>
+        <v>63.401893654194403</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>73.182461646938577</v>
+        <v>73.38145319387057</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>85.775356209496707</v>
+        <v>86.008394596271046</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15953,23 +15953,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.053447540813693</v>
+        <v>45.176387943710786</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>51.753108137292152</v>
+        <v>51.894162109725862</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>72.36566400158371</v>
+        <v>72.562447209640396</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.171560469975589</v>
+        <v>88.411077365902869</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>109.53332464134081</v>
+        <v>109.83059637352747</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15979,23 +15979,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>45.989881831417854</v>
+        <v>46.115354029380534</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>54.295784392738383</v>
+        <v>54.443712884037474</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>82.164058178238278</v>
+        <v>82.387332861752583</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>105.47870703287926</v>
+        <v>105.76501647870262</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>139.14515110009165</v>
+        <v>139.52248298904931</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>139.14515110009165</v>
+        <v>139.52248298904931</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>105.47870703287926</v>
+        <v>105.76501647870262</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16075,7 +16075,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>82.164058178238278</v>
+        <v>82.387332861752583</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>54.295784392738383</v>
+        <v>54.443712884037474</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>45.989881831417854</v>
+        <v>46.115354029380534</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-59.9</v>
+        <v>-58.45</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0706254578317598</v>
+        <v>2.065018767923072</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0706254578317598</v>
+        <v>2.065018767923072</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>80.323401137467158</v>
+        <v>80.530494373367446</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3155248905.8084812</v>
+        <v>3155205174.1096029</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878686379.1155</v>
+        <v>2878653580.3413415</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16411,7 +16411,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.2285137017123664</v>
+        <v>0.22851341166576811</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>59.9</v>
+        <v>58.45</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>39.920926895373249</v>
+        <v>40.029990734186157</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>82.164058178238278</v>
+        <v>82.387332861752583</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16582,7 +16582,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>54.295784392738383</v>
+        <v>54.443712884037474</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>105.47870703287926</v>
+        <v>105.76501647870262</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>78.466505813516505</v>
+        <v>78.679783591828055</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>45.989881831417854</v>
+        <v>46.115354029380534</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16799,7 +16799,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>139.14515110009165</v>
+        <v>139.52248298904931</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>78.252775679635405</v>
+        <v>78.465475605444368</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>78.25757979312236</v>
+        <v>78.470292707595817</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.15201687930591179</v>
+        <v>0.15202910680097503</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0706254578317598</v>
+        <v>2.065018767923072</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.0418608936875957</v>
+        <v>4.0309166349858367</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>40.065421147973325</v>
+        <v>40.174323509987516</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>44.107282041660923</v>
+        <v>44.205240144973352</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.43634865781330423</v>
+        <v>0.43662815010190104</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>59.9</v>
+        <v>58.45</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12493740306462042</v>
+        <v>0.13533159592642741</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DD9309-0D51-48CC-80F7-A3A61B40EBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6203EF04-CFF5-4BF6-81A8-28D4564E6209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>58.45</v>
+        <v>54.25</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>79737.302258600001</v>
+        <v>74007.675749000002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0653656200000001</v>
+        <v>1.0667112500000002</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>44.205240144973352</v>
+        <v>44.250954726078248</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>318</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13533159592642741</v>
+        <v>0.16523666770490664</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177486510.10960329</v>
+        <v>177466191.56481656</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155649456.10960329</v>
+        <v>155629137.56481656</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008429381.6043395</v>
+        <v>-1008424301.9681427</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3155205174.1096029</v>
+        <v>3155184855.5648165</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878653580.3413415</v>
+        <v>2878638341.4327517</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.8461528914527629E-2</v>
+        <v>4.1491316575080379E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5329662411002084E-2</v>
+        <v>3.8016844194438813E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>28.100954563176753</v>
+        <v>28.136299052476378</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.22287949744135632</v>
+        <v>0.22316100956499893</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12805072085.449562</v>
+        <v>12805664367.485912</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>10.000084798220231</v>
+        <v>10.013178717820995</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.1518308702305307</v>
+        <v>2.1545487805136769</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>40.029990734186157</v>
+        <v>40.080865541246055</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>139.52 HKD</v>
+        <v>139.7 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>105.77 HKD</v>
+        <v>105.9 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>82.39 HKD</v>
+        <v>82.49 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>54.44 HKD</v>
+        <v>54.51 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>46.12 HKD</v>
+        <v>46.17 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>78.465475605444368</v>
+        <v>78.564693346218675</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>2.065018767923072</v>
+        <v>2.0624137975483054</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>4.0309166349858367</v>
+        <v>4.0258317328142921</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>40.174323509987516</v>
+        <v>40.225122993263959</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>44.205240144973352</v>
+        <v>44.250954726078248</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.43662815010190104</v>
+        <v>0.43675774904290321</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,6 +5199,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5215,17 +5226,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5826,23 +5826,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.065018767923072</v>
+        <v>2.0624137975483054</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8772897890209745</v>
+        <v>1.8749216341348229</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2202383628636335</v>
+        <v>1.218699062187635</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.032509383961536</v>
+        <v>1.0312068987741527</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.70398367088286551</v>
+        <v>0.70309561280055854</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7164,23 +7164,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.065018767923072</v>
+        <v>2.0624137975483054</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8772897890209745</v>
+        <v>1.8749216341348229</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2202383628636335</v>
+        <v>1.218699062187635</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.032509383961536</v>
+        <v>1.0312068987741527</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.70398367088286551</v>
+        <v>0.70309561280055854</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8517,11 +8517,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.694625036051445</v>
+        <v>22.723289907259943</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3241437751721001</v>
+        <v>1.3258162597677499</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12805072085.449562</v>
+        <v>12805664367.485912</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8779,11 +8779,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2538927458.6966977</v>
+        <v>-2538631317.6785235</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2586850405.2752185</v>
+        <v>-2586554264.2570438</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>363</v>
@@ -8795,11 +8795,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.0812471756199784</v>
+        <v>7.0820732300903257</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.9500628483722524</v>
+        <v>6.9508585783195169</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>330</v>
@@ -8812,7 +8812,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5173700810.550437</v>
+        <v>5173108528.5140877</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>364</v>
@@ -8927,11 +8927,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-304051494.52055252</v>
+        <v>-304435532.45540881</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-0.22287949744135632</v>
+        <v>-0.22316100956499893</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8944,11 +8944,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13642083561.459667</v>
+        <v>13659946244.52136</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>10.000084798220231</v>
+        <v>10.013178717820995</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8961,11 +8961,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2935520761.4877348</v>
+        <v>2939228525.9660749</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>2.1518308702305307</v>
+        <v>2.1545487805136769</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8978,11 +8978,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16273552828.426849</v>
+        <v>16294739238.032028</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>11.929036171009404</v>
+        <v>11.944566488769674</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9562,28 +9562,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155649456.10960329</v>
+        <v>155629137.56481656</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155649456.10960329</v>
+        <v>155629137.56481656</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129287805.3720926</v>
+        <v>129271123.62123284</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>123037739.38095842</v>
+        <v>123022596.55985366</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68147856.781257391</v>
+        <v>68137458.250550002</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>137135764.41195753</v>
+        <v>137118501.10002863</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9617,28 +9617,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033717526.4173579</v>
+        <v>4033697207.872571</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691714316.1096029</v>
+        <v>4691693997.5648165</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4549955597.3720922</v>
+        <v>4549938915.621233</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3869990947.3809586</v>
+        <v>3869975804.5598536</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025238856.7812576</v>
+        <v>3025228458.2505498</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2471195636.4119577</v>
+        <v>2471178373.1000285</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008429381.6043395</v>
+        <v>-1008424301.9681427</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9784,30 +9784,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878653580.3413415</v>
+        <v>2878638341.4327517</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3155205174.1096029</v>
+        <v>3155184855.5648165</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071399701.3720922</v>
+        <v>3071383019.621233</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574478254.3809586</v>
+        <v>2574463111.5598536</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701719201.7812576</v>
+        <v>1701708803.2505498</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1432969868.4119577</v>
+        <v>1432952605.1000285</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -9892,30 +9892,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878653580.3413415</v>
+        <v>2878638341.4327517</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3155205174.1096029</v>
+        <v>3155184855.5648165</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071399701.3720922</v>
+        <v>3071383019.621233</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574478254.3809586</v>
+        <v>2574463111.5598536</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701719201.7812576</v>
+        <v>1701708803.2505498</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1432969868.4119577</v>
+        <v>1432952605.1000285</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10753,23 +10753,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29620650797688824</v>
+        <v>0.29620779077265491</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30730154351562466</v>
+        <v>0.30730267019619834</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31044512101845317</v>
+        <v>0.31044633575858799</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.40417687755767528</v>
+        <v>0.40417826682322355</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36928703885420316</v>
+        <v>0.36928961864262017</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10891,28 +10891,28 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177486510.10960329</v>
+        <v>177466191.56481656</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>177486510.10960329</v>
+        <v>177466191.56481656</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>145718395.3720926</v>
+        <v>145701713.62123284</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132275539.38095842</v>
+        <v>132260396.55985366</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90833223.781257391</v>
+        <v>90822825.250550002</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150798446.41195753</v>
+        <v>150781183.10002863</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -11003,28 +11003,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155649456.10960329</v>
+        <v>155629137.56481656</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155649456.10960329</v>
+        <v>155629137.56481656</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129287805.3720926</v>
+        <v>129271123.62123284</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>123037739.38095842</v>
+        <v>123022596.55985366</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68147856.781257391</v>
+        <v>68137458.250550002</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>137135764.41195753</v>
+        <v>137118501.10002863</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -12090,30 +12090,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8484122582052678E-3</v>
+        <v>4.8477793444510206E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8431849808157476E-3</v>
+        <v>4.8425527494324666E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8096951287202772E-3</v>
+        <v>3.8092035712620461E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8244249850611007E-3</v>
+        <v>3.8239542954688769E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.259034588833698E-3</v>
+        <v>2.2586898877432963E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.940100593177104E-3</v>
+        <v>4.9394787094703563E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12147,30 +12147,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12564853093638731</v>
+        <v>0.12564789802263307</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14598727729610292</v>
+        <v>0.14598664506471964</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13407253395101432</v>
+        <v>0.13407204239355611</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12029227898358617</v>
+        <v>0.12029180829399394</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10028369988052439</v>
+        <v>0.10028335517943399</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.9020942725214519E-2</v>
+        <v>8.9020320841507766E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.1412132734096827E-2</v>
+        <v>3.1411974505658267E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12319,30 +12319,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.9668795862835826E-2</v>
+        <v>8.9668321177520147E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8177293339715949E-2</v>
+        <v>9.8176661108332675E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0504254805735235E-2</v>
+        <v>9.0503763248277011E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.002340590040781E-2</v>
+        <v>8.0022935210815577E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.6410321892376943E-2</v>
+        <v>5.6409977191286528E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1620489573247864E-2</v>
+        <v>5.1619867689541105E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12426,30 +12426,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.9668795862835826E-2</v>
+        <v>8.9668321177520147E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8177293339715949E-2</v>
+        <v>9.8176661108332675E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0504254805735235E-2</v>
+        <v>9.0503763248277011E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.002340590040781E-2</v>
+        <v>8.0022935210815577E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.6410321892376943E-2</v>
+        <v>5.6409977191286528E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1620489573247864E-2</v>
+        <v>5.1619867689541105E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12495,28 +12495,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.065018767923072</v>
+        <v>2.0624137975483054</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.065018767923072</v>
+        <v>2.0624137975483054</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8772897890209745</v>
+        <v>1.8749216341348229</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2202383628636335</v>
+        <v>1.218699062187635</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.032509383961536</v>
+        <v>1.0312068987741527</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.70398367088286551</v>
+        <v>0.70309561280055854</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12551,28 +12551,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>2817091970.3603725</v>
+        <v>2813538278.1422806</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>2817091970.3603725</v>
+        <v>2813538278.1422806</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2560992700.327611</v>
+        <v>2557762071.0384364</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1664645255.2129474</v>
+        <v>1662545346.174984</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1408545985.1801863</v>
+        <v>1406769139.0711403</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>960372262.62285423</v>
+        <v>959160776.6394136</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12606,28 +12606,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.97861444308499612</v>
+        <v>0.97738511908443848</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.89283955080840471</v>
+        <v>0.89171899807392518</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.83381941438085505</v>
+        <v>0.83277209475289193</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.64659518967784668</v>
+        <v>0.64578332418507889</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82771939324995847</v>
+        <v>0.82668029711309887</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.67019710867134674</v>
+        <v>0.66935973543413785</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12661,28 +12661,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5329662411002084E-2</v>
+        <v>3.8016844194438813E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5329662411002084E-2</v>
+        <v>3.8016844194438813E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.2117874919092806E-2</v>
+        <v>3.4560767449489826E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.0876618697410323E-2</v>
+        <v>2.2464498842168387E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.7664831205501042E-2</v>
+        <v>1.9008422097219407E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2044203094659802E-2</v>
+        <v>1.2960287793558683E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12798,26 +12798,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14024655922312423</v>
+        <v>-0.14024716659564185</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1156066406315297E-2</v>
+        <v>3.1155381329823539E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17570187094398859</v>
+        <v>0.17570216078875833</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27923484081468075</v>
+        <v>0.27923423237853906</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.22420046887657219</v>
+        <v>0.22420481304855389</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13409,23 +13409,23 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6337007730264776</v>
+        <v>1.6337112936215754</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90433268543953171</v>
+        <v>0.90433759718530093</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8950524494420777</v>
+        <v>1.8950635960147739</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5511801527974964</v>
+        <v>3.5512018527827096</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.4567526304579377</v>
+        <v>3.4567942752399841</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13517,28 +13517,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12564853093638731</v>
+        <v>0.12564789802263307</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14598727729610292</v>
+        <v>0.14598664506471964</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13407253395101432</v>
+        <v>0.13407204239355611</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12029227898358617</v>
+        <v>0.12029180829399394</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10028369988052439</v>
+        <v>0.10028335517943399</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.9020942725214519E-2</v>
+        <v>8.9020320841507766E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13803,30 +13803,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2480763650541404</v>
+        <v>2.2509039241981106</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4640485493816349</v>
+        <v>2.4671449243000385</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.3986009026727704</v>
+        <v>2.4016174564464232</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0105315052648312</v>
+        <v>2.013059104058601</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3289527936284766</v>
+        <v>1.3306232213848301</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.11907376247394</v>
+        <v>1.1204737307862713</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13860,30 +13860,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.8461528914527629E-2</v>
+        <v>4.1491316575080379E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.2156519236640461E-2</v>
+        <v>4.54773257935491E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.1036799019209071E-2</v>
+        <v>4.4269446201777383E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.439745945705442E-2</v>
+        <v>3.710708025914472E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.2736574741291302E-2</v>
+        <v>2.4527616984052168E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.9145829982445507E-2</v>
+        <v>2.0653893655046475E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13917,23 +13917,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6332187806310476E-2</v>
+        <v>6.0693389442928063E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4531552997593775E-2</v>
+        <v>5.8753350649020396E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7715703569462621E-2</v>
+        <v>5.1409822555485533E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.083714620090248E-2</v>
+        <v>4.3998731713230418E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9182938713593443E-2</v>
+        <v>3.1442263001097454E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878653580.3413415</v>
+        <v>2878638341.4327517</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35983169754.266769</v>
+        <v>35982979267.909393</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12805072085.449562</v>
+        <v>12805664367.485912</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14801,7 +14801,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51258257032.216331</v>
+        <v>51258658827.895309</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14815,7 +14815,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0653656200000001</v>
+        <v>1.0667112500000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>40.029990734186157</v>
+        <v>40.080865541246055</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>78.470292707595817</v>
+        <v>78.569516507168387</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14917,7 +14917,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3096891341.1778636</v>
+        <v>3096874946.9703827</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2867491982.5720954</v>
+        <v>2867476802.7503538</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3331674239.8455558</v>
+        <v>3331656602.7531528</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14951,7 +14951,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2856373662.4190292</v>
+        <v>2856358541.4550347</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3584256603.6652412</v>
+        <v>3584237629.4617734</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2845298452.0789204</v>
+        <v>2845283389.7444596</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3855987853.5764122</v>
+        <v>3855967440.8922229</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2834266184.3991823</v>
+        <v>2834251180.4669271</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15005,7 +15005,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>4148319713.4167886</v>
+        <v>4148297753.1971407</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15017,7 +15017,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2823276692.87534</v>
+        <v>2823261747.1188445</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15027,7 +15027,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4462813965.7549715</v>
+        <v>4462790340.6774197</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2812329811.6485186</v>
+        <v>2812314923.8422127</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4801150795.7117167</v>
+        <v>4801125379.5593176</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2801425375.5029383</v>
+        <v>2801410545.4221287</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>5165137767.3466883</v>
+        <v>5165110424.3336802</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2790563219.863421</v>
+        <v>2790548447.2842841</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>5556719480.5670166</v>
+        <v>5556690064.61339</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2779743180.7929077</v>
+        <v>2779728465.4924889</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15115,7 +15115,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5977987960.1496935</v>
+        <v>5977956314.1007557</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2768965094.9899831</v>
+        <v>2768950436.7461915</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15137,7 +15137,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>6431193832.381135</v>
+        <v>6431159787.1679115</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2758228799.7864132</v>
+        <v>2758214198.3780193</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15159,7 +15159,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>6918758349.0250883</v>
+        <v>6918721722.7610741</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2747534133.1446857</v>
+        <v>2747519588.3513179</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15181,7 +15181,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>7443286322.8569326</v>
+        <v>7443246919.8663607</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2736880933.65557</v>
+        <v>2736866445.2577109</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15203,7 +15203,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>8007580043.8724318</v>
+        <v>8007537653.6448784</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15215,7 +15215,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2726269040.535676</v>
+        <v>2726254608.3146596</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>8614654250.5182762</v>
+        <v>8614608646.5840073</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2715698293.6250319</v>
+        <v>2715683917.36304</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>9267752235.9281807</v>
+        <v>9267703174.6482391</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15259,7 +15259,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2705168533.3846655</v>
+        <v>2705154212.8647242</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>9970363175.2120972</v>
+        <v>9970310394.4766598</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2694679600.8941922</v>
+        <v>2694665335.9001694</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>10726240766.369555</v>
+        <v>10726183984.197615</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2684231337.8494225</v>
+        <v>2684217128.1660237</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>11539423284.416183</v>
+        <v>11539362197.449062</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2673823586.5599723</v>
+        <v>2673809431.9727373</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>12414255155.862555</v>
+        <v>12414189437.743212</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2663456189.9468775</v>
+        <v>2663442090.2421784</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>13355410168.806988</v>
+        <v>13355339468.436462</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>2653128991.5402288</v>
+        <v>2653114946.5052667</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>14367916442.642181</v>
+        <v>14367840382.303837</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>2642841835.4768076</v>
+        <v>2642827844.8996072</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>15457183290.776325</v>
+        <v>15457101464.117907</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
@@ -15413,7 +15413,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>2632594566.4977355</v>
+        <v>2632580630.1671448</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>16629030119.882706</v>
+        <v>16628942089.745398</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>2622387029.9461284</v>
+        <v>2622373147.6518121</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>17889717520.072056</v>
+        <v>17889622816.154968</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
@@ -15457,7 +15457,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>2612219071.7647643</v>
+        <v>2612205243.297204</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>19245980712.0868</v>
+        <v>19245878828.434387</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>2602090538.4937572</v>
+        <v>2602076763.6442475</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>20705065530.208843</v>
+        <v>20704955922.507824</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
@@ -15501,7 +15501,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>2592001277.2682424</v>
+        <v>2591987555.828886</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>22274767133.11948</v>
+        <v>22274649215.790863</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
@@ -15523,7 +15523,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>2581951135.8160682</v>
+        <v>2581937467.5797749</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>23963471649.52417</v>
+        <v>23963344792.594784</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
@@ -15545,7 +15545,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>2571939962.4554973</v>
+        <v>2571926347.2159791</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>25780200981.033901</v>
+        <v>25780064506.770767</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>2561967606.0929179</v>
+        <v>2561954043.6446862</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38711141764.723297</v>
+        <v>38710936837.129784</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3847010008.5354066</v>
+        <v>3846989643.3777971</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>85205836130.412384</v>
+        <v>85205385070.945892</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15621,7 +15621,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>85205836130.412384</v>
+        <v>85205385070.945892</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15651,19 +15651,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37144175172.782967</v>
+        <v>37143978540.338562</v>
       </c>
       <c r="C56" s="124">
-        <v>38339952196.941292</v>
+        <v>38339749234.337227</v>
       </c>
       <c r="D56" s="124">
-        <v>40841971869.335205</v>
+        <v>40841755661.633034</v>
       </c>
       <c r="E56" s="124">
-        <v>42151408787.499352</v>
+        <v>42151185647.949028</v>
       </c>
       <c r="F56" s="124">
-        <v>43502007355.800133</v>
+        <v>43501777066.501656</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15672,19 +15672,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>38306249693.821854</v>
+        <v>38306046909.630844</v>
       </c>
       <c r="C57" s="124">
-        <v>40862165143.114365</v>
+        <v>40861948828.513817</v>
       </c>
       <c r="D57" s="124">
-        <v>46787079307.101334</v>
+        <v>46786831627.411896</v>
       </c>
       <c r="E57" s="124">
-        <v>50221463647.692871</v>
+        <v>50221197787.188156</v>
       </c>
       <c r="F57" s="124">
-        <v>54020097615.321075</v>
+        <v>54019811645.750031</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15693,19 +15693,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>39744639126.678787</v>
+        <v>39744428727.995613</v>
       </c>
       <c r="C58" s="124">
-        <v>44150189573.239868</v>
+        <v>44149955852.618637</v>
       </c>
       <c r="D58" s="124">
-        <v>55430671151.205193</v>
+        <v>55430377714.392746</v>
       </c>
       <c r="E58" s="124">
-        <v>62642177236.327507</v>
+        <v>62641845623.514038</v>
       </c>
       <c r="F58" s="124">
-        <v>71181265996.342804</v>
+        <v>71180889179.620834</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15714,19 +15714,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>41210127287.779991</v>
+        <v>41209909131.150436</v>
       </c>
       <c r="C59" s="124">
-        <v>47689175936.640396</v>
+        <v>47688923481.465614</v>
       </c>
       <c r="D59" s="124">
-        <v>65910806139.720123</v>
+        <v>65910457223.561325</v>
       </c>
       <c r="E59" s="124">
-        <v>78689595706.517838</v>
+        <v>78689179142.481049</v>
       </c>
       <c r="F59" s="124">
-        <v>94858348086.02388</v>
+        <v>94857845928.450836</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15735,19 +15735,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>42573112597.556252</v>
+        <v>42572887225.606087</v>
       </c>
       <c r="C60" s="124">
-        <v>51175197898.363251</v>
+        <v>51174926989.015862</v>
       </c>
       <c r="D60" s="124">
-        <v>77640861532.948776</v>
+        <v>77640450520.661743</v>
       </c>
       <c r="E60" s="124">
-        <v>97934974603.138916</v>
+        <v>97934456158.63559</v>
       </c>
       <c r="F60" s="124">
-        <v>125362590514.66646</v>
+        <v>125361926874.87646</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15756,19 +15756,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>43775455243.183952</v>
+        <v>43775223506.317291</v>
       </c>
       <c r="C61" s="124">
-        <v>54439888359.426582</v>
+        <v>54439600167.583008</v>
       </c>
       <c r="D61" s="124">
-        <v>90221591751.255188</v>
+        <v>90221114139.569397</v>
       </c>
       <c r="E61" s="124">
-        <v>120156630298.0439</v>
+        <v>120155994217.37132</v>
       </c>
       <c r="F61" s="124">
-        <v>163382942955.31973</v>
+        <v>163382078044.81091</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15818,23 +15818,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>40.029990734186157</v>
+        <v>40.080865541246055</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>40.029990734186157</v>
+        <v>40.080865541246055</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>40.029990734186157</v>
+        <v>40.080865541246055</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>40.029990734186157</v>
+        <v>40.080865541246055</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>40.029990734186157</v>
+        <v>40.080865541246055</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15845,23 +15845,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>40.936674629355146</v>
+        <v>40.988689834658786</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>41.870513311523482</v>
+        <v>41.92370306950059</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>43.82445849229174</v>
+        <v>43.880105860538926</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>44.847059546950462</v>
+        <v>44.903993110367736</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>45.901805675768408</v>
+        <v>45.960065865410428</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15872,23 +15872,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>41.844193437112963</v>
+        <v>41.897350090786894</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>43.840228372289118</v>
+        <v>43.895895575391165</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>48.467273317188045</v>
+        <v>48.52876027065394</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>51.149346046370127</v>
+        <v>51.214206425840629</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>54.115878490716625</v>
+        <v>54.184470080598523</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15899,23 +15899,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>42.96749959309922</v>
+        <v>43.022069105625356</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>46.408001743689113</v>
+        <v>46.466898610689064</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>55.217461900699547</v>
+        <v>55.287439027252766</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>60.849267164494158</v>
+        <v>60.926327797069796</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>67.517844360300259</v>
+        <v>67.603292517748443</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15926,23 +15926,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>44.11196842420032</v>
+        <v>44.16797741332018</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>49.171763126490248</v>
+        <v>49.234136164892192</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>63.401893654194403</v>
+        <v>63.482164899400622</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>73.38145319387057</v>
+        <v>73.474276412518535</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>86.008394596271046</v>
+        <v>86.117099581293871</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15953,23 +15953,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.176387943710786</v>
+        <v>45.233735725939368</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>51.894162109725862</v>
+        <v>51.959959295215604</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>72.562447209640396</v>
+        <v>72.654240308539926</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.411077365902869</v>
+        <v>88.522804369101337</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>109.83059637352747</v>
+        <v>109.96926416831596</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15979,23 +15979,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>46.115354029380534</v>
+        <v>46.173882813368081</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>54.443712884037474</v>
+        <v>54.512716813620528</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>82.387332861752583</v>
+        <v>82.491483390184314</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>105.76501647870262</v>
+        <v>105.89857071605786</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>139.52248298904931</v>
+        <v>139.6984962970092</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>139.52248298904931</v>
+        <v>139.6984962970092</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>105.76501647870262</v>
+        <v>105.89857071605786</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16075,7 +16075,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>82.387332861752583</v>
+        <v>82.491483390184314</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>54.443712884037474</v>
+        <v>54.512716813620528</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>46.115354029380534</v>
+        <v>46.173882813368081</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-58.45</v>
+        <v>-54.25</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.065018767923072</v>
+        <v>2.0624137975483054</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.065018767923072</v>
+        <v>2.0624137975483054</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>80.530494373367446</v>
+        <v>80.627107143766978</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3155205174.1096029</v>
+        <v>3155184855.5648165</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878653580.3413415</v>
+        <v>2878638341.4327517</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16411,7 +16411,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.22851341166576811</v>
+        <v>0.22851327690218692</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>58.45</v>
+        <v>54.25</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>40.029990734186157</v>
+        <v>40.080865541246055</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>82.387332861752583</v>
+        <v>82.491483390184314</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16582,7 +16582,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>54.443712884037474</v>
+        <v>54.512716813620528</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>105.76501647870262</v>
+        <v>105.89857071605786</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>78.679783591828055</v>
+        <v>78.779270882389881</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>46.115354029380534</v>
+        <v>46.173882813368081</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16799,7 +16799,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>139.52248298904931</v>
+        <v>139.6984962970092</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>78.465475605444368</v>
+        <v>78.564693346218675</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>78.470292707595817</v>
+        <v>78.569516507168387</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.15202910680097503</v>
+        <v>0.15203478789298383</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.065018767923072</v>
+        <v>2.0624137975483054</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.0309166349858367</v>
+        <v>4.0258317328142921</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>40.174323509987516</v>
+        <v>40.225122993263959</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>44.205240144973352</v>
+        <v>44.250954726078248</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.43662815010190104</v>
+        <v>0.43675774904290321</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>58.45</v>
+        <v>54.25</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13533159592642741</v>
+        <v>0.16523666770490664</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6203EF04-CFF5-4BF6-81A8-28D4564E6209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F486BDF-8806-4348-AFC2-0DFEC895EF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="420">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2331,6 +2331,22 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Price Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Cash Yield</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3004,7 +3020,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3697,29 +3713,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3732,6 +3748,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4130,13 +4149,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4194,7 +4213,12 @@
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="E19" s="348">
+        <v>3.4500000000000003E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="str">
@@ -4203,7 +4227,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>44.250954726078248</v>
+        <v>38.289885084736959</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>318</v>
@@ -4218,7 +4242,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16523666770490664</v>
+        <v>0.10804060157997641</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4262,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4289,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4315,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4350,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4372,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4418,13 +4442,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4440,7 +4464,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>350</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4486,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>355</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4538,22 +4562,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4635,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4663,13 +4687,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4706,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4792,13 +4816,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4824,13 +4848,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4856,7 +4880,7 @@
       </c>
       <c r="C107" s="256">
         <f>Valuation_Model!C74</f>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="D107" s="257">
         <f>Valuation_Model!D74</f>
@@ -4864,7 +4888,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>139.7 HKD</v>
+        <v>105.9 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4878,7 +4902,7 @@
       </c>
       <c r="C108" s="243">
         <f>Valuation_Model!C75</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D108" s="244">
         <f>Valuation_Model!D75</f>
@@ -4886,11 +4910,11 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>105.9 HKD</v>
+        <v>82.49 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -4900,7 +4924,7 @@
       </c>
       <c r="C109" s="243">
         <f>Valuation_Model!C76</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D109" s="244">
         <f>Valuation_Model!D76</f>
@@ -4908,11 +4932,11 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>82.49 HKD</v>
+        <v>66.11 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
-        <v>0.42499999999999999</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -4934,7 +4958,7 @@
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
-        <v>0.255</v>
+        <v>0.26999999999999996</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -4956,7 +4980,7 @@
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -4965,7 +4989,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>78.564693346218675</v>
+        <v>66.921979202973958</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4973,13 +4997,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>385</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +5016,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>383</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>384</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5067,7 +5091,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>40.225122993263959</v>
+        <v>34.264053351922669</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5076,7 +5100,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>44.250954726078248</v>
+        <v>38.289885084736959</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5089,7 +5113,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.43675774904290321</v>
+        <v>0.42784290690799853</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5103,13 +5127,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5170,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>396</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5184,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>397</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>398</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,17 +5223,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5226,6 +5239,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -14862,7 +14886,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14882,7 +14906,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>78.569516507168387</v>
+        <v>66.920168335604359</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14917,11 +14941,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3096874946.9703827</v>
+        <v>3054712697.0013571</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14929,7 +14953,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2867476802.7503538</v>
+        <v>2828437682.4086637</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14939,11 +14963,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3331656602.7531528</v>
+        <v>3241556789.8595276</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14951,7 +14975,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2856358541.4550347</v>
+        <v>2779112474.1594028</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14961,11 +14985,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3584237629.4617734</v>
+        <v>3439829360.1225491</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -14973,7 +14997,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2845283389.7444596</v>
+        <v>2730647449.673059</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14983,11 +15007,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3855967440.8922229</v>
+        <v>3650229440.3035474</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -14995,7 +15019,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2834251180.4669271</v>
+        <v>2683027608.1795964</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15005,11 +15029,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>4148297753.1971407</v>
+        <v>3873498819.8321714</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15017,7 +15041,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2823261747.1188445</v>
+        <v>2636238210.5078487</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15027,11 +15051,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4462790340.6774197</v>
+        <v>4110424660.3176589</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15039,7 +15063,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2812314923.8422127</v>
+        <v>2590264774.5234909</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15049,11 +15073,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4801125379.5593176</v>
+        <v>4361842270.7766771</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15061,7 +15085,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2801410545.4221287</v>
+        <v>2545093070.6465669</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15071,11 +15095,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>5165110424.3336802</v>
+        <v>4628638052.6103392</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15083,7 +15107,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2790548447.2842841</v>
+        <v>2500709117.447185</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15093,11 +15117,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>5556690064.61339</v>
+        <v>4911752624.7132235</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15105,7 +15129,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2779728465.4924889</v>
+        <v>2457099177.3180232</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15115,11 +15139,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5977956314.1007557</v>
+        <v>5212184139.7323503</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15127,7 +15151,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2768950436.7461915</v>
+        <v>2414249752.2222967</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15137,11 +15161,11 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>6431159787.1679115</v>
+        <v>5530991803.1679411</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
@@ -15149,7 +15173,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2758214198.3780193</v>
+        <v>2372147579.5158854</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15159,11 +15183,11 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>6918721722.7610741</v>
+        <v>5869299607.7229662</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
@@ -15171,7 +15195,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2747519588.3513179</v>
+        <v>2330779627.842309</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15181,11 +15205,11 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>7443246919.8663607</v>
+        <v>6228300296.0673494</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
@@ -15193,7 +15217,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2736866445.2577109</v>
+        <v>2290133093.0993013</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15203,11 +15227,11 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>8007537653.6448784</v>
+        <v>6609259565.9879999</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
@@ -15215,7 +15239,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2726254608.3146596</v>
+        <v>2250195394.475709</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15225,11 +15249,11 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>8614608646.5840073</v>
+        <v>7013520532.7504206</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
@@ -15237,7 +15261,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2715683917.36304</v>
+        <v>2210954170.5575194</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15247,11 +15271,11 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>9267703174.6482391</v>
+        <v>7442508464.4044466</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
@@ -15259,7 +15283,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2705154212.8647242</v>
+        <v>2172397275.5017829</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15269,11 +15293,11 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>9970310394.4766598</v>
+        <v>7897735806.7289705</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
@@ -15281,7 +15305,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2694665335.9001694</v>
+        <v>2134512775.2772627</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15291,11 +15315,11 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>10726183984.197615</v>
+        <v>8380807515.5316763</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
@@ -15303,7 +15327,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2684217128.1660237</v>
+        <v>2097288943.9706452</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15313,11 +15337,11 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>11539362197.449062</v>
+        <v>8893426715.1034107</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
@@ -15325,7 +15349,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2673809431.9727373</v>
+        <v>2060714260.1571665</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15335,11 +15359,11 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>12414189437.743212</v>
+        <v>9437400702.77672</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
@@ -15347,7 +15371,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2663442090.2421784</v>
+        <v>2024777403.3345287</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15357,11 +15381,11 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>13355339468.436462</v>
+        <v>10014647320.758284</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E41" s="125">
         <f t="shared" si="0"/>
@@ -15369,7 +15393,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>2653114946.5052667</v>
+        <v>1989467250.4190066</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15379,11 +15403,11 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>14367840382.303837</v>
+        <v>10627201717.699909</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E42" s="125">
         <f t="shared" si="0"/>
@@ -15391,7 +15415,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>2642827844.8996072</v>
+        <v>1954772872.3026624</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15401,11 +15425,11 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>15457101464.117907</v>
+        <v>11277223523.846722</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E43" s="125">
         <f t="shared" si="0"/>
@@ -15413,7 +15437,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>2632580630.1671448</v>
+        <v>1920683530.4705927</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15423,11 +15447,11 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>16628942089.745398</v>
+        <v>11967004465.059414</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E44" s="125">
         <f t="shared" si="0"/>
@@ -15435,7 +15459,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>2622373147.6518121</v>
+        <v>1887188673.6771736</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15445,11 +15469,11 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>17889622816.154968</v>
+        <v>12698976442.55459</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E45" s="125">
         <f t="shared" si="0"/>
@@ -15457,7 +15481,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>2612205243.297204</v>
+        <v>1854277934.6802647</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15467,11 +15491,11 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>19245878828.434387</v>
+        <v>13475720106.849295</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E46" s="125">
         <f t="shared" si="0"/>
@@ -15479,7 +15503,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>2602076763.6442475</v>
+        <v>1821941127.0323675</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15489,11 +15513,11 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>20704955922.507824</v>
+        <v>14299973956.138134</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E47" s="125">
         <f t="shared" si="0"/>
@@ -15501,7 +15525,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>2591987555.828886</v>
+        <v>1790168241.9277415</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15511,11 +15535,11 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>22274649215.790863</v>
+        <v>15174643991.180353</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E48" s="125">
         <f t="shared" si="0"/>
@@ -15523,7 +15547,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>2581937467.5797749</v>
+        <v>1758949445.1045055</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15533,11 +15557,11 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>23963344792.594784</v>
+        <v>16102813960.736256</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E49" s="125">
         <f t="shared" si="0"/>
@@ -15545,7 +15569,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>2571926347.2159791</v>
+        <v>1728275073.8007624</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15555,11 +15579,11 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>25780064506.770767</v>
+        <v>17087756233.674442</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="E50" s="125">
         <f t="shared" si="0"/>
@@ -15567,7 +15591,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>2561954043.6446862</v>
+        <v>1698135633.763804</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15577,7 +15601,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38710936837.129784</v>
+        <v>38183908712.51696</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15589,7 +15613,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3846989643.3777971</v>
+        <v>3794614994.1750507</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15600,7 +15624,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>85205385070.945892</v>
+        <v>70307254618.17218</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15621,7 +15645,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>85205385070.945892</v>
+        <v>70307254618.17218</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15633,15 +15657,15 @@
       </c>
       <c r="D55" s="132">
         <f>C76</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E55" s="132">
         <f>C75</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F55" s="132">
         <f>C74</f>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H55" s="121"/>
     </row>
@@ -15657,13 +15681,13 @@
         <v>38339749234.337227</v>
       </c>
       <c r="D56" s="124">
+        <v>39571817232.211975</v>
+      </c>
+      <c r="E56" s="124">
         <v>40841755661.633034</v>
       </c>
-      <c r="E56" s="124">
+      <c r="F56" s="124">
         <v>42151185647.949028</v>
-      </c>
-      <c r="F56" s="124">
-        <v>43501777066.501656</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15678,13 +15702,13 @@
         <v>40861948828.513817</v>
       </c>
       <c r="D57" s="124">
+        <v>43678550185.483231</v>
+      </c>
+      <c r="E57" s="124">
         <v>46786831627.411896</v>
       </c>
-      <c r="E57" s="124">
+      <c r="F57" s="124">
         <v>50221197787.188156</v>
-      </c>
-      <c r="F57" s="124">
-        <v>54019811645.750031</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15699,13 +15723,13 @@
         <v>44149955852.618637</v>
       </c>
       <c r="D58" s="124">
+        <v>49327519805.158142</v>
+      </c>
+      <c r="E58" s="124">
         <v>55430377714.392746</v>
       </c>
-      <c r="E58" s="124">
+      <c r="F58" s="124">
         <v>62641845623.514038</v>
-      </c>
-      <c r="F58" s="124">
-        <v>71180889179.620834</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15720,13 +15744,13 @@
         <v>47688923481.465614</v>
       </c>
       <c r="D59" s="124">
+        <v>55771458671.891273</v>
+      </c>
+      <c r="E59" s="124">
         <v>65910457223.561325</v>
       </c>
-      <c r="E59" s="124">
+      <c r="F59" s="124">
         <v>78689179142.481049</v>
-      </c>
-      <c r="F59" s="124">
-        <v>94857845928.450836</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15741,13 +15765,13 @@
         <v>51174926989.015862</v>
       </c>
       <c r="D60" s="124">
+        <v>62524510676.924438</v>
+      </c>
+      <c r="E60" s="124">
         <v>77640450520.661743</v>
       </c>
-      <c r="E60" s="124">
+      <c r="F60" s="124">
         <v>97934456158.63559</v>
-      </c>
-      <c r="F60" s="124">
-        <v>125361926874.87646</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15762,13 +15786,13 @@
         <v>54439600167.583008</v>
       </c>
       <c r="D61" s="124">
+        <v>69276704501.23262</v>
+      </c>
+      <c r="E61" s="124">
         <v>90221114139.569397</v>
       </c>
-      <c r="E61" s="124">
+      <c r="F61" s="124">
         <v>120155994217.37132</v>
-      </c>
-      <c r="F61" s="124">
-        <v>163382078044.81091</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15800,15 +15824,15 @@
       </c>
       <c r="D64" s="133">
         <f>D55</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E64" s="133">
         <f>E55</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F64" s="133">
         <f>F55</f>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -15853,15 +15877,15 @@
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>43.880105860538926</v>
+        <v>42.887098384354509</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>44.903993110367736</v>
+        <v>43.880105860538926</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>45.960065865410428</v>
+        <v>44.903993110367736</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15880,15 +15904,15 @@
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>48.52876027065394</v>
+        <v>46.098290699520824</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>51.214206425840629</v>
+        <v>48.52876027065394</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>54.184470080598523</v>
+        <v>51.214206425840629</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15907,15 +15931,15 @@
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>55.287439027252766</v>
+        <v>50.515409620501202</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>60.926327797069796</v>
+        <v>55.287439027252766</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>67.603292517748443</v>
+        <v>60.926327797069796</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15934,15 +15958,15 @@
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>63.482164899400622</v>
+        <v>55.554141674352422</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>73.474276412518535</v>
+        <v>63.482164899400622</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>86.117099581293871</v>
+        <v>73.474276412518535</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15961,15 +15985,15 @@
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>72.654240308539926</v>
+        <v>60.834579664654996</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>88.522804369101337</v>
+        <v>72.654240308539926</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>109.96926416831596</v>
+        <v>88.522804369101337</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15987,15 +16011,15 @@
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>82.491483390184314</v>
+        <v>66.114346614648767</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>105.89857071605786</v>
+        <v>82.491483390184314</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>139.6984962970092</v>
+        <v>105.89857071605786</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16022,7 +16046,7 @@
       </c>
       <c r="C74" s="143">
         <f>Scenarios!C56</f>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="D74" s="146">
         <f>Scenarios!C55</f>
@@ -16030,7 +16054,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>139.6984962970092</v>
+        <v>105.89857071605786</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16044,7 +16068,7 @@
       </c>
       <c r="C75" s="143">
         <f>Scenarios!C38</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D75" s="146">
         <f>Scenarios!C37</f>
@@ -16052,11 +16076,11 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>105.89857071605786</v>
+        <v>82.491483390184314</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H75" s="121"/>
     </row>
@@ -16067,7 +16091,7 @@
       </c>
       <c r="C76" s="143">
         <f>Scenarios!C26</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D76" s="146">
         <f>Scenarios!C25</f>
@@ -16075,11 +16099,11 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>82.491483390184314</v>
+        <v>66.114346614648767</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
-        <v>0.42499999999999999</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="H76" s="121"/>
     </row>
@@ -16102,7 +16126,7 @@
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
-        <v>0.255</v>
+        <v>0.26999999999999996</v>
       </c>
       <c r="H77" s="121"/>
     </row>
@@ -16125,7 +16149,7 @@
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
@@ -16189,7 +16213,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16271,7 +16295,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>80.627107143766978</v>
+        <v>68.98439300052226</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16512,7 +16536,7 @@
         <v>136</v>
       </c>
       <c r="C26" s="165">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D26" s="165"/>
       <c r="E26" s="345"/>
@@ -16524,7 +16548,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>82.491483390184314</v>
+        <v>66.114346614648767</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16628,7 +16652,7 @@
         <v>136</v>
       </c>
       <c r="C38" s="165">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
       <c r="E38" s="345"/>
@@ -16640,7 +16664,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>105.89857071605786</v>
+        <v>82.491483390184314</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16667,7 +16691,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>78.779270882389881</v>
+        <v>65.909285029447403</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16755,7 +16779,7 @@
         <v>149</v>
       </c>
       <c r="C52" s="166">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
       <c r="E52" s="345"/>
@@ -16787,7 +16811,7 @@
         <v>136</v>
       </c>
       <c r="C56" s="165">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
       <c r="E56" s="345"/>
@@ -16799,7 +16823,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>139.6984962970092</v>
+        <v>105.89857071605786</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16825,7 +16849,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>78.564693346218675</v>
+        <v>66.921979202973958</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16874,7 +16898,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>7.5812443125109999E-2</v>
+        <v>6.1165848114483959E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -16887,7 +16911,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>78.569516507168387</v>
+        <v>66.920168335604359</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16950,7 +16974,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.15203478789298383</v>
+        <v>0.17848495563082312</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -17022,7 +17046,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>40.225122993263959</v>
+        <v>34.264053351922669</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17032,7 +17056,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>44.250954726078248</v>
+        <v>38.289885084736959</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17043,7 +17067,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.43675774904290321</v>
+        <v>0.42784290690799853</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17073,49 +17097,106 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16523666770490664</v>
+        <v>0.10804060157997641</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="320" t="s">
+    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B89" s="109" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="149" t="s">
+        <v>418</v>
+      </c>
+      <c r="C90" s="135">
+        <f>Thesis!E19</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C91" s="117">
+        <f>PV(C90, C76, -C77, 0)</f>
+        <v>5.7836579195627378</v>
+      </c>
+      <c r="D91" s="117"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C92" s="117">
+        <f>C60/(1+C90)^C76</f>
+        <v>60.447353536814227</v>
+      </c>
+      <c r="D92" s="117"/>
+    </row>
+    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B93" s="111" t="s">
+        <v>416</v>
+      </c>
+      <c r="C93" s="112">
+        <f>C91+C92</f>
+        <v>66.231011456376962</v>
+      </c>
+      <c r="D93" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E93" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" s="329">
+        <f>(1-C93/C60)</f>
+        <v>1.0324974766530715E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="100"/>
+    </row>
+    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E95" s="320" t="s">
         <v>336</v>
       </c>
-      <c r="F89" s="317"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="316"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="313" t="s">
+      <c r="F95" s="317"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="316"/>
+    </row>
+    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E96" s="313" t="s">
         <v>337</v>
       </c>
-      <c r="F90" s="318" t="s">
+      <c r="F96" s="318" t="s">
         <v>338</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="316"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="314" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="316"/>
+    </row>
+    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E97" s="314" t="s">
         <v>337</v>
       </c>
-      <c r="F91" s="318" t="s">
+      <c r="F97" s="318" t="s">
         <v>339</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="316"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="315" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="316"/>
+    </row>
+    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E98" s="315" t="s">
         <v>337</v>
       </c>
-      <c r="F92" s="319" t="s">
+      <c r="F98" s="319" t="s">
         <v>340</v>
       </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="316"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F486BDF-8806-4348-AFC2-0DFEC895EF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FE5C3A-20DD-4494-9986-32FE6EAF4EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1321,10 +1321,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1821,14 +1817,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implied Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2326,15 +2314,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CNS_03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
   </si>
   <si>
     <t>Sell Price Output</t>
@@ -2345,8 +2329,35 @@
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>in contrast to a cash yield of</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNS_03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
   </si>
 </sst>
 </file>
@@ -3713,6 +3724,9 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3748,9 +3762,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4028,7 +4039,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4048,15 +4059,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="247" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4080,13 +4091,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4113,7 +4124,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4123,7 +4134,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4149,24 +4160,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
-        <v>374</v>
-      </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="B12" s="339" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4176,10 +4187,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4189,7 +4200,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0667112500000002</v>
+        <v>1.06671125</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4202,21 +4213,21 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="E19" s="348">
+        <v>411</v>
+      </c>
+      <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
@@ -4227,10 +4238,10 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>38.289885084736959</v>
+        <v>38.289885084736952</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4238,7 +4249,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>373</v>
+        <v>416</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4253,7 +4264,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4262,22 +4273,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
-        <v>375</v>
-      </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="B25" s="339" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
-        <v>351</v>
-      </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="B26" s="342" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4289,13 +4300,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="340" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4315,13 +4326,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="340" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4350,13 +4361,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="340" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4372,17 +4383,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4397,7 +4408,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4430,7 +4441,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4442,13 +4453,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="340" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4464,13 +4475,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
-        <v>350</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="340" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4486,26 +4497,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
-        <v>355</v>
-      </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="B53" s="339" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
-        <v>376</v>
-      </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="B54" s="339" t="s">
+        <v>373</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4531,25 +4542,25 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.1491316575080379E-2</v>
+        <v>4.1491316575080373E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8016844194438813E-2</v>
+        <v>3.801684419443882E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4562,22 +4573,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
-        <v>377</v>
-      </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="B63" s="339" t="s">
+        <v>374</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="342" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4586,7 +4597,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4594,26 +4605,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4630,27 +4641,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
-        <v>378</v>
-      </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="B73" s="339" t="s">
+        <v>375</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
-        <v>379</v>
-      </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="B74" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4662,11 +4673,11 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>28.136299052476378</v>
+        <v>28.136299052476371</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4675,7 +4686,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4687,13 +4698,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
-        <v>380</v>
-      </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="B81" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4706,13 +4717,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
-        <v>356</v>
-      </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="B85" s="339" t="s">
+        <v>355</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4729,11 +4740,11 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.22316100956499893</v>
+        <v>0.22316100956499887</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4747,7 +4758,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C90" s="188">
         <f>BS!C66</f>
@@ -4760,7 +4771,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
@@ -4773,11 +4784,11 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>10.013178717820995</v>
+        <v>10.013178717820992</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4804,11 +4815,11 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.1545487805136769</v>
+        <v>2.1545487805136765</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4816,21 +4827,21 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
-        <v>381</v>
-      </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="B98" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>40.080865541246055</v>
+        <v>40.080865541246048</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4839,7 +4850,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4848,13 +4859,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
-        <v>382</v>
-      </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="B104" s="340" t="s">
+        <v>379</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4989,7 +5000,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>66.921979202973958</v>
+        <v>66.921979202973944</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4997,17 +5008,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
-        <v>385</v>
-      </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="B115" s="343" t="s">
+        <v>382</v>
+      </c>
+      <c r="C115" s="343"/>
+      <c r="D115" s="343"/>
+      <c r="E115" s="343"/>
+      <c r="F115" s="343"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -5016,22 +5027,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
-        <v>383</v>
-      </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="B119" s="344" t="s">
+        <v>380</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
-        <v>384</v>
-      </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="B120" s="339" t="s">
+        <v>381</v>
+      </c>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5040,7 +5051,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C122" s="251">
         <f>E20</f>
@@ -5049,7 +5060,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C123" s="250">
         <f>C19</f>
@@ -5062,7 +5073,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0624137975483054</v>
+        <v>2.0624137975483059</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5071,7 +5082,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="234" t="s">
-        <v>265</v>
+        <v>417</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5081,7 +5092,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>4.0258317328142921</v>
+        <v>4.025831732814293</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5091,7 +5102,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>34.264053351922669</v>
+        <v>34.264053351922662</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5100,7 +5111,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>38.289885084736959</v>
+        <v>38.289885084736952</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5116,109 +5127,156 @@
         <v>0.42784290690799853</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A132" s="247" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="234" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="236" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C133" s="240">
+        <f>Scenarios!C91</f>
+        <v>5.7836579195627387</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C134" s="240">
+        <f>Scenarios!C92</f>
+        <v>60.447353536814212</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B135" s="80" t="s">
+        <v>419</v>
+      </c>
+      <c r="C135" s="239">
+        <f>Scenarios!C93</f>
+        <v>66.231011456376947</v>
+      </c>
+      <c r="D135" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="238" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!F93</f>
+        <v>1.0324974766530715E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A138" s="247" t="s">
+        <v>386</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="338" t="s">
+        <v>388</v>
+      </c>
+      <c r="C140" s="339"/>
+      <c r="D140" s="339"/>
+      <c r="E140" s="339"/>
+      <c r="F140" s="339"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="234" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B143" s="341" t="s">
+        <v>392</v>
+      </c>
+      <c r="C143" s="341"/>
+      <c r="D143" s="341"/>
+      <c r="E143" s="341"/>
+      <c r="F143" s="341"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="B132" s="36"/>
-      <c r="C132" s="36"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="238" t="s">
         <v>391</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="234" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="340" t="s">
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="340" t="s">
+        <v>393</v>
+      </c>
+      <c r="C149" s="340"/>
+      <c r="D149" s="340"/>
+      <c r="E149" s="340"/>
+      <c r="F149" s="340"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="337" t="s">
+        <v>394</v>
+      </c>
+      <c r="C152" s="337"/>
+      <c r="D152" s="337"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+    </row>
+    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="337" t="s">
         <v>395</v>
       </c>
-      <c r="C137" s="340"/>
-      <c r="D137" s="340"/>
-      <c r="E137" s="340"/>
-      <c r="F137" s="340"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B138" s="238" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B139" s="238" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+      <c r="C153" s="337"/>
+      <c r="D153" s="337"/>
+      <c r="E153" s="337"/>
+      <c r="F153" s="337"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B155" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B156" s="238" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B157" s="238" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
-        <v>396</v>
-      </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="1" t="s">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B158" s="238" t="s">
         <v>400</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
-        <v>397</v>
-      </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
-        <v>398</v>
-      </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="238" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="238" t="s">
-        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -5245,14 +5303,14 @@
     <mergeCell ref="B115:F115"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B149:F149"/>
     <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5767,7 +5825,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C22" s="181">
         <v>5154661132</v>
@@ -5793,7 +5851,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C23" s="181">
         <v>-7421783375</v>
@@ -5819,7 +5877,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C24" s="181">
         <v>-2983143705</v>
@@ -5850,23 +5908,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0624137975483054</v>
+        <v>2.0624137975483059</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8749216341348229</v>
+        <v>1.8749216341348234</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.218699062187635</v>
+        <v>1.2186990621876352</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0312068987741527</v>
+        <v>1.0312068987741529</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.70309561280055854</v>
+        <v>0.70309561280055877</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -5880,7 +5938,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7135,7 +7193,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7188,23 +7246,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0624137975483054</v>
+        <v>2.0624137975483059</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8749216341348229</v>
+        <v>1.8749216341348234</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.218699062187635</v>
+        <v>1.2186990621876352</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0312068987741527</v>
+        <v>1.0312068987741529</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.70309561280055854</v>
+        <v>0.70309561280055877</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8508,13 +8566,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C45" s="261" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8522,7 +8580,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8541,11 +8599,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.723289907259943</v>
+        <v>22.723289907259939</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3258162597677499</v>
+        <v>1.3258162597677496</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8675,7 +8733,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8698,7 +8756,7 @@
         <v>2.749989365273205E-2</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8720,7 +8778,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8787,7 +8845,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8799,7 +8857,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8810,12 +8868,12 @@
         <v>-2586554264.2570438</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8826,12 +8884,12 @@
         <v>6.9508585783195169</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8839,12 +8897,12 @@
         <v>5173108528.5140877</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8852,7 +8910,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8928,7 +8986,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8939,23 +8997,23 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>299</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-304435532.45540881</v>
+        <v>-304435532.45540875</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-0.22316100956499893</v>
+        <v>-0.22316100956499887</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -8964,15 +9022,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13659946244.52136</v>
+        <v>13659946244.521357</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>10.013178717820995</v>
+        <v>10.013178717820992</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -8985,11 +9043,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2939228525.9660749</v>
+        <v>2939228525.9660745</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>2.1545487805136769</v>
+        <v>2.1545487805136765</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -8998,15 +9056,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16294739238.032028</v>
+        <v>16294739238.032022</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>11.944566488769674</v>
+        <v>11.94456648876967</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9869,7 +9927,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9894,7 +9952,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10222,7 +10280,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10282,7 +10340,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10406,7 +10464,7 @@
         <v>-1522888768.25</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10464,7 +10522,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10772,7 +10830,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10911,7 +10969,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10966,7 +11024,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11099,7 +11157,7 @@
         <v>3.430552260533988E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11126,7 +11184,7 @@
         <v>7.6514823945754068E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11441,7 +11499,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12002,7 +12060,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12519,28 +12577,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0624137975483054</v>
+        <v>2.0624137975483059</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0624137975483054</v>
+        <v>2.0624137975483059</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8749216341348229</v>
+        <v>1.8749216341348234</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.218699062187635</v>
+        <v>1.2186990621876352</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0312068987741527</v>
+        <v>1.0312068987741529</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.70309561280055854</v>
+        <v>0.70309561280055877</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12575,28 +12633,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>2813538278.1422806</v>
+        <v>2813538278.1422811</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>2813538278.1422806</v>
+        <v>2813538278.1422811</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2557762071.0384364</v>
+        <v>2557762071.0384374</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1662545346.174984</v>
+        <v>1662545346.1749842</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1406769139.0711403</v>
+        <v>1406769139.0711405</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>959160776.6394136</v>
+        <v>959160776.63941395</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12630,28 +12688,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.97738511908443848</v>
+        <v>0.9773851190844387</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.89171899807392518</v>
+        <v>0.89171899807392541</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.83277209475289193</v>
+        <v>0.83277209475289216</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.64578332418507889</v>
+        <v>0.645783324185079</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82668029711309887</v>
+        <v>0.82668029711309898</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66935973543413785</v>
+        <v>0.66935973543413807</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12681,32 +12739,32 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8016844194438813E-2</v>
+        <v>3.801684419443882E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8016844194438813E-2</v>
+        <v>3.801684419443882E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.4560767449489826E-2</v>
+        <v>3.4560767449489833E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.2464498842168387E-2</v>
+        <v>2.246449884216839E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.9008422097219407E-2</v>
+        <v>1.900842209721941E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2960287793558683E-2</v>
+        <v>1.2960287793558687E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13375,7 +13433,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13427,7 +13485,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13827,30 +13885,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2509039241981106</v>
+        <v>2.2509039241981101</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4671449243000385</v>
+        <v>2.4671449243000381</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.4016174564464232</v>
+        <v>2.4016174564464228</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.013059104058601</v>
+        <v>2.0130591040586006</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3306232213848301</v>
+        <v>1.3306232213848299</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1204737307862713</v>
+        <v>1.1204737307862711</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13880,34 +13938,34 @@
     <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1491316575080379E-2</v>
+        <v>4.1491316575080373E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.54773257935491E-2</v>
+        <v>4.5477325793549087E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.4269446201777383E-2</v>
+        <v>4.4269446201777377E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.710708025914472E-2</v>
+        <v>3.7107080259144713E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.4527616984052168E-2</v>
+        <v>2.4527616984052165E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.0653893655046475E-2</v>
+        <v>2.0653893655046471E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13936,7 +13994,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14765,10 +14823,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="345" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14783,8 +14841,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14799,8 +14857,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14815,8 +14873,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14839,7 +14897,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0667112500000002</v>
+        <v>1.06671125</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14853,7 +14911,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>40.080865541246055</v>
+        <v>40.080865541246048</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14886,7 +14944,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14906,7 +14964,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>66.920168335604359</v>
+        <v>66.92016833560433</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14945,7 +15003,7 @@
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14967,7 +15025,7 @@
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14989,7 +15047,7 @@
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -15011,7 +15069,7 @@
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15033,7 +15091,7 @@
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15055,7 +15113,7 @@
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15077,7 +15135,7 @@
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15099,7 +15157,7 @@
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15121,7 +15179,7 @@
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15143,7 +15201,7 @@
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15165,7 +15223,7 @@
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
@@ -15187,7 +15245,7 @@
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
@@ -15209,7 +15267,7 @@
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
@@ -15231,7 +15289,7 @@
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
@@ -15253,7 +15311,7 @@
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
@@ -15275,7 +15333,7 @@
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
@@ -15297,7 +15355,7 @@
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
@@ -15319,7 +15377,7 @@
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
@@ -15341,7 +15399,7 @@
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
@@ -15363,7 +15421,7 @@
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
@@ -15385,7 +15443,7 @@
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E41" s="125">
         <f t="shared" si="0"/>
@@ -15407,7 +15465,7 @@
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E42" s="125">
         <f t="shared" si="0"/>
@@ -15429,7 +15487,7 @@
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E43" s="125">
         <f t="shared" si="0"/>
@@ -15451,7 +15509,7 @@
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E44" s="125">
         <f t="shared" si="0"/>
@@ -15473,7 +15531,7 @@
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E45" s="125">
         <f t="shared" si="0"/>
@@ -15495,7 +15553,7 @@
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E46" s="125">
         <f t="shared" si="0"/>
@@ -15517,7 +15575,7 @@
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E47" s="125">
         <f t="shared" si="0"/>
@@ -15539,7 +15597,7 @@
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E48" s="125">
         <f t="shared" si="0"/>
@@ -15561,7 +15619,7 @@
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E49" s="125">
         <f t="shared" si="0"/>
@@ -15583,7 +15641,7 @@
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="E50" s="125">
         <f t="shared" si="0"/>
@@ -15842,23 +15900,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>40.080865541246055</v>
+        <v>40.080865541246048</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>40.080865541246055</v>
+        <v>40.080865541246048</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>40.080865541246055</v>
+        <v>40.080865541246048</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>40.080865541246055</v>
+        <v>40.080865541246048</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>40.080865541246055</v>
+        <v>40.080865541246048</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15869,23 +15927,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>40.988689834658786</v>
+        <v>40.988689834658771</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>41.92370306950059</v>
+        <v>41.923703069500576</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>42.887098384354509</v>
+        <v>42.887098384354502</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>43.880105860538926</v>
+        <v>43.880105860538919</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>44.903993110367736</v>
+        <v>44.903993110367729</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15896,23 +15954,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>41.897350090786894</v>
+        <v>41.897350090786887</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>43.895895575391165</v>
+        <v>43.895895575391158</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>46.098290699520824</v>
+        <v>46.098290699520817</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>48.52876027065394</v>
+        <v>48.528760270653926</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>51.214206425840629</v>
+        <v>51.214206425840622</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15923,23 +15981,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>43.022069105625356</v>
+        <v>43.022069105625341</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>46.466898610689064</v>
+        <v>46.46689861068905</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>50.515409620501202</v>
+        <v>50.515409620501188</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>55.287439027252766</v>
+        <v>55.287439027252759</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>60.926327797069796</v>
+        <v>60.926327797069789</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -15950,23 +16008,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>44.16797741332018</v>
+        <v>44.167977413320173</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>49.234136164892192</v>
+        <v>49.234136164892185</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>55.554141674352422</v>
+        <v>55.554141674352408</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>63.482164899400622</v>
+        <v>63.482164899400608</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>73.474276412518535</v>
+        <v>73.47427641251852</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -15977,23 +16035,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.233735725939368</v>
+        <v>45.233735725939361</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>51.959959295215604</v>
+        <v>51.959959295215597</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>60.834579664654996</v>
+        <v>60.834579664654981</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>72.654240308539926</v>
+        <v>72.654240308539912</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>88.522804369101337</v>
+        <v>88.522804369101323</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16003,23 +16061,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>46.173882813368081</v>
+        <v>46.173882813368074</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>54.512716813620528</v>
+        <v>54.512716813620521</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>66.114346614648767</v>
+        <v>66.114346614648753</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>82.491483390184314</v>
+        <v>82.4914833901843</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>105.89857071605786</v>
+        <v>105.89857071605785</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16054,7 +16112,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>105.89857071605786</v>
+        <v>105.89857071605785</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16076,7 +16134,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>82.491483390184314</v>
+        <v>82.4914833901843</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16099,7 +16157,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.114346614648767</v>
+        <v>66.114346614648753</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16122,7 +16180,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>54.512716813620528</v>
+        <v>54.512716813620521</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16145,7 +16203,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>46.173882813368081</v>
+        <v>46.173882813368074</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16161,7 +16219,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16233,7 +16291,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16266,7 +16324,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0624137975483054</v>
+        <v>2.0624137975483059</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16275,7 +16333,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0624137975483054</v>
+        <v>2.0624137975483059</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16287,7 +16345,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16295,12 +16353,12 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>68.98439300052226</v>
+        <v>68.984393000522246</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16310,11 +16368,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 青島啤酒股份(0168.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16335,8 +16393,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16357,8 +16415,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16368,8 +16426,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16380,10 +16438,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>281</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16401,8 +16459,8 @@
         <v>2.1321347914251776E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16419,8 +16477,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15185942572632172</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16437,8 +16495,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22851327690218692</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16454,7 +16512,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16464,25 +16522,25 @@
       <c r="C18" s="151">
         <v>30</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>342</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>313</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>312</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16492,23 +16550,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>40.080865541246055</v>
+        <v>40.080865541246048</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16528,8 +16586,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16539,8 +16597,8 @@
         <v>0.06</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16548,14 +16606,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.114346614648767</v>
+        <v>66.114346614648753</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16565,8 +16623,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16586,8 +16644,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16597,8 +16655,8 @@
         <v>0.04</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16606,14 +16664,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>54.512716813620528</v>
+        <v>54.512716813620521</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16623,8 +16681,8 @@
         <v>0.3</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16644,8 +16702,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16655,8 +16713,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16664,14 +16722,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>82.491483390184314</v>
+        <v>82.4914833901843</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16682,8 +16740,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16691,7 +16749,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>65.909285029447403</v>
+        <v>65.909285029447389</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16745,8 +16803,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16756,8 +16814,8 @@
         <v>0.02</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16765,14 +16823,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>46.173882813368081</v>
+        <v>46.173882813368074</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16782,12 +16840,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16803,8 +16861,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16814,8 +16872,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16823,14 +16881,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>105.89857071605786</v>
+        <v>105.89857071605785</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16840,8 +16898,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16849,14 +16907,14 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>66.921979202973958</v>
+        <v>66.921979202973944</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16865,7 +16923,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16874,10 +16932,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16890,7 +16948,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16898,11 +16956,11 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>6.1165848114483959E-2</v>
+        <v>6.1165848114484E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16911,27 +16969,27 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>66.920168335604359</v>
+        <v>66.92016833560433</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16941,19 +16999,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16963,18 +17021,18 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.17848495563082312</v>
+        <v>0.17848495563082309</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16993,7 +17051,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17007,7 +17065,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0624137975483054</v>
+        <v>2.0624137975483059</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17016,12 +17074,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C123</f>
@@ -17034,7 +17092,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.0258317328142921</v>
+        <v>4.025831732814293</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17046,7 +17104,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>34.264053351922669</v>
+        <v>34.264053351922662</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17056,7 +17114,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>38.289885084736959</v>
+        <v>38.289885084736952</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17075,12 +17133,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17093,7 +17151,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17105,12 +17163,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B89" s="109" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B90" s="149" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C90" s="135">
         <f>Thesis!E19</f>
@@ -17123,7 +17181,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>5.7836579195627378</v>
+        <v>5.7836579195627387</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17133,21 +17191,20 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>60.447353536814227</v>
+        <v>60.447353536814212</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B93" s="111" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>66.231011456376962</v>
-      </c>
-      <c r="D93" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
+        <v>66.231011456376947</v>
+      </c>
+      <c r="D93" t="s">
+        <v>412</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>128</v>
@@ -17162,7 +17219,7 @@
     </row>
     <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E95" s="320" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
@@ -17170,30 +17227,30 @@
     </row>
     <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E96" s="313" t="s">
+        <v>336</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>337</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>338</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
     <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E97" s="314" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
     <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E98" s="315" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FE5C3A-20DD-4494-9986-32FE6EAF4EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32082FEB-F9BC-4B22-A288-947E4DFF0450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1357,10 +1357,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rough Estimate only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2325,31 +2321,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>@Cash Yield</t>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Implied Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Sell)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Above:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 5: Determining the Investment Decision</t>
+    <t>Liabilities to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3031,7 +3043,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3727,6 +3739,11 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4039,7 +4056,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4059,10 +4076,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4091,13 +4108,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4124,7 +4141,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4160,24 +4177,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>371</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="342" t="s">
+        <v>370</v>
+      </c>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4187,10 +4204,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4213,19 +4230,19 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
@@ -4237,11 +4254,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="252">
-        <f>C129</f>
+        <f>C133</f>
         <v>38.289885084736952</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4249,7 +4266,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4264,7 +4281,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4273,22 +4290,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>372</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="342" t="s">
+        <v>371</v>
+      </c>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>350</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="345" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4300,13 +4317,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="343" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4326,13 +4343,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="343" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4361,13 +4378,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="343" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4383,17 +4400,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4408,7 +4425,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4453,13 +4470,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="343" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4475,13 +4492,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
-        <v>349</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="B50" s="343" t="s">
+        <v>348</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4497,22 +4514,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>354</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="342" t="s">
+        <v>353</v>
+      </c>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>373</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="342" t="s">
+        <v>372</v>
+      </c>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4542,7 +4559,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4551,7 +4568,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4560,7 +4577,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4573,22 +4590,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
-        <v>374</v>
-      </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="B63" s="342" t="s">
+        <v>373</v>
+      </c>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4597,7 +4614,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4605,26 +4622,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4641,27 +4658,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="342" t="s">
+        <v>374</v>
+      </c>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="342" t="s">
         <v>375</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
-        <v>376</v>
-      </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4673,7 +4690,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4686,7 +4703,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4698,13 +4715,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
-        <v>377</v>
-      </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="B81" s="342" t="s">
+        <v>376</v>
+      </c>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4717,13 +4734,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
-        <v>355</v>
-      </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="B85" s="342" t="s">
+        <v>354</v>
+      </c>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4740,7 +4757,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4751,537 +4768,577 @@
         <v>HKD</v>
       </c>
     </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B88" s="337" t="s">
+        <v>420</v>
+      </c>
+      <c r="C88" s="338">
+        <f>BS!G30/BS!G27</f>
+        <v>0.72207550313588764</v>
+      </c>
+    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="337" t="s">
+        <v>421</v>
+      </c>
+      <c r="C89" s="338">
+        <f>BS!G31/BS!G27</f>
+        <v>9.5579625064196368E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="337" t="s">
+        <v>423</v>
+      </c>
+      <c r="C90" s="339">
+        <f>BS!C50</f>
+        <v>7.3592411949940734E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B93" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C90" s="188">
+      <c r="C93" s="188">
         <f>BS!C66</f>
         <v>17978772896</v>
       </c>
-      <c r="D90" s="1" t="str">
+      <c r="D93" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B91" s="47" t="s">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B94" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
         <v>12805664367.485912</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B92" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C95" s="248">
+        <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>10.013178717820992</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B98" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="C95" s="188">
+      <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
         <v>2755411575.5</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B96" s="47" t="s">
-        <v>289</v>
-      </c>
-      <c r="C96" s="248">
-        <f>C95*C28*Exchange_Rate/Common_Shares</f>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B99" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C99" s="248">
+        <f>C98*C28*Exchange_Rate/Common_Shares</f>
         <v>2.1545487805136765</v>
       </c>
-      <c r="D96" s="1" t="str">
+      <c r="D99" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
-        <v>378</v>
-      </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B100" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C100" s="248">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="342" t="s">
+        <v>377</v>
+      </c>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B103" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
         <v>40.080865541246048</v>
       </c>
-      <c r="D100" s="1" t="str">
+      <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A102" s="247" t="s">
-        <v>370</v>
-      </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
-    </row>
-    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
-        <v>379</v>
-      </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
-    </row>
-    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B106" s="260" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B104" s="337" t="s">
+        <v>422</v>
+      </c>
+      <c r="C104" s="248">
+        <f>BS!D47</f>
+        <v>1.3258162597677496</v>
+      </c>
+      <c r="D104" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A106" s="247" t="s">
+        <v>369</v>
+      </c>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+    </row>
+    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="343" t="s">
+        <v>378</v>
+      </c>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B110" s="260" t="s">
         <v>119</v>
       </c>
-      <c r="C106" s="260" t="s">
+      <c r="C110" s="260" t="s">
         <v>134</v>
       </c>
-      <c r="D106" s="260" t="s">
+      <c r="D110" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="E106" s="260" t="s">
+      <c r="E110" s="260" t="s">
         <v>261</v>
       </c>
-      <c r="F106" s="260" t="s">
+      <c r="F110" s="260" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="255" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C107" s="256">
+      <c r="C111" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D107" s="257">
+      <c r="D111" s="257">
         <f>Valuation_Model!D74</f>
         <v>30</v>
       </c>
-      <c r="E107" s="258" t="str">
+      <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>105.9 HKD</v>
       </c>
-      <c r="F107" s="259">
+      <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="242" t="str">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C108" s="243">
+      <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.08</v>
       </c>
-      <c r="D108" s="244">
+      <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
         <v>30</v>
       </c>
-      <c r="E108" s="245" t="str">
+      <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>82.49 HKD</v>
       </c>
-      <c r="F108" s="246">
+      <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="242" t="str">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C109" s="243">
+      <c r="C113" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.06</v>
       </c>
-      <c r="D109" s="244">
+      <c r="D113" s="244">
         <f>Valuation_Model!D76</f>
         <v>30</v>
       </c>
-      <c r="E109" s="245" t="str">
+      <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>66.11 HKD</v>
       </c>
-      <c r="F109" s="246">
+      <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="242" t="str">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C110" s="243">
+      <c r="C114" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.04</v>
       </c>
-      <c r="D110" s="244">
+      <c r="D114" s="244">
         <f>Valuation_Model!D77</f>
         <v>30</v>
       </c>
-      <c r="E110" s="245" t="str">
+      <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>54.51 HKD</v>
       </c>
-      <c r="F110" s="246">
+      <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.26999999999999996</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B111" s="242" t="str">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C111" s="243">
+      <c r="C115" s="243">
         <f>Valuation_Model!C78</f>
         <v>0.02</v>
       </c>
-      <c r="D111" s="244">
+      <c r="D115" s="244">
         <f>Valuation_Model!D78</f>
         <v>30</v>
       </c>
-      <c r="E111" s="245" t="str">
+      <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>46.17 HKD</v>
       </c>
-      <c r="F111" s="246">
+      <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B113" s="235" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B117" s="235" t="s">
         <v>260</v>
       </c>
-      <c r="C113" s="241">
+      <c r="C117" s="241">
         <f>Scenarios!C60</f>
         <v>66.921979202973944</v>
       </c>
-      <c r="D113" s="236" t="str">
+      <c r="D117" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="343" t="s">
-        <v>382</v>
-      </c>
-      <c r="C115" s="343"/>
-      <c r="D115" s="343"/>
-      <c r="E115" s="343"/>
-      <c r="F115" s="343"/>
-    </row>
-    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A117" s="247" t="s">
-        <v>420</v>
-      </c>
-      <c r="B117" s="36"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="344" t="s">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="346" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A121" s="247" t="s">
+        <v>418</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="347" t="s">
+        <v>379</v>
+      </c>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="342" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="344"/>
-      <c r="D119" s="344"/>
-      <c r="E119" s="344"/>
-      <c r="F119" s="344"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
-        <v>381</v>
-      </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="234" t="s">
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B125" s="234" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="1" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C122" s="251">
+      <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C123" s="250">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="236" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="236" t="s">
         <v>263</v>
       </c>
-      <c r="C124" s="237">
+      <c r="C128" s="237">
         <f>Scenarios!C77</f>
         <v>2.0624137975483059</v>
       </c>
-      <c r="D124" s="236" t="str">
+      <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="234" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B130" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B131" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C127" s="240">
+      <c r="C131" s="240">
         <f>Scenarios!C81</f>
         <v>4.025831732814293</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C128" s="240">
+      <c r="C132" s="240">
         <f>Scenarios!C82</f>
         <v>34.264053351922662</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B129" s="80" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="80" t="s">
         <v>262</v>
       </c>
-      <c r="C129" s="239">
+      <c r="C133" s="239">
         <f>Scenarios!C83</f>
         <v>38.289885084736952</v>
       </c>
-      <c r="D129" s="47" t="str">
+      <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B130" s="238" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C130" s="92">
+      <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.42784290690799853</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B132" s="234" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B133" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="234" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C133" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>5.7836579195627387</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>5.5410264563317959</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C134" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>60.447353536814212</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B135" s="80" t="s">
-        <v>419</v>
-      </c>
-      <c r="C135" s="239">
+        <v>56.628583084232254</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="80" t="s">
+        <v>417</v>
+      </c>
+      <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>66.231011456376947</v>
-      </c>
-      <c r="D135" s="101" t="str">
+        <v>62.169609540564053</v>
+      </c>
+      <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="238" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="92">
+      <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>1.0324974766530715E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A138" s="247" t="s">
+        <v>7.1013585058445239E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A142" s="247" t="s">
+        <v>385</v>
+      </c>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="341" t="s">
+        <v>387</v>
+      </c>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="234" t="s">
         <v>386</v>
       </c>
-      <c r="B138" s="36"/>
-      <c r="C138" s="36"/>
-      <c r="D138" s="36"/>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="338" t="s">
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B147" s="344" t="s">
+        <v>391</v>
+      </c>
+      <c r="C147" s="344"/>
+      <c r="D147" s="344"/>
+      <c r="E147" s="344"/>
+      <c r="F147" s="344"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="238" t="s">
         <v>388</v>
       </c>
-      <c r="C140" s="339"/>
-      <c r="D140" s="339"/>
-      <c r="E140" s="339"/>
-      <c r="F140" s="339"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="234" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B143" s="341" t="s">
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="238" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C143" s="341"/>
-      <c r="D143" s="341"/>
-      <c r="E143" s="341"/>
-      <c r="F143" s="341"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="238" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="238" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="238" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B148" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="340" t="s">
-        <v>393</v>
-      </c>
-      <c r="C149" s="340"/>
-      <c r="D149" s="340"/>
-      <c r="E149" s="340"/>
-      <c r="F149" s="340"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="337" t="s">
-        <v>394</v>
-      </c>
-      <c r="C152" s="337"/>
-      <c r="D152" s="337"/>
-      <c r="E152" s="337"/>
-      <c r="F152" s="337"/>
-    </row>
-    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="337" t="s">
-        <v>395</v>
-      </c>
-      <c r="C153" s="337"/>
-      <c r="D153" s="337"/>
-      <c r="E153" s="337"/>
-      <c r="F153" s="337"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B156" s="238" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="340" t="s">
+        <v>393</v>
+      </c>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B159" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B160" s="238" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" s="238" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="238" t="s">
         <v>399</v>
-      </c>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B158" s="238" t="s">
-        <v>400</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
@@ -5290,24 +5347,24 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5825,7 +5882,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C22" s="181">
         <v>5154661132</v>
@@ -5851,7 +5908,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C23" s="181">
         <v>-7421783375</v>
@@ -5877,7 +5934,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C24" s="181">
         <v>-2983143705</v>
@@ -5938,7 +5995,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7193,7 +7250,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8572,7 +8629,7 @@
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>274</v>
+        <v>422</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8580,7 +8637,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8733,7 +8790,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8756,7 +8813,7 @@
         <v>2.749989365273205E-2</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8778,7 +8835,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8845,7 +8902,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8857,7 +8914,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8868,12 +8925,12 @@
         <v>-2586554264.2570438</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8884,12 +8941,12 @@
         <v>6.9508585783195169</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8897,12 +8954,12 @@
         <v>5173108528.5140877</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8910,7 +8967,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8986,7 +9043,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8997,15 +9054,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>298</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9022,7 +9079,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9056,7 +9113,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9927,7 +9984,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9952,7 +10009,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10280,7 +10337,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10340,7 +10397,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10464,7 +10521,7 @@
         <v>-1522888768.25</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10522,7 +10579,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10830,7 +10887,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10969,7 +11026,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11024,7 +11081,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11157,7 +11214,7 @@
         <v>3.430552260533988E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11184,7 +11241,7 @@
         <v>7.6514823945754068E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11499,7 +11556,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12060,7 +12117,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12739,7 +12796,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13433,7 +13490,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13485,7 +13542,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13994,7 +14051,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14823,10 +14880,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="348" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14841,8 +14898,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="348"/>
+      <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14857,8 +14914,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="348"/>
+      <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14873,8 +14930,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="348"/>
+      <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16219,7 +16276,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16291,7 +16348,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16345,7 +16402,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16358,7 +16415,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16368,11 +16425,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="350" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 青島啤酒股份(0168.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="350"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16393,8 +16450,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="350"/>
+      <c r="F8" s="350"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16415,8 +16472,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="350"/>
+      <c r="F9" s="350"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16426,8 +16483,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="350"/>
+      <c r="F10" s="350"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16438,10 +16495,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>281</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>280</v>
+      </c>
+      <c r="E11" s="350"/>
+      <c r="F11" s="350"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16459,8 +16516,8 @@
         <v>2.1321347914251776E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="350"/>
+      <c r="F12" s="350"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16477,8 +16534,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15185942572632172</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="350"/>
+      <c r="F13" s="350"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16495,8 +16552,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22851327690218692</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="350"/>
+      <c r="F14" s="350"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16512,7 +16569,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16522,25 +16579,25 @@
       <c r="C18" s="151">
         <v>30</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>341</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="350" t="s">
+        <v>340</v>
+      </c>
+      <c r="F18" s="351"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="351"/>
+      <c r="F19" s="351"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>312</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>311</v>
+      </c>
+      <c r="E20" s="351"/>
+      <c r="F20" s="351"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16550,12 +16607,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="351"/>
+      <c r="F21" s="351"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16565,8 +16622,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="351"/>
+      <c r="F22" s="351"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16586,8 +16643,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="349"/>
+      <c r="F25" s="349"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16597,8 +16654,8 @@
         <v>0.06</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="349"/>
+      <c r="F26" s="349"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16612,8 +16669,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="349"/>
+      <c r="F27" s="349"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16623,8 +16680,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="349"/>
+      <c r="F28" s="349"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16644,8 +16701,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="349"/>
+      <c r="F31" s="349"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16655,8 +16712,8 @@
         <v>0.04</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="349"/>
+      <c r="F32" s="349"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16670,8 +16727,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="349"/>
+      <c r="F33" s="349"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16681,8 +16738,8 @@
         <v>0.3</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="349"/>
+      <c r="F34" s="349"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16702,8 +16759,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16713,8 +16770,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="349"/>
+      <c r="F38" s="349"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16728,8 +16785,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="349"/>
+      <c r="F39" s="349"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16740,8 +16797,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16803,8 +16860,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="349"/>
+      <c r="F49" s="349"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16814,8 +16871,8 @@
         <v>0.02</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16829,8 +16886,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="349"/>
+      <c r="F51" s="349"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16840,12 +16897,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="349"/>
+      <c r="F52" s="349"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16861,8 +16918,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="349"/>
+      <c r="F55" s="349"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16872,8 +16929,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="349"/>
+      <c r="F56" s="349"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16887,8 +16944,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="349"/>
+      <c r="F57" s="349"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16898,8 +16955,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16914,7 +16971,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16923,7 +16980,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16932,10 +16989,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16948,7 +17005,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16960,7 +17017,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16976,20 +17033,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16999,19 +17056,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17021,14 +17078,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17051,7 +17108,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17074,15 +17131,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C123</f>
+        <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
@@ -17133,12 +17190,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17151,7 +17208,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17163,16 +17220,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B89" s="109" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B90" s="149" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C90" s="135">
-        <f>Thesis!E19</f>
-        <v>3.4500000000000003E-2</v>
+        <f>(Thesis!E19+Thesis!C67)/2</f>
+        <v>5.7250000000000002E-2</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.35">
@@ -17181,7 +17238,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>5.7836579195627387</v>
+        <v>5.5410264563317959</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17191,27 +17248,27 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>60.447353536814212</v>
+        <v>56.628583084232254</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B93" s="111" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>66.231011456376947</v>
+        <v>62.169609540564053</v>
       </c>
       <c r="D93" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>128</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>1.0324974766530715E-2</v>
+        <v>7.1013585058445239E-2</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.35">
@@ -17219,7 +17276,7 @@
     </row>
     <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E95" s="320" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
@@ -17227,30 +17284,30 @@
     </row>
     <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E96" s="313" t="s">
+        <v>335</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>336</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>337</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
     <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E97" s="314" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
     <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E98" s="315" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32082FEB-F9BC-4B22-A288-947E4DFF0450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21684002-40DF-4C6B-B55B-472594F1DE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <definedName name="Market_currency">Thesis!$D$6</definedName>
     <definedName name="Market_Price">Thesis!$C$6</definedName>
     <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="428">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -180,10 +181,6 @@
   </si>
   <si>
     <t>Total Liabilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HKD</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1581,10 +1578,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Operating Expenses Multiple (months)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1789,10 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2278,10 +2267,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CNY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO/Net Income</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2291,14 +2276,6 @@
   </si>
   <si>
     <t>Net Change in Cash</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0168.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>青島啤酒股份</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2365,11 +2342,34 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Implied Return</t>
+  </si>
+  <si>
+    <t>Target Return</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>青島啤酒股份</t>
+  </si>
+  <si>
+    <t>0168.HK</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
     <t>CNS_03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -2377,26 +2377,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="18">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.00\x"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="181" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="182" formatCode="#,##0_ "/>
-    <numFmt numFmtId="183" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="184" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="185" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="186" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="187" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="188" formatCode="0.000_ "/>
-    <numFmt numFmtId="189" formatCode="#,##0_);\(#,##0\)"/>
-    <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="192" formatCode="0.0\x"/>
-    <numFmt numFmtId="193" formatCode="0\x"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="180" formatCode="0.0\x"/>
+    <numFmt numFmtId="181" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3071,7 +3071,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3113,23 +3113,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3138,13 +3138,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3215,10 +3215,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3229,7 +3229,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3267,7 +3267,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3277,7 +3277,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3288,29 +3288,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="185" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3326,7 +3326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3340,38 +3340,38 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="39" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="187" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3391,17 +3391,17 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3416,11 +3416,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3429,51 +3429,51 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3489,7 +3489,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -3523,21 +3523,21 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3546,7 +3546,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3556,13 +3556,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3573,7 +3573,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3592,9 +3592,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3603,23 +3603,23 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="191" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3637,13 +3637,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="192" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3651,7 +3651,7 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3688,7 +3688,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3710,21 +3710,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3735,7 +3735,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3743,30 +3743,30 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4057,7 +4057,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
@@ -4067,24 +4067,24 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" s="44">
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="247" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4096,7 +4096,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
         <v>0168.HK Stock Information</v>
@@ -4106,30 +4106,30 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="50">
         <v>54.25</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>41</v>
+        <v>405</v>
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
@@ -4139,9 +4139,9 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="B8" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4149,9 +4149,9 @@
       <c r="D8" s="5"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4160,7 +4160,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="B10" s="4" t="str">
         <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
         <v>Capitalization (HKD):</v>
@@ -4172,29 +4172,29 @@
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="342" t="s">
-        <v>370</v>
-      </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="24.4" customHeight="1">
+      <c r="B12" s="340" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="B15" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4202,17 +4202,17 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="B17" s="4" t="s">
         <v>1</v>
       </c>
@@ -4225,30 +4225,30 @@
       </c>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6">
       <c r="B18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>424</v>
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6">
       <c r="B20" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
@@ -4258,15 +4258,15 @@
         <v>38.289885084736952</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4275,13 +4275,13 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6">
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.9">
       <c r="A23" s="247" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4289,45 +4289,45 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="342" t="s">
-        <v>371</v>
-      </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="345" t="s">
-        <v>349</v>
-      </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B25" s="340" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
+    </row>
+    <row r="26" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B26" s="342" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
+        <v>231</v>
+      </c>
+      <c r="C28" s="108">
+        <f>scaling_factor</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C28" s="108">
-        <f>Data!C3</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="343" t="s">
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="B30" s="47" t="s">
         <v>233</v>
-      </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="47" t="s">
-        <v>234</v>
       </c>
       <c r="C30" s="188">
         <f>Normalized_FCF!C8</f>
@@ -4338,22 +4338,22 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6">
       <c r="B31" s="47"/>
       <c r="C31" s="76"/>
     </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="343" t="s">
+    <row r="32" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B32" s="341" t="s">
+        <v>234</v>
+      </c>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="47" t="s">
         <v>235</v>
-      </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B33" s="47" t="s">
-        <v>236</v>
       </c>
       <c r="C33" s="188">
         <f>Normalized_FCF!C9</f>
@@ -4364,9 +4364,9 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="52" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C34" s="188">
         <f>Normalized_FCF!C10</f>
@@ -4377,18 +4377,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="341" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="47" t="s">
         <v>238</v>
-      </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" s="47" t="s">
-        <v>239</v>
       </c>
       <c r="C37" s="188">
         <f>Normalized_FCF!C11</f>
@@ -4399,18 +4399,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="343" t="s">
-        <v>242</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
+      <c r="B39" s="341" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4423,9 +4423,9 @@
       <c r="E40" s="321"/>
       <c r="F40" s="321"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6">
       <c r="B41" s="47" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4438,9 +4438,9 @@
       <c r="E41" s="321"/>
       <c r="F41" s="321"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
@@ -4451,14 +4451,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6">
       <c r="B44" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4469,18 +4469,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="343" t="s">
-        <v>243</v>
-      </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6">
+      <c r="B47" s="341" t="s">
+        <v>242</v>
+      </c>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
@@ -4491,18 +4491,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="343" t="s">
-        <v>348</v>
+    <row r="50" spans="1:6">
+      <c r="B50" s="341" t="s">
+        <v>346</v>
       </c>
       <c r="C50" s="344"/>
       <c r="D50" s="344"/>
       <c r="E50" s="344"/>
       <c r="F50" s="344"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6">
       <c r="B51" s="47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4513,27 +4513,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="342" t="s">
-        <v>353</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="342" t="s">
-        <v>372</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B53" s="340" t="s">
+        <v>351</v>
+      </c>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
+    </row>
+    <row r="54" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B54" s="340" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
+    </row>
+    <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4544,9 +4544,9 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6">
       <c r="B57" s="47" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
@@ -4557,27 +4557,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6">
       <c r="B58" s="254" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
         <v>4.1491316575080373E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6">
       <c r="B59" s="254" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
         <v>3.801684419443882E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" ht="13.9">
       <c r="A61" s="247" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4585,115 +4585,115 @@
       <c r="E61" s="36"/>
       <c r="F61" s="36"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6">
       <c r="A62" s="233"/>
     </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
-        <v>373</v>
-      </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="345" t="s">
-        <v>254</v>
-      </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B63" s="340" t="s">
+        <v>370</v>
+      </c>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="B64" s="342" t="s">
+        <v>253</v>
+      </c>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
+    </row>
+    <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6">
       <c r="B68" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="B69" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="B70" s="80" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C70" s="263">
         <f>SUM(C67:C69)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6">
       <c r="C71" s="122"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6">
       <c r="B72" s="332" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C72" s="122"/>
     </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="342" t="s">
-        <v>375</v>
-      </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B73" s="340" t="s">
+        <v>371</v>
+      </c>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B74" s="340" t="s">
+        <v>372</v>
+      </c>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C76" s="263">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6">
       <c r="B77" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C77" s="248">
-        <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
+        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>28.136299052476371</v>
       </c>
       <c r="D77" s="1" t="str">
@@ -4701,9 +4701,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6" ht="13.9">
       <c r="A79" s="247" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4711,40 +4711,40 @@
       <c r="E79" s="36"/>
       <c r="F79" s="36"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6">
       <c r="A80" s="233"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="342" t="s">
-        <v>376</v>
-      </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:6">
+      <c r="B81" s="340" t="s">
+        <v>373</v>
+      </c>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
+    </row>
+    <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6">
       <c r="B84" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="342" t="s">
-        <v>354</v>
-      </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B85" s="340" t="s">
+        <v>352</v>
+      </c>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
+    </row>
+    <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C86" s="188">
         <f>Valuation_Model!C7</f>
@@ -4755,12 +4755,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6">
       <c r="B87" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C87" s="248">
-        <f>C86*C28*Exchange_Rate/Common_Shares</f>
+        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.22316100956499887</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4768,41 +4768,41 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:6">
       <c r="B88" s="337" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C88" s="338">
         <f>BS!G30/BS!G27</f>
         <v>0.72207550313588764</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:6">
       <c r="B89" s="337" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C89" s="338">
         <f>BS!G31/BS!G27</f>
         <v>9.5579625064196368E-3</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:6">
       <c r="B90" s="337" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="339">
         <f>BS!C50</f>
         <v>7.3592411949940734E-2</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6">
       <c r="B92" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
       <c r="B93" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C93" s="188">
         <f>BS!C66</f>
@@ -4813,9 +4813,9 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6">
       <c r="B94" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
@@ -4826,12 +4826,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6">
       <c r="B95" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C95" s="248">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
+        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>10.013178717820992</v>
       </c>
       <c r="D95" s="1" t="str">
@@ -4839,14 +4839,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6">
       <c r="B97" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>258</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B98" s="47" t="s">
-        <v>259</v>
       </c>
       <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
@@ -4857,12 +4857,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C99" s="248">
-        <f>C98*C28*Exchange_Rate/Common_Shares</f>
+        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>2.1545487805136765</v>
       </c>
       <c r="D99" s="1" t="str">
@@ -4870,18 +4870,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="342" t="s">
-        <v>377</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B101" s="340" t="s">
+        <v>374</v>
+      </c>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
+    </row>
+    <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
@@ -4892,9 +4892,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6">
       <c r="B104" s="337" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4905,9 +4905,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" ht="13.9">
       <c r="A106" s="247" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
@@ -4915,33 +4915,33 @@
       <c r="E106" s="36"/>
       <c r="F106" s="36"/>
     </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="343" t="s">
-        <v>378</v>
-      </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B108" s="341" t="s">
+        <v>375</v>
+      </c>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C110" s="260" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D110" s="260" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E110" s="260" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F110" s="260" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
@@ -4963,7 +4963,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6">
       <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
@@ -4985,7 +4985,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6">
       <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
@@ -5007,7 +5007,7 @@
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6">
       <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
@@ -5029,7 +5029,7 @@
         <v>0.26999999999999996</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6">
       <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
@@ -5051,9 +5051,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6">
       <c r="B117" s="235" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
@@ -5064,18 +5064,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="346" t="s">
-        <v>381</v>
-      </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B119" s="345" t="s">
+        <v>378</v>
+      </c>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5083,50 +5083,50 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="347" t="s">
-        <v>379</v>
-      </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="342" t="s">
-        <v>380</v>
-      </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6">
+      <c r="B123" s="343" t="s">
+        <v>376</v>
+      </c>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="340" t="s">
+        <v>377</v>
+      </c>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
+    </row>
+    <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="B126" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6">
       <c r="B127" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6">
       <c r="B128" s="236" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
@@ -5137,12 +5137,19 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+      <c r="C130" s="338">
+        <f>C19</f>
+        <v>0.25</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5152,7 +5159,7 @@
         <v>4.025831732814293</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5162,9 +5169,9 @@
         <v>34.264053351922662</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6">
       <c r="B133" s="80" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
@@ -5175,65 +5182,72 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6">
       <c r="B134" s="238" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.42784290690799853</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!C90</f>
+        <v>0.06</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>5.5410264563317959</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+        <v>5.5128567255811802</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>56.628583084232254</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+        <v>56.188984197503579</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>62.169609540564053</v>
+        <v>61.70184092308476</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6">
       <c r="B140" s="238" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>7.1013585058445239E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+        <v>7.8003345717802763E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9">
       <c r="A142" s="247" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B142" s="36"/>
       <c r="C142" s="36"/>
@@ -5241,103 +5255,114 @@
       <c r="E142" s="36"/>
       <c r="F142" s="36"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6">
+      <c r="B144" s="347" t="s">
+        <v>384</v>
+      </c>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
+    </row>
+    <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6">
       <c r="B147" s="344" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C147" s="344"/>
       <c r="D147" s="344"/>
       <c r="E147" s="344"/>
       <c r="F147" s="344"/>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:6">
       <c r="B148" s="238" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6">
       <c r="B149" s="238" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
+      <c r="B150" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6">
+      <c r="B152" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
+    </row>
+    <row r="155" spans="2:6">
+      <c r="B155" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="1" t="s">
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B157" s="346" t="s">
+        <v>391</v>
+      </c>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
+    </row>
+    <row r="159" spans="2:6">
+      <c r="B159" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6">
+      <c r="B160" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="343" t="s">
-        <v>392</v>
-      </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B155" s="1" t="s">
+    <row r="162" spans="2:2">
+      <c r="B162" s="238" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B156" s="340" t="s">
-        <v>393</v>
-      </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B159" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B160" s="238" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B161" s="238" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B162" s="238" t="s">
-        <v>399</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5354,17 +5379,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5389,7 +5403,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
@@ -5397,7 +5411,7 @@
     <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>CNY</v>
@@ -5446,9 +5460,9 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -5462,7 +5476,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5470,7 +5484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5496,9 +5510,9 @@
       <c r="L4" s="181"/>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="181">
         <f>19209915823+2328256391</f>
@@ -5527,9 +5541,9 @@
       <c r="L5" s="181"/>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="181">
         <f>1406578781+C7</f>
@@ -5558,9 +5572,9 @@
       <c r="L6" s="181"/>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="189">
         <v>4602519864</v>
@@ -5584,9 +5598,9 @@
       <c r="L7" s="189"/>
       <c r="M7" s="189"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="181">
         <v>102766675</v>
@@ -5610,9 +5624,9 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C9" s="181">
         <v>48272283</v>
@@ -5636,9 +5650,9 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C10" s="181"/>
       <c r="D10" s="181"/>
@@ -5652,9 +5666,9 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" s="181"/>
       <c r="D11" s="181"/>
@@ -5668,7 +5682,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -5694,9 +5708,9 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="181">
         <v>616771200</v>
@@ -5720,9 +5734,9 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="181">
         <v>1389716314</v>
@@ -5746,9 +5760,9 @@
       <c r="L14" s="181"/>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="182">
         <v>4491776686</v>
@@ -5772,9 +5786,9 @@
       <c r="L15" s="182"/>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="181">
         <v>146792828</v>
@@ -5798,15 +5812,15 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="181">
         <v>1191305772</v>
@@ -5828,9 +5842,9 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="181">
         <f>C19</f>
@@ -5856,9 +5870,9 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="181">
         <v>583532518</v>
@@ -5880,9 +5894,9 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181">
         <v>5154661132</v>
@@ -5906,9 +5920,9 @@
       <c r="L22" s="181"/>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181">
         <v>-7421783375</v>
@@ -5932,9 +5946,9 @@
       <c r="L23" s="181"/>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181">
         <v>-2983143705</v>
@@ -5958,7 +5972,7 @@
       <c r="L24" s="181"/>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -5990,7 +6004,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -5998,7 +6012,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6025,7 +6039,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6052,7 +6066,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6079,7 +6093,7 @@
       <c r="L30" s="182"/>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6106,9 +6120,9 @@
       <c r="L31" s="182"/>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C32" s="183">
         <f>BS!G28</f>
@@ -6133,9 +6147,9 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6149,12 +6163,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6203,9 +6217,9 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" s="183">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -6252,9 +6266,9 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C38" s="184">
         <f>IF(C36="","",C36+C37)</f>
@@ -6301,9 +6315,9 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39" s="183">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -6350,9 +6364,9 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" s="185">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -6399,9 +6413,9 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C41" s="185">
         <f>IF(C$4="","",C39-C40)</f>
@@ -6448,9 +6462,9 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" s="183">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -6497,9 +6511,9 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C43" s="186">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -6546,9 +6560,9 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C44" s="187">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -6595,9 +6609,9 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C45" s="188">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -6644,9 +6658,9 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" s="183">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -6693,9 +6707,9 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" s="186">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -6742,9 +6756,9 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" s="183">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6791,12 +6805,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -6845,9 +6859,9 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" s="183">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6894,14 +6908,14 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C55" s="188">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6948,9 +6962,9 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C56" s="188">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6997,9 +7011,9 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C57" s="188">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7046,9 +7060,9 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C58" s="188">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7095,15 +7109,15 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C61" s="183">
         <f>IF(C$4="","",-C19)</f>
@@ -7150,9 +7164,9 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C62" s="183">
         <f>IF(C$4="","",-C20)</f>
@@ -7199,9 +7213,9 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C63" s="183">
         <f>IF(C$4="","",-C21)</f>
@@ -7248,9 +7262,9 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7297,7 +7311,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7346,12 +7360,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7401,9 +7415,9 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -7450,7 +7464,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -7500,9 +7514,9 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -7549,7 +7563,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -7599,9 +7613,9 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -7615,13 +7629,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -7670,9 +7684,9 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C77" s="185">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -7704,9 +7718,9 @@
       <c r="L77" s="335"/>
       <c r="M77" s="335"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C78" s="185">
         <f t="shared" si="40"/>
@@ -7738,7 +7752,7 @@
       <c r="L78" s="335"/>
       <c r="M78" s="335"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -7787,7 +7801,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -7868,7 +7882,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -7879,7 +7893,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -7892,13 +7906,13 @@
         <v>FY Report</v>
       </c>
       <c r="H1" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7907,27 +7921,27 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C3" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D3" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G3" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H3" s="204" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -7940,7 +7954,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="19">
         <v>17978772896</v>
@@ -7949,7 +7963,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -7970,7 +7984,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -7982,7 +7996,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -7991,9 +8005,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8003,7 +8017,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G7" s="19">
         <v>2021804089</v>
@@ -8012,9 +8026,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8024,7 +8038,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8033,7 +8047,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8045,7 +8059,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8054,7 +8068,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8066,7 +8080,7 @@
       </c>
       <c r="H10" s="295"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8079,9 +8093,9 @@
       </c>
       <c r="H11" s="295"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8092,7 +8106,7 @@
         <v>1983023757.2</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8103,34 +8117,34 @@
         <v>17393978059.799999</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C14" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D14" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G14" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H14" s="204" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8139,7 +8153,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -8148,7 +8162,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8159,7 +8173,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8168,9 +8182,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8179,7 +8193,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G17" s="19">
         <v>2498379750</v>
@@ -8188,9 +8202,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8199,7 +8213,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8208,7 +8222,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8220,7 +8234,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G19" s="19">
         <v>391873803</v>
@@ -8229,7 +8243,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8240,7 +8254,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8249,7 +8263,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8260,7 +8274,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G21" s="19">
         <v>41138918</v>
@@ -8269,7 +8283,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8281,7 +8295,7 @@
       </c>
       <c r="H22" s="295"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8294,9 +8308,9 @@
       </c>
       <c r="H23" s="295"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -8307,7 +8321,7 @@
         <v>3136231637.1000004</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -8318,24 +8332,24 @@
         <v>1542329122.0999999</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C26" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F26" s="205" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G26" s="206" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H26" s="207" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8354,7 +8368,7 @@
         <v>2494718755.1999969</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8362,14 +8376,14 @@
         <v>0</v>
       </c>
       <c r="F28" s="210" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G28" s="181">
         <v>799157484</v>
       </c>
       <c r="H28" s="209"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8377,7 +8391,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="211" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -8388,7 +8402,7 @@
         <v>1695561271.1999969</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8404,16 +8418,16 @@
       </c>
       <c r="H30" s="209"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>217159673</v>
       </c>
       <c r="F31" s="211" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G31" s="212">
         <f>C31+C40</f>
@@ -8421,7 +8435,7 @@
       </c>
       <c r="H31" s="209"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8430,7 +8444,7 @@
         <v>17305171626</v>
       </c>
       <c r="F32" s="213" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G32" s="214">
         <f>G35+G40</f>
@@ -8441,7 +8455,7 @@
         <v>24055562576.199997</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8452,25 +8466,25 @@
       <c r="G33" s="2"/>
       <c r="H33" s="216"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="217" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G34" s="218" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H34" s="219" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C35" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="220" t="s">
         <v>31</v>
@@ -8484,7 +8498,7 @@
         <v>5119255394.3000002</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -8492,7 +8506,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="211" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G36" s="212">
         <f>C4+C15</f>
@@ -8500,7 +8514,7 @@
       </c>
       <c r="H36" s="216"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -8508,7 +8522,7 @@
         <v>68236710</v>
       </c>
       <c r="F37" s="211" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G37" s="212">
         <f>C6</f>
@@ -8516,7 +8530,7 @@
       </c>
       <c r="H37" s="216"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -8524,7 +8538,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="211" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G38" s="212">
         <f>C7+C17</f>
@@ -8532,7 +8546,7 @@
       </c>
       <c r="H38" s="216"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -8540,7 +8554,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="211" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G39" s="212">
         <f>C7+C17+C19+C20</f>
@@ -8551,16 +8565,16 @@
         <v>1264990032.7</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>68236710</v>
       </c>
       <c r="F40" s="220" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G40" s="214">
         <f>G12+G24</f>
@@ -8571,7 +8585,7 @@
         <v>18936307181.899998</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -8580,7 +8594,7 @@
         <v>3970275812</v>
       </c>
       <c r="F41" s="211" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G41" s="212">
         <f>C70</f>
@@ -8591,7 +8605,7 @@
         <v>16180895606.399998</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -8599,7 +8613,7 @@
         <v>4038512522</v>
       </c>
       <c r="F42" s="222" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G42" s="223">
         <f>C82</f>
@@ -8610,9 +8624,9 @@
         <v>2755411575.5</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8621,23 +8635,23 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C45" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="F45" s="287" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8649,7 +8663,7 @@
       </c>
       <c r="F46" s="283"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -8664,25 +8678,25 @@
       </c>
       <c r="F47" s="283"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="283"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C49" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="283"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -8694,9 +8708,9 @@
       </c>
       <c r="F50" s="283"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C51" s="202"/>
       <c r="D51" s="92">
@@ -8705,24 +8719,24 @@
       </c>
       <c r="F51" s="283"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="283"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C53" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F53" s="283"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -8734,9 +8748,9 @@
       </c>
       <c r="F54" s="283"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -8748,24 +8762,24 @@
       </c>
       <c r="F55" s="283"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="283"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C57" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F57" s="283"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -8774,9 +8788,9 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -8785,24 +8799,24 @@
       </c>
       <c r="F59" s="283"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="283"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C61" s="262" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F61" s="283"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -8813,12 +8827,12 @@
         <v>2.749989365273205E-2</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -8827,23 +8841,23 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C65" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F65" s="287" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8854,12 +8868,12 @@
         <v>12805664367.485912</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8867,9 +8881,9 @@
       </c>
       <c r="F67" s="283"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8877,9 +8891,9 @@
       </c>
       <c r="F68" s="283"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8887,9 +8901,9 @@
       </c>
       <c r="F69" s="283"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -8897,24 +8911,24 @@
       </c>
       <c r="F70" s="283"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="283"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="285" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C72" s="261" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F72" s="283"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8925,12 +8939,12 @@
         <v>-2586554264.2570438</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8941,12 +8955,12 @@
         <v>6.9508585783195169</v>
       </c>
       <c r="F74" s="283" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" ht="15" customHeight="1">
+      <c r="B75" s="80" t="s">
         <v>328</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="80" t="s">
-        <v>329</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8954,12 +8968,12 @@
         <v>5173108528.5140877</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8967,27 +8981,27 @@
         <v>2</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="283"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C78" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F78" s="283"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8999,9 +9013,9 @@
       </c>
       <c r="F79" s="283"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9013,9 +9027,9 @@
       </c>
       <c r="F80" s="283"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9027,9 +9041,9 @@
       </c>
       <c r="F81" s="283"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9041,9 +9055,9 @@
       </c>
       <c r="F82" s="283"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9052,24 +9066,24 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>297</v>
       </c>
-      <c r="D85" s="270" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="267" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
         <v>-304435532.45540875</v>
       </c>
       <c r="D86" s="248">
-        <f>C86*$H$1/Common_Shares</f>
+        <f>C86*scaling_factor/Common_Shares</f>
         <v>-0.22316100956499887</v>
       </c>
       <c r="E86" s="269" t="str">
@@ -9077,16 +9091,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
         <v>13659946244.521357</v>
       </c>
       <c r="D87" s="248">
-        <f>C87*$H$1/Common_Shares</f>
+        <f>C87*scaling_factor/Common_Shares</f>
         <v>10.013178717820992</v>
       </c>
       <c r="E87" s="269" t="str">
@@ -9094,16 +9108,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="268" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
         <v>2939228525.9660745</v>
       </c>
       <c r="D88" s="248">
-        <f>C88*$H$1/Common_Shares</f>
+        <f>C88*scaling_factor/Common_Shares</f>
         <v>2.1545487805136765</v>
       </c>
       <c r="E88" s="269" t="str">
@@ -9111,9 +9125,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9142,7 +9156,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
@@ -9154,14 +9168,14 @@
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -9211,15 +9225,15 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -9234,13 +9248,13 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="D3" s="9"/>
@@ -9248,7 +9262,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9305,10 +9319,10 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="191">
         <f>C25</f>
@@ -9360,10 +9374,10 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="184">
         <f>C4+C5</f>
@@ -9415,10 +9429,10 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="191">
         <f>C35</f>
@@ -9470,10 +9484,10 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" s="192">
         <f>C6+C7</f>
@@ -9527,10 +9541,10 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="191">
         <f>BS!$G$39*BS!D58</f>
@@ -9582,10 +9596,10 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="191">
         <f>-C4*C78</f>
@@ -9637,10 +9651,10 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C11" s="193">
         <f>C63</f>
@@ -9694,10 +9708,10 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="191">
         <f>C50</f>
@@ -9749,10 +9763,10 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
@@ -9804,10 +9818,10 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -9859,10 +9873,10 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C15" s="191">
         <f>-C4*C83</f>
@@ -9916,10 +9930,10 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
@@ -9973,10 +9987,10 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="191">
         <f>-C4*C85</f>
@@ -9984,7 +9998,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9999,17 +10013,17 @@
       <c r="P17" s="195"/>
       <c r="Q17" s="195"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" s="191">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10024,10 +10038,10 @@
       <c r="P18" s="196"/>
       <c r="Q18" s="196"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
@@ -10081,7 +10095,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10100,15 +10114,15 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10123,10 +10137,10 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10144,10 +10158,10 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="197">
         <f>-C4*C28</f>
@@ -10201,10 +10215,10 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="191">
         <f>-C4*C29</f>
@@ -10258,10 +10272,10 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" s="184">
         <f>C23+C24</f>
@@ -10315,21 +10329,21 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="302"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E27" s="302"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="63">
         <f>AVERAGE(G28:J28)</f>
@@ -10337,7 +10351,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10385,7 +10399,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10397,7 +10411,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10445,10 +10459,10 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -10500,28 +10514,28 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="302"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" s="302"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C33" s="198">
         <f>AVERAGE(G33:J33)</f>
         <v>-1522888768.25</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10568,10 +10582,10 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="198">
         <f>AVERAGE(G34:J34)</f>
@@ -10579,7 +10593,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10627,10 +10641,10 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="184">
         <f>C33+C34</f>
@@ -10684,18 +10698,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="302"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E37" s="302"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -10753,7 +10767,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -10811,10 +10825,10 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -10866,28 +10880,28 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="302"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E42" s="302"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C43" s="296">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10935,18 +10949,18 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10961,14 +10975,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E46" s="302"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11023,10 +11037,10 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11078,10 +11092,10 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11135,10 +11149,10 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
@@ -11190,31 +11204,31 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="302"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E52" s="302"/>
       <c r="G52" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C53" s="87">
         <f>G53</f>
         <v>3.430552260533988E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11231,17 +11245,17 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>7.6514823945754068E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11258,10 +11272,10 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -11313,24 +11327,24 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="302"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E57" s="302"/>
       <c r="G57" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C58" s="191">
         <f>BS!$C67*C66</f>
@@ -11382,10 +11396,10 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C59" s="191">
         <f>BS!$C68*C67</f>
@@ -11437,10 +11451,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C60" s="191">
         <f>BS!$C69*C68</f>
@@ -11492,10 +11506,10 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C61" s="184">
         <f>SUM(C58:C60)</f>
@@ -11547,16 +11561,16 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C62" s="297">
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11603,10 +11617,10 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C63" s="184">
         <f>C61+C62</f>
@@ -11658,24 +11672,24 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="302"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E65" s="302"/>
       <c r="G65" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C66" s="177">
         <f>G66</f>
@@ -11697,10 +11711,10 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C67" s="177">
         <f>G67</f>
@@ -11722,10 +11736,10 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C68" s="177">
         <f>G68</f>
@@ -11747,10 +11761,10 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -11774,18 +11788,18 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>60</v>
+        <v>426</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -11800,10 +11814,10 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -11821,10 +11835,10 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -11878,10 +11892,10 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -11935,10 +11949,10 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -11992,10 +12006,10 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12049,10 +12063,10 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12106,10 +12120,10 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -12117,7 +12131,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>364</v>
+        <v>427</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12165,10 +12179,10 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12222,10 +12236,10 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -12279,10 +12293,10 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -12336,10 +12350,10 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -12393,7 +12407,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12451,10 +12465,10 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -12508,10 +12522,10 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C85" s="298">
         <v>0</v>
@@ -12534,10 +12548,10 @@
       <c r="P85" s="253"/>
       <c r="Q85" s="253"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -12558,10 +12572,10 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -12615,18 +12629,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="302"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E89" s="302"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -12682,19 +12696,19 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
         <v>Dividend (HKD)</v>
       </c>
       <c r="C91" s="74">
-        <f>C90*Common_Shares/$C$3</f>
+        <f>C90*Common_Shares/scaling_factor</f>
         <v>2813538278.1422811</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
-        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
+        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>2813538278.1422811</v>
       </c>
       <c r="H91" s="74">
@@ -12738,18 +12752,18 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C92" s="23">
-        <f>C90/(C19*$C$3/Common_Shares)</f>
+        <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.9773851190844387</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
-        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.89171899807392541</v>
       </c>
       <c r="H92" s="171">
@@ -12793,10 +12807,10 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -12848,14 +12862,14 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="302"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
@@ -12873,10 +12887,10 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C96" s="77">
         <f>C4/G4-1</f>
@@ -12930,10 +12944,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
@@ -12987,18 +13001,18 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -13013,17 +13027,17 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="302"/>
       <c r="G100" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13080,10 +13094,10 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C102" s="200">
         <f>BS!C4</f>
@@ -13137,10 +13151,10 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C103" s="200">
         <f>BS!C6+BS!C7</f>
@@ -13194,7 +13208,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13251,7 +13265,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13308,21 +13322,21 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="302"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
       <c r="E107" s="303"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -13335,10 +13349,10 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C108" s="94">
         <f>C102/C$4</f>
@@ -13392,10 +13406,10 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -13449,10 +13463,10 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C110" s="94">
         <f>BS!$G$38/C$4</f>
@@ -13476,21 +13490,21 @@
       <c r="P110" s="225"/>
       <c r="Q110" s="225"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="302"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E112" s="302"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13539,10 +13553,10 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13591,11 +13605,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="302"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -13649,10 +13663,10 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C117" s="23">
         <f>C81</f>
@@ -13704,9 +13718,9 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C118" s="42">
         <f>C4/C101</f>
@@ -13758,9 +13772,9 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C119" s="15">
         <f>C101/C105</f>
@@ -13814,10 +13828,10 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C120" s="102">
         <f>C8/C105</f>
@@ -13871,7 +13885,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -13890,15 +13904,15 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C122" s="54"/>
       <c r="D122" s="56"/>
       <c r="E122" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F122" s="56"/>
       <c r="G122" s="37"/>
@@ -13913,10 +13927,10 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
@@ -13934,7 +13948,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -13992,10 +14006,10 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14049,9 +14063,9 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14099,688 +14113,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14802,7 +14816,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
@@ -14811,34 +14825,34 @@
     <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="131" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C3" s="107">
-        <f>Normalized_FCF!C3</f>
+        <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
@@ -14849,7 +14863,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F4" s="135">
         <f>Thesis!C76</f>
@@ -14857,9 +14871,9 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8">
       <c r="B5" s="227" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="228">
         <f>Thesis!C70</f>
@@ -14868,9 +14882,9 @@
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
       <c r="B6" s="150" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -14881,14 +14895,14 @@
         <v>CNY</v>
       </c>
       <c r="E6" s="348" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C7" s="226">
         <f>BS!G31</f>
@@ -14902,9 +14916,9 @@
       <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
@@ -14918,9 +14932,9 @@
       <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8">
       <c r="B9" s="227" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C9" s="229">
         <f>BS!H42</f>
@@ -14934,9 +14948,9 @@
       <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
@@ -14948,9 +14962,9 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="230" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
@@ -14962,12 +14976,12 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="112">
-        <f>(C10*C3)/Common_Shares*C11</f>
+        <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
         <v>40.080865541246048</v>
       </c>
       <c r="D12" t="str">
@@ -14976,12 +14990,12 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -14989,15 +15003,15 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
@@ -15005,9 +15019,9 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
@@ -15015,12 +15029,12 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="141">
-        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
+        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
         <v>66.92016833560433</v>
       </c>
       <c r="D18" t="str">
@@ -15029,28 +15043,28 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="129" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="129" t="s">
+      <c r="D20" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="129" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="129" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" s="129" t="s">
+      <c r="F20" s="130" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="130" t="s">
-        <v>112</v>
-      </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15072,7 +15086,7 @@
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15094,7 +15108,7 @@
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15116,7 +15130,7 @@
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15138,7 +15152,7 @@
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15160,7 +15174,7 @@
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15182,7 +15196,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15204,7 +15218,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15226,7 +15240,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15248,7 +15262,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15270,7 +15284,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15292,7 +15306,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15314,7 +15328,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15336,7 +15350,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15358,7 +15372,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15380,7 +15394,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15402,7 +15416,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15424,7 +15438,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15446,7 +15460,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -15468,7 +15482,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -15490,7 +15504,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -15512,7 +15526,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -15534,7 +15548,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -15556,7 +15570,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -15578,7 +15592,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -15600,7 +15614,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -15622,7 +15636,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -15644,7 +15658,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -15666,7 +15680,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -15688,7 +15702,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -15710,9 +15724,9 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -15732,10 +15746,10 @@
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
@@ -15743,13 +15757,13 @@
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C54" s="137"/>
       <c r="D54" s="137"/>
@@ -15757,7 +15771,7 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
         <v>70307254618.17218</v>
@@ -15784,7 +15798,7 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
@@ -15806,7 +15820,7 @@
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
@@ -15827,7 +15841,7 @@
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
@@ -15848,7 +15862,7 @@
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
@@ -15869,7 +15883,7 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
@@ -15890,7 +15904,7 @@
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
@@ -15911,16 +15925,16 @@
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" s="115"/>
       <c r="D63" s="115"/>
@@ -15928,7 +15942,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0.02</v>
@@ -15951,7 +15965,7 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
@@ -15977,7 +15991,7 @@
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16004,7 +16018,7 @@
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16031,7 +16045,7 @@
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16058,7 +16072,7 @@
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16085,7 +16099,7 @@
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16111,7 +16125,7 @@
         <v>88.522804369101323</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16137,24 +16151,24 @@
         <v>105.89857071605785</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C73" s="172" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D73" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" s="173" t="s">
         <v>114</v>
       </c>
-      <c r="E73" s="173" t="s">
-        <v>115</v>
-      </c>
       <c r="F73" s="173" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16176,7 +16190,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16199,7 +16213,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16222,7 +16236,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16245,7 +16259,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16267,38 +16281,38 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C80" s="156" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16329,7 +16343,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I98"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -16339,22 +16353,22 @@
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I2" s="278"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H3" s="276">
         <v>0</v>
@@ -16364,16 +16378,16 @@
         <v>-54.25</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C4" s="121">
         <v>3</v>
       </c>
       <c r="D4" s="121"/>
       <c r="E4" s="156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F4" s="156"/>
       <c r="H4" s="276">
@@ -16384,7 +16398,7 @@
         <v>2.0624137975483059</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9">
       <c r="H5" s="276">
         <v>2</v>
       </c>
@@ -16393,16 +16407,16 @@
         <v>2.0624137975483059</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="107">
         <f>Valuation_Model!C3</f>
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16413,9 +16427,9 @@
         <v>68.984393000522246</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16438,9 +16452,9 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
@@ -16460,9 +16474,9 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
@@ -16482,7 +16496,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9">
       <c r="E10" s="350"/>
       <c r="F10" s="350"/>
       <c r="H10" s="276">
@@ -16493,9 +16507,9 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E11" s="350"/>
       <c r="F11" s="350"/>
@@ -16507,9 +16521,9 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C12" s="159">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16526,9 +16540,9 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C13" s="159">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16544,9 +16558,9 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16555,49 +16569,49 @@
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="151">
         <v>30</v>
       </c>
       <c r="E18" s="350" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F18" s="351"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6">
       <c r="E19" s="351"/>
       <c r="F19" s="351"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E20" s="351"/>
       <c r="F20" s="351"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16610,9 +16624,9 @@
       <c r="E21" s="351"/>
       <c r="F21" s="351"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16625,18 +16639,18 @@
       <c r="E22" s="351"/>
       <c r="F22" s="351"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" s="167">
         <f>C18</f>
@@ -16646,9 +16660,9 @@
       <c r="E25" s="349"/>
       <c r="F25" s="349"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C26" s="165">
         <v>0.06</v>
@@ -16657,9 +16671,9 @@
       <c r="E26" s="349"/>
       <c r="F26" s="349"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
@@ -16672,9 +16686,9 @@
       <c r="E27" s="349"/>
       <c r="F27" s="349"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C28" s="166">
         <v>0.5</v>
@@ -16683,18 +16697,18 @@
       <c r="E28" s="349"/>
       <c r="F28" s="349"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C31" s="167">
         <f>C18</f>
@@ -16704,9 +16718,9 @@
       <c r="E31" s="349"/>
       <c r="F31" s="349"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C32" s="165">
         <v>0.04</v>
@@ -16715,9 +16729,9 @@
       <c r="E32" s="349"/>
       <c r="F32" s="349"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
@@ -16730,9 +16744,9 @@
       <c r="E33" s="349"/>
       <c r="F33" s="349"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C34" s="166">
         <v>0.3</v>
@@ -16741,18 +16755,18 @@
       <c r="E34" s="349"/>
       <c r="F34" s="349"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C37" s="167">
         <f>C18</f>
@@ -16762,9 +16776,9 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C38" s="165">
         <v>0.08</v>
@@ -16773,9 +16787,9 @@
       <c r="E38" s="349"/>
       <c r="F38" s="349"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
@@ -16788,9 +16802,9 @@
       <c r="E39" s="349"/>
       <c r="F39" s="349"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C40" s="168">
         <f>1-C28-C34</f>
@@ -16800,9 +16814,9 @@
       <c r="E40" s="349"/>
       <c r="F40" s="349"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -16813,23 +16827,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="151">
         <v>30</v>
@@ -16837,23 +16851,23 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E48" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C49" s="167">
         <f>C46</f>
@@ -16863,9 +16877,9 @@
       <c r="E49" s="349"/>
       <c r="F49" s="349"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C50" s="165">
         <v>0.02</v>
@@ -16874,9 +16888,9 @@
       <c r="E50" s="349"/>
       <c r="F50" s="349"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
@@ -16889,9 +16903,9 @@
       <c r="E51" s="349"/>
       <c r="F51" s="349"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C52" s="166">
         <v>0.05</v>
@@ -16900,18 +16914,18 @@
       <c r="E52" s="349"/>
       <c r="F52" s="349"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E54" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C55" s="167">
         <f>C46</f>
@@ -16921,9 +16935,9 @@
       <c r="E55" s="349"/>
       <c r="F55" s="349"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C56" s="165">
         <v>0.1</v>
@@ -16932,9 +16946,9 @@
       <c r="E56" s="349"/>
       <c r="F56" s="349"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
@@ -16947,9 +16961,9 @@
       <c r="E57" s="349"/>
       <c r="F57" s="349"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="166">
         <v>0.05</v>
@@ -16958,9 +16972,9 @@
       <c r="E58" s="349"/>
       <c r="F58" s="349"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -16971,33 +16985,33 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C64" s="167">
         <f>C18</f>
@@ -17005,24 +17019,24 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C65" s="152">
         <v>6.1165848114484E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
@@ -17033,20 +17047,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="13.15">
+      <c r="B68" s="109" t="s">
+        <v>358</v>
+      </c>
+      <c r="E68" s="282" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B68" s="109" t="s">
-        <v>360</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17054,21 +17068,21 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17076,39 +17090,39 @@
       </c>
       <c r="E71" s="281"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
         <v>0.17848495563082309</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
       <c r="B76" s="275" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17116,9 +17130,9 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
@@ -17129,23 +17143,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -17155,9 +17169,9 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
@@ -17165,9 +17179,9 @@
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
@@ -17178,24 +17192,24 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
         <v>0.42784290690799853</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17206,108 +17220,108 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.10804060157997641</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>(Thesis!E19+Thesis!C67)/2</f>
-        <v>5.7250000000000002E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>5.5410264563317959</v>
+        <v>5.5128567255811802</v>
       </c>
       <c r="D91" s="117"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>56.628583084232254</v>
+        <v>56.188984197503579</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>62.169609540564053</v>
+        <v>61.70184092308476</v>
       </c>
       <c r="D93" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E93" s="147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>7.1013585058445239E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+        <v>7.8003345717802763E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8">
       <c r="B94" s="100"/>
     </row>
-    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+    <row r="95" spans="2:8" ht="14.65">
       <c r="E95" s="320" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:8" ht="13.9">
       <c r="E96" s="313" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F96" s="318" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="97" spans="5:8" ht="13.9">
       <c r="E97" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>335</v>
-      </c>
-      <c r="F97" s="318" t="s">
-        <v>337</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="98" spans="5:8" ht="13.9">
       <c r="E98" s="315" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21684002-40DF-4C6B-B55B-472594F1DE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1A47AD-997B-40F2-9E69-D2A79AC206D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1A47AD-997B-40F2-9E69-D2A79AC206D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BC0774-F274-4B6B-B80D-A6799B78E799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3744,29 +3744,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4177,13 +4177,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4290,22 +4290,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4317,13 +4317,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4343,13 +4343,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4378,13 +4378,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4400,13 +4400,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4470,13 +4470,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4492,7 +4492,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4514,22 +4514,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4590,22 +4590,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4663,22 +4663,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4715,13 +4715,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4734,13 +4734,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4871,13 +4871,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4916,13 +4916,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5065,13 +5065,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5084,22 +5084,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="C136" s="92">
         <f>Scenarios!C90</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>418</v>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>5.5128567255811802</v>
+        <v>5.3150403841201985</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>56.188984197503579</v>
+        <v>53.124824724201986</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>61.70184092308476</v>
+        <v>58.439865108322181</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>7.8003345717802763E-2</v>
+        <v>0.1267463125817837</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5256,13 +5256,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5299,13 +5299,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5313,22 +5313,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5352,17 +5352,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5379,6 +5368,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -17242,8 +17242,8 @@
         <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.06</v>
+        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>5.5128567255811802</v>
+        <v>5.3150403841201985</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17262,7 +17262,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>56.188984197503579</v>
+        <v>53.124824724201986</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17272,7 +17272,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>61.70184092308476</v>
+        <v>58.439865108322181</v>
       </c>
       <c r="D93" t="s">
         <v>405</v>
@@ -17282,7 +17282,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>7.8003345717802763E-2</v>
+        <v>0.1267463125817837</v>
       </c>
     </row>
     <row r="94" spans="2:8">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BC0774-F274-4B6B-B80D-A6799B78E799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1C1565-BEE8-4310-9AE1-CBFAE620347D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="430">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2287,10 +2287,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>in contrast to a cash yield of</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -2346,6 +2342,15 @@
   </si>
   <si>
     <t>Target Return</t>
+  </si>
+  <si>
+    <t>in contrast to a position yield of</t>
+  </si>
+  <si>
+    <t>Position Price Output</t>
+  </si>
+  <si>
+    <t>@ Position Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -3736,37 +3741,37 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4079,7 +4084,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4111,10 +4116,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4125,7 +4130,7 @@
         <v>54.25</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4177,13 +4182,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4207,7 +4212,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4230,7 +4235,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4242,10 +4247,10 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="E19" s="336">
-        <v>3.4500000000000003E-2</v>
+        <v>419</v>
+      </c>
+      <c r="E19" s="339">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4266,7 +4271,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4290,22 +4295,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4317,13 +4322,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4343,13 +4348,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4378,13 +4383,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4400,13 +4405,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4470,13 +4475,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4492,7 +4497,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4514,22 +4519,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4590,22 +4595,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4629,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4641,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4663,22 +4668,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4715,13 +4720,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4734,13 +4739,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4769,28 +4774,28 @@
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="337" t="s">
-        <v>414</v>
-      </c>
-      <c r="C88" s="338">
+      <c r="B88" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
         <v>0.72207550313588764</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="337" t="s">
-        <v>415</v>
-      </c>
-      <c r="C89" s="338">
+      <c r="B89" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
         <v>9.5579625064196368E-3</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="337" t="s">
-        <v>417</v>
-      </c>
-      <c r="C90" s="339">
+      <c r="B90" s="336" t="s">
+        <v>416</v>
+      </c>
+      <c r="C90" s="338">
         <f>BS!C50</f>
         <v>7.3592411949940734E-2</v>
       </c>
@@ -4871,13 +4876,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4893,8 +4898,8 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="337" t="s">
-        <v>416</v>
+      <c r="B104" s="336" t="s">
+        <v>415</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4916,13 +4921,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5065,17 +5070,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5084,22 +5089,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5139,14 +5144,14 @@
     </row>
     <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C130" s="338">
+        <v>408</v>
+      </c>
+      <c r="C130" s="337">
         <f>C19</f>
         <v>0.25</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5193,14 +5198,14 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C136" s="92">
-        <f>Scenarios!C90</f>
+        <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -5209,7 +5214,7 @@
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C91</f>
+        <f>Scenarios!C97</f>
         <v>5.3150403841201985</v>
       </c>
     </row>
@@ -5219,16 +5224,16 @@
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C92</f>
+        <f>Scenarios!C98</f>
         <v>53.124824724201986</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C93</f>
+        <f>Scenarios!C99</f>
         <v>58.439865108322181</v>
       </c>
       <c r="D139" s="101" t="str">
@@ -5241,7 +5246,7 @@
         <v>263</v>
       </c>
       <c r="C140" s="92">
-        <f>Scenarios!F93</f>
+        <f>Scenarios!F99</f>
         <v>0.1267463125817837</v>
       </c>
     </row>
@@ -5256,13 +5261,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B144" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5299,13 +5304,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5313,22 +5318,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5352,6 +5357,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5368,17 +5384,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -6009,7 +6014,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8643,7 +8648,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -11799,7 +11804,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12131,7 +12136,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16342,7 +16347,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I98"/>
+  <dimension ref="B2:I104"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -17234,16 +17239,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>413</v>
-      </c>
-      <c r="C90" s="135">
-        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.08</v>
+        <v>421</v>
+      </c>
+      <c r="C90" s="168">
+        <f>Thesis!E19</f>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17252,9 +17257,11 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>5.3150403841201985</v>
+        <v>4.3444364716874029</v>
       </c>
       <c r="D91" s="117"/>
+      <c r="E91" s="100"/>
+      <c r="F91" s="100"/>
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
@@ -17262,69 +17269,123 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>53.124824724201986</v>
+        <v>38.727997223943255</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>407</v>
+        <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>58.439865108322181</v>
-      </c>
-      <c r="D93" t="s">
-        <v>405</v>
+        <v>43.072433695630657</v>
+      </c>
+      <c r="D93" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.1267463125817837</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8">
-      <c r="B94" s="100"/>
-    </row>
-    <row r="95" spans="2:8" ht="14.65">
-      <c r="E95" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F95" s="317"/>
+        <v>0.35637836464770067</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
+      <c r="B95" s="109" t="s">
+        <v>405</v>
+      </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9">
-      <c r="E96" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>334</v>
+    <row r="96" spans="2:8">
+      <c r="B96" s="149" t="s">
+        <v>412</v>
+      </c>
+      <c r="C96" s="135">
+        <f>Thesis!C67</f>
+        <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9">
-      <c r="E97" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F97" s="318" t="s">
-        <v>335</v>
-      </c>
+    <row r="97" spans="2:8">
+      <c r="B97" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C97" s="117">
+        <f>PV(C96, C76, -C77, 0)</f>
+        <v>5.3150403841201985</v>
+      </c>
+      <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9">
-      <c r="E98" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F98" s="319" t="s">
-        <v>336</v>
-      </c>
+    <row r="98" spans="2:8">
+      <c r="B98" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C98" s="117">
+        <f>C60/(1+C96)^C76</f>
+        <v>53.124824724201986</v>
+      </c>
+      <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>
+    </row>
+    <row r="99" spans="2:8" ht="13.15">
+      <c r="B99" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="112">
+        <f>C97+C98</f>
+        <v>58.439865108322181</v>
+      </c>
+      <c r="D99" t="s">
+        <v>404</v>
+      </c>
+      <c r="E99" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" s="329">
+        <f>(1-C99/C60)</f>
+        <v>0.1267463125817837</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
+      <c r="B100" s="100"/>
+    </row>
+    <row r="101" spans="2:8" ht="14.65">
+      <c r="E101" s="320" t="s">
+        <v>332</v>
+      </c>
+      <c r="F101" s="317"/>
+    </row>
+    <row r="102" spans="2:8" ht="13.9">
+      <c r="E102" s="313" t="s">
+        <v>333</v>
+      </c>
+      <c r="F102" s="318" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="13.9">
+      <c r="E103" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F103" s="318" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" ht="13.9">
+      <c r="E104" s="315" t="s">
+        <v>333</v>
+      </c>
+      <c r="F104" s="319" t="s">
+        <v>336</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1C1565-BEE8-4310-9AE1-CBFAE620347D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C4CA05-93B2-4BCF-9063-8E591D30FE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3749,29 +3749,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4182,13 +4182,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4222,7 +4222,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.06671125</v>
+        <v>1.0671017599999999</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4244,7 +4244,7 @@
         <v>277</v>
       </c>
       <c r="C19" s="249">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>419</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>38.289885084736952</v>
+        <v>34.215998183334875</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10804060157997641</v>
+        <v>0.10815463230293121</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4295,22 +4295,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4322,13 +4322,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4348,13 +4348,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4383,13 +4383,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4405,13 +4405,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177466191.56481656</v>
+        <v>177460304.59321538</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155629137.56481656</v>
+        <v>155623250.59321538</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4475,13 +4475,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008424301.9681427</v>
+        <v>-1008422830.2252425</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4497,7 +4497,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4519,22 +4519,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3155184855.5648165</v>
+        <v>3155178968.593215</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878638341.4327517</v>
+        <v>2878633926.2040505</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.1491316575080373E-2</v>
+        <v>4.1506442378573941E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.801684419443882E-2</v>
+        <v>3.8002931783848878E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4595,22 +4595,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4668,22 +4668,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>28.136299052476371</v>
+        <v>28.146556237970447</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4720,13 +4720,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4739,13 +4739,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.22316100956499887</v>
+        <v>0.2232427060933192</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12805664367.485912</v>
+        <v>12805835971.681217</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>10.013178717820992</v>
+        <v>10.016978652827861</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1545487805136765</v>
+        <v>2.1553375345877317</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,13 +4876,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>40.080865541246048</v>
+        <v>40.095629719292724</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>1.3258162597677496</v>
+        <v>1.3263016249568782</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4921,13 +4921,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>105.9 HKD</v>
+        <v>105.94 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>82.49 HKD</v>
+        <v>82.52 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>66.11 HKD</v>
+        <v>66.14 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>54.51 HKD</v>
+        <v>54.53 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>46.17 HKD</v>
+        <v>46.19 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>66.921979202973944</v>
+        <v>66.946528402184271</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5070,13 +5070,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5089,22 +5089,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C127" s="250">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0624137975483059</v>
+        <v>2.0616590492738016</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C130" s="337">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>418</v>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>4.025831732814293</v>
+        <v>3.7442055560320755</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>34.264053351922662</v>
+        <v>30.471792627302801</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>38.289885084736952</v>
+        <v>34.215998183334875</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.42784290690799853</v>
+        <v>0.48890556388853013</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C97</f>
-        <v>5.3150403841201985</v>
+        <v>5.3130953246158432</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C98</f>
-        <v>53.124824724201986</v>
+        <v>53.144312670026373</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C99</f>
-        <v>58.439865108322181</v>
+        <v>58.457407994642217</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F99</f>
-        <v>0.1267463125817837</v>
+        <v>0.12680449024247054</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5261,13 +5261,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5304,13 +5304,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5318,22 +5318,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5357,17 +5357,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5384,6 +5373,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5984,23 +5984,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0624137975483059</v>
+        <v>2.0616590492738016</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8749216341348234</v>
+        <v>1.8742354993398194</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2186990621876352</v>
+        <v>1.2182530745708826</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0312068987741529</v>
+        <v>1.0308295246369008</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.70309561280055877</v>
+        <v>0.70283831225243232</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7322,23 +7322,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0624137975483059</v>
+        <v>2.0616590492738016</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8749216341348234</v>
+        <v>1.8742354993398194</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2186990621876352</v>
+        <v>1.2182530745708826</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0312068987741529</v>
+        <v>1.0308295246369008</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.70309561280055877</v>
+        <v>0.70283831225243232</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8675,11 +8675,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.723289907259939</v>
+        <v>22.731608627008775</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3258162597677496</v>
+        <v>1.3263016249568782</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12805664367.485912</v>
+        <v>12805835971.681217</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -8937,11 +8937,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2538631317.6785235</v>
+        <v>-2538545515.5808711</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2586554264.2570438</v>
+        <v>-2586468462.1593919</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -8953,11 +8953,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.0820732300903257</v>
+        <v>7.0823126020988791</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.9508585783195169</v>
+        <v>6.9510891623205309</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -8970,7 +8970,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5173108528.5140877</v>
+        <v>5172936924.3187838</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9085,11 +9085,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-304435532.45540875</v>
+        <v>-304546982.59693408</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.22316100956499887</v>
+        <v>-0.2232427060933192</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9102,11 +9102,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13659946244.521357</v>
+        <v>13665130103.652336</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>10.013178717820992</v>
+        <v>10.016978652827861</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9119,11 +9119,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2939228525.9660745</v>
+        <v>2940304541.7404227</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.1545487805136765</v>
+        <v>2.1553375345877317</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9136,11 +9136,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16294739238.032022</v>
+        <v>16300887662.795826</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>11.94456648876967</v>
+        <v>11.949073481322273</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9720,28 +9720,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155629137.56481656</v>
+        <v>155623250.59321538</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155629137.56481656</v>
+        <v>155623250.59321538</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129271123.62123284</v>
+        <v>129266290.35218722</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>123022596.55985366</v>
+        <v>123018209.1709564</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68137458.250550002</v>
+        <v>68134445.443500534</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>137118501.10002863</v>
+        <v>137113499.33301559</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9775,28 +9775,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033697207.872571</v>
+        <v>4033691320.90097</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691693997.5648165</v>
+        <v>4691688110.593215</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4549938915.621233</v>
+        <v>4549934082.3521872</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3869975804.5598536</v>
+        <v>3869971417.1709566</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025228458.2505498</v>
+        <v>3025225445.4435005</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2471178373.1000285</v>
+        <v>2471173371.3330154</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008424301.9681427</v>
+        <v>-1008422830.2252425</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9942,30 +9942,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878638341.4327517</v>
+        <v>2878633926.2040505</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3155184855.5648165</v>
+        <v>3155178968.593215</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071383019.621233</v>
+        <v>3071378186.3521872</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574463111.5598536</v>
+        <v>2574458724.1709566</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701708803.2505498</v>
+        <v>1701705790.4435005</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1432952605.1000285</v>
+        <v>1432947603.3330154</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -10050,30 +10050,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878638341.4327517</v>
+        <v>2878633926.2040505</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3155184855.5648165</v>
+        <v>3155178968.593215</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071383019.621233</v>
+        <v>3071378186.3521872</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574463111.5598536</v>
+        <v>2574458724.1709566</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701708803.2505498</v>
+        <v>1701705790.4435005</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1432952605.1000285</v>
+        <v>1432947603.3330154</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10911,23 +10911,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29620779077265491</v>
+        <v>0.29620816244417508</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30730267019619834</v>
+        <v>0.30730299663531957</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31044633575858799</v>
+        <v>0.31044668771178346</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.40417826682322355</v>
+        <v>0.40417866934235924</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36928961864262017</v>
+        <v>0.3692903661015618</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -11049,28 +11049,28 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177466191.56481656</v>
+        <v>177460304.59321538</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>177466191.56481656</v>
+        <v>177460304.59321538</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>145701713.62123284</v>
+        <v>145696880.35218722</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132260396.55985366</v>
+        <v>132256009.1709564</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90822825.250550002</v>
+        <v>90819812.443500534</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150781183.10002863</v>
+        <v>150776181.33301559</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -11161,28 +11161,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155629137.56481656</v>
+        <v>155623250.59321538</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155629137.56481656</v>
+        <v>155623250.59321538</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129271123.62123284</v>
+        <v>129266290.35218722</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>123022596.55985366</v>
+        <v>123018209.1709564</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68137458.250550002</v>
+        <v>68134445.443500534</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>137118501.10002863</v>
+        <v>137113499.33301559</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -12248,30 +12248,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8477793444510206E-3</v>
+        <v>4.8475959678688707E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8425527494324666E-3</v>
+        <v>4.8423695705563305E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8092035712620461E-3</v>
+        <v>3.8090611503934584E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8239542954688769E-3</v>
+        <v>3.8238179207288805E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2586898877432963E-3</v>
+        <v>2.2585900161456308E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.9394787094703563E-3</v>
+        <v>4.9392985286670918E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12305,30 +12305,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12564789802263307</v>
+        <v>0.12564771464605093</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14598664506471964</v>
+        <v>0.14598646188584349</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13407204239355611</v>
+        <v>0.13407189997268751</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12029180829399394</v>
+        <v>0.12029167191925395</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10028335517943399</v>
+        <v>0.10028325530783633</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.9020320841507766E-2</v>
+        <v>8.9020140660704489E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.1411974505658267E-2</v>
+        <v>3.1411928661512732E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12477,30 +12477,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.9668321177520147E-2</v>
+        <v>8.9668183645083527E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8176661108332675E-2</v>
+        <v>9.8176477929456524E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0503763248277011E-2</v>
+        <v>9.0503620827408426E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.0022935210815577E-2</v>
+        <v>8.002279883607559E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.6409977191286528E-2</v>
+        <v>5.640987731968887E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1619867689541105E-2</v>
+        <v>5.1619687508737834E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12584,30 +12584,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.9668321177520147E-2</v>
+        <v>8.9668183645083527E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8176661108332675E-2</v>
+        <v>9.8176477929456524E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0503763248277011E-2</v>
+        <v>9.0503620827408426E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.0022935210815577E-2</v>
+        <v>8.002279883607559E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.6409977191286528E-2</v>
+        <v>5.640987731968887E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1619867689541105E-2</v>
+        <v>5.1619687508737834E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12653,28 +12653,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0624137975483059</v>
+        <v>2.0616590492738016</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0624137975483059</v>
+        <v>2.0616590492738016</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8749216341348234</v>
+        <v>1.8742354993398194</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2186990621876352</v>
+        <v>1.2182530745708826</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0312068987741529</v>
+        <v>1.0308295246369008</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.70309561280055877</v>
+        <v>0.70283831225243232</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12709,28 +12709,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2813538278.1422811</v>
+        <v>2812508652.9704537</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2813538278.1422811</v>
+        <v>2812508652.9704537</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2557762071.0384374</v>
+        <v>2556826048.1549578</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1662545346.1749842</v>
+        <v>1661936931.3007226</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1406769139.0711405</v>
+        <v>1406254326.4852269</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>959160776.63941395</v>
+        <v>958809768.05810916</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12764,28 +12764,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.9773851190844387</v>
+        <v>0.97702893979270444</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.89171899807392541</v>
+        <v>0.89139433324267314</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.83277209475289216</v>
+        <v>0.8324686486074343</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.645783324185079</v>
+        <v>0.64554809743003738</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82668029711309898</v>
+        <v>0.82637923334487062</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66935973543413807</v>
+        <v>0.66911711623504688</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12819,28 +12819,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.801684419443882E-2</v>
+        <v>3.8002931783848878E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.801684419443882E-2</v>
+        <v>3.8002931783848878E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.4560767449489833E-2</v>
+        <v>3.4548119803498978E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.246449884216839E-2</v>
+        <v>2.2456277872274333E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.900842209721941E-2</v>
+        <v>1.9001465891924439E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2960287793558687E-2</v>
+        <v>1.2955544926312117E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12956,26 +12956,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14024716659564185</v>
+        <v>-0.14024734257304416</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1155381329823539E-2</v>
+        <v>3.1155182838988438E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17570216078875833</v>
+        <v>0.17570224476704266</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27923423237853906</v>
+        <v>0.27923405609317009</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.22420481304855389</v>
+        <v>0.22420607171386564</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13567,23 +13567,23 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6337112936215754</v>
+        <v>1.6337143418201361</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90433759718530093</v>
+        <v>0.90433902029461877</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8950635960147739</v>
+        <v>1.8950668255794594</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5512018527827096</v>
+        <v>3.5512081400540088</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.4567942752399841</v>
+        <v>3.4568063413333543</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13675,28 +13675,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12564789802263307</v>
+        <v>0.12564771464605093</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14598664506471964</v>
+        <v>0.14598646188584349</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13407204239355611</v>
+        <v>0.13407189997268751</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12029180829399394</v>
+        <v>0.12029167191925395</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10028335517943399</v>
+        <v>0.10028325530783633</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.9020320841507766E-2</v>
+        <v>8.9020140660704489E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13961,30 +13961,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2509039241981101</v>
+        <v>2.2517244990376364</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4671449243000381</v>
+        <v>2.4680435111102197</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.4016174564464228</v>
+        <v>2.4024928786755262</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0130591040586006</v>
+        <v>2.0137926285823964</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3306232213848299</v>
+        <v>1.3311079896667009</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1204737307862711</v>
+        <v>1.1208800100945866</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14018,30 +14018,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1491316575080373E-2</v>
+        <v>4.1506442378573941E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.5477325793549087E-2</v>
+        <v>4.5493889605718332E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.4269446201777377E-2</v>
+        <v>4.4285583017060391E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.7107080259144713E-2</v>
+        <v>3.7120601448523437E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.4527616984052165E-2</v>
+        <v>2.4536552804916144E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.0653893655046471E-2</v>
+        <v>2.0661382674554592E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14861,7 +14861,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878638341.4327517</v>
+        <v>2878633926.2040505</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14893,7 +14893,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35982979267.909393</v>
+        <v>35982924077.550629</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14927,7 +14927,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12805664367.485912</v>
+        <v>12805835971.681217</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51258658827.895309</v>
+        <v>51258775241.731842</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.06671125</v>
+        <v>1.0671017599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14987,7 +14987,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>40.080865541246048</v>
+        <v>40.095629719292724</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>66.92016833560433</v>
+        <v>66.944716874656692</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3054712697.0013571</v>
+        <v>3054708011.7114477</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15087,7 +15087,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2828437682.4086637</v>
+        <v>2828433344.1772661</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3241556789.8595276</v>
+        <v>3241551817.9898872</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2779112474.1594028</v>
+        <v>2779108211.5825505</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3439829360.1225491</v>
+        <v>3439824084.1442857</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15131,7 +15131,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2730647449.673059</v>
+        <v>2730643261.4314108</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3650229440.3035474</v>
+        <v>3650223841.6155987</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2683027608.1795964</v>
+        <v>2683023492.9768176</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15163,7 +15163,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3873498819.8321714</v>
+        <v>3873492878.6957259</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2636238210.5078487</v>
+        <v>2636234167.0702124</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4110424660.3176589</v>
+        <v>4110418355.7865639</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15197,7 +15197,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2590264774.5234909</v>
+        <v>2590260801.599483</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4361842270.7766771</v>
+        <v>4361835580.6235914</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2545093070.6465669</v>
+        <v>2545089167.0064983</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4628638052.6103392</v>
+        <v>4628630953.2483654</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2500709117.447185</v>
+        <v>2500705281.8828111</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4911752624.7132235</v>
+        <v>4911745091.1127539</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2457099177.3180232</v>
+        <v>2457095408.6421695</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15273,7 +15273,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5212184139.7323503</v>
+        <v>5212176145.332818</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15285,7 +15285,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2414249752.2222967</v>
+        <v>2414246049.2684922</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15295,7 +15295,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>5530991803.1679411</v>
+        <v>5530983319.7841816</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15307,7 +15307,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2372147579.5158854</v>
+        <v>2372143941.1380014</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5869299607.7229662</v>
+        <v>5869290605.4458447</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2330779627.842309</v>
+        <v>2330776052.9142051</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>6228300296.0673494</v>
+        <v>6228290743.1583118</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15351,7 +15351,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2290133093.0993013</v>
+        <v>2290129580.5144734</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15361,7 +15361,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>6609259565.9879999</v>
+        <v>6609249428.7671795</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15373,7 +15373,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2250195394.475709</v>
+        <v>2250191943.1469522</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>7013520532.7504206</v>
+        <v>7013509775.477891</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2210954170.5575194</v>
+        <v>2210950779.4165864</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>7442508464.4044466</v>
+        <v>7442497049.1542196</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2172397275.5017829</v>
+        <v>2172393943.4990568</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7897735806.7289705</v>
+        <v>7897723693.2552824</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2134512775.2772627</v>
+        <v>2134509501.3814306</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15449,7 +15449,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>8380807515.5316763</v>
+        <v>8380794661.1270962</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2097288943.9706452</v>
+        <v>2097285727.1683793</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15471,7 +15471,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8893426715.1034107</v>
+        <v>8893413074.4482727</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2060714260.1571665</v>
+        <v>2060711099.4528103</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>9437400702.77672</v>
+        <v>9437386227.7793407</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15505,7 +15505,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2024777403.3345287</v>
+        <v>2024774297.7497888</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>10014647320.758284</v>
+        <v>10014631960.385414</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
@@ -15527,7 +15527,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>1989467250.4190066</v>
+        <v>1989464198.992651</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>10627201717.699909</v>
+        <v>10627185417.796804</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
@@ -15549,7 +15549,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>1954772872.3026624</v>
+        <v>1954769874.0902207</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>11277223523.846722</v>
+        <v>11277206226.94622</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
@@ -15571,7 +15571,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>1920683530.4705927</v>
+        <v>1920680584.5440667</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>11967004465.059414</v>
+        <v>11966986110.179323</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>1887188673.6771736</v>
+        <v>1887185779.1247468</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15603,7 +15603,7 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>12698976442.55459</v>
+        <v>12698956964.982693</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>1854277934.6802647</v>
+        <v>1854275090.6060233</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>13475720106.849295</v>
+        <v>13475699437.915192</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>1821941127.0323675</v>
+        <v>1821938332.5560207</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>14299973956.138134</v>
+        <v>14299952022.971148</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
@@ -15659,7 +15659,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>1790168241.9277415</v>
+        <v>1790165496.1843503</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15669,7 +15669,7 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>15174643991.180353</v>
+        <v>15174620716.452604</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
@@ -15681,7 +15681,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>1758949445.1045055</v>
+        <v>1758946747.2442143</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>16102813960.736256</v>
+        <v>16102789262.390047</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
@@ -15703,7 +15703,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>1728275073.8007624</v>
+        <v>1728272422.9885366</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>17087756233.674442</v>
+        <v>17087730024.632938</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>1698135633.763804</v>
+        <v>1698133029.1791706</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38183908712.51696</v>
+        <v>38183850146.393097</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15747,7 +15747,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3794614994.1750507</v>
+        <v>3794609174.0298834</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15758,7 +15758,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>70307254618.17218</v>
+        <v>70307146781.55928</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15779,7 +15779,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>70307254618.17218</v>
+        <v>70307146781.55928</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15809,19 +15809,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37143978540.338562</v>
+        <v>37143921569.249916</v>
       </c>
       <c r="C56" s="124">
-        <v>38339749234.337227</v>
+        <v>38339690429.186615</v>
       </c>
       <c r="D56" s="124">
-        <v>39571817232.211975</v>
+        <v>39571756537.326935</v>
       </c>
       <c r="E56" s="124">
-        <v>40841755661.633034</v>
+        <v>40841693018.928253</v>
       </c>
       <c r="F56" s="124">
-        <v>42151185647.949028</v>
+        <v>42151120996.852715</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15830,19 +15830,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>38306046909.630844</v>
+        <v>38305988156.172546</v>
       </c>
       <c r="C57" s="124">
-        <v>40861948828.513817</v>
+        <v>40861886154.836929</v>
       </c>
       <c r="D57" s="124">
-        <v>43678550185.483231</v>
+        <v>43678483191.729401</v>
       </c>
       <c r="E57" s="124">
-        <v>46786831627.411896</v>
+        <v>46786759866.204926</v>
       </c>
       <c r="F57" s="124">
-        <v>50221197787.188156</v>
+        <v>50221120758.382324</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15851,19 +15851,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>39744428727.995613</v>
+        <v>39744367768.360672</v>
       </c>
       <c r="C58" s="124">
-        <v>44149955852.618637</v>
+        <v>44149888135.827179</v>
       </c>
       <c r="D58" s="124">
-        <v>49327519805.158142</v>
+        <v>49327444147.067284</v>
       </c>
       <c r="E58" s="124">
-        <v>55430377714.392746</v>
+        <v>55430292695.795212</v>
       </c>
       <c r="F58" s="124">
-        <v>62641845623.514038</v>
+        <v>62641749544.034134</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15872,19 +15872,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>41209909131.150436</v>
+        <v>41209845923.775299</v>
       </c>
       <c r="C59" s="124">
-        <v>47688923481.465614</v>
+        <v>47688850336.638535</v>
       </c>
       <c r="D59" s="124">
-        <v>55771458671.891273</v>
+        <v>55771373130.146935</v>
       </c>
       <c r="E59" s="124">
-        <v>65910457223.561325</v>
+        <v>65910356130.715332</v>
       </c>
       <c r="F59" s="124">
-        <v>78689179142.481049</v>
+        <v>78689058449.750336</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15893,19 +15893,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>42572887225.606087</v>
+        <v>42572821927.707817</v>
       </c>
       <c r="C60" s="124">
-        <v>51174926989.015862</v>
+        <v>51174848497.389038</v>
       </c>
       <c r="D60" s="124">
-        <v>62524510676.924438</v>
+        <v>62524414777.411758</v>
       </c>
       <c r="E60" s="124">
-        <v>77640450520.661743</v>
+        <v>77640331436.461182</v>
       </c>
       <c r="F60" s="124">
-        <v>97934456158.63559</v>
+        <v>97934305947.67804</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15914,19 +15914,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>43775223506.317291</v>
+        <v>43775156364.286819</v>
       </c>
       <c r="C61" s="124">
-        <v>54439600167.583008</v>
+        <v>54439516668.630852</v>
       </c>
       <c r="D61" s="124">
-        <v>69276704501.23262</v>
+        <v>69276598245.267883</v>
       </c>
       <c r="E61" s="124">
-        <v>90221114139.569397</v>
+        <v>90220975759.264053</v>
       </c>
       <c r="F61" s="124">
-        <v>120155994217.37132</v>
+        <v>120155809923.22545</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15976,23 +15976,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>40.080865541246048</v>
+        <v>40.095629719292724</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>40.080865541246048</v>
+        <v>40.095629719292724</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>40.080865541246048</v>
+        <v>40.095629719292724</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>40.080865541246048</v>
+        <v>40.095629719292724</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>40.080865541246048</v>
+        <v>40.095629719292724</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16003,23 +16003,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>40.988689834658771</v>
+        <v>41.003784963203103</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>41.923703069500576</v>
+        <v>41.939139060365541</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>42.887098384354502</v>
+        <v>42.902885584325901</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>43.880105860538919</v>
+        <v>43.896255064832964</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>44.903993110367729</v>
+        <v>44.920515576313107</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16030,23 +16030,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>41.897350090786887</v>
+        <v>41.912776474581975</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>43.895895575391158</v>
+        <v>43.912050535880553</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>46.098290699520817</v>
+        <v>46.115248550798292</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>48.528760270653926</v>
+        <v>48.546604158050883</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>51.214206425840622</v>
+        <v>51.233029301955909</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16057,23 +16057,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>43.022069105625341</v>
+        <v>43.037905509641739</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>46.46689861068905</v>
+        <v>46.483990839260144</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>50.515409620501188</v>
+        <v>50.533977747815236</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>55.287439027252759</v>
+        <v>55.307746814453012</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>60.926327797069789</v>
+        <v>60.948691260746351</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16084,23 +16084,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>44.167977413320173</v>
+        <v>44.184231562188131</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>49.234136164892185</v>
+        <v>49.252237199520067</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>55.554141674352408</v>
+        <v>55.574546688928521</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>63.482164899400608</v>
+        <v>63.505460102365326</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>73.47427641251852</v>
+        <v>73.50121427442275</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16111,23 +16111,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.233735725939361</v>
+        <v>45.250378400699937</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>51.959959295215597</v>
+        <v>51.979054038128268</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>60.834579664654981</v>
+        <v>60.85690968123135</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>72.654240308539912</v>
+        <v>72.680879223435667</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>88.522804369101323</v>
+        <v>88.555228224112724</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16137,23 +16137,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>46.173882813368074</v>
+        <v>46.190868222013052</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>54.512716813620521</v>
+        <v>54.532742173148371</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>66.114346614648753</v>
+        <v>66.138601388595319</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>82.4914833901843</v>
+        <v>82.521708506195239</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>105.89857071605785</v>
+        <v>105.93732896701056</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>105.89857071605785</v>
+        <v>105.93732896701056</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>82.4914833901843</v>
+        <v>82.521708506195239</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16233,7 +16233,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.114346614648753</v>
+        <v>66.138601388595319</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>54.512716813620521</v>
+        <v>54.532742173148371</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16279,7 +16279,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>46.173882813368074</v>
+        <v>46.190868222013052</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0624137975483059</v>
+        <v>2.0616590492738016</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0624137975483059</v>
+        <v>2.0616590492738016</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>68.984393000522246</v>
+        <v>69.00818745145807</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3155184855.5648165</v>
+        <v>3155178968.593215</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878638341.4327517</v>
+        <v>2878633926.2040505</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.22851327690218692</v>
+        <v>0.22851323785629307</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>40.080865541246048</v>
+        <v>40.095629719292724</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.114346614648753</v>
+        <v>66.138601388595319</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>54.512716813620521</v>
+        <v>54.532742173148371</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16798,7 +16798,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>82.4914833901843</v>
+        <v>82.521708506195239</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>65.909285029447389</v>
+        <v>65.933465047481221</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>46.173882813368074</v>
+        <v>46.190868222013052</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16957,7 +16957,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>105.89857071605785</v>
+        <v>105.93732896701056</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>66.921979202973944</v>
+        <v>66.946528402184271</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>66.92016833560433</v>
+        <v>66.944716874656692</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.17848495563082309</v>
+        <v>0.17848682771924601</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0624137975483059</v>
+        <v>2.0616590492738016</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17159,7 +17159,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.025831732814293</v>
+        <v>3.7442055560320755</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>34.264053351922662</v>
+        <v>30.471792627302801</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>38.289885084736952</v>
+        <v>34.215998183334875</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.42784290690799853</v>
+        <v>0.48890556388853013</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10804060157997641</v>
+        <v>0.10815463230293121</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.3444364716874029</v>
+        <v>4.3428466084239803</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>38.727997223943255</v>
+        <v>38.742203936449229</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>43.072433695630657</v>
+        <v>43.085050544873212</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.35637836464770067</v>
+        <v>0.35642591821882319</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>5.3150403841201985</v>
+        <v>5.3130953246158432</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17329,7 +17329,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>53.124824724201986</v>
+        <v>53.144312670026373</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17341,7 +17341,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>58.439865108322181</v>
+        <v>58.457407994642217</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17351,7 +17351,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.1267463125817837</v>
+        <v>0.12680449024247054</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C4CA05-93B2-4BCF-9063-8E591D30FE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F574E58-2C7E-4812-BAAE-9E6DF59BDC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2302,10 +2302,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Result (Sell)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2338,9 +2334,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Implied Return</t>
-  </si>
-  <si>
     <t>Target Return</t>
   </si>
   <si>
@@ -2351,6 +2344,15 @@
   </si>
   <si>
     <t>@ Position Yield</t>
+  </si>
+  <si>
+    <t>Result (Target)</t>
+  </si>
+  <si>
+    <t>Base Equity Return</t>
+  </si>
+  <si>
+    <t>Entry Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -3749,29 +3751,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4061,7 +4063,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4084,7 +4086,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4116,10 +4118,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4182,13 +4184,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4212,7 +4214,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4222,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0671017599999999</v>
+        <v>1.06707424</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4235,7 +4237,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4247,7 +4249,7 @@
         <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E19" s="339">
         <v>0.2</v>
@@ -4260,7 +4262,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>34.215998183334875</v>
+        <v>34.215307295933449</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4275,7 +4277,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10815463230293121</v>
+        <v>0.1081465969032307</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4295,22 +4297,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4322,13 +4324,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4348,13 +4350,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4383,13 +4385,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4405,13 +4407,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4419,7 +4421,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177460304.59321538</v>
+        <v>177460719.3184393</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4449,7 +4451,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155623250.59321538</v>
+        <v>155623665.3184393</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4475,13 +4477,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4489,7 +4491,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008422830.2252425</v>
+        <v>-1008422933.9065485</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4497,7 +4499,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4519,22 +4521,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4542,7 +4544,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3155178968.593215</v>
+        <v>3155179383.3184395</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4555,7 +4557,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878633926.2040505</v>
+        <v>2878634237.2479687</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4568,7 +4570,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.1506442378573941E-2</v>
+        <v>4.1505376433752697E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4577,7 +4579,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8002931783848878E-2</v>
+        <v>3.8003911884992247E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4595,22 +4597,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4634,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4646,7 +4648,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4668,22 +4670,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4699,7 +4701,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>28.146556237970447</v>
+        <v>28.145833394138553</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4720,13 +4722,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4739,13 +4741,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4766,7 +4768,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.2232427060933192</v>
+        <v>0.2232369487799101</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4775,7 +4777,7 @@
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="336" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
@@ -4784,7 +4786,7 @@
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="336" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
@@ -4793,7 +4795,7 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C90" s="338">
         <f>BS!C50</f>
@@ -4824,7 +4826,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12805835971.681217</v>
+        <v>12805823882.513279</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4837,7 +4839,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>10.016978652827861</v>
+        <v>10.016710864009678</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4868,7 +4870,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1553375345877317</v>
+        <v>2.1552819495524758</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,13 +4878,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4890,7 +4892,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>40.095629719292724</v>
+        <v>40.094589258920792</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4899,11 +4901,11 @@
     </row>
     <row r="104" spans="1:6">
       <c r="B104" s="336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>1.3263016249568782</v>
+        <v>1.3262674203270228</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4921,13 +4923,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4961,7 +4963,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>105.94 HKD</v>
+        <v>105.93 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -5062,7 +5064,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>66.946528402184271</v>
+        <v>66.944798372320093</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5070,17 +5072,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5089,22 +5091,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5135,228 +5137,293 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0616590492738016</v>
+        <v>2.0617122197608295</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
         <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>3.7442055560320755</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
+        <v>3.7443021196384669</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>30.471792627302801</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>30.471005176294984</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
       <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>34.215998183334875</v>
+        <v>34.215307295933449</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="2:4">
       <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.48890556388853013</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+        <v>0.48890267611769256</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C136" s="92">
-        <f>Scenarios!C96</f>
-        <v>0.08</v>
+        <v>420</v>
+      </c>
+      <c r="C136" s="337">
+        <f>Scenarios!C90</f>
+        <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C97</f>
-        <v>5.3130953246158432</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <f>Scenarios!C91</f>
+        <v>4.3429586110702658</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C98</f>
-        <v>53.144312670026373</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+        <f>Scenarios!C92</f>
+        <v>38.741202761759311</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
       <c r="B139" s="80" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C99</f>
-        <v>58.457407994642217</v>
-      </c>
-      <c r="D139" s="101" t="str">
+        <f>Scenarios!C93</f>
+        <v>43.084161372829577</v>
+      </c>
+      <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="2:4">
       <c r="B140" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C140" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.35642256873771183</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="234" t="s">
+        <v>408</v>
+      </c>
+      <c r="C142" s="92">
+        <f>Scenarios!C96</f>
+        <v>0.08</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C143" s="240">
+        <f>Scenarios!C97</f>
+        <v>5.3132323501177732</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C144" s="240">
+        <f>Scenarios!C98</f>
+        <v>53.142939316542261</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C145" s="239">
+        <f>Scenarios!C99</f>
+        <v>58.456171666660033</v>
+      </c>
+      <c r="D145" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="B146" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12680449024247054</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9">
-      <c r="A142" s="247" t="s">
+        <v>0.1268003924434834</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="13.9">
+      <c r="A148" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B142" s="36"/>
-      <c r="C142" s="36"/>
-      <c r="D142" s="36"/>
-      <c r="E142" s="36"/>
-      <c r="F142" s="36"/>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B148" s="36"/>
+      <c r="C148" s="36"/>
+      <c r="D148" s="36"/>
+      <c r="E148" s="36"/>
+      <c r="F148" s="36"/>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6">
-      <c r="B146" s="234" t="s">
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
-      <c r="B147" s="344" t="s">
+    <row r="153" spans="1:6">
+      <c r="B153" s="344" t="s">
         <v>388</v>
       </c>
-      <c r="C147" s="344"/>
-      <c r="D147" s="344"/>
-      <c r="E147" s="344"/>
-      <c r="F147" s="344"/>
-    </row>
-    <row r="148" spans="2:6">
-      <c r="B148" s="238" t="s">
+      <c r="C153" s="344"/>
+      <c r="D153" s="344"/>
+      <c r="E153" s="344"/>
+      <c r="F153" s="344"/>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="B154" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="149" spans="2:6">
-      <c r="B149" s="238" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
-      <c r="B150" s="238" t="s">
+    <row r="156" spans="1:6">
+      <c r="B156" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="152" spans="2:6">
-      <c r="B152" s="1" t="s">
+    <row r="158" spans="1:6">
+      <c r="B158" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+    <row r="159" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6">
-      <c r="B155" s="1" t="s">
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+    <row r="162" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
+    </row>
+    <row r="163" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6">
-      <c r="B159" s="1" t="s">
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="160" spans="2:6">
-      <c r="B160" s="238" t="s">
+    <row r="166" spans="2:6">
+      <c r="B166" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="238" t="s">
+    <row r="167" spans="2:6">
+      <c r="B167" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="238" t="s">
+    <row r="168" spans="2:6">
+      <c r="B168" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5373,20 +5440,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5984,23 +6040,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0616590492738016</v>
+        <v>2.0617122197608295</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8742354993398194</v>
+        <v>1.8742838361462086</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2182530745708826</v>
+        <v>1.2182844934950356</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0308295246369008</v>
+        <v>1.0308561098804148</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.70283831225243232</v>
+        <v>0.70285643855482827</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -6014,7 +6070,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7322,23 +7378,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0616590492738016</v>
+        <v>2.0617122197608295</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8742354993398194</v>
+        <v>1.8742838361462086</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2182530745708826</v>
+        <v>1.2182844934950356</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0308295246369008</v>
+        <v>1.0308561098804148</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.70283831225243232</v>
+        <v>0.70285643855482827</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8648,7 +8704,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8675,11 +8731,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.731608627008775</v>
+        <v>22.73102239063202</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3263016249568782</v>
+        <v>1.3262674203270228</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8870,7 +8926,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12805835971.681217</v>
+        <v>12805823882.513279</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -8937,11 +8993,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2538545515.5808711</v>
+        <v>-2538551560.1648393</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2586468462.1593919</v>
+        <v>-2586474506.74336</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -8953,11 +9009,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.0823126020988791</v>
+        <v>7.0822957382959597</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.9510891623205309</v>
+        <v>6.9510729176438479</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -8970,7 +9026,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5172936924.3187838</v>
+        <v>5172949013.4867201</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9085,11 +9141,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-304546982.59693408</v>
+        <v>-304539128.48847389</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.2232427060933192</v>
+        <v>-0.2232369487799101</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9102,11 +9158,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13665130103.652336</v>
+        <v>13664764787.006706</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>10.016978652827861</v>
+        <v>10.016710864009678</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9119,11 +9175,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2940304541.7404227</v>
+        <v>2940228712.8138652</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.1553375345877317</v>
+        <v>2.1552819495524758</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9136,11 +9192,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16300887662.795826</v>
+        <v>16300454371.332098</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>11.949073481322273</v>
+        <v>11.948755864782244</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9720,28 +9776,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155623250.59321538</v>
+        <v>155623665.3184393</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155623250.59321538</v>
+        <v>155623665.3184393</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129266290.35218722</v>
+        <v>129266630.84620064</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>123018209.1709564</v>
+        <v>123018518.25361659</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68134445.443500534</v>
+        <v>68134657.689654052</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>137113499.33301559</v>
+        <v>137113851.69736946</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9775,28 +9831,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033691320.90097</v>
+        <v>4033691735.626194</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691688110.593215</v>
+        <v>4691688525.3184395</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4549934082.3521872</v>
+        <v>4549934422.8462009</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3869971417.1709566</v>
+        <v>3869971726.2536168</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025225445.4435005</v>
+        <v>3025225657.6896539</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2471173371.3330154</v>
+        <v>2471173723.6973696</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9830,7 +9886,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008422830.2252425</v>
+        <v>-1008422933.9065485</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9942,30 +9998,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878633926.2040505</v>
+        <v>2878634237.2479687</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3155178968.593215</v>
+        <v>3155179383.3184395</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071378186.3521872</v>
+        <v>3071378526.8462009</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574458724.1709566</v>
+        <v>2574459033.2536168</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701705790.4435005</v>
+        <v>1701706002.6896539</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1432947603.3330154</v>
+        <v>1432947955.6973696</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -10050,30 +10106,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878633926.2040505</v>
+        <v>2878634237.2479687</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3155178968.593215</v>
+        <v>3155179383.3184395</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071378186.3521872</v>
+        <v>3071378526.8462009</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574458724.1709566</v>
+        <v>2574459033.2536168</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701705790.4435005</v>
+        <v>1701706002.6896539</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1432947603.3330154</v>
+        <v>1432947955.6973696</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10911,23 +10967,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29620816244417508</v>
+        <v>0.29620813626063885</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30730299663531957</v>
+        <v>0.30730297363832204</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31044668771178346</v>
+        <v>0.31044666291736767</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.40417866934235924</v>
+        <v>0.4041786409856753</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.3692903661015618</v>
+        <v>0.36929031344449442</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -11049,28 +11105,28 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177460304.59321538</v>
+        <v>177460719.3184393</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>177460304.59321538</v>
+        <v>177460719.3184393</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>145696880.35218722</v>
+        <v>145697220.84620064</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132256009.1709564</v>
+        <v>132256318.25361659</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90819812.443500534</v>
+        <v>90820024.689654052</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150776181.33301559</v>
+        <v>150776533.69736946</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -11161,28 +11217,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155623250.59321538</v>
+        <v>155623665.3184393</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155623250.59321538</v>
+        <v>155623665.3184393</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129266290.35218722</v>
+        <v>129266630.84620064</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>123018209.1709564</v>
+        <v>123018518.25361659</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68134445.443500534</v>
+        <v>68134657.689654052</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>137113499.33301559</v>
+        <v>137113851.69736946</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -11804,7 +11860,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12136,7 +12192,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12248,30 +12304,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8475959678688707E-3</v>
+        <v>4.8476088863776126E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8423695705563305E-3</v>
+        <v>4.8423824751370843E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8090611503934584E-3</v>
+        <v>3.809071183655146E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8238179207288805E-3</v>
+        <v>3.8238275280530558E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2585900161456308E-3</v>
+        <v>2.2585970518973742E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.9392985286670918E-3</v>
+        <v>4.9393112220396853E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12305,30 +12361,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12564771464605093</v>
+        <v>0.12564772756455966</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14598646188584349</v>
+        <v>0.14598647479042426</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13407189997268751</v>
+        <v>0.1340719100059492</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12029167191925395</v>
+        <v>0.12029168152657813</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10028325530783633</v>
+        <v>0.10028326234358806</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.9020140660704489E-2</v>
+        <v>8.9020153354077092E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12362,7 +12418,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.1411928661512732E-2</v>
+        <v>3.1411931891139916E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12477,30 +12533,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.9668183645083527E-2</v>
+        <v>8.9668193333965085E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8176477929456524E-2</v>
+        <v>9.8176490834037303E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0503620827408426E-2</v>
+        <v>9.050363086067012E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.002279883607559E-2</v>
+        <v>8.0022808443399762E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.640987731968887E-2</v>
+        <v>5.6409884355440608E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1619687508737834E-2</v>
+        <v>5.1619700202110437E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12584,30 +12640,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.9668183645083527E-2</v>
+        <v>8.9668193333965085E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8176477929456524E-2</v>
+        <v>9.8176490834037303E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0503620827408426E-2</v>
+        <v>9.050363086067012E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.002279883607559E-2</v>
+        <v>8.0022808443399762E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.640987731968887E-2</v>
+        <v>5.6409884355440608E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1619687508737834E-2</v>
+        <v>5.1619700202110437E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12653,28 +12709,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0616590492738016</v>
+        <v>2.0617122197608295</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0616590492738016</v>
+        <v>2.0617122197608295</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8742354993398194</v>
+        <v>1.8742838361462086</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2182530745708826</v>
+        <v>1.2182844934950356</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0308295246369008</v>
+        <v>1.0308561098804148</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.70283831225243232</v>
+        <v>0.70285643855482827</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12709,28 +12765,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2812508652.9704537</v>
+        <v>2812581187.9780736</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2812508652.9704537</v>
+        <v>2812581187.9780736</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2556826048.1549578</v>
+        <v>2556891989.0709763</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1661936931.3007226</v>
+        <v>1661979792.8961346</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1406254326.4852269</v>
+        <v>1406290593.9890368</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>958809768.05810916</v>
+        <v>958834495.9016161</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12764,28 +12820,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.97702893979270444</v>
+        <v>0.9770540319380614</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.89139433324267314</v>
+        <v>0.89141720526202217</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.8324686486074343</v>
+        <v>0.83249002580495424</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.64554809743003738</v>
+        <v>0.6455646687046771</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82637923334487062</v>
+        <v>0.82640044271237556</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66911711623504688</v>
+        <v>0.66913420832160109</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12819,28 +12875,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8002931783848878E-2</v>
+        <v>3.8003911884992247E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8002931783848878E-2</v>
+        <v>3.8003911884992247E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.4548119803498978E-2</v>
+        <v>3.4549010804538406E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.2456277872274333E-2</v>
+        <v>2.2456857022949965E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.9001465891924439E-2</v>
+        <v>1.9001955942496124E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2955544926312117E-2</v>
+        <v>1.2955879051701903E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12956,26 +13012,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14024734257304416</v>
+        <v>-0.14024733017577828</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1155182838988438E-2</v>
+        <v>3.1155196822279629E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17570224476704266</v>
+        <v>0.17570223885093661</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27923405609317009</v>
+        <v>0.27923406851212884</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.22420607171386564</v>
+        <v>0.22420598304327699</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13567,23 +13623,23 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6337143418201361</v>
+        <v>1.6337141270803495</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90433902029461877</v>
+        <v>0.90433892003930338</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8950668255794594</v>
+        <v>1.8950665980628092</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5512081400540088</v>
+        <v>3.5512076971277531</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.4568063413333543</v>
+        <v>3.4568054912987605</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13675,28 +13731,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12564771464605093</v>
+        <v>0.12564772756455966</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14598646188584349</v>
+        <v>0.14598647479042426</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13407189997268751</v>
+        <v>0.1340719100059492</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12029167191925395</v>
+        <v>0.12029168152657813</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10028325530783633</v>
+        <v>0.10028326234358806</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.9020140660704489E-2</v>
+        <v>8.9020153354077092E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13961,30 +14017,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2517244990376364</v>
+        <v>2.2516666715310838</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4680435111102197</v>
+        <v>2.4679801859482113</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.4024928786755262</v>
+        <v>2.4024311859666461</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0137926285823964</v>
+        <v>2.0137409356810756</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3311079896667009</v>
+        <v>1.3310738271020619</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1208800100945866</v>
+        <v>1.1208513788007279</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14018,30 +14074,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1506442378573941E-2</v>
+        <v>4.1505376433752697E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.5493889605718332E-2</v>
+        <v>4.5492722321626017E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.4285583017060391E-2</v>
+        <v>4.428444582426997E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.7120601448523437E-2</v>
+        <v>3.7119648583982957E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.4536552804916144E-2</v>
+        <v>2.453592308022234E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.0661382674554592E-2</v>
+        <v>2.0660854908769177E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14861,7 +14917,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878633926.2040505</v>
+        <v>2878634237.2479687</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14893,7 +14949,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35982924077.550629</v>
+        <v>35982927965.599609</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14927,7 +14983,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12805835971.681217</v>
+        <v>12805823882.513279</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14959,7 +15015,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51258775241.731842</v>
+        <v>51258767040.612885</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14973,7 +15029,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0671017599999999</v>
+        <v>1.06707424</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14987,7 +15043,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>40.095629719292724</v>
+        <v>40.094589258920792</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15040,7 +15096,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>66.944716874656692</v>
+        <v>66.942986891315115</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15075,7 +15131,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3054708011.7114477</v>
+        <v>3054708341.7806311</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15087,7 +15143,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2828433344.1772661</v>
+        <v>2828433649.7968802</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15097,7 +15153,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3241551817.9898872</v>
+        <v>3241552168.2480321</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15109,7 +15165,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2779108211.5825505</v>
+        <v>2779108511.8724551</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15119,7 +15175,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3439824084.1442857</v>
+        <v>3439824455.8262668</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15131,7 +15187,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2730643261.4314108</v>
+        <v>2730643556.4845505</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15141,7 +15197,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3650223841.6155987</v>
+        <v>3650224236.0318236</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15153,7 +15209,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2683023492.9768176</v>
+        <v>2683023782.8845177</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15163,7 +15219,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3873492878.6957259</v>
+        <v>3873493297.2367539</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15175,7 +15231,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2636234167.0702124</v>
+        <v>2636234451.9222035</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15185,7 +15241,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4110418355.7865639</v>
+        <v>4110418799.9280086</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15197,7 +15253,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2590260801.599483</v>
+        <v>2590261081.4839315</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15207,7 +15263,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4361835580.6235914</v>
+        <v>4361836051.931324</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15219,7 +15275,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2545089167.0064983</v>
+        <v>2545089442.0100336</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15229,7 +15285,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4628630953.2483654</v>
+        <v>4628631453.3840351</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15241,7 +15297,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2500705281.8828111</v>
+        <v>2500705552.0905514</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15251,7 +15307,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4911745091.1127539</v>
+        <v>4911745621.8396463</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15263,7 +15319,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2457095408.6421695</v>
+        <v>2457095674.1377492</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15273,7 +15329,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5212176145.332818</v>
+        <v>5212176708.5220718</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15285,7 +15341,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2414246049.2684922</v>
+        <v>2414246310.1340871</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15295,7 +15351,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>5530983319.7841816</v>
+        <v>5530983917.4213829</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15307,7 +15363,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2372143941.1380014</v>
+        <v>2372144197.4543533</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15317,7 +15373,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5869290605.4458447</v>
+        <v>5869291239.638032</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15329,7 +15385,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2330776052.9142051</v>
+        <v>2330776304.7606483</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15339,7 +15395,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>6228290743.1583118</v>
+        <v>6228291416.1414022</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15351,7 +15407,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2290129580.5144734</v>
+        <v>2290129827.9689593</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15361,7 +15417,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>6609249428.7671795</v>
+        <v>6609250142.9138517</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15373,7 +15429,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2250191943.1469522</v>
+        <v>2250192186.2860718</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15383,7 +15439,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>7013509775.477891</v>
+        <v>7013510533.3059502</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15395,7 +15451,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2210950779.4165864</v>
+        <v>2210951018.3155956</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15405,7 +15461,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>7442497049.1542196</v>
+        <v>7442497853.335474</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15417,7 +15473,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2172393943.4990568</v>
+        <v>2172394178.2318988</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15427,7 +15483,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7897723693.2552824</v>
+        <v>7897724546.6249657</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15439,7 +15495,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2134509501.3814306</v>
+        <v>2134509732.0207603</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15449,7 +15505,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>8380794661.1270962</v>
+        <v>8380795566.6938601</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15461,7 +15517,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2097285727.1683793</v>
+        <v>2097285953.7855825</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15471,7 +15527,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8893413074.4482727</v>
+        <v>8893414035.4047966</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15483,7 +15539,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2060711099.4528103</v>
+        <v>2060711322.1180298</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15493,7 +15549,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>9437386227.7793407</v>
+        <v>9437387247.5135841</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15505,7 +15561,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2024774297.7497888</v>
+        <v>2024774516.5319426</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15515,7 +15571,7 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>10014631960.385414</v>
+        <v>10014633042.492567</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
@@ -15527,7 +15583,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>1989464198.992651</v>
+        <v>1989464413.9594564</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15537,7 +15593,7 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>10627185417.796804</v>
+        <v>10627186566.091959</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
@@ -15549,7 +15605,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>1954769874.0902207</v>
+        <v>1954770085.3082137</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15559,7 +15615,7 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>11277206226.94622</v>
+        <v>11277207445.477823</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
@@ -15571,7 +15627,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>1920680584.5440667</v>
+        <v>1920680792.0786228</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15581,7 +15637,7 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>11966986110.179323</v>
+        <v>11966987403.243446</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
@@ -15593,7 +15649,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>1887185779.1247468</v>
+        <v>1887185983.0401022</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15603,7 +15659,7 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>12698956964.982693</v>
+        <v>12698958337.138178</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
@@ -15615,7 +15671,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>1854275090.6060233</v>
+        <v>1854275290.9652927</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15625,7 +15681,7 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>13475699437.915192</v>
+        <v>13475700893.999731</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
@@ -15637,7 +15693,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>1821938332.5560207</v>
+        <v>1821938529.4212186</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15647,7 +15703,7 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>14299952022.971148</v>
+        <v>14299953568.118332</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
@@ -15659,7 +15715,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>1790165496.1843503</v>
+        <v>1790165689.61641</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15669,7 +15725,7 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>15174620716.452604</v>
+        <v>15174622356.110027</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
@@ -15681,7 +15737,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>1758946747.2442143</v>
+        <v>1758946937.3030069</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15691,7 +15747,7 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>16102789262.390047</v>
+        <v>16102791002.338507</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
@@ -15703,7 +15759,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>1728272422.9885366</v>
+        <v>1728272609.7328882</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15713,7 +15769,7 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>17087730024.632938</v>
+        <v>17087731871.006823</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
@@ -15725,7 +15781,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>1698133029.1791706</v>
+        <v>1698133212.6668823</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15735,7 +15791,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38183850146.393097</v>
+        <v>38183854272.257889</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15747,7 +15803,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3794609174.0298834</v>
+        <v>3794609584.0473208</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15758,7 +15814,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>70307146781.55928</v>
+        <v>70307154378.430206</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15779,7 +15835,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>70307146781.55928</v>
+        <v>70307154378.430206</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15809,19 +15865,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37143921569.249916</v>
+        <v>37143925582.747704</v>
       </c>
       <c r="C56" s="124">
-        <v>38339690429.186615</v>
+        <v>38339694571.890358</v>
       </c>
       <c r="D56" s="124">
-        <v>39571756537.326935</v>
+        <v>39571760813.15863</v>
       </c>
       <c r="E56" s="124">
-        <v>40841693018.928253</v>
+        <v>40841697431.979904</v>
       </c>
       <c r="F56" s="124">
-        <v>42151120996.852715</v>
+        <v>42151125551.391495</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15830,19 +15886,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>38305988156.172546</v>
+        <v>38305992295.234665</v>
       </c>
       <c r="C57" s="124">
-        <v>40861886154.836929</v>
+        <v>40861890570.070511</v>
       </c>
       <c r="D57" s="124">
-        <v>43678483191.729401</v>
+        <v>43678487911.303642</v>
       </c>
       <c r="E57" s="124">
-        <v>46786759866.204926</v>
+        <v>46786764921.636581</v>
       </c>
       <c r="F57" s="124">
-        <v>50221120758.382324</v>
+        <v>50221126184.905663</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15851,19 +15907,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>39744367768.360672</v>
+        <v>39744372062.84346</v>
       </c>
       <c r="C58" s="124">
-        <v>44149888135.827179</v>
+        <v>44149892906.337967</v>
       </c>
       <c r="D58" s="124">
-        <v>49327444147.067284</v>
+        <v>49327449477.026527</v>
       </c>
       <c r="E58" s="124">
-        <v>55430292695.795212</v>
+        <v>55430298685.183197</v>
       </c>
       <c r="F58" s="124">
-        <v>62641749544.034134</v>
+        <v>62641756312.63887</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15872,19 +15928,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>41209845923.775299</v>
+        <v>41209850376.606827</v>
       </c>
       <c r="C59" s="124">
-        <v>47688850336.638535</v>
+        <v>47688855489.543419</v>
       </c>
       <c r="D59" s="124">
-        <v>55771373130.146935</v>
+        <v>55771379156.389549</v>
       </c>
       <c r="E59" s="124">
-        <v>65910356130.715332</v>
+        <v>65910363252.501587</v>
       </c>
       <c r="F59" s="124">
-        <v>78689058449.750336</v>
+        <v>78689066952.308716</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15893,19 +15949,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>42572821927.707817</v>
+        <v>42572826527.812469</v>
       </c>
       <c r="C60" s="124">
-        <v>51174848497.389038</v>
+        <v>51174854026.965141</v>
       </c>
       <c r="D60" s="124">
-        <v>62524414777.411758</v>
+        <v>62524421533.338188</v>
       </c>
       <c r="E60" s="124">
-        <v>77640331436.461182</v>
+        <v>77640339825.70192</v>
       </c>
       <c r="F60" s="124">
-        <v>97934305947.67804</v>
+        <v>97934316529.735733</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15914,19 +15970,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>43775156364.286819</v>
+        <v>43775161094.306854</v>
       </c>
       <c r="C61" s="124">
-        <v>54439516668.630852</v>
+        <v>54439522550.962891</v>
       </c>
       <c r="D61" s="124">
-        <v>69276598245.267883</v>
+        <v>69276605730.7854</v>
       </c>
       <c r="E61" s="124">
-        <v>90220975759.264053</v>
+        <v>90220985507.876266</v>
       </c>
       <c r="F61" s="124">
-        <v>120155809923.22545</v>
+        <v>120155822906.37471</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15976,23 +16032,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>40.095629719292724</v>
+        <v>40.094589258920792</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>40.095629719292724</v>
+        <v>40.094589258920792</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>40.095629719292724</v>
+        <v>40.094589258920792</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>40.095629719292724</v>
+        <v>40.094589258920792</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>40.095629719292724</v>
+        <v>40.094589258920792</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16003,23 +16059,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>41.003784963203103</v>
+        <v>41.002721180105254</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>41.939139060365541</v>
+        <v>41.938051256036331</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>42.902885584325901</v>
+        <v>42.901773029607163</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>43.896255064832964</v>
+        <v>43.895116998964816</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>44.920515576313107</v>
+        <v>44.919351205969669</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16030,23 +16086,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>41.912776474581975</v>
+        <v>41.911689347281673</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>43.912050535880553</v>
+        <v>43.910912064362115</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>46.115248550798292</v>
+        <v>46.114053498002825</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>48.546604158050883</v>
+        <v>48.545346664565017</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>51.233029301955909</v>
+        <v>51.231702817229042</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16057,23 +16113,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>43.037905509641739</v>
+        <v>43.036789487418147</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>46.483990839260144</v>
+        <v>46.482786316635185</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>50.533977747815236</v>
+        <v>50.532669215732369</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>55.307746814453012</v>
+        <v>55.306315685150956</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>60.948691260746351</v>
+        <v>60.947115263920722</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16084,23 +16140,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>44.184231562188131</v>
+        <v>44.183086100671517</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>49.252237199520067</v>
+        <v>49.250961584368191</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>55.574546688928521</v>
+        <v>55.573108707823991</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>63.505460102365326</v>
+        <v>63.503818444058048</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>73.50121427442275</v>
+        <v>73.499315910847926</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16111,23 +16167,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.250378400699937</v>
+        <v>45.249205559007244</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>51.979054038128268</v>
+        <v>51.977708394418876</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>60.85690968123135</v>
+        <v>60.855336041488009</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>72.680879223435667</v>
+        <v>72.679001927238588</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>88.555228224112724</v>
+        <v>88.552943251922756</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16137,23 +16193,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>46.190868222013052</v>
+        <v>46.18967122719625</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>54.532742173148371</v>
+        <v>54.531330947074245</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>66.138601388595319</v>
+        <v>66.136892107452724</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>82.521708506195239</v>
+        <v>82.519578483423444</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>105.93732896701056</v>
+        <v>105.9345975976059</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16188,7 +16244,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>105.93732896701056</v>
+        <v>105.9345975976059</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16210,7 +16266,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>82.521708506195239</v>
+        <v>82.519578483423444</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16233,7 +16289,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.138601388595319</v>
+        <v>66.136892107452724</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16256,7 +16312,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>54.532742173148371</v>
+        <v>54.531330947074245</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16279,7 +16335,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>46.190868222013052</v>
+        <v>46.18967122719625</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16400,7 +16456,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0616590492738016</v>
+        <v>2.0617122197608295</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16409,7 +16465,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0616590492738016</v>
+        <v>2.0617122197608295</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16429,7 +16485,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>69.00818745145807</v>
+        <v>69.006510592080929</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16463,7 +16519,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3155178968.593215</v>
+        <v>3155179383.3184395</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16485,7 +16541,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878633926.2040505</v>
+        <v>2878634237.2479687</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16569,7 +16625,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.22851323785629307</v>
+        <v>0.22851324060700184</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16635,7 +16691,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>40.095629719292724</v>
+        <v>40.094589258920792</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16682,7 +16738,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.138601388595319</v>
+        <v>66.136892107452724</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16740,7 +16796,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>54.532742173148371</v>
+        <v>54.531330947074245</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16798,7 +16854,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>82.521708506195239</v>
+        <v>82.519578483423444</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16825,7 +16881,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>65.933465047481221</v>
+        <v>65.931761034533324</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16899,7 +16955,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>46.190868222013052</v>
+        <v>46.18967122719625</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16957,7 +17013,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>105.93732896701056</v>
+        <v>105.9345975976059</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16983,7 +17039,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>66.946528402184271</v>
+        <v>66.944798372320093</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17045,7 +17101,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>66.944716874656692</v>
+        <v>66.942986891315115</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17108,7 +17164,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.17848682771924601</v>
+        <v>0.17848669583450025</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17141,7 +17197,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0616590492738016</v>
+        <v>2.0617122197608295</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17168,7 +17224,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.7442055560320755</v>
+        <v>3.7443021196384669</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17180,7 +17236,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>30.471792627302801</v>
+        <v>30.471005176294984</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17190,7 +17246,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>34.215998183334875</v>
+        <v>34.215307295933449</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17201,7 +17257,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.48890556388853013</v>
+        <v>0.48890267611769256</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17231,7 +17287,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10815463230293121</v>
+        <v>0.1081465969032307</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17239,12 +17295,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>
@@ -17257,7 +17313,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.3428466084239803</v>
+        <v>4.3429586110702658</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17269,7 +17325,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>38.742203936449229</v>
+        <v>38.741202761759311</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17279,7 +17335,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>43.085050544873212</v>
+        <v>43.084161372829577</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17346,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.35642591821882319</v>
+        <v>0.35642256873771183</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17302,7 +17358,7 @@
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!C67</f>
@@ -17317,7 +17373,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>5.3130953246158432</v>
+        <v>5.3132323501177732</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17329,7 +17385,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>53.144312670026373</v>
+        <v>53.142939316542261</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17341,7 +17397,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>58.457407994642217</v>
+        <v>58.456171666660033</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17351,7 +17407,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.12680449024247054</v>
+        <v>0.1268003924434834</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F574E58-2C7E-4812-BAAE-9E6DF59BDC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87122896-5D13-4648-9DAF-A381949F3DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3751,29 +3751,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4129,7 +4129,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>54.25</v>
+        <v>56.45</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>74007.675749000002</v>
+        <v>77008.908682600013</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4184,13 +4184,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1081465969032307</v>
+        <v>9.3068045296727409E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4297,22 +4297,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4324,13 +4324,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4350,13 +4350,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4385,13 +4385,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4407,13 +4407,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4477,13 +4477,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4499,7 +4499,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4521,22 +4521,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.1505376433752697E-2</v>
+        <v>3.9887806404447897E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8003911884992247E-2</v>
+        <v>3.652280283012984E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4597,22 +4597,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4670,22 +4670,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4722,13 +4722,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4741,13 +4741,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4878,13 +4878,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4923,13 +4923,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5072,13 +5072,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5091,22 +5091,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5317,13 +5317,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5360,13 +5360,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5374,22 +5374,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5413,17 +5413,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5440,6 +5429,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12875,28 +12875,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8003911884992247E-2</v>
+        <v>3.652280283012984E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8003911884992247E-2</v>
+        <v>3.652280283012984E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.4549010804538406E-2</v>
+        <v>3.3202548027390762E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.2456857022949965E-2</v>
+        <v>2.1581656217803995E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.9001955942496124E-2</v>
+        <v>1.826140141506492E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2955879051701903E-2</v>
+        <v>1.2450955510271536E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14074,30 +14074,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1505376433752697E-2</v>
+        <v>3.9887806404447897E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.5492722321626017E-2</v>
+        <v>4.3719755286947937E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.428444582426997E-2</v>
+        <v>4.2558568396220478E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.7119648583982957E-2</v>
+        <v>3.567300151782242E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.453592308022234E-2</v>
+        <v>2.3579695785687544E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.0660854908769177E-2</v>
+        <v>1.9855648871580655E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14131,23 +14131,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0693389442928063E-2</v>
+        <v>5.8328013769332991E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8753350649020396E-2</v>
+        <v>5.6463583218943424E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1409822555485533E-2</v>
+        <v>4.9406251082995394E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3998731713230418E-2</v>
+        <v>4.2283989290394154E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1442263001097454E-2</v>
+        <v>3.0216878083428465E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-54.25</v>
+        <v>-56.45</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>54.25</v>
+        <v>56.45</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>54.25</v>
+        <v>56.45</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1081465969032307</v>
+        <v>9.3068045296727409E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87122896-5D13-4648-9DAF-A381949F3DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD4B71C-B651-43B2-99DB-D292C5D05799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2340,12 +2340,6 @@
     <t>in contrast to a position yield of</t>
   </si>
   <si>
-    <t>Position Price Output</t>
-  </si>
-  <si>
-    <t>@ Position Yield</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2353,6 +2347,15 @@
   </si>
   <si>
     <t>Entry Yield</t>
+  </si>
+  <si>
+    <t>Result (Entry)</t>
+  </si>
+  <si>
+    <t>Entry Price Output</t>
+  </si>
+  <si>
+    <t>@ Entry Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -3751,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4086,7 +4089,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4118,10 +4121,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4184,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4214,7 +4217,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4237,7 +4240,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4297,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4324,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4350,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4385,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4407,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4477,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4499,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4521,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4597,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4636,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4648,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4670,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4722,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4741,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4878,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4923,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5072,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5091,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5146,7 +5149,7 @@
     </row>
     <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
@@ -5200,14 +5203,14 @@
     </row>
     <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C136" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="2:4">
@@ -5261,7 +5264,7 @@
         <v>0.08</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="2:4">
@@ -5317,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5360,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5374,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5413,6 +5416,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5429,17 +5443,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6070,7 +6073,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -11860,7 +11863,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12192,7 +12195,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -17295,12 +17298,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD4B71C-B651-43B2-99DB-D292C5D05799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E38AD8F-1BC0-4B52-A997-DE74F78A3862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>56.45</v>
+        <v>54.65</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>77008.908682600013</v>
+        <v>74553.354464199991</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4227,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.06707424</v>
+        <v>1.0739449931617173</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>34.215307295933449</v>
+        <v>34.387950625486518</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.3068045296727409E-2</v>
+        <v>0.10734290687447179</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177460719.3184393</v>
+        <v>177357837.13662779</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155623665.3184393</v>
+        <v>155520783.13662779</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008422933.9065485</v>
+        <v>-1008397213.3610955</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3155179383.3184395</v>
+        <v>3155076501.1366282</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878634237.2479687</v>
+        <v>2878557075.6116099</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.9887806404447897E-2</v>
+        <v>4.1465766109394828E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.652280283012984E-2</v>
+        <v>3.748439251511098E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>28.145833394138553</v>
+        <v>28.326301473480335</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.2232369487799101</v>
+        <v>0.22467434265012642</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12805823882.513279</v>
+        <v>12808822880.167248</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>10.016710864009678</v>
+        <v>10.083568090361801</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1552819495524758</v>
+        <v>2.1691595315558421</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>40.094589258920792</v>
+        <v>40.354354752747859</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>1.3262674203270228</v>
+        <v>1.3348070848882203</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>105.93 HKD</v>
+        <v>106.62 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>82.52 HKD</v>
+        <v>83.05 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>66.14 HKD</v>
+        <v>66.56 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>54.53 HKD</v>
+        <v>54.88 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>46.19 HKD</v>
+        <v>46.49 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>66.944798372320093</v>
+        <v>67.376724540900142</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0617122197608295</v>
+        <v>2.0485220509508149</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>3.7443021196384669</v>
+        <v>3.7203472841573748</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>30.471005176294984</v>
+        <v>30.667603341329144</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>34.215307295933449</v>
+        <v>34.387950625486518</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.48890267611769256</v>
+        <v>0.48961676513954355</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>4.3429586110702658</v>
+        <v>4.3151737647343547</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>38.741202761759311</v>
+        <v>38.991160035243141</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>43.084161372829577</v>
+        <v>43.306333799977494</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35642256873771183</v>
+        <v>0.35725082964386368</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>5.3132323501177732</v>
+        <v>5.2792400058161935</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>53.142939316542261</v>
+        <v>53.485816234901414</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>58.456171666660033</v>
+        <v>58.765056240717605</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.1268003924434834</v>
+        <v>0.12781369766580053</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6043,23 +6043,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0617122197608295</v>
+        <v>2.0485220509508149</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8742838361462086</v>
+        <v>1.8622927735916499</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2182844934950356</v>
+        <v>1.2104903028345724</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0308561098804148</v>
+        <v>1.0242610254754074</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.70285643855482827</v>
+        <v>0.69835979009686866</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7381,23 +7381,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0617122197608295</v>
+        <v>2.0485220509508149</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8742838361462086</v>
+        <v>1.8622927735916499</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2182844934950356</v>
+        <v>1.2104903028345724</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0308561098804148</v>
+        <v>1.0242610254754074</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.70285643855482827</v>
+        <v>0.69835979009686866</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8734,11 +8734,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.73102239063202</v>
+        <v>22.877384506879434</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3262674203270228</v>
+        <v>1.3348070848882203</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12805823882.513279</v>
+        <v>12808822880.167248</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -8996,11 +8996,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2538551560.1648393</v>
+        <v>-2537052061.3378563</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2586474506.74336</v>
+        <v>-2584975007.9163766</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9012,11 +9012,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.0822957382959597</v>
+        <v>7.0864816571873206</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.9510729176438479</v>
+        <v>6.9551051135661925</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9029,7 +9029,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5172949013.4867201</v>
+        <v>5169950015.8327532</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9144,11 +9144,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-304539128.48847389</v>
+        <v>-306500016.58931386</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.2232369487799101</v>
+        <v>-0.22467434265012642</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9161,11 +9161,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13664764787.006706</v>
+        <v>13755971200.450863</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>10.016710864009678</v>
+        <v>10.083568090361801</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9178,11 +9178,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2940228712.8138652</v>
+        <v>2959160465.6080642</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.1552819495524758</v>
+        <v>2.1691595315558421</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9195,11 +9195,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16300454371.332098</v>
+        <v>16408631649.469614</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>11.948755864782244</v>
+        <v>12.028053279267516</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9779,28 +9779,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155623665.3184393</v>
+        <v>155520783.13662779</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155623665.3184393</v>
+        <v>155520783.13662779</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129266630.84620064</v>
+        <v>129182163.43266767</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>123018518.25361659</v>
+        <v>122941843.15259959</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68134657.689654052</v>
+        <v>68082005.123338923</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>137113851.69736946</v>
+        <v>137026439.571394</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9834,28 +9834,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033691735.626194</v>
+        <v>4033588853.4443822</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691688525.3184395</v>
+        <v>4691585643.1366282</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4549934422.8462009</v>
+        <v>4549849955.4326677</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3869971726.2536168</v>
+        <v>3869895051.1525998</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025225657.6896539</v>
+        <v>3025173005.1233387</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2471173723.6973696</v>
+        <v>2471086311.571394</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008422933.9065485</v>
+        <v>-1008397213.3610955</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10001,30 +10001,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878634237.2479687</v>
+        <v>2878557075.6116099</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3155179383.3184395</v>
+        <v>3155076501.1366282</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071378526.8462009</v>
+        <v>3071294059.4326677</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574459033.2536168</v>
+        <v>2574382358.1525998</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701706002.6896539</v>
+        <v>1701653350.1233387</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1432947955.6973696</v>
+        <v>1432860543.571394</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -10109,30 +10109,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878634237.2479687</v>
+        <v>2878557075.6116099</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3155179383.3184395</v>
+        <v>3155076501.1366282</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071378526.8462009</v>
+        <v>3071294059.4326677</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574459033.2536168</v>
+        <v>2574382358.1525998</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701706002.6896539</v>
+        <v>1701653350.1233387</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1432947955.6973696</v>
+        <v>1432860543.571394</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10970,23 +10970,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29620813626063885</v>
+        <v>0.29621463183412866</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30730297363832204</v>
+        <v>0.30730867868081979</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31044666291736767</v>
+        <v>0.31045281386692181</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.4041786409856753</v>
+        <v>0.40418567563878821</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36929031344449442</v>
+        <v>0.36930337670790581</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -11108,28 +11108,28 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177460719.3184393</v>
+        <v>177357837.13662779</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>177460719.3184393</v>
+        <v>177357837.13662779</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>145697220.84620064</v>
+        <v>145612753.43266767</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132256318.25361659</v>
+        <v>132179643.15259959</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90820024.689654052</v>
+        <v>90767372.123338923</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150776533.69736946</v>
+        <v>150689121.571394</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -11220,28 +11220,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155623665.3184393</v>
+        <v>155520783.13662779</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155623665.3184393</v>
+        <v>155520783.13662779</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129266630.84620064</v>
+        <v>129182163.43266767</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>123018518.25361659</v>
+        <v>122941843.15259959</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68134657.689654052</v>
+        <v>68082005.123338923</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>137113851.69736946</v>
+        <v>137026439.571394</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -12307,30 +12307,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8476088863776126E-3</v>
+        <v>4.8444041515592999E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8423824751370843E-3</v>
+        <v>4.8391811954783094E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.809071183655146E-3</v>
+        <v>3.8065822010867898E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8238275280530558E-3</v>
+        <v>3.8214442091336993E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2585970518973742E-3</v>
+        <v>2.2568516709842437E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.9393112220396853E-3</v>
+        <v>4.9361623374490462E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12364,30 +12364,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12564772756455966</v>
+        <v>0.12564452282974134</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14598647479042426</v>
+        <v>0.14598327351076551</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1340719100059492</v>
+        <v>0.13406942102338085</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12029168152657813</v>
+        <v>0.12028929820765877</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10028326234358806</v>
+        <v>0.10028151696267493</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.9020153354077092E-2</v>
+        <v>8.901700446948646E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.1411931891139916E-2</v>
+        <v>3.1411130707435335E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12536,30 +12536,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.9668193333965085E-2</v>
+        <v>8.9665789782851349E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8176490834037303E-2</v>
+        <v>9.8173289554378526E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.050363086067012E-2</v>
+        <v>9.0501141878101751E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.0022808443399762E-2</v>
+        <v>8.0020425124480404E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.6409884355440608E-2</v>
+        <v>5.6408138974527476E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1619700202110437E-2</v>
+        <v>5.1616551317519799E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12643,30 +12643,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.9668193333965085E-2</v>
+        <v>8.9665789782851349E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8176490834037303E-2</v>
+        <v>9.8173289554378526E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.050363086067012E-2</v>
+        <v>9.0501141878101751E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.0022808443399762E-2</v>
+        <v>8.0020425124480404E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.6409884355440608E-2</v>
+        <v>5.6408138974527476E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1619700202110437E-2</v>
+        <v>5.1616551317519799E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12712,28 +12712,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0617122197608295</v>
+        <v>2.0485220509508149</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0617122197608295</v>
+        <v>2.0485220509508149</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8742838361462086</v>
+        <v>1.8622927735916499</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2182844934950356</v>
+        <v>1.2104903028345724</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0308561098804148</v>
+        <v>1.0242610254754074</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.70285643855482827</v>
+        <v>0.69835979009686866</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12768,28 +12768,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2812581187.9780736</v>
+        <v>2794587202.0542741</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2812581187.9780736</v>
+        <v>2794587202.0542741</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2556891989.0709763</v>
+        <v>2540533820.0493402</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1661979792.8961346</v>
+        <v>1651346983.0320709</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1406290593.9890368</v>
+        <v>1397293601.027137</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>958834495.9016161</v>
+        <v>952700182.51850247</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12823,28 +12823,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.9770540319380614</v>
+        <v>0.9708291788727188</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.89141720526202217</v>
+        <v>0.88574308770247356</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.83249002580495424</v>
+        <v>0.82718677237914162</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.6455646687046771</v>
+        <v>0.64145365889513495</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82640044271237556</v>
+        <v>0.82113880651770754</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66913420832160109</v>
+        <v>0.6648938633929472</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12878,28 +12878,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.652280283012984E-2</v>
+        <v>3.748439251511098E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.652280283012984E-2</v>
+        <v>3.748439251511098E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.3202548027390762E-2</v>
+        <v>3.4076720468282709E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.1581656217803995E-2</v>
+        <v>2.2149868304383757E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.826140141506492E-2</v>
+        <v>1.874219625755549E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2450955510271536E-2</v>
+        <v>1.2778770175606014E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13015,26 +13015,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14024733017577828</v>
+        <v>-0.14025040567144642</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1155196822279629E-2</v>
+        <v>3.1151727879448643E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17570223885093661</v>
+        <v>0.17570370650686051</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27923406851212884</v>
+        <v>0.27923098764886056</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.22420598304327699</v>
+        <v>0.22422798060808891</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13626,23 +13626,23 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6337141270803495</v>
+        <v>1.6337673999800049</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90433892003930338</v>
+        <v>0.90436379136977685</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8950665980628092</v>
+        <v>1.8951230405032182</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5512076971277531</v>
+        <v>3.5513175786137552</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.4568054912987605</v>
+        <v>3.4570163748480591</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13734,28 +13734,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12564772756455966</v>
+        <v>0.12564452282974134</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14598647479042426</v>
+        <v>0.14598327351076551</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.1340719100059492</v>
+        <v>0.13406942102338085</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12029168152657813</v>
+        <v>0.12028929820765877</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10028326234358806</v>
+        <v>0.10028151696267493</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.9020153354077092E-2</v>
+        <v>8.901700446948646E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -14020,30 +14020,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2516666715310838</v>
+        <v>2.2661041178784269</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4679801859482113</v>
+        <v>2.483790198923904</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.4024311859666461</v>
+        <v>2.4178336341714357</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0137409356810756</v>
+        <v>2.0266467919742963</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3310738271020619</v>
+        <v>1.3396029894932009</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1208513788007279</v>
+        <v>1.1279995820276592</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14077,30 +14077,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.9887806404447897E-2</v>
+        <v>4.1465766109394828E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.3719755286947937E-2</v>
+        <v>4.5449042981224229E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.2558568396220478E-2</v>
+        <v>4.4242152500849695E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.567300151782242E-2</v>
+        <v>3.7084113302365898E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.3579695785687544E-2</v>
+        <v>2.4512406029152809E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>1.9855648871580655E-2</v>
+        <v>2.0640431510112703E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14134,23 +14134,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8328013769332991E-2</v>
+        <v>6.0249156034379643E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6463583218943424E-2</v>
+        <v>5.8323316975468553E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9406251082995394E-2</v>
+        <v>5.1033538401374021E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2283989290394154E-2</v>
+        <v>4.3676691590901193E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0216878083428465E-2</v>
+        <v>3.1212127498802141E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878634237.2479687</v>
+        <v>2878557075.6116099</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35982927965.599609</v>
+        <v>35981963445.145126</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12805823882.513279</v>
+        <v>12808822880.167248</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51258767040.612885</v>
+        <v>51260801517.812378</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.06707424</v>
+        <v>1.0739449931617173</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15046,7 +15046,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>40.094589258920792</v>
+        <v>40.354354752747859</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>66.942986891315115</v>
+        <v>67.374901444872336</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3054708341.7806311</v>
+        <v>3054626460.4873424</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2828433649.7968802</v>
+        <v>2828357833.7845759</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3241552168.2480321</v>
+        <v>3241465278.6159945</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2779108511.8724551</v>
+        <v>2779034018.0178275</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15178,7 +15178,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3439824455.8262668</v>
+        <v>3439732251.5161934</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2730643556.4845505</v>
+        <v>2730570361.7304535</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3650224236.0318236</v>
+        <v>3650126391.9669247</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15212,7 +15212,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2683023782.8845177</v>
+        <v>2682951864.5758977</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3873493297.2367539</v>
+        <v>3873389468.4566426</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2636234451.9222035</v>
+        <v>2636163787.7990913</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4110418799.9280086</v>
+        <v>4110308620.3725033</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2590261081.4839315</v>
+        <v>2590191649.6745486</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4361836051.931324</v>
+        <v>4361719133.1498613</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2545089442.0100336</v>
+        <v>2545021221.0240245</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4628631453.3840351</v>
+        <v>4628507383.1661434</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2500705552.0905514</v>
+        <v>2500638520.8123312</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4911745621.8396463</v>
+        <v>4911613962.761652</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2457095674.1377492</v>
+        <v>2457029811.8199692</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5212176708.5220718</v>
+        <v>5212036996.4049091</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2414246310.1340871</v>
+        <v>2414181596.3912106</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>5530983917.4213829</v>
+        <v>5530835659.6940823</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2372144197.4543533</v>
+        <v>2372080612.2563496</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5869291239.638032</v>
+        <v>5869133913.6011019</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15388,7 +15388,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2330776304.7606483</v>
+        <v>2330713828.4267898</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>6228291416.1414022</v>
+        <v>6228124467.1239929</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2290129827.9689593</v>
+        <v>2290068441.1617317</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>6609250142.9138517</v>
+        <v>6609072982.3182011</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2250192186.2860718</v>
+        <v>2250131870.005188</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>7013510533.3059502</v>
+        <v>7013322536.5322142</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2210951018.3155956</v>
+        <v>2210891753.8921151</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>7442497853.335474</v>
+        <v>7442298357.5796299</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2172394178.2318988</v>
+        <v>2172335947.3224492</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7897724546.6249657</v>
+        <v>7897512848.5420189</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2134509732.0207603</v>
+        <v>2134452516.6018591</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>8380795566.6938601</v>
+        <v>8380570919.9181261</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2097285953.7855825</v>
+        <v>2097229736.1480613</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8893414035.4047966</v>
+        <v>8893175647.9184971</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2060711322.1180298</v>
+        <v>2060656084.8615484</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>9437387247.5135841</v>
+        <v>9437134278.8545074</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2024774516.5319426</v>
+        <v>2024720242.5596082</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>10014633042.492567</v>
+        <v>10014364600.790913</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>1989464413.9594564</v>
+        <v>1989411086.4725282</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>10627186566.091959</v>
+        <v>10626901704.925953</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>1954770085.3082137</v>
+        <v>1954717687.8009043</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>11277207445.477823</v>
+        <v>11276905160.537003</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
@@ -15630,7 +15630,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>1920680792.0786228</v>
+        <v>1920629308.3329904</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>11966987403.243446</v>
+        <v>11966666628.787848</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>1887185983.0401022</v>
+        <v>1887135397.1210296</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>12698958337.138178</v>
+        <v>12698617942.24095</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>1854275290.9652927</v>
+        <v>1854225587.2155561</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>13475700893.999731</v>
+        <v>13475339678.559919</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>1821938529.4212186</v>
+        <v>1821889692.4566414</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>14299953568.118332</v>
+        <v>14299570258.629793</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>1790165689.61641</v>
+        <v>1790117704.3211</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>15174622356.110027</v>
+        <v>15174215601.171532</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>1758946937.3030069</v>
+        <v>1758899788.8246784</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>16102791002.338507</v>
+        <v>16102359367.889221</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>1728272609.7328882</v>
+        <v>1728226283.4782653</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>17087731871.006823</v>
+        <v>17087273835.270372</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>1698133212.6668823</v>
+        <v>1698087694.2971814</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38183854272.257889</v>
+        <v>38182830756.091782</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3794609584.0473208</v>
+        <v>3794507869.7409115</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>70307154378.430206</v>
+        <v>70305269798.927399</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15838,7 +15838,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>70307154378.430206</v>
+        <v>70305269798.927399</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15868,19 +15868,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37143925582.747704</v>
+        <v>37142929941.814354</v>
       </c>
       <c r="C56" s="124">
-        <v>38339694571.890358</v>
+        <v>38338666878.43338</v>
       </c>
       <c r="D56" s="124">
-        <v>39571760813.15863</v>
+        <v>39570700094.232132</v>
       </c>
       <c r="E56" s="124">
-        <v>40841697431.979904</v>
+        <v>40840602672.470436</v>
       </c>
       <c r="F56" s="124">
-        <v>42151125551.391495</v>
+        <v>42149995692.731491</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15889,19 +15889,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>38305992295.234665</v>
+        <v>38304965505.165405</v>
       </c>
       <c r="C57" s="124">
-        <v>40861890570.070511</v>
+        <v>40860795269.285065</v>
       </c>
       <c r="D57" s="124">
-        <v>43678487911.303642</v>
+        <v>43677317111.777512</v>
       </c>
       <c r="E57" s="124">
-        <v>46786764921.636581</v>
+        <v>46785510804.911865</v>
       </c>
       <c r="F57" s="124">
-        <v>50221126184.905663</v>
+        <v>50219780010.311447</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15910,19 +15910,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>39744372062.84346</v>
+        <v>39743306717.081665</v>
       </c>
       <c r="C58" s="124">
-        <v>44149892906.337967</v>
+        <v>44148709470.826218</v>
       </c>
       <c r="D58" s="124">
-        <v>49327449477.026527</v>
+        <v>49326127257.38855</v>
       </c>
       <c r="E58" s="124">
-        <v>55430298685.183197</v>
+        <v>55428812878.999466</v>
       </c>
       <c r="F58" s="124">
-        <v>62641756312.63887</v>
+        <v>62640077203.720146</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15931,19 +15931,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>41209850376.606827</v>
+        <v>41208745748.77742</v>
       </c>
       <c r="C59" s="124">
-        <v>47688855489.543419</v>
+        <v>47687577192.329414</v>
       </c>
       <c r="D59" s="124">
-        <v>55771379156.389549</v>
+        <v>55769884207.562073</v>
       </c>
       <c r="E59" s="124">
-        <v>65910363252.501587</v>
+        <v>65908596528.749123</v>
       </c>
       <c r="F59" s="124">
-        <v>78689066952.308716</v>
+        <v>78686957696.088852</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15952,19 +15952,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>42572826527.812469</v>
+        <v>42571685365.480423</v>
       </c>
       <c r="C60" s="124">
-        <v>51174854026.965141</v>
+        <v>51173482287.747276</v>
       </c>
       <c r="D60" s="124">
-        <v>62524421533.338188</v>
+        <v>62522745569.57193</v>
       </c>
       <c r="E60" s="124">
-        <v>77640339825.70192</v>
+        <v>77638258680.556427</v>
       </c>
       <c r="F60" s="124">
-        <v>97934316529.735733</v>
+        <v>97931691405.633011</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15973,19 +15973,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>43775161094.306854</v>
+        <v>43773987703.461227</v>
       </c>
       <c r="C61" s="124">
-        <v>54439522550.962891</v>
+        <v>54438063302.480301</v>
       </c>
       <c r="D61" s="124">
-        <v>69276605730.7854</v>
+        <v>69274748775.083801</v>
       </c>
       <c r="E61" s="124">
-        <v>90220985507.876266</v>
+        <v>90218567139.197876</v>
       </c>
       <c r="F61" s="124">
-        <v>120155822906.37471</v>
+        <v>120152602135.98524</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16035,23 +16035,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>40.094589258920792</v>
+        <v>40.354354752747859</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>40.094589258920792</v>
+        <v>40.354354752747859</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>40.094589258920792</v>
+        <v>40.354354752747859</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>40.094589258920792</v>
+        <v>40.354354752747859</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>40.094589258920792</v>
+        <v>40.354354752747859</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16062,23 +16062,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>41.002721180105254</v>
+        <v>41.268309518873885</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>41.938051256036331</v>
+        <v>42.209636831411537</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>42.901773029607163</v>
+        <v>43.17953788612359</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>43.895116998964816</v>
+        <v>44.179251070979859</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>44.919351205969669</v>
+        <v>45.210052558389805</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16089,23 +16089,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>41.911689347281673</v>
+        <v>42.183105892911904</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>43.910912064362115</v>
+        <v>44.195147412650478</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>46.114053498002825</v>
+        <v>46.412415153992924</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>48.545346664565017</v>
+        <v>48.859297512814656</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>51.231702817229042</v>
+        <v>51.562878294378812</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16116,23 +16116,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>43.036789487418147</v>
+        <v>43.315420055049948</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>46.482786316635185</v>
+        <v>46.783512248098567</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>50.532669215732369</v>
+        <v>50.859362564046556</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>55.306315685150956</v>
+        <v>55.663617145071896</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>60.947115263920722</v>
+        <v>61.340584928622697</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16143,23 +16143,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>44.183086100671517</v>
+        <v>44.469066599827926</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>49.250961584368191</v>
+        <v>49.569436760163882</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>55.573108707823991</v>
+        <v>55.932120816127906</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>63.503818444058048</v>
+        <v>63.913681416639925</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>73.499315910847926</v>
+        <v>73.973268946233659</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16170,23 +16170,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.249205559007244</v>
+        <v>45.542021902329289</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>51.977708394418876</v>
+        <v>52.313667179698434</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>60.855336041488009</v>
+        <v>61.248217227612578</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>72.679001927238588</v>
+        <v>73.147695196924502</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>88.552943251922756</v>
+        <v>89.123418538944378</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16196,23 +16196,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>46.18967122719625</v>
+        <v>46.48851773599425</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>54.531330947074245</v>
+        <v>54.883663287579118</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>66.136892107452724</v>
+        <v>66.563638067301085</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>82.519578483423444</v>
+        <v>83.051368479571153</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>105.9345975976059</v>
+        <v>106.6165221969155</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>105.9345975976059</v>
+        <v>106.6165221969155</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>82.519578483423444</v>
+        <v>83.051368479571153</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16292,7 +16292,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.136892107452724</v>
+        <v>66.563638067301085</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>54.531330947074245</v>
+        <v>54.883663287579118</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>46.18967122719625</v>
+        <v>46.48851773599425</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-56.45</v>
+        <v>-54.65</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0617122197608295</v>
+        <v>2.0485220509508149</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0617122197608295</v>
+        <v>2.0485220509508149</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>69.006510592080929</v>
+        <v>69.42524659185095</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16522,7 +16522,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3155179383.3184395</v>
+        <v>3155076501.1366282</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878634237.2479687</v>
+        <v>2878557075.6116099</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.22851324060700184</v>
+        <v>0.22851255820868932</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16679,7 +16679,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>56.45</v>
+        <v>54.65</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>40.094589258920792</v>
+        <v>40.354354752747859</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.136892107452724</v>
+        <v>66.563638067301085</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16799,7 +16799,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>54.531330947074245</v>
+        <v>54.883663287579118</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>82.519578483423444</v>
+        <v>83.051368479571153</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>65.931761034533324</v>
+        <v>66.357191715838511</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>46.18967122719625</v>
+        <v>46.48851773599425</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>105.9345975976059</v>
+        <v>106.6165221969155</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>66.944798372320093</v>
+        <v>67.376724540900142</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>66.942986891315115</v>
+        <v>67.374901444872336</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.17848669583450025</v>
+        <v>0.17851941247108333</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17200,7 +17200,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0617122197608295</v>
+        <v>2.0485220509508149</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.7443021196384669</v>
+        <v>3.7203472841573748</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17239,7 +17239,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>30.471005176294984</v>
+        <v>30.667603341329144</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>34.215307295933449</v>
+        <v>34.387950625486518</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17260,7 +17260,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.48890267611769256</v>
+        <v>0.48961676513954355</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>56.45</v>
+        <v>54.65</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.3068045296727409E-2</v>
+        <v>0.10734290687447179</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.3429586110702658</v>
+        <v>4.3151737647343547</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>38.741202761759311</v>
+        <v>38.991160035243141</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>43.084161372829577</v>
+        <v>43.306333799977494</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.35642256873771183</v>
+        <v>0.35725082964386368</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>5.3132323501177732</v>
+        <v>5.2792400058161935</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>53.142939316542261</v>
+        <v>53.485816234901414</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>58.456171666660033</v>
+        <v>58.765056240717605</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.1268003924434834</v>
+        <v>0.12781369766580053</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E38AD8F-1BC0-4B52-A997-DE74F78A3862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2ACDD0-9AD6-4648-A1EC-97536861664B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>54.65</v>
+        <v>54</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>74553.354464199991</v>
+        <v>73666.626552000002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4227,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0739449931617173</v>
+        <v>1.0737034399999998</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>34.387950625486518</v>
+        <v>34.381875852171149</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10734290687447179</v>
+        <v>0.11184849157270471</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177357837.13662779</v>
+        <v>177361431.80505371</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155520783.13662779</v>
+        <v>155524377.80505371</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008397213.3610955</v>
+        <v>-1008398112.0282021</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3155076501.1366282</v>
+        <v>3155080095.8050537</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878557075.6116099</v>
+        <v>2878559771.6129293</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.1465766109394828E-2</v>
+        <v>4.1955491566384277E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.748439251511098E-2</v>
+        <v>3.7944127980758587E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>28.326301473480335</v>
+        <v>28.319956807309385</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.22467434265012642</v>
+        <v>0.22462380859282413</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12808822880.167248</v>
+        <v>12808718096.209652</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>10.083568090361801</v>
+        <v>10.081217609413219</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1691595315558421</v>
+        <v>2.1686716412574998</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>40.354354752747859</v>
+        <v>40.345222249387277</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>1.3348070848882203</v>
+        <v>1.334506858271689</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>106.62 HKD</v>
+        <v>106.59 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>83.05 HKD</v>
+        <v>83.03 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>66.56 HKD</v>
+        <v>66.55 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>54.88 HKD</v>
+        <v>54.87 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>46.49 HKD</v>
+        <v>46.48 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>67.376724540900142</v>
+        <v>67.361539432485785</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0485220509508149</v>
+        <v>2.0489829109609636</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>3.7203472841573748</v>
+        <v>3.721184257958237</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>30.667603341329144</v>
+        <v>30.660691594212913</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>34.387950625486518</v>
+        <v>34.381875852171149</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.48961676513954355</v>
+        <v>0.48959189261654346</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>4.3151737647343547</v>
+        <v>4.3161445578112883</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>38.991160035243141</v>
+        <v>38.98237235676261</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>43.306333799977494</v>
+        <v>43.298516914573895</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35725082964386368</v>
+        <v>0.35722198038584685</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>5.2792400058161935</v>
+        <v>5.2804276867598912</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>53.485816234901414</v>
+        <v>53.473761806258715</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>58.765056240717605</v>
+        <v>58.754189493018607</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12781369766580053</v>
+        <v>0.12777840310633093</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,6 +5416,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5432,17 +5443,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6043,23 +6043,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0485220509508149</v>
+        <v>2.0489829109609636</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8622927735916499</v>
+        <v>1.8627117372372397</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2104903028345724</v>
+        <v>1.2107626292042057</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0242610254754074</v>
+        <v>1.0244914554804818</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.69835979009686866</v>
+        <v>0.69851690146396483</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7381,23 +7381,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0485220509508149</v>
+        <v>2.0489829109609636</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8622927735916499</v>
+        <v>1.8627117372372397</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2104903028345724</v>
+        <v>1.2107626292042057</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0242610254754074</v>
+        <v>1.0244914554804818</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.69835979009686866</v>
+        <v>0.69851690146396483</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8734,11 +8734,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.877384506879434</v>
+        <v>22.872238894585834</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3348070848882203</v>
+        <v>1.334506858271689</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12808822880.167248</v>
+        <v>12808718096.209652</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -8996,11 +8996,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2537052061.3378563</v>
+        <v>-2537104453.3166528</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2584975007.9163766</v>
+        <v>-2585027399.8951735</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9012,11 +9012,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.0864816571873206</v>
+        <v>7.0863353191852569</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.9551051135661925</v>
+        <v>6.9549641511455791</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9029,7 +9029,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5169950015.8327532</v>
+        <v>5170054799.7903471</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9144,11 +9144,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-306500016.58931386</v>
+        <v>-306431078.1906575</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.22467434265012642</v>
+        <v>-0.22462380859282413</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9161,11 +9161,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13755971200.450863</v>
+        <v>13752764681.890553</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>10.083568090361801</v>
+        <v>10.081217609413219</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9178,11 +9178,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2959160465.6080642</v>
+        <v>2958494887.2301693</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.1691595315558421</v>
+        <v>2.1686716412574998</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9195,11 +9195,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16408631649.469614</v>
+        <v>16404828490.930065</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>12.028053279267516</v>
+        <v>12.025265442077895</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9779,28 +9779,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155520783.13662779</v>
+        <v>155524377.80505371</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155520783.13662779</v>
+        <v>155524377.80505371</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129182163.43266767</v>
+        <v>129185114.69535571</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>122941843.15259959</v>
+        <v>122944522.15453975</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68082005.123338923</v>
+        <v>68083844.786090463</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>137026439.571394</v>
+        <v>137029493.72133282</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9834,28 +9834,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033588853.4443822</v>
+        <v>4033592448.1128082</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691585643.1366282</v>
+        <v>4691589237.8050537</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4549849955.4326677</v>
+        <v>4549852906.6953554</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3869895051.1525998</v>
+        <v>3869897730.1545396</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025173005.1233387</v>
+        <v>3025174844.7860904</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2471086311.571394</v>
+        <v>2471089365.721333</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008397213.3610955</v>
+        <v>-1008398112.0282021</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10001,30 +10001,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878557075.6116099</v>
+        <v>2878559771.6129293</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3155076501.1366282</v>
+        <v>3155080095.8050537</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071294059.4326677</v>
+        <v>3071297010.6953554</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574382358.1525998</v>
+        <v>2574385037.1545396</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701653350.1233387</v>
+        <v>1701655189.7860904</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1432860543.571394</v>
+        <v>1432863597.721333</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -10109,30 +10109,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878557075.6116099</v>
+        <v>2878559771.6129293</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3155076501.1366282</v>
+        <v>3155080095.8050537</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071294059.4326677</v>
+        <v>3071297010.6953554</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574382358.1525998</v>
+        <v>2574385037.1545396</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701653350.1233387</v>
+        <v>1701655189.7860904</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1432860543.571394</v>
+        <v>1432863597.721333</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10970,23 +10970,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29621463183412866</v>
+        <v>0.29621440487619816</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30730867868081979</v>
+        <v>0.30730847934500488</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31045281386692181</v>
+        <v>0.31045259895072802</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.40418567563878821</v>
+        <v>0.40418542984627359</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36930337670790581</v>
+        <v>0.36930292026634559</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -11108,28 +11108,28 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177357837.13662779</v>
+        <v>177361431.80505371</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>177357837.13662779</v>
+        <v>177361431.80505371</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>145612753.43266767</v>
+        <v>145615704.69535571</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132179643.15259959</v>
+        <v>132182322.15453975</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90767372.123338923</v>
+        <v>90769211.786090463</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150689121.571394</v>
+        <v>150692175.72133282</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -11220,28 +11220,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155520783.13662779</v>
+        <v>155524377.80505371</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155520783.13662779</v>
+        <v>155524377.80505371</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129182163.43266767</v>
+        <v>129185114.69535571</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>122941843.15259959</v>
+        <v>122944522.15453975</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68082005.123338923</v>
+        <v>68083844.786090463</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>137026439.571394</v>
+        <v>137029493.72133282</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -12307,30 +12307,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8444041515592999E-3</v>
+        <v>4.8445161239034128E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8391811954783094E-3</v>
+        <v>4.8392930471003234E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8065822010867898E-3</v>
+        <v>3.8066691652908291E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8214442091336993E-3</v>
+        <v>3.8215274814857965E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2568516709842437E-3</v>
+        <v>2.2569126539994672E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.9361623374490462E-3</v>
+        <v>4.9362723584052068E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12364,30 +12364,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12564452282974134</v>
+        <v>0.12564463480208546</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14598327351076551</v>
+        <v>0.1459833853623875</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13406942102338085</v>
+        <v>0.13406950798758488</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12028929820765877</v>
+        <v>0.12028938148001087</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10028151696267493</v>
+        <v>0.10028157794569015</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.901700446948646E-2</v>
+        <v>8.9017114490442625E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.1411130707435335E-2</v>
+        <v>3.1411158700521365E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12536,30 +12536,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.9665789782851349E-2</v>
+        <v>8.9665873762109438E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8173289554378526E-2</v>
+        <v>9.8173401406000532E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0501141878101751E-2</v>
+        <v>9.0501228842305784E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.0020425124480404E-2</v>
+        <v>8.0020508396832488E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.6408138974527476E-2</v>
+        <v>5.6408199957542704E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1616551317519799E-2</v>
+        <v>5.1616661338475964E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12643,30 +12643,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.9665789782851349E-2</v>
+        <v>8.9665873762109438E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8173289554378526E-2</v>
+        <v>9.8173401406000532E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0501141878101751E-2</v>
+        <v>9.0501228842305784E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.0020425124480404E-2</v>
+        <v>8.0020508396832488E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.6408138974527476E-2</v>
+        <v>5.6408199957542704E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1616551317519799E-2</v>
+        <v>5.1616661338475964E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12712,28 +12712,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0485220509508149</v>
+        <v>2.0489829109609636</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0485220509508149</v>
+        <v>2.0489829109609636</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8622927735916499</v>
+        <v>1.8627117372372397</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2104903028345724</v>
+        <v>1.2107626292042057</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0242610254754074</v>
+        <v>1.0244914554804818</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.69835979009686866</v>
+        <v>0.69851690146396483</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12768,28 +12768,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2794587202.0542741</v>
+        <v>2795215905.7998366</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2794587202.0542741</v>
+        <v>2795215905.7998366</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2540533820.0493402</v>
+        <v>2541105368.9089422</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1651346983.0320709</v>
+        <v>1651718489.7908125</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1397293601.027137</v>
+        <v>1397607952.8999183</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>952700182.51850247</v>
+        <v>952914513.34085333</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12823,28 +12823,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.9708291788727188</v>
+        <v>0.97104667874713158</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.88574308770247356</v>
+        <v>0.88594134567813754</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82718677237914162</v>
+        <v>0.82737207116729639</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.64145365889513495</v>
+        <v>0.6415973003076697</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82113880651770754</v>
+        <v>0.82132265178564601</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.6648938633929472</v>
+        <v>0.66504202832444248</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12878,28 +12878,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.748439251511098E-2</v>
+        <v>3.7944127980758587E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.748439251511098E-2</v>
+        <v>3.7944127980758587E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.4076720468282709E-2</v>
+        <v>3.4494661800689622E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.2149868304383757E-2</v>
+        <v>2.2421530170448255E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.874219625755549E-2</v>
+        <v>1.8972063990379293E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2778770175606014E-2</v>
+        <v>1.2935498175258608E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13015,26 +13015,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14025040567144642</v>
+        <v>-0.14025029821240009</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1151727879448643E-2</v>
+        <v>3.1151849085302441E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17570370650686051</v>
+        <v>0.17570365522648124</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27923098764886056</v>
+        <v>0.27923109529498258</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.22422798060808891</v>
+        <v>0.2242272119944213</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13626,23 +13626,23 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6337673999800049</v>
+        <v>1.6337655385844432</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90436379136977685</v>
+        <v>0.90436292235088855</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8951230405032182</v>
+        <v>1.8951210683668718</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5513175786137552</v>
+        <v>3.5513137392773797</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.4570163748480591</v>
+        <v>3.457009006214808</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13734,28 +13734,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12564452282974134</v>
+        <v>0.12564463480208546</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14598327351076551</v>
+        <v>0.1459833853623875</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13406942102338085</v>
+        <v>0.13406950798758488</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12028929820765877</v>
+        <v>0.12028938148001087</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10028151696267493</v>
+        <v>0.10028157794569015</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.901700446948646E-2</v>
+        <v>8.9017114490442625E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -14020,30 +14020,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2661041178784269</v>
+        <v>2.265596544584751</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.483790198923904</v>
+        <v>2.4832343706862736</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.4178336341714357</v>
+        <v>2.4172921345753231</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0266467919742963</v>
+        <v>2.0261930643670132</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3396029894932009</v>
+        <v>1.3393031320985471</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1279995820276592</v>
+        <v>1.1277482746310141</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14077,30 +14077,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1465766109394828E-2</v>
+        <v>4.1955491566384277E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.5449042981224229E-2</v>
+        <v>4.5985821679375434E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.4242152500849695E-2</v>
+        <v>4.4764669158802277E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.7084113302365898E-2</v>
+        <v>3.7522093784574322E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.4512406029152809E-2</v>
+        <v>2.48019098536768E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.0640431510112703E-2</v>
+        <v>2.0884227307981743E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14134,23 +14134,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0249156034379643E-2</v>
+        <v>6.0974377357015698E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8323316975468553E-2</v>
+        <v>5.9025356902025115E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1033538401374021E-2</v>
+        <v>5.1647830993242411E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3676691590901193E-2</v>
+        <v>4.4202429545236115E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1212127498802141E-2</v>
+        <v>3.1587829033509943E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878557075.6116099</v>
+        <v>2878559771.6129293</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35981963445.145126</v>
+        <v>35981997145.161613</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12808822880.167248</v>
+        <v>12808718096.209652</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51260801517.812378</v>
+        <v>51260730433.871262</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0739449931617173</v>
+        <v>1.0737034399999998</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15046,7 +15046,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>40.354354752747859</v>
+        <v>40.345222249387277</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>67.374901444872336</v>
+        <v>67.359716744804103</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3054626460.4873424</v>
+        <v>3054629321.3918691</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2828357833.7845759</v>
+        <v>2828360482.7702489</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3241465278.6159945</v>
+        <v>3241468314.5101733</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2779034018.0178275</v>
+        <v>2779036620.8077617</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15178,7 +15178,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3439732251.5161934</v>
+        <v>3439735473.1034141</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2730570361.7304535</v>
+        <v>2730572919.1302567</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3650126391.9669247</v>
+        <v>3650129810.6052599</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15212,7 +15212,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2682951864.5758977</v>
+        <v>2682954377.37713</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3873389468.4566426</v>
+        <v>3873393096.1988912</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2636163787.7990913</v>
+        <v>2636166256.7795086</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4110308620.3725033</v>
+        <v>4110312470.0086832</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2590191649.6745486</v>
+        <v>2590194075.5983438</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4361719133.1498613</v>
+        <v>4361723218.2523031</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2545021221.0240245</v>
+        <v>2545023604.6420631</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4628507383.1661434</v>
+        <v>4628511718.1373405</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2500638520.8123312</v>
+        <v>2500640862.8623843</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4911613962.761652</v>
+        <v>4911618562.8850384</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2457029811.8199692</v>
+        <v>2457032113.0269418</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5212036996.4049091</v>
+        <v>5212041877.8987446</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2414181596.3912106</v>
+        <v>2414183857.4673676</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>5530835659.6940823</v>
+        <v>5530840839.7686281</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2372080612.2563496</v>
+        <v>2372082833.9015326</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5869133913.6011019</v>
+        <v>5869139410.5193005</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15388,7 +15388,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2330713828.4267898</v>
+        <v>2330716011.3286366</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>6228124467.1239929</v>
+        <v>6228130300.2658558</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2290068441.1617317</v>
+        <v>2290070585.9958892</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>6609072982.3182011</v>
+        <v>6609079172.2491322</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2250131870.005188</v>
+        <v>2250133977.4355187</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>7013322536.5322142</v>
+        <v>7013329105.0755205</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2210891753.8921151</v>
+        <v>2210893824.5709062</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>7442298357.5796299</v>
+        <v>7442305327.8934584</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2172335947.3224492</v>
+        <v>2172337981.8906116</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7897512848.5420189</v>
+        <v>7897520245.201005</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2134452516.6018591</v>
+        <v>2134454515.6891274</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>8380570919.9181261</v>
+        <v>8380578769.0000324</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2097229736.1480613</v>
+        <v>2097231700.3731878</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8893175647.9184971</v>
+        <v>8893183977.0961552</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2060656084.8615484</v>
+        <v>2060658014.832495</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>9437134278.8545074</v>
+        <v>9437143117.4933796</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2024720242.5596082</v>
+        <v>2024722138.8737342</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>10014364600.790913</v>
+        <v>10014373980.052628</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>1989411086.4725282</v>
+        <v>1989412949.7167761</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>10626901704.925953</v>
+        <v>10626911657.878166</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>1954717687.8009043</v>
+        <v>1954719518.551981</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>11276905160.537003</v>
+        <v>11276915722.269979</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
@@ -15630,7 +15630,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>1920629308.3329904</v>
+        <v>1920631107.1575449</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>11966666628.787848</v>
+        <v>11966677836.538179</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>1887135397.1210296</v>
+        <v>1887137164.5758295</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>12698617942.24095</v>
+        <v>12698629835.522837</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>1854225587.2155561</v>
+        <v>1854227323.8476601</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>13475339678.559919</v>
+        <v>13475352299.30448</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>1821889692.4566414</v>
+        <v>1821891398.8035665</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>14299570258.629793</v>
+        <v>14299583651.332897</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>1790117704.3211</v>
+        <v>1790119380.9109907</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>15174215601.171532</v>
+        <v>15174229813.05068</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>1758899788.8246784</v>
+        <v>1758901436.1764684</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>16102359367.889221</v>
+        <v>16102374449.050013</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>1728226283.4782653</v>
+        <v>1728227902.1018388</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>17087273835.270372</v>
+        <v>17087289838.883152</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>1698087694.2971814</v>
+        <v>1698089284.6935306</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38182830756.091782</v>
+        <v>38182866517.398361</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3794507869.7409115</v>
+        <v>3794511423.6041679</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>70305269798.927399</v>
+        <v>70305335645.493988</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15838,7 +15838,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>70305269798.927399</v>
+        <v>70305335645.493988</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15868,19 +15868,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37142929941.814354</v>
+        <v>37142964729.169792</v>
       </c>
       <c r="C56" s="124">
-        <v>38338666878.43338</v>
+        <v>38338702785.693085</v>
       </c>
       <c r="D56" s="124">
-        <v>39570700094.232132</v>
+        <v>39570737155.390503</v>
       </c>
       <c r="E56" s="124">
-        <v>40840602672.470436</v>
+        <v>40840640922.995193</v>
       </c>
       <c r="F56" s="124">
-        <v>42149995692.731491</v>
+        <v>42150035169.608627</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15889,19 +15889,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>38304965505.165405</v>
+        <v>38305001380.861053</v>
       </c>
       <c r="C57" s="124">
-        <v>40860795269.285065</v>
+        <v>40860833538.721817</v>
       </c>
       <c r="D57" s="124">
-        <v>43677317111.777512</v>
+        <v>43677358019.114571</v>
       </c>
       <c r="E57" s="124">
-        <v>46785510804.911865</v>
+        <v>46785554623.323502</v>
       </c>
       <c r="F57" s="124">
-        <v>50219780010.311447</v>
+        <v>50219827045.193718</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15910,19 +15910,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>39743306717.081665</v>
+        <v>39743343939.900093</v>
       </c>
       <c r="C58" s="124">
-        <v>44148709470.826218</v>
+        <v>44148750819.660309</v>
       </c>
       <c r="D58" s="124">
-        <v>49326127257.38855</v>
+        <v>49326173455.292801</v>
       </c>
       <c r="E58" s="124">
-        <v>55428812878.999466</v>
+        <v>55428864792.561958</v>
       </c>
       <c r="F58" s="124">
-        <v>62640077203.720146</v>
+        <v>62640135871.214432</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15931,19 +15931,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>41208745748.77742</v>
+        <v>41208784344.097923</v>
       </c>
       <c r="C59" s="124">
-        <v>47687577192.329414</v>
+        <v>47687621855.599106</v>
       </c>
       <c r="D59" s="124">
-        <v>55769884207.562073</v>
+        <v>55769936440.56543</v>
       </c>
       <c r="E59" s="124">
-        <v>65908596528.749123</v>
+        <v>65908658257.475883</v>
       </c>
       <c r="F59" s="124">
-        <v>78686957696.088852</v>
+        <v>78687031392.783478</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15952,19 +15952,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>42571685365.480423</v>
+        <v>42571725237.304008</v>
       </c>
       <c r="C60" s="124">
-        <v>51173482287.747276</v>
+        <v>51173530215.848801</v>
       </c>
       <c r="D60" s="124">
-        <v>62522745569.57193</v>
+        <v>62522804127.175659</v>
       </c>
       <c r="E60" s="124">
-        <v>77638258680.556427</v>
+        <v>77638331395.059692</v>
       </c>
       <c r="F60" s="124">
-        <v>97931691405.633011</v>
+        <v>97931783126.575928</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15973,19 +15973,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>43773987703.461227</v>
+        <v>43774028701.338112</v>
       </c>
       <c r="C61" s="124">
-        <v>54438063302.480301</v>
+        <v>54438114288.125763</v>
       </c>
       <c r="D61" s="124">
-        <v>69274748775.083801</v>
+        <v>69274813656.484161</v>
       </c>
       <c r="E61" s="124">
-        <v>90218567139.197876</v>
+        <v>90218651636.176682</v>
       </c>
       <c r="F61" s="124">
-        <v>120152602135.98524</v>
+        <v>120152714668.60675</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16035,23 +16035,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>40.354354752747859</v>
+        <v>40.345222249387277</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>40.354354752747859</v>
+        <v>40.345222249387277</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>40.354354752747859</v>
+        <v>40.345222249387277</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>40.354354752747859</v>
+        <v>40.345222249387277</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>40.354354752747859</v>
+        <v>40.345222249387277</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16062,23 +16062,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>41.268309518873885</v>
+        <v>41.258972303370008</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>42.209636831411537</v>
+        <v>42.200088772725003</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>43.17953788612359</v>
+        <v>43.169772584165223</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>44.179251070979859</v>
+        <v>44.169261848280186</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>45.210052558389805</v>
+        <v>45.199832451635878</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16089,23 +16089,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>42.183105892911904</v>
+        <v>42.173563776757199</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>44.195147412650478</v>
+        <v>44.18515462940897</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>46.412415153992924</v>
+        <v>46.401925736072727</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>48.859297512814656</v>
+        <v>48.848260029989461</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>51.562878294378812</v>
+        <v>51.551235250056592</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16116,23 +16116,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>43.315420055049948</v>
+        <v>43.305624317526203</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>46.783512248098567</v>
+        <v>46.772939710001836</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>50.859362564046556</v>
+        <v>50.847877096683668</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>55.663617145071896</v>
+        <v>55.651055596825458</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>61.340584928622697</v>
+        <v>61.326751824840379</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16143,23 +16143,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>44.469066599827926</v>
+        <v>44.459012462801766</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>49.569436760163882</v>
+        <v>49.558240216811008</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>55.932120816127906</v>
+        <v>55.919499127091129</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>63.913681416639925</v>
+        <v>63.89927197788294</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>73.973268946233659</v>
+        <v>73.956606310928862</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16170,23 +16170,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.542021902329289</v>
+        <v>45.5317274394273</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>52.313667179698434</v>
+        <v>52.301855969940064</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>61.248217227612578</v>
+        <v>61.234404812808258</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>73.147695196924502</v>
+        <v>73.131217477742396</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>89.123418538944378</v>
+        <v>89.103362497631537</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16196,23 +16196,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>46.48851773599425</v>
+        <v>46.478011272238469</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>54.883663287579118</v>
+        <v>54.871276437284678</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>66.563638067301085</v>
+        <v>66.54863507804717</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>83.051368479571153</v>
+        <v>83.032672486291318</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>106.6165221969155</v>
+        <v>106.59254796306674</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>106.6165221969155</v>
+        <v>106.59254796306674</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>83.051368479571153</v>
+        <v>83.032672486291318</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16292,7 +16292,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.563638067301085</v>
+        <v>66.54863507804717</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>54.883663287579118</v>
+        <v>54.871276437284678</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>46.48851773599425</v>
+        <v>46.478011272238469</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-54.65</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0485220509508149</v>
+        <v>2.0489829109609636</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0485220509508149</v>
+        <v>2.0489829109609636</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>69.42524659185095</v>
+        <v>69.410522343446743</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16522,7 +16522,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3155076501.1366282</v>
+        <v>3155080095.8050537</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878557075.6116099</v>
+        <v>2878559771.6129293</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.22851255820868932</v>
+        <v>0.22851258205217873</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16679,7 +16679,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>54.65</v>
+        <v>54</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>40.354354752747859</v>
+        <v>40.345222249387277</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.563638067301085</v>
+        <v>66.54863507804717</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16799,7 +16799,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>54.883663287579118</v>
+        <v>54.871276437284678</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>83.051368479571153</v>
+        <v>83.032672486291318</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>66.357191715838511</v>
+        <v>66.342234967467249</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>46.48851773599425</v>
+        <v>46.478011272238469</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>106.6165221969155</v>
+        <v>106.59254796306674</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>67.376724540900142</v>
+        <v>67.361539432485785</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>67.374901444872336</v>
+        <v>67.359716744804103</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.17851941247108333</v>
+        <v>0.17851826937729676</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17200,7 +17200,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0485220509508149</v>
+        <v>2.0489829109609636</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.7203472841573748</v>
+        <v>3.721184257958237</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17239,7 +17239,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>30.667603341329144</v>
+        <v>30.660691594212913</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>34.387950625486518</v>
+        <v>34.381875852171149</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17260,7 +17260,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.48961676513954355</v>
+        <v>0.48959189261654346</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>54.65</v>
+        <v>54</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10734290687447179</v>
+        <v>0.11184849157270471</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.3151737647343547</v>
+        <v>4.3161445578112883</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>38.991160035243141</v>
+        <v>38.98237235676261</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>43.306333799977494</v>
+        <v>43.298516914573895</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.35725082964386368</v>
+        <v>0.35722198038584685</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>5.2792400058161935</v>
+        <v>5.2804276867598912</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>53.485816234901414</v>
+        <v>53.473761806258715</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>58.765056240717605</v>
+        <v>58.754189493018607</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.12781369766580053</v>
+        <v>0.12777840310633093</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2ACDD0-9AD6-4648-A1EC-97536861664B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7043A676-2102-4DFF-9939-278191EEF3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>54</v>
+        <v>53.55</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>73666.626552000002</v>
+        <v>73052.737997399992</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4227,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0737034399999998</v>
+        <v>1.0742246600000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>34.381875852171149</v>
+        <v>34.394984382396515</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11184849157270471</v>
+        <v>0.11521291318800975</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177361431.80505371</v>
+        <v>177353677.29966182</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155524377.80505371</v>
+        <v>155516623.29966182</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008398112.0282021</v>
+        <v>-1008396173.401854</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3155080095.8050537</v>
+        <v>3155072341.2996616</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878559771.6129293</v>
+        <v>2878553955.7338853</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.1955491566384277E-2</v>
+        <v>4.2328511280438831E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7944127980758587E-2</v>
+        <v>3.8244420777520896E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>28.319956807309385</v>
+        <v>28.333647238343744</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.22462380859282413</v>
+        <v>0.22473285026779055</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12808718096.209652</v>
+        <v>12808944138.689201</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>10.081217609413219</v>
+        <v>10.086289443999483</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1686716412574998</v>
+        <v>2.1697244040509736</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>40.345222249387277</v>
+        <v>40.364928236126403</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>1.334506858271689</v>
+        <v>1.3351546830236229</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>106.59 HKD</v>
+        <v>106.64 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>83.03 HKD</v>
+        <v>83.07 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>66.55 HKD</v>
+        <v>66.58 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>54.87 HKD</v>
+        <v>54.9 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>46.48 HKD</v>
+        <v>46.5 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>67.361539432485785</v>
+        <v>67.394305644906538</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0489829109609636</v>
+        <v>2.0479887326362438</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>3.721184257958237</v>
+        <v>3.7193787178965021</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>30.660691594212913</v>
+        <v>30.675605664500011</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>34.381875852171149</v>
+        <v>34.394984382396515</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.48959189261654346</v>
+        <v>0.48964554121797699</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>4.3161445578112883</v>
+        <v>4.3140503395809766</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>38.98237235676261</v>
+        <v>39.001334285246841</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>43.298516914573895</v>
+        <v>43.315384624827814</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35722198038584685</v>
+        <v>0.35728420657596816</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>5.2804276867598912</v>
+        <v>5.2778655927944689</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>53.473761806258715</v>
+        <v>53.499772682094424</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>58.754189493018607</v>
+        <v>58.777638274888893</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12777840310633093</v>
+        <v>0.12785453144094927</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6043,23 +6043,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0489829109609636</v>
+        <v>2.0479887326362438</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8627117372372397</v>
+        <v>1.8618079387602215</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2107626292042057</v>
+        <v>1.2101751601941442</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0244914554804818</v>
+        <v>1.0239943663181219</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.69851690146396483</v>
+        <v>0.69817797703508311</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7381,23 +7381,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0489829109609636</v>
+        <v>2.0479887326362438</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8627117372372397</v>
+        <v>1.8618079387602215</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2107626292042057</v>
+        <v>1.2101751601941442</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0244914554804818</v>
+        <v>1.0239943663181219</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.69851690146396483</v>
+        <v>0.69817797703508311</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8734,11 +8734,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.872238894585834</v>
+        <v>22.883342024102344</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.334506858271689</v>
+        <v>1.3351546830236229</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12808718096.209652</v>
+        <v>12808944138.689201</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -8996,11 +8996,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2537104453.3166528</v>
+        <v>-2536991432.0768795</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2585027399.8951735</v>
+        <v>-2584914378.6553998</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9012,11 +9012,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.0863353191852569</v>
+        <v>7.0866510105956015</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.9549641511455791</v>
+        <v>6.9552682458101591</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9029,7 +9029,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5170054799.7903471</v>
+        <v>5169828757.3107996</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9144,11 +9144,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-306431078.1906575</v>
+        <v>-306579832.49340481</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.22462380859282413</v>
+        <v>-0.22473285026779055</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9161,11 +9161,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13752764681.890553</v>
+        <v>13759683662.342402</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>10.081217609413219</v>
+        <v>10.086289443999483</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9178,11 +9178,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2958494887.2301693</v>
+        <v>2959931062.851552</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.1686716412574998</v>
+        <v>2.1697244040509736</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9195,11 +9195,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16404828490.930065</v>
+        <v>16413034892.70055</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>12.025265442077895</v>
+        <v>12.031280997782666</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9779,28 +9779,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155524377.80505371</v>
+        <v>155516623.29966182</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155524377.80505371</v>
+        <v>155516623.29966182</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129185114.69535571</v>
+        <v>129178748.16033334</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>122944522.15453975</v>
+        <v>122938742.94696665</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68083844.786090463</v>
+        <v>68079876.221250579</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>137029493.72133282</v>
+        <v>137022905.23545256</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9834,28 +9834,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033592448.1128082</v>
+        <v>4033584693.6074162</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691589237.8050537</v>
+        <v>4691581483.2996616</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4549852906.6953554</v>
+        <v>4549846540.1603336</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3869897730.1545396</v>
+        <v>3869891950.9469666</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025174844.7860904</v>
+        <v>3025170876.2212505</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2471089365.721333</v>
+        <v>2471082777.2354527</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008398112.0282021</v>
+        <v>-1008396173.401854</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10001,30 +10001,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878559771.6129293</v>
+        <v>2878553955.7338853</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3155080095.8050537</v>
+        <v>3155072341.2996616</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071297010.6953554</v>
+        <v>3071290644.1603336</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574385037.1545396</v>
+        <v>2574379257.9469666</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701655189.7860904</v>
+        <v>1701651221.2212505</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1432863597.721333</v>
+        <v>1432857009.2354527</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -10109,30 +10109,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878559771.6129293</v>
+        <v>2878553955.7338853</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3155080095.8050537</v>
+        <v>3155072341.2996616</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071297010.6953554</v>
+        <v>3071290644.1603336</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574385037.1545396</v>
+        <v>2574379257.9469666</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701655189.7860904</v>
+        <v>1701651221.2212505</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1432863597.721333</v>
+        <v>1432857009.2354527</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10970,23 +10970,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29621440487619816</v>
+        <v>0.29621489447575172</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30730847934500488</v>
+        <v>0.30730890935735339</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31045259895072802</v>
+        <v>0.31045306257349414</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.40418542984627359</v>
+        <v>0.40418596007618501</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36930292026634559</v>
+        <v>0.36930390491449183</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -11108,28 +11108,28 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177361431.80505371</v>
+        <v>177353677.29966182</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>177361431.80505371</v>
+        <v>177353677.29966182</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>145615704.69535571</v>
+        <v>145609338.16033334</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132182322.15453975</v>
+        <v>132176542.94696665</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90769211.786090463</v>
+        <v>90765243.221250579</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150692175.72133282</v>
+        <v>150685587.23545256</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -11220,28 +11220,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155524377.80505371</v>
+        <v>155516623.29966182</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155524377.80505371</v>
+        <v>155516623.29966182</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129185114.69535571</v>
+        <v>129178748.16033334</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>122944522.15453975</v>
+        <v>122938742.94696665</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68083844.786090463</v>
+        <v>68079876.221250579</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>137029493.72133282</v>
+        <v>137022905.23545256</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -12307,30 +12307,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8445161239034128E-3</v>
+        <v>4.8442745744631628E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8392930471003234E-3</v>
+        <v>4.8390517580846953E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8066691652908291E-3</v>
+        <v>3.8064815640132628E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8215274814857965E-3</v>
+        <v>3.8213478443602476E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2569126539994672E-3</v>
+        <v>2.2567810999687935E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.9362723584052068E-3</v>
+        <v>4.9360350185460918E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12364,30 +12364,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12564463480208546</v>
+        <v>0.1256443932526452</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.1459833853623875</v>
+        <v>0.14598314407337187</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13406950798758488</v>
+        <v>0.13406932038630734</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12028938148001087</v>
+        <v>0.12028920184288532</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10028157794569015</v>
+        <v>0.10028144639165948</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.9017114490442625E-2</v>
+        <v>8.9016877150583498E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.1411158700521365E-2</v>
+        <v>3.1411098313161301E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12536,30 +12536,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.9665873762109438E-2</v>
+        <v>8.966569260002924E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8173401406000532E-2</v>
+        <v>9.8173160116984903E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0501228842305784E-2</v>
+        <v>9.0501041241028243E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.0020508396832488E-2</v>
+        <v>8.0020328759706952E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.6408199957542704E-2</v>
+        <v>5.6408068403512028E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1616661338475964E-2</v>
+        <v>5.1616423998616844E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12643,30 +12643,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.9665873762109438E-2</v>
+        <v>8.966569260002924E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8173401406000532E-2</v>
+        <v>9.8173160116984903E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0501228842305784E-2</v>
+        <v>9.0501041241028243E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.0020508396832488E-2</v>
+        <v>8.0020328759706952E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.6408199957542704E-2</v>
+        <v>5.6408068403512028E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1616661338475964E-2</v>
+        <v>5.1616423998616844E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12712,28 +12712,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0489829109609636</v>
+        <v>2.0479887326362438</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0489829109609636</v>
+        <v>2.0479887326362438</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8627117372372397</v>
+        <v>1.8618079387602215</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2107626292042057</v>
+        <v>1.2101751601941442</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0244914554804818</v>
+        <v>1.0239943663181219</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.69851690146396483</v>
+        <v>0.69817797703508311</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12768,28 +12768,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2795215905.7998366</v>
+        <v>2793859650.9225545</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2795215905.7998366</v>
+        <v>2793859650.9225545</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2541105368.9089422</v>
+        <v>2539872409.929595</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1651718489.7908125</v>
+        <v>1650917066.454237</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1397607952.8999183</v>
+        <v>1396929825.4612772</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>952914513.34085333</v>
+        <v>952452153.72359812</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12823,28 +12823,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.97104667874713158</v>
+        <v>0.97057748226583507</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.88594134567813754</v>
+        <v>0.88551365822936612</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82737207116729639</v>
+        <v>0.8269723397096389</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.6415973003076697</v>
+        <v>0.64128743321635584</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82132265178564601</v>
+        <v>0.82092605584516964</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66504202832444248</v>
+        <v>0.66472240257372917</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -12878,28 +12878,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7944127980758587E-2</v>
+        <v>3.8244420777520896E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7944127980758587E-2</v>
+        <v>3.8244420777520896E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.4494661800689622E-2</v>
+        <v>3.4767655252291724E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.2421530170448255E-2</v>
+        <v>2.259897591398962E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.8972063990379293E-2</v>
+        <v>1.9122210388760448E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2935498175258608E-2</v>
+        <v>1.3037870719609396E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13015,26 +13015,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14025029821240009</v>
+        <v>-0.14025053002585097</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1151849085302441E-2</v>
+        <v>3.1151587616916165E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17570365522648124</v>
+        <v>0.17570376584984015</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27923109529498258</v>
+        <v>0.27923086307800893</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.2242272119944213</v>
+        <v>0.22422887006872716</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13626,23 +13626,23 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6337655385844432</v>
+        <v>1.63376955403712</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90436292235088855</v>
+        <v>0.90436479702146999</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8951210683668718</v>
+        <v>1.8951253227120683</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5513137392773797</v>
+        <v>3.5513220215967323</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.457009006214808</v>
+        <v>3.4570249020473156</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13734,28 +13734,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12564463480208546</v>
+        <v>0.1256443932526452</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.1459833853623875</v>
+        <v>0.14598314407337187</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13406950798758488</v>
+        <v>0.13406932038630734</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12028938148001087</v>
+        <v>0.12028920184288532</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10028157794569015</v>
+        <v>0.10028144639165948</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.9017114490442625E-2</v>
+        <v>8.9016877150583498E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -14020,30 +14020,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.265596544584751</v>
+        <v>2.2666917790674992</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4832343706862736</v>
+        <v>2.4844337290054028</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.4172921345753231</v>
+        <v>2.4184605747542012</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0261930643670132</v>
+        <v>2.0271721113883259</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3393031320985471</v>
+        <v>1.3399501601487296</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1277482746310141</v>
+        <v>1.1282905421813463</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14077,30 +14077,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1955491566384277E-2</v>
+        <v>4.2328511280438831E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.5985821679375434E-2</v>
+        <v>4.6394654136422089E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.4764669158802277E-2</v>
+        <v>4.5162662460395915E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.7522093784574322E-2</v>
+        <v>3.7855688354590585E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.48019098536768E-2</v>
+        <v>2.5022411954224645E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.0884227307981743E-2</v>
+        <v>2.1069851394609641E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14134,23 +14134,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0974377357015698E-2</v>
+        <v>6.148676708270491E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9025356902025115E-2</v>
+        <v>5.9521368304563151E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1647830993242411E-2</v>
+        <v>5.2081846379740254E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4202429545236115E-2</v>
+        <v>4.4573878533011209E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1587829033509943E-2</v>
+        <v>3.1853272974968011E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878559771.6129293</v>
+        <v>2878553955.7338853</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35981997145.161613</v>
+        <v>35981924446.673569</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12808718096.209652</v>
+        <v>12808944138.689201</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51260730433.871262</v>
+        <v>51260883777.86277</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0737034399999998</v>
+        <v>1.0742246600000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15046,7 +15046,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>40.345222249387277</v>
+        <v>40.364928236126403</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>67.359716744804103</v>
+        <v>67.392482076101331</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3054629321.3918691</v>
+        <v>3054623149.7796507</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2828360482.7702489</v>
+        <v>2828354768.3144913</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3241468314.5101733</v>
+        <v>3241461765.4060593</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2779036620.8077617</v>
+        <v>2779031006.0065665</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15178,7 +15178,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3439735473.1034141</v>
+        <v>3439728523.4177928</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2730572919.1302567</v>
+        <v>2730567402.2457452</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3650129810.6052599</v>
+        <v>3650122435.8362231</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15212,7 +15212,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2682954377.37713</v>
+        <v>2682948956.7017307</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3873393096.1988912</v>
+        <v>3873385270.3458519</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2636166256.7795086</v>
+        <v>2636160930.6354275</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4110312470.0086832</v>
+        <v>4110304165.4807053</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2590194075.5983438</v>
+        <v>2590188842.3370461</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4361723218.2523031</v>
+        <v>4361714405.7708282</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2545023604.6420631</v>
+        <v>2545018462.643764</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4628511718.1373405</v>
+        <v>4628502366.6329622</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2500640862.8623843</v>
+        <v>2500635810.5355453</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4911618562.8850384</v>
+        <v>4911608639.3879642</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2457032113.0269418</v>
+        <v>2457027148.8077803</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5212041877.8987446</v>
+        <v>5212031347.422555</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2414183857.4673676</v>
+        <v>2414178979.8193698</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>5530840839.7686281</v>
+        <v>5530829665.1869316</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2372082833.9015326</v>
+        <v>2372078041.3149829</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5869139410.5193005</v>
+        <v>5869127552.4348373</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15388,7 +15388,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2330716011.3286366</v>
+        <v>2330711302.3201451</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>6228130300.2658558</v>
+        <v>6228117716.8715992</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2290070585.9958892</v>
+        <v>2290065959.1079354</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>6609079172.2491322</v>
+        <v>6609065819.1808939</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2250133977.4355187</v>
+        <v>2250129431.236001</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>7013329105.0755205</v>
+        <v>7013314935.2555389</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2210893824.5709062</v>
+        <v>2210889357.6526961</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>7442305327.8934584</v>
+        <v>7442290291.3644199</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2172337981.8906116</v>
+        <v>2172333592.87112</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7897520245.201005</v>
+        <v>7897504288.9499149</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2134454515.6891274</v>
+        <v>2134450203.2098765</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>8380578769.0000324</v>
+        <v>8380561836.7713108</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2097231700.3731878</v>
+        <v>2097227463.0993893</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8893183977.0961552</v>
+        <v>8893166009.1933041</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2060658014.832495</v>
+        <v>2060653851.4526396</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>9437143117.4933796</v>
+        <v>9437124050.568512</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2024722138.8737342</v>
+        <v>2024718048.0991831</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>10014373980.052628</v>
+        <v>10014353746.883129</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>1989412949.7167761</v>
+        <v>1989408930.281363</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>10626911657.878166</v>
+        <v>10626890187.129696</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>1954719518.551981</v>
+        <v>1954715569.2116208</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>11276915722.269979</v>
+        <v>11276892938.244968</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
@@ -15630,7 +15630,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>1920631107.1575449</v>
+        <v>1920627226.6898479</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15640,7 +15640,7 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>11966677836.538179</v>
+        <v>11966653658.908955</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
@@ -15652,7 +15652,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>1887137164.5758295</v>
+        <v>1887133351.7797232</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>12698629835.522837</v>
+        <v>12698604179.048414</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>1854227323.8476601</v>
+        <v>1854223577.5430174</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>13475352299.30448</v>
+        <v>13475325073.530041</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>1821891398.8035665</v>
+        <v>1821887717.8308413</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>14299583651.332897</v>
+        <v>14299554760.270876</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>1790119380.9109907</v>
+        <v>1790115764.1308577</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>15174229813.05068</v>
+        <v>15174199154.842346</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>1758901436.1764684</v>
+        <v>1758897882.469471</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>16102374449.050013</v>
+        <v>16102341915.606363</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>1728227902.1018388</v>
+        <v>1728224410.3680425</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>17087289838.883152</v>
+        <v>17087255315.503832</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>1698089284.6935306</v>
+        <v>1698085853.8521831</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38182866517.398361</v>
+        <v>38182789372.245636</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3794511423.6041679</v>
+        <v>3794503757.124671</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>70305335645.493988</v>
+        <v>70305193599.693069</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15838,7 +15838,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>70305335645.493988</v>
+        <v>70305193599.693069</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15868,19 +15868,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37142964729.169792</v>
+        <v>37142889685.047958</v>
       </c>
       <c r="C56" s="124">
-        <v>38338702785.693085</v>
+        <v>38338625325.68676</v>
       </c>
       <c r="D56" s="124">
-        <v>39570737155.390503</v>
+        <v>39570657206.166153</v>
       </c>
       <c r="E56" s="124">
-        <v>40840640922.995193</v>
+        <v>40840558408.041</v>
       </c>
       <c r="F56" s="124">
-        <v>42150035169.608627</v>
+        <v>42149950009.137527</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15889,19 +15889,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>38305001380.861053</v>
+        <v>38304923988.94548</v>
       </c>
       <c r="C57" s="124">
-        <v>40860833538.721817</v>
+        <v>40860750982.9702</v>
       </c>
       <c r="D57" s="124">
-        <v>43677358019.114571</v>
+        <v>43677269772.820816</v>
       </c>
       <c r="E57" s="124">
-        <v>46785554623.323502</v>
+        <v>46785460097.189507</v>
       </c>
       <c r="F57" s="124">
-        <v>50219827045.193718</v>
+        <v>50219725580.411713</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15910,19 +15910,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>39743343939.900093</v>
+        <v>39743263641.938789</v>
       </c>
       <c r="C58" s="124">
-        <v>44148750819.660309</v>
+        <v>44148661620.958511</v>
       </c>
       <c r="D58" s="124">
-        <v>49326173455.292801</v>
+        <v>49326073796.059967</v>
       </c>
       <c r="E58" s="124">
-        <v>55428864792.561958</v>
+        <v>55428752803.37336</v>
       </c>
       <c r="F58" s="124">
-        <v>62640135871.214432</v>
+        <v>62640009312.281334</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15931,19 +15931,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>41208784344.097923</v>
+        <v>41208701085.342056</v>
       </c>
       <c r="C59" s="124">
-        <v>47687621855.599106</v>
+        <v>47687525506.916924</v>
       </c>
       <c r="D59" s="124">
-        <v>55769936440.56543</v>
+        <v>55769823762.271301</v>
       </c>
       <c r="E59" s="124">
-        <v>65908658257.475883</v>
+        <v>65908525094.778305</v>
       </c>
       <c r="F59" s="124">
-        <v>78687031392.783478</v>
+        <v>78686872412.497101</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15952,19 +15952,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>42571725237.304008</v>
+        <v>42571639224.844902</v>
       </c>
       <c r="C60" s="124">
-        <v>51173530215.848801</v>
+        <v>51173426824.192696</v>
       </c>
       <c r="D60" s="124">
-        <v>62522804127.175659</v>
+        <v>62522677805.301147</v>
       </c>
       <c r="E60" s="124">
-        <v>77638331395.059692</v>
+        <v>77638174533.580215</v>
       </c>
       <c r="F60" s="124">
-        <v>97931783126.575928</v>
+        <v>97931585263.946564</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15973,19 +15973,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>43774028701.338112</v>
+        <v>43773940259.729683</v>
       </c>
       <c r="C61" s="124">
-        <v>54438114288.125763</v>
+        <v>54438004300.662155</v>
       </c>
       <c r="D61" s="124">
-        <v>69274813656.484161</v>
+        <v>69274673692.763107</v>
       </c>
       <c r="E61" s="124">
-        <v>90218651636.176682</v>
+        <v>90218469357.257004</v>
       </c>
       <c r="F61" s="124">
-        <v>120152714668.60675</v>
+        <v>120152471910.52258</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16035,23 +16035,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>40.345222249387277</v>
+        <v>40.364928236126403</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>40.345222249387277</v>
+        <v>40.364928236126403</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>40.345222249387277</v>
+        <v>40.364928236126403</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>40.345222249387277</v>
+        <v>40.364928236126403</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>40.345222249387277</v>
+        <v>40.364928236126403</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16062,23 +16062,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>41.258972303370008</v>
+        <v>41.279120015080039</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>42.200088772725003</v>
+        <v>42.220691438876045</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>43.169772584165223</v>
+        <v>43.190844014779287</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>44.169261848280186</v>
+        <v>44.190816451906592</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>45.199832451635878</v>
+        <v>45.221885253612918</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16089,23 +16089,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>42.173563776757199</v>
+        <v>42.194153620197028</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>44.18515462940897</v>
+        <v>44.206716915922236</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>46.401925736072727</v>
+        <v>46.42455965387984</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>48.848260029989461</v>
+        <v>48.872076554506236</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>51.551235250056592</v>
+        <v>51.576358446617036</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16116,23 +16116,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>43.305624317526203</v>
+        <v>43.326761421573295</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>46.772939710001836</v>
+        <v>46.795752983351662</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>50.847877096683668</v>
+        <v>50.872660275907336</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>55.651055596825458</v>
+        <v>55.678160728178128</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>61.326751824840379</v>
+        <v>61.356600700765469</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16143,23 +16143,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>44.459012462801766</v>
+        <v>44.480707137644828</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>49.558240216811008</v>
+        <v>49.582399959887397</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>55.919499127091129</v>
+        <v>55.946734029391642</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>63.89927197788294</v>
+        <v>63.930364461274657</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>73.956606310928862</v>
+        <v>73.9925607100012</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16170,23 +16170,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.5317274394273</v>
+        <v>45.553940686050225</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>52.301855969940064</v>
+        <v>52.327342031503029</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>61.234404812808258</v>
+        <v>61.26420904634891</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>73.131217477742396</v>
+        <v>73.166772867417436</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>89.103362497631537</v>
+        <v>89.146639140250329</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16196,23 +16196,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>46.478011272238469</v>
+        <v>46.500681971308808</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>54.871276437284678</v>
+        <v>54.898004607864458</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>66.54863507804717</v>
+        <v>66.581008316316257</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>83.032672486291318</v>
+        <v>83.073014436477592</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>106.59254796306674</v>
+        <v>106.64427922618833</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>106.59254796306674</v>
+        <v>106.64427922618833</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>83.032672486291318</v>
+        <v>83.073014436477592</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16292,7 +16292,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.54863507804717</v>
+        <v>66.581008316316257</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>54.871276437284678</v>
+        <v>54.898004607864458</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>46.478011272238469</v>
+        <v>46.500681971308808</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-54</v>
+        <v>-53.55</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0489829109609636</v>
+        <v>2.0479887326362438</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0489829109609636</v>
+        <v>2.0479887326362438</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>69.410522343446743</v>
+        <v>69.44229437754278</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16522,7 +16522,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3155080095.8050537</v>
+        <v>3155072341.2996616</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878559771.6129293</v>
+        <v>2878553955.7338853</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.22851258205217873</v>
+        <v>0.22851253061636267</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16679,7 +16679,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>54</v>
+        <v>53.55</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>40.345222249387277</v>
+        <v>40.364928236126403</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.54863507804717</v>
+        <v>66.581008316316257</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16799,7 +16799,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>54.871276437284678</v>
+        <v>54.898004607864458</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>83.032672486291318</v>
+        <v>83.073014436477592</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>66.342234967467249</v>
+        <v>66.374508427812984</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>46.478011272238469</v>
+        <v>46.500681971308808</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>106.59254796306674</v>
+        <v>106.64427922618833</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>67.361539432485785</v>
+        <v>67.394305644906538</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>67.359716744804103</v>
+        <v>67.392482076101331</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.17851826937729676</v>
+        <v>0.17852073528547371</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17200,7 +17200,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0489829109609636</v>
+        <v>2.0479887326362438</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.721184257958237</v>
+        <v>3.7193787178965021</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17239,7 +17239,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>30.660691594212913</v>
+        <v>30.675605664500011</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>34.381875852171149</v>
+        <v>34.394984382396515</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17260,7 +17260,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.48959189261654346</v>
+        <v>0.48964554121797699</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>54</v>
+        <v>53.55</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11184849157270471</v>
+        <v>0.11521291318800975</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.3161445578112883</v>
+        <v>4.3140503395809766</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>38.98237235676261</v>
+        <v>39.001334285246841</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>43.298516914573895</v>
+        <v>43.315384624827814</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.35722198038584685</v>
+        <v>0.35728420657596816</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>5.2804276867598912</v>
+        <v>5.2778655927944689</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>53.473761806258715</v>
+        <v>53.499772682094424</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>58.754189493018607</v>
+        <v>58.777638274888893</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.12777840310633093</v>
+        <v>0.12785453144094927</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7043A676-2102-4DFF-9939-278191EEF3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3EE826-C8B9-4E71-8C7B-DA7901FE0CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2358,6 +2358,27 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
@@ -2367,7 +2388,7 @@
     <t>0168.HK</t>
   </si>
   <si>
-    <t>CNY</t>
+    <t/>
   </si>
   <si>
     <t>CNS_03</t>
@@ -3053,7 +3074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3754,29 +3775,36 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4066,13 +4094,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4089,7 +4116,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4107,9 +4134,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>0168.HK Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>425</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4121,340 +4147,332 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>425</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>1364196788</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>428</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>434</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>53.55</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C13" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>1364196788</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (HKD):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>73052.737997399992</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>CNY/HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1.0742246600000001</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C15" s="32" t="str">
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>1.0742246600000001</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>CNY/HKD</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="C22" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>428</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>435</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E19" s="339">
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>34.394984382396515</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="330">
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C21" s="280">
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>0.11521291318800975</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
         <v>362</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>3878068070.3077545</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>1191305772</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-1191305772</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C37" s="188">
+      <c r="C42" s="188">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>177353677.29966182</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-21837054</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>155516623.29966182</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4462,405 +4480,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-146634564.47167698</v>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
+        <v>177353677.29966182</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-21837054</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>155516623.29966182</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-146634564.47167698</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-1008396173.401854</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
-        <v>351</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
-        <v>369</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>3155072341.2996616</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>3155072341.2996616</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>2878553955.7338853</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
         <v>398</v>
       </c>
-      <c r="C58" s="92">
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>4.2328511280438831E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
         <v>316</v>
       </c>
-      <c r="C59" s="92">
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>3.8244420777520896E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
         <v>363</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C67" s="311">
+      <c r="C72" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D68" s="286" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
+      <c r="D73" s="286" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D69" s="286" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
+      <c r="D74" s="286" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
+    <row r="76" spans="1:6">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
+      <c r="C81" s="263">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>28.333647238343744</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
         <v>365</v>
       </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>285396383</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.22473285026779055</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
         <v>412</v>
       </c>
-      <c r="C88" s="337">
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>0.72207550313588764</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
         <v>413</v>
       </c>
-      <c r="C89" s="337">
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>9.5579625064196368E-3</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
         <v>415</v>
       </c>
-      <c r="C90" s="338">
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>7.3592411949940734E-2</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>17978772896</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>12808944138.689201</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>10.086289443999483</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>2755411575.5</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4869,591 +4895,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1697244040509736</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>12808944138.689201</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>10.086289443999483</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>40.364928236126403</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>2755411575.5</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
+        <f>Reporting_currency</f>
+        <v>CNY</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>414</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>1.3351546830236229</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.1697244040509736</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>40.364928236126403</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>1.3351546830236229</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
         <v>366</v>
       </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>30</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>106.64 HKD</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.08</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>30</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>83.07 HKD</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.06</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>30</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>66.58 HKD</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.04</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>30</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>54.9 HKD</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.26999999999999996</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>0.02</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>30</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>46.5 HKD</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>67.394305644906538</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
         <v>410</v>
       </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>2.0479887326362438</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
         <v>418</v>
       </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>0168.HK</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>3.7193787178965021</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>30.675605664500011</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>34.394984382396515</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+      <c r="D139" s="342" t="str">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.48964554121797699</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
         <v>421</v>
       </c>
-      <c r="C136" s="337">
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>4.3140503395809766</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>39.001334285246841</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>43.315384624827814</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+      <c r="D147" s="342" t="str">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.35728420657596816</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
-      <c r="C142" s="92">
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>5.2778655927944689</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>53.499772682094424</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="C145" s="239">
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>58.777638274888893</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+      <c r="D155" s="342" t="str">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>0.12785453144094927</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="238" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
-        <v>389</v>
-      </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
-        <v>390</v>
-      </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
-        <v>391</v>
-      </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5477,7 +5600,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -6073,7 +6196,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9235,7 +9358,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -11863,7 +11986,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12195,7 +12318,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -14930,7 +15053,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -14940,7 +15063,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -14958,10 +15081,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -14976,8 +15099,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -14992,8 +15115,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15008,8 +15131,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15035,7 +15158,7 @@
         <v>1.0742246600000001</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>CNY/HKD</v>
       </c>
       <c r="H11" s="121"/>
@@ -16503,11 +16626,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 青島啤酒股份(0168.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16528,8 +16651,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16550,8 +16673,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16561,8 +16684,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16575,8 +16698,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16594,8 +16717,8 @@
         <v>2.1321347914251776E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16612,8 +16735,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.15185942572632172</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16630,8 +16753,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.22851253061636267</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16657,21 +16780,21 @@
       <c r="C18" s="151">
         <v>30</v>
       </c>
-      <c r="E18" s="350" t="s">
+      <c r="E18" s="353" t="s">
         <v>338</v>
       </c>
-      <c r="F18" s="351"/>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>310</v>
       </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16685,8 +16808,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16700,8 +16823,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16721,8 +16844,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16732,8 +16855,8 @@
         <v>0.06</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16747,8 +16870,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16758,8 +16881,8 @@
         <v>0.5</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16779,8 +16902,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16790,8 +16913,8 @@
         <v>0.04</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16805,8 +16928,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16816,8 +16939,8 @@
         <v>0.3</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16837,8 +16960,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16848,8 +16971,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16863,8 +16986,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -16875,8 +16998,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -16938,8 +17061,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -16949,8 +17072,8 @@
         <v>0.02</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -16964,8 +17087,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -16975,8 +17098,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -16996,8 +17119,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17007,8 +17130,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17022,8 +17145,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17033,8 +17156,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17052,7 +17175,7 @@
         <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
@@ -17217,7 +17340,7 @@
         <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17306,7 +17429,7 @@
         <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17364,7 +17487,7 @@
         <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3EE826-C8B9-4E71-8C7B-DA7901FE0CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203CC38C-44BC-4D35-9485-0E083996479B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5566,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8565,7 +8565,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>799157484</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203CC38C-44BC-4D35-9485-0E083996479B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A5F0BF-5198-400A-B917-C27CF2F293E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4206,7 +4206,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>53.55</v>
+        <v>55</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4226,8 +4226,7 @@
         <v>430</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>73052.737997399992</v>
+        <v>1.08195318</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4264,13 +4263,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4319,7 +4318,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4335,7 +4334,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>34.394984382396515</v>
+        <v>27.814699897667847</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4349,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11521291318800975</v>
+        <v>0.10499062561528705</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4370,22 +4369,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4396,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4422,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4457,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4479,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4549,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4571,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4593,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4643,7 +4642,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.2328511280438831E-2</v>
+        <v>4.1212577801227258E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4651,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8244420777520896E-2</v>
+        <v>3.7236158775204434E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4670,22 +4669,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4742,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4794,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4813,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4950,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4995,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5144,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5163,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5201,7 +5200,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5236,7 +5235,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5246,7 +5245,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>3.7193787178965021</v>
+        <v>3.2540928842179375</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5255,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>30.675605664500011</v>
+        <v>24.560607013449911</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5264,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>34.394984382396515</v>
+        <v>27.814699897667847</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5290,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.48964554121797699</v>
+        <v>0.58728412391069718</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5443,13 +5442,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5485,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5499,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5538,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5565,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13001,28 +13000,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8244420777520896E-2</v>
+        <v>3.7236158775204434E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8244420777520896E-2</v>
+        <v>3.7236158775204434E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.4767655252291724E-2</v>
+        <v>3.3851053432004029E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.259897591398962E-2</v>
+        <v>2.2003184730802622E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.9122210388760448E-2</v>
+        <v>1.8618079387602217E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.3037870719609396E-2</v>
+        <v>1.2694145037001512E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -14200,30 +14199,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.2328511280438831E-2</v>
+        <v>4.1212577801227258E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.6394654136422089E-2</v>
+        <v>4.517152234555278E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.5162662460395915E-2</v>
+        <v>4.3972010450076385E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.7855688354590585E-2</v>
+        <v>3.6857674752515016E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.5022411954224645E-2</v>
+        <v>2.4362730184522355E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.1069851394609641E-2</v>
+        <v>2.0514373494206296E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14257,23 +14256,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.148676708270491E-2</v>
+        <v>5.9865752314160865E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9521368304563151E-2</v>
+        <v>5.7952168594715567E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2081846379740254E-2</v>
+        <v>5.0708779520638007E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4573878533011209E-2</v>
+        <v>4.3398749008050005E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1853272974968011E-2</v>
+        <v>3.1013504869264307E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16562,7 +16561,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-53.55</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16802,7 +16801,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>53.55</v>
+        <v>55</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17341,7 +17340,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17350,7 +17349,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.7193787178965021</v>
+        <v>3.2540928842179375</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17362,7 +17361,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>30.675605664500011</v>
+        <v>24.560607013449911</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17372,7 +17371,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>34.394984382396515</v>
+        <v>27.814699897667847</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17383,7 +17382,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.48964554121797699</v>
+        <v>0.58728412391069718</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17400,7 +17399,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>53.55</v>
+        <v>55</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17412,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11521291318800975</v>
+        <v>0.10499062561528705</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A5F0BF-5198-400A-B917-C27CF2F293E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362BDF82-CDCE-4DF8-BC7D-716539BE7E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4226,7 +4226,8 @@
         <v>430</v>
       </c>
       <c r="C14" s="35">
-        <v>1.08195318</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>75030.823340000003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4263,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4369,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4396,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4422,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4457,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4479,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4549,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4571,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4593,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4669,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4742,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4794,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4813,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4950,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4995,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5144,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5163,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5442,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5485,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5499,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5538,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5565,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362BDF82-CDCE-4DF8-BC7D-716539BE7E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2E0627-8E99-49F5-9F7D-4B46FF29CC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4206,7 +4206,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>55</v>
+        <v>54.25</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>75030.823340000003</v>
+        <v>74007.675749000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4254,7 +4254,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0742246600000001</v>
+        <v>1.0828863799999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>27.814699897667847</v>
+        <v>27.987109440361163</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10499062561528705</v>
+        <v>0.11274933088119332</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C45" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177353677.29966182</v>
+        <v>177225904.43726471</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C47" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155516623.29966182</v>
+        <v>155388850.43726471</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008396173.401854</v>
+        <v>-1008364230.1862549</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3155072341.2996616</v>
+        <v>3154944568.4372644</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878553955.7338853</v>
+        <v>2878458126.0870876</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.1212577801227258E-2</v>
+        <v>4.2117835327130211E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7236158775204434E-2</v>
+        <v>3.7448984621733884E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>28.333647238343744</v>
+        <v>28.561157081210169</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.22473285026779055</v>
+        <v>0.22654492282235422</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12808944138.689201</v>
+        <v>12812668695.34053</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>10.086289443999483</v>
+        <v>10.170574028383234</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1697244040509736</v>
+        <v>2.187219389936939</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>40.364928236126403</v>
+        <v>40.692405576707991</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>1.3351546830236229</v>
+        <v>1.3459203416904415</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>106.64 HKD</v>
+        <v>107.5 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>83.07 HKD</v>
+        <v>83.74 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>66.58 HKD</v>
+        <v>67.12 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>54.9 HKD</v>
+        <v>55.34 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>46.5 HKD</v>
+        <v>46.88 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>67.394305644906538</v>
+        <v>67.938819971772304</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0479887326362438</v>
+        <v>2.0316074157290633</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>3.2540928842179375</v>
+        <v>3.2280642611438459</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>24.560607013449911</v>
+        <v>24.759045179217317</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>27.814699897667847</v>
+        <v>27.987109440361163</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.58728412391069718</v>
+        <v>0.58805423096854725</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>4.3140503395809766</v>
+        <v>4.279543398873721</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>39.001334285246841</v>
+        <v>39.316446742923787</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>43.315384624827814</v>
+        <v>43.595990141797508</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35728420657596816</v>
+        <v>0.35830516102706711</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>5.2778655927944689</v>
+        <v>5.2356493503458212</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>53.499772682094424</v>
+        <v>53.932025710457864</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>58.777638274888893</v>
+        <v>59.167675060803688</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12785453144094927</v>
+        <v>0.12910358046567361</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -6166,23 +6166,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0479887326362438</v>
+        <v>2.0316074157290633</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8618079387602215</v>
+        <v>1.8469158324809665</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2101751601941442</v>
+        <v>1.2004952911126283</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0239943663181219</v>
+        <v>1.0158037078645317</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.69817797703508311</v>
+        <v>0.69259343718036237</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7356,11 +7356,11 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-1191305772</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-1140399624</v>
       </c>
       <c r="E62" s="183">
@@ -7504,23 +7504,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0479887326362438</v>
+        <v>2.0316074157290633</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8618079387602215</v>
+        <v>1.8469158324809665</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2101751601941442</v>
+        <v>1.2004952911126283</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0239943663181219</v>
+        <v>1.0158037078645317</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.69817797703508311</v>
+        <v>0.69259343718036237</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8857,11 +8857,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.883342024102344</v>
+        <v>23.067855663248373</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3351546830236229</v>
+        <v>1.3459203416904415</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12808944138.689201</v>
+        <v>12812668695.34053</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9119,11 +9119,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2536991432.0768795</v>
+        <v>-2535129153.751214</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2584914378.6553998</v>
+        <v>-2583052100.3297343</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9135,11 +9135,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.0866510105956015</v>
+        <v>7.091856787413346</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.9552682458101591</v>
+        <v>6.9602827189219125</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9152,7 +9152,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5169828757.3107996</v>
+        <v>5166104200.6594687</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9267,11 +9267,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-306579832.49340481</v>
+        <v>-309051856.05196351</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.22473285026779055</v>
+        <v>-0.22654492282235422</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9284,11 +9284,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13759683662.342402</v>
+        <v>13874664421.636629</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>10.086289443999483</v>
+        <v>10.170574028383234</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9301,11 +9301,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2959931062.851552</v>
+        <v>2983797666.4032917</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.1697244040509736</v>
+        <v>2.187219389936939</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9318,11 +9318,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16413034892.70055</v>
+        <v>16549410231.987957</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>12.031280997782666</v>
+        <v>12.131248495497818</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9902,28 +9902,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155516623.29966182</v>
+        <v>155388850.43726471</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155516623.29966182</v>
+        <v>155388850.43726471</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129178748.16033334</v>
+        <v>129073845.22168684</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>122938742.94696665</v>
+        <v>122843517.54487051</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68079876.221250579</v>
+        <v>68014485.217753351</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>137022905.23545256</v>
+        <v>136914345.15879551</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9957,28 +9957,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033584693.6074162</v>
+        <v>4033456920.7450194</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691581483.2996616</v>
+        <v>4691453710.4372644</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4549846540.1603336</v>
+        <v>4549741637.2216873</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3869891950.9469666</v>
+        <v>3869796725.5448704</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025170876.2212505</v>
+        <v>3025105485.2177534</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2471082777.2354527</v>
+        <v>2470974217.1587954</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008396173.401854</v>
+        <v>-1008364230.1862549</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10124,30 +10124,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878553955.7338853</v>
+        <v>2878458126.0870876</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3155072341.2996616</v>
+        <v>3154944568.4372644</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071290644.1603336</v>
+        <v>3071185741.2216873</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574379257.9469666</v>
+        <v>2574284032.5448704</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701651221.2212505</v>
+        <v>1701585830.2177534</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1432857009.2354527</v>
+        <v>1432748449.1587954</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -10232,30 +10232,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878553955.7338853</v>
+        <v>2878458126.0870876</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3155072341.2996616</v>
+        <v>3154944568.4372644</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071290644.1603336</v>
+        <v>3071185741.2216873</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574379257.9469666</v>
+        <v>2574284032.5448704</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701651221.2212505</v>
+        <v>1701585830.2177534</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1432857009.2354527</v>
+        <v>1432748449.1587954</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -11093,23 +11093,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29621489447575172</v>
+        <v>0.29622296195915621</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30730890935735339</v>
+        <v>0.30731599494819223</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31045306257349414</v>
+        <v>0.31046070199742576</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.40418596007618501</v>
+        <v>0.40419469700309812</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36930390491449183</v>
+        <v>0.36932012995639996</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -11231,28 +11231,28 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177353677.29966182</v>
+        <v>177225904.43726471</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>177353677.29966182</v>
+        <v>177225904.43726471</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>145609338.16033334</v>
+        <v>145504435.22168684</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132176542.94696665</v>
+        <v>132081317.54487051</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90765243.221250579</v>
+        <v>90699852.217753351</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150685587.23545256</v>
+        <v>150577027.15879551</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -11343,28 +11343,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155516623.29966182</v>
+        <v>155388850.43726471</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155516623.29966182</v>
+        <v>155388850.43726471</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129178748.16033334</v>
+        <v>129073845.22168684</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>122938742.94696665</v>
+        <v>122843517.54487051</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68079876.221250579</v>
+        <v>68014485.217753351</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>137022905.23545256</v>
+        <v>136914345.15879551</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -12430,30 +12430,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8442745744631628E-3</v>
+        <v>4.8402945058667402E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8390517580846953E-3</v>
+        <v>4.8350759805678009E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8064815640132628E-3</v>
+        <v>3.8033904123520538E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8213478443602476E-3</v>
+        <v>3.8183879199596431E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2567810999687935E-3</v>
+        <v>2.2546134523614312E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.9360350185460918E-3</v>
+        <v>4.9321243122369936E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12487,30 +12487,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.1256443932526452</v>
+        <v>0.12564041318404878</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14598314407337187</v>
+        <v>0.14597916829585497</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13406932038630734</v>
+        <v>0.13406622923464612</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12028920184288532</v>
+        <v>0.12028624191848471</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10028144639165948</v>
+        <v>0.10027927874405212</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.9016877150583498E-2</v>
+        <v>8.9012966444274394E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.1411098313161301E-2</v>
+        <v>3.1410103296012196E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12659,30 +12659,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.966569260002924E-2</v>
+        <v>8.9662707548581938E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8173160116984903E-2</v>
+        <v>9.8169184339468002E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0501041241028243E-2</v>
+        <v>9.0497950089367035E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.0020328759706952E-2</v>
+        <v>8.0017368835306343E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.6408068403512028E-2</v>
+        <v>5.6405900755904674E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1616423998616844E-2</v>
+        <v>5.1612513292307739E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12766,30 +12766,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.966569260002924E-2</v>
+        <v>8.9662707548581938E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8173160116984903E-2</v>
+        <v>9.8169184339468002E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0501041241028243E-2</v>
+        <v>9.0497950089367035E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.0020328759706952E-2</v>
+        <v>8.0017368835306343E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.6408068403512028E-2</v>
+        <v>5.6405900755904674E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1616423998616844E-2</v>
+        <v>5.1612513292307739E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12835,28 +12835,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0479887326362438</v>
+        <v>2.0316074157290633</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0479887326362438</v>
+        <v>2.0316074157290633</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8618079387602215</v>
+        <v>1.8469158324809665</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2101751601941442</v>
+        <v>1.2004952911126283</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0239943663181219</v>
+        <v>1.0158037078645317</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.69817797703508311</v>
+        <v>0.69259343718036237</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12891,28 +12891,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2793859650.9225545</v>
+        <v>2771512311.0145688</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2793859650.9225545</v>
+        <v>2771512311.0145688</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2539872409.929595</v>
+        <v>2519556646.3768806</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1650917066.454237</v>
+        <v>1637711820.1449726</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1396929825.4612772</v>
+        <v>1385756155.5072844</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>952452153.72359812</v>
+        <v>944833742.39133012</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12946,28 +12946,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.97057748226583507</v>
+        <v>0.96284614526670265</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.88551365822936612</v>
+        <v>0.87846624588633559</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.8269723397096389</v>
+        <v>0.82038562909406632</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.64128743321635584</v>
+        <v>0.63618147781694978</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82092605584516964</v>
+        <v>0.81439098216394301</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.66472240257372917</v>
+        <v>0.65945542844319049</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13001,28 +13001,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7236158775204434E-2</v>
+        <v>3.7448984621733884E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7236158775204434E-2</v>
+        <v>3.7448984621733884E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.3851053432004029E-2</v>
+        <v>3.404453147430353E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.2003184730802622E-2</v>
+        <v>2.2128945458297297E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.8618079387602217E-2</v>
+        <v>1.8724492310866942E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2694145037001512E-2</v>
+        <v>1.2766699302863822E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13138,26 +13138,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14025053002585097</v>
+        <v>-0.14025434978253615</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1151587616916165E-2</v>
+        <v>3.1147279233665337E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17570376584984015</v>
+        <v>0.17570558866527541</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27923086307800893</v>
+        <v>0.27922703669499116</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.22422887006872716</v>
+        <v>0.22425619183356593</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13749,23 +13749,23 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.63376955403712</v>
+        <v>1.6338357204650518</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90436479702146999</v>
+        <v>0.90439568754155231</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8951253227120683</v>
+        <v>1.8951954253381176</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5513220215967323</v>
+        <v>3.5514584969402678</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.4570249020473156</v>
+        <v>3.457286842577485</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13857,28 +13857,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.1256443932526452</v>
+        <v>0.12564041318404878</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14598314407337187</v>
+        <v>0.14597916829585497</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13406932038630734</v>
+        <v>0.13406622923464612</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12028920184288532</v>
+        <v>0.12028624191848471</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10028144639165948</v>
+        <v>0.10027927874405212</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.9016877150583498E-2</v>
+        <v>8.9012966444274394E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -14143,30 +14143,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2666917790674992</v>
+        <v>2.284892566496814</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.4844337290054028</v>
+        <v>2.5043648635358693</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.4184605747542012</v>
+        <v>2.4378779065261731</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0271721113883259</v>
+        <v>2.0434420764039483</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3399501601487296</v>
+        <v>1.3507025790943274</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1282905421813463</v>
+        <v>1.137302033847174</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14200,30 +14200,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1212577801227258E-2</v>
+        <v>4.2117835327130211E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.517152234555278E-2</v>
+        <v>4.6163407622781004E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.3972010450076385E-2</v>
+        <v>4.4937841594952496E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.6857674752515016E-2</v>
+        <v>3.7667135048920705E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.4362730184522355E-2</v>
+        <v>2.4897743393443823E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.0514373494206296E-2</v>
+        <v>2.0964092789809659E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14257,23 +14257,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9865752314160865E-2</v>
+        <v>6.0693389442928063E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7952168594715567E-2</v>
+        <v>5.8753350649020396E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0708779520638007E-2</v>
+        <v>5.1409822555485533E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3398749008050005E-2</v>
+        <v>4.3998731713230418E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1013504869264307E-2</v>
+        <v>3.1442263001097454E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878553955.7338853</v>
+        <v>2878458126.0870876</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35981924446.673569</v>
+        <v>35980726576.088593</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12808944138.689201</v>
+        <v>12812668695.34053</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51260883777.86277</v>
+        <v>51263410463.929123</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0742246600000001</v>
+        <v>1.0828863799999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15169,7 +15169,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>40.364928236126403</v>
+        <v>40.692405576707991</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>67.392482076101331</v>
+        <v>67.936981760311028</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3054623149.7796507</v>
+        <v>3054521458.6312323</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2828354768.3144913</v>
+        <v>2828260609.8437333</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3241461765.4060593</v>
+        <v>3241353854.2323022</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2779031006.0065665</v>
+        <v>2778938489.5681601</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3439728523.4177928</v>
+        <v>3439614011.7655716</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2730567402.2457452</v>
+        <v>2730476499.2042398</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3650122435.8362231</v>
+        <v>3650000919.9816751</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2682948956.7017307</v>
+        <v>2682859638.9210496</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3873385270.3458519</v>
+        <v>3873256321.8710008</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2636160930.6354275</v>
+        <v>2636073170.470161</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4110304165.4807053</v>
+        <v>4110167329.7630272</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2590188842.3370461</v>
+        <v>2590102612.6238928</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4361714405.7708282</v>
+        <v>4361569200.3804255</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2545018462.643764</v>
+        <v>2544933736.6931238</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4628502366.6329622</v>
+        <v>4628348279.6317053</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2500635810.5355453</v>
+        <v>2500552562.12326</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15433,7 +15433,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4911608639.3879642</v>
+        <v>4911445127.5245914</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2457027148.8077803</v>
+        <v>2456945352.1670141</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5212031347.422555</v>
+        <v>5211857834.2173834</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2414178979.8193698</v>
+        <v>2414098609.632638</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>5530829665.1869316</v>
+        <v>5530645538.8994055</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2372078041.3149829</v>
+        <v>2371999072.7063093</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5869127552.4348373</v>
+        <v>5868932163.9067745</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2330711302.3201451</v>
+        <v>2330633710.8473701</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15521,7 +15521,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>6228117716.8715992</v>
+        <v>6227910377.2385054</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2290065959.1079354</v>
+        <v>2289989720.7551446</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>6609065819.1808939</v>
+        <v>6608845797.4432945</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2250129431.236001</v>
+        <v>2250054522.4060955</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>7013314935.2555389</v>
+        <v>7013081455.7017555</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2210889357.6526961</v>
+        <v>2210815755.1600866</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>7442290291.3644199</v>
+        <v>7442042530.8357115</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2172333592.87112</v>
+        <v>2172261273.9345522</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7897504288.9499149</v>
+        <v>7897241373.9383392</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2134450203.2098765</v>
+        <v>2134379145.4453785</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>8380561836.7713108</v>
+        <v>8380282840.3400707</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15643,7 +15643,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2097227463.0993893</v>
+        <v>2097157644.5133445</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8893166009.1933041</v>
+        <v>8892869947.7087269</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2060653851.4526396</v>
+        <v>2060585250.4349785</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>9437124050.568512</v>
+        <v>9436809880.2321358</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15687,7 +15687,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2024718048.0991831</v>
+        <v>2024650643.4166942</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>10014353746.883129</v>
+        <v>10014020360.051676</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
@@ -15709,7 +15709,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>1989408930.281363</v>
+        <v>1989342701.0711219</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>10626890187.129696</v>
+        <v>10626536408.409946</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>1954715569.2116208</v>
+        <v>1954650494.9745324</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>11276892938.244968</v>
+        <v>11276517520.349781</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>1920627226.6898479</v>
+        <v>1920563287.2843013</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15763,7 +15763,7 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>11966653658.908955</v>
+        <v>11966255278.259811</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>1887133351.7797232</v>
+        <v>1887070527.4153578</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>12698604179.048414</v>
+        <v>12698181431.108994</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>1854223577.5430174</v>
+        <v>1854161848.7745969</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>13475325073.530041</v>
+        <v>13474876467.854366</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>1821887717.8308413</v>
+        <v>1821827065.5522358</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>14299554760.270876</v>
+        <v>14299078715.248579</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
@@ -15841,7 +15841,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>1790115764.1308577</v>
+        <v>1790056169.5691292</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>15174199154.842346</v>
+        <v>15173693992.12252</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>1758897882.469471</v>
+        <v>1758839327.179064</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>16102341915.606363</v>
+        <v>16101805854.180344</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>1728224410.3680425</v>
+        <v>1728166876.2250738</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>17087255315.503832</v>
+        <v>17086686465.426048</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
@@ -15907,7 +15907,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>1698085853.8521831</v>
+        <v>1698029323.0488322</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15917,7 +15917,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38182789372.245636</v>
+        <v>38181518232.890404</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3794503757.124671</v>
+        <v>3794377434.6862488</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>70305193599.693069</v>
+        <v>70302853076.647736</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15961,7 +15961,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>70305193599.693069</v>
+        <v>70302853076.647736</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15991,19 +15991,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37142889685.047958</v>
+        <v>37141653164.887383</v>
       </c>
       <c r="C56" s="124">
-        <v>38338625325.68676</v>
+        <v>38337348998.412666</v>
       </c>
       <c r="D56" s="124">
-        <v>39570657206.166153</v>
+        <v>39569339863.444107</v>
       </c>
       <c r="E56" s="124">
-        <v>40840558408.041</v>
+        <v>40839198789.167274</v>
       </c>
       <c r="F56" s="124">
-        <v>42149950009.137527</v>
+        <v>42148546799.441254</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16012,19 +16012,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>38304923988.94548</v>
+        <v>38303648783.619156</v>
       </c>
       <c r="C57" s="124">
-        <v>40860750982.9702</v>
+        <v>40859390691.867523</v>
       </c>
       <c r="D57" s="124">
-        <v>43677269772.820816</v>
+        <v>43675815717.277733</v>
       </c>
       <c r="E57" s="124">
-        <v>46785460097.189507</v>
+        <v>46783902567.198624</v>
       </c>
       <c r="F57" s="124">
-        <v>50219725580.411713</v>
+        <v>50218053720.638153</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16033,19 +16033,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>39743263641.938789</v>
+        <v>39741940552.993446</v>
       </c>
       <c r="C58" s="124">
-        <v>44148661620.958511</v>
+        <v>44147191872.357376</v>
       </c>
       <c r="D58" s="124">
-        <v>49326073796.059967</v>
+        <v>49324431686.757011</v>
       </c>
       <c r="E58" s="124">
-        <v>55428752803.37336</v>
+        <v>55426907530.40461</v>
       </c>
       <c r="F58" s="124">
-        <v>62640009312.281334</v>
+        <v>62637923970.106033</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16054,19 +16054,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>41208701085.342056</v>
+        <v>41207329210.667908</v>
       </c>
       <c r="C59" s="124">
-        <v>47687525506.916924</v>
+        <v>47685937946.358307</v>
       </c>
       <c r="D59" s="124">
-        <v>55769823762.271301</v>
+        <v>55767967134.743988</v>
       </c>
       <c r="E59" s="124">
-        <v>65908525094.778305</v>
+        <v>65906330940.776695</v>
       </c>
       <c r="F59" s="124">
-        <v>78686872412.497101</v>
+        <v>78684252855.835342</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16075,19 +16075,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>42571639224.844902</v>
+        <v>42570221976.735863</v>
       </c>
       <c r="C60" s="124">
-        <v>51173426824.192696</v>
+        <v>51171723214.848076</v>
       </c>
       <c r="D60" s="124">
-        <v>62522677805.301147</v>
+        <v>62520596369.197105</v>
       </c>
       <c r="E60" s="124">
-        <v>77638174533.580215</v>
+        <v>77635589889.012833</v>
       </c>
       <c r="F60" s="124">
-        <v>97931585263.946564</v>
+        <v>97928325033.507767</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16096,19 +16096,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>43773940259.729683</v>
+        <v>43772482985.939247</v>
       </c>
       <c r="C61" s="124">
-        <v>54438004300.662155</v>
+        <v>54436192010.601006</v>
       </c>
       <c r="D61" s="124">
-        <v>69274673692.763107</v>
+        <v>69272367476.651108</v>
       </c>
       <c r="E61" s="124">
-        <v>90218469357.257004</v>
+        <v>90215465903.374878</v>
       </c>
       <c r="F61" s="124">
-        <v>120152471910.52258</v>
+        <v>120148471926.80779</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16158,23 +16158,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>40.364928236126403</v>
+        <v>40.692405576707991</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>40.364928236126403</v>
+        <v>40.692405576707991</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>40.364928236126403</v>
+        <v>40.692405576707991</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>40.364928236126403</v>
+        <v>40.692405576707991</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>40.364928236126403</v>
+        <v>40.692405576707991</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16185,23 +16185,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>41.279120015080039</v>
+        <v>41.613938014145504</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>42.220691438876045</v>
+        <v>42.56306994594366</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>43.190844014779287</v>
+        <v>43.541012527074386</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>44.190816451906592</v>
+        <v>44.549014413080187</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>45.221885253612918</v>
+        <v>45.588362357216958</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16212,23 +16212,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>42.194153620197028</v>
+        <v>42.536319037332831</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>44.206716915922236</v>
+        <v>44.565042552577879</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>46.42455965387984</v>
+        <v>46.800693836275137</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>48.872076554506236</v>
+        <v>49.267863490420694</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>51.576358446617036</v>
+        <v>51.993859874251022</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16239,23 +16239,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>43.326761421573295</v>
+        <v>43.678021305819279</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>46.795752983351662</v>
+        <v>47.174867725762788</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>50.872660275907336</v>
+        <v>51.284511239310696</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>55.678160728178128</v>
+        <v>56.128598275355671</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>61.356600700765469</v>
+        <v>61.852634248169259</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16266,23 +16266,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>44.480707137644828</v>
+        <v>44.841232825418722</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>49.582399959887397</v>
+        <v>49.983890558481903</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>55.946734029391642</v>
+        <v>56.399328131602253</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>63.930364461274657</v>
+        <v>64.447064482846159</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>73.9925607100012</v>
+        <v>74.590056848930331</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16293,23 +16293,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.553940686050225</v>
+        <v>45.923084085264612</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>52.327342031503029</v>
+        <v>52.750873609648714</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>61.26420904634891</v>
+        <v>61.759500719238567</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>73.166772867417436</v>
+        <v>73.757638202316045</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>89.146639140250329</v>
+        <v>89.865817531148267</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16319,23 +16319,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>46.500681971308808</v>
+        <v>46.877427390807853</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>54.898004607864458</v>
+        <v>55.342177758691939</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>66.581008316316257</v>
+        <v>67.118992133859507</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>83.073014436477592</v>
+        <v>83.74342362409007</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>106.64427922618833</v>
+        <v>107.50395789624191</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>106.64427922618833</v>
+        <v>107.50395789624191</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>83.073014436477592</v>
+        <v>83.74342362409007</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16415,7 +16415,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.581008316316257</v>
+        <v>67.118992133859507</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>54.898004607864458</v>
+        <v>55.342177758691939</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>46.500681971308808</v>
+        <v>46.877427390807853</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-55</v>
+        <v>-54.25</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0479887326362438</v>
+        <v>2.0316074157290633</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0479887326362438</v>
+        <v>2.0316074157290633</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>69.44229437754278</v>
+        <v>69.970427387501374</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3155072341.2996616</v>
+        <v>3154944568.4372644</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878553955.7338853</v>
+        <v>2878458126.0870876</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.22851253061636267</v>
+        <v>0.22851168306080338</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>55</v>
+        <v>54.25</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>40.364928236126403</v>
+        <v>40.692405576707991</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.581008316316257</v>
+        <v>67.118992133859507</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>54.898004607864458</v>
+        <v>55.342177758691939</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16980,7 +16980,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>83.073014436477592</v>
+        <v>83.74342362409007</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>66.374508427812984</v>
+        <v>66.910834119355357</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>46.500681971308808</v>
+        <v>46.877427390807853</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>106.64427922618833</v>
+        <v>107.50395789624191</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>67.394305644906538</v>
+        <v>67.938819971772304</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>67.392482076101331</v>
+        <v>67.936981760311028</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.17852073528547371</v>
+        <v>0.17856136595451899</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0479887326362438</v>
+        <v>2.0316074157290633</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.2540928842179375</v>
+        <v>3.2280642611438459</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17362,7 +17362,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>24.560607013449911</v>
+        <v>24.759045179217317</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>27.814699897667847</v>
+        <v>27.987109440361163</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.58728412391069718</v>
+        <v>0.58805423096854725</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>55</v>
+        <v>54.25</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10499062561528705</v>
+        <v>0.11274933088119332</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.3140503395809766</v>
+        <v>4.279543398873721</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>39.001334285246841</v>
+        <v>39.316446742923787</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>43.315384624827814</v>
+        <v>43.595990141797508</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.35728420657596816</v>
+        <v>0.35830516102706711</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>5.2778655927944689</v>
+        <v>5.2356493503458212</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17511,7 +17511,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>53.499772682094424</v>
+        <v>53.932025710457864</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17523,7 +17523,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>58.777638274888893</v>
+        <v>59.167675060803688</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.12785453144094927</v>
+        <v>0.12910358046567361</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2E0627-8E99-49F5-9F7D-4B46FF29CC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF73A8F0-C669-4AB4-8DE2-5321E113DCAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4254,7 +4254,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0828863799999999</v>
+        <v>1.08281703</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>27.987109440361163</v>
+        <v>27.985727390895594</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11274933088119332</v>
+        <v>0.11272920573653655</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C45" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177225904.43726471</v>
+        <v>177226919.33197579</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C47" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155388850.43726471</v>
+        <v>155389865.33197579</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008364230.1862549</v>
+        <v>-1008364483.9099326</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3154944568.4372644</v>
+        <v>3154945583.3319759</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878458126.0870876</v>
+        <v>2878458887.258121</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.2117835327130211E-2</v>
+        <v>4.2115149161674061E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7448984621733884E-2</v>
+        <v>3.7451383075961665E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>28.561157081210169</v>
+        <v>28.559335525260224</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.22654492282235422</v>
+        <v>0.22653041447624528</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12812668695.34053</v>
+        <v>12812639111.336733</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>10.170574028383234</v>
+        <v>10.16989920445369</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.187219389936939</v>
+        <v>2.1870793164560149</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>40.692405576707991</v>
+        <v>40.689783631693679</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>1.3459203416904415</v>
+        <v>1.3458341465203663</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>67.12 HKD</v>
+        <v>67.11 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>46.88 HKD</v>
+        <v>46.87 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>67.938819971772304</v>
+        <v>67.934460321660282</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0316074157290633</v>
+        <v>2.0317375318709203</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>3.2280642611438459</v>
+        <v>3.2282710054508783</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>24.759045179217317</v>
+        <v>24.757456385444716</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>27.987109440361163</v>
+        <v>27.985727390895594</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.58805423096854725</v>
+        <v>0.58804813847954274</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>4.279543398873721</v>
+        <v>4.2798174861169844</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>39.316446742923787</v>
+        <v>39.313923797257111</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>43.595990141797508</v>
+        <v>43.593741283374094</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35830516102706711</v>
+        <v>0.35829708402828619</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>5.2356493503458212</v>
+        <v>5.235984672262993</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>53.932025710457864</v>
+        <v>53.928564879639374</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>59.167675060803688</v>
+        <v>59.164549551902368</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12910358046567361</v>
+        <v>0.1290936989597562</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5539,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5566,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6166,23 +6166,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0316074157290633</v>
+        <v>2.0317375318709203</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8469158324809665</v>
+        <v>1.8470341198826548</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2004952911126283</v>
+        <v>1.2005721779237255</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0158037078645317</v>
+        <v>1.0158687659354602</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.69259343718036237</v>
+        <v>0.69263779495599553</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -7504,23 +7504,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0316074157290633</v>
+        <v>2.0317375318709203</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8469158324809665</v>
+        <v>1.8470341198826548</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2004952911126283</v>
+        <v>1.2005721779237255</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0158037078645317</v>
+        <v>1.0158687659354602</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.69259343718036237</v>
+        <v>0.69263779495599553</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8857,11 +8857,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>23.067855663248373</v>
+        <v>23.066378356099818</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3459203416904415</v>
+        <v>1.3458341465203663</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12812668695.34053</v>
+        <v>12812639111.336733</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9119,11 +9119,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2535129153.751214</v>
+        <v>-2535143945.7531133</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2583052100.3297343</v>
+        <v>-2583066892.3316336</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9135,11 +9135,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.091856787413346</v>
+        <v>7.0918154080040061</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.9602827189219125</v>
+        <v>6.9602428606760798</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9152,7 +9152,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5166104200.6594687</v>
+        <v>5166133784.6632671</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9267,11 +9267,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-309051856.05196351</v>
+        <v>-309032063.81280249</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.22654492282235422</v>
+        <v>-0.22653041447624528</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9284,11 +9284,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13874664421.636629</v>
+        <v>13873743828.999479</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>10.170574028383234</v>
+        <v>10.16989920445369</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9301,11 +9301,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2983797666.4032917</v>
+        <v>2983606578.6105309</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.187219389936939</v>
+        <v>2.1870793164560149</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9318,11 +9318,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16549410231.987957</v>
+        <v>16548318343.797207</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>12.131248495497818</v>
+        <v>12.130448106433459</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9902,28 +9902,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155388850.43726471</v>
+        <v>155389865.33197579</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155388850.43726471</v>
+        <v>155389865.33197579</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129073845.22168684</v>
+        <v>129074678.46151268</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>122843517.54487051</v>
+        <v>122844273.91641244</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68014485.217753351</v>
+        <v>68015004.615866184</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>136914345.15879551</v>
+        <v>136915207.44712156</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9957,28 +9957,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033456920.7450194</v>
+        <v>4033457935.6397305</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691453710.4372644</v>
+        <v>4691454725.3319759</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4549741637.2216873</v>
+        <v>4549742470.4615126</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3869796725.5448704</v>
+        <v>3869797481.9164124</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025105485.2177534</v>
+        <v>3025106004.6158662</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2470974217.1587954</v>
+        <v>2470975079.4471216</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008364230.1862549</v>
+        <v>-1008364483.9099326</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10124,30 +10124,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878458126.0870876</v>
+        <v>2878458887.258121</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3154944568.4372644</v>
+        <v>3154945583.3319759</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071185741.2216873</v>
+        <v>3071186574.4615126</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574284032.5448704</v>
+        <v>2574284788.9164124</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701585830.2177534</v>
+        <v>1701586349.6158662</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1432748449.1587954</v>
+        <v>1432749311.4471216</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -10232,30 +10232,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878458126.0870876</v>
+        <v>2878458887.258121</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3154944568.4372644</v>
+        <v>3154945583.3319759</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071185741.2216873</v>
+        <v>3071186574.4615126</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574284032.5448704</v>
+        <v>2574284788.9164124</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701585830.2177534</v>
+        <v>1701586349.6158662</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1432748449.1587954</v>
+        <v>1432749311.4471216</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -11093,23 +11093,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29622296195915621</v>
+        <v>0.29622289787772832</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30731599494819223</v>
+        <v>0.30731593866634166</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31046070199742576</v>
+        <v>0.31046064131630718</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.40419469700309812</v>
+        <v>0.4041946276045506</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36932012995639996</v>
+        <v>0.36932000107592711</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -11231,28 +11231,28 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177225904.43726471</v>
+        <v>177226919.33197579</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>177225904.43726471</v>
+        <v>177226919.33197579</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>145504435.22168684</v>
+        <v>145505268.46151268</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132081317.54487051</v>
+        <v>132082073.91641244</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90699852.217753351</v>
+        <v>90700371.615866184</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150577027.15879551</v>
+        <v>150577889.44712156</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -11343,28 +11343,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155388850.43726471</v>
+        <v>155389865.33197579</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155388850.43726471</v>
+        <v>155389865.33197579</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129073845.22168684</v>
+        <v>129074678.46151268</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>122843517.54487051</v>
+        <v>122844273.91641244</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68014485.217753351</v>
+        <v>68015004.615866184</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>136914345.15879551</v>
+        <v>136915207.44712156</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -12430,30 +12430,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8402945058667402E-3</v>
+        <v>4.8403261193916509E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8350759805678009E-3</v>
+        <v>4.8351075600088387E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8033904123520538E-3</v>
+        <v>3.8034149652454718E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8183879199596431E-3</v>
+        <v>3.8184114305202035E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2546134523614312E-3</v>
+        <v>2.2546306698992625E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.9321243122369936E-3</v>
+        <v>4.9321553748200428E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12487,30 +12487,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12564041318404878</v>
+        <v>0.12564044479757369</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14597916829585497</v>
+        <v>0.14597919987529603</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13406622923464612</v>
+        <v>0.13406625378753953</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12028624191848471</v>
+        <v>0.12028626542904527</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10027927874405212</v>
+        <v>0.10027929596158995</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.9012966444274394E-2</v>
+        <v>8.9012997506857455E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.1410103296012196E-2</v>
+        <v>3.1410111199393423E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12659,30 +12659,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.9662707548581938E-2</v>
+        <v>8.966273125872562E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.8169184339468002E-2</v>
+        <v>9.816921591890905E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0497950089367035E-2</v>
+        <v>9.0497974642260434E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.0017368835306343E-2</v>
+        <v>8.0017392345866897E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.6405900755904674E-2</v>
+        <v>5.64059179734425E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1612513292307739E-2</v>
+        <v>5.1612544354890794E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12766,30 +12766,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.9662707548581938E-2</v>
+        <v>8.966273125872562E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.8169184339468002E-2</v>
+        <v>9.816921591890905E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0497950089367035E-2</v>
+        <v>9.0497974642260434E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.0017368835306343E-2</v>
+        <v>8.0017392345866897E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.6405900755904674E-2</v>
+        <v>5.64059179734425E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1612513292307739E-2</v>
+        <v>5.1612544354890794E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12835,28 +12835,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0316074157290633</v>
+        <v>2.0317375318709203</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0316074157290633</v>
+        <v>2.0317375318709203</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8469158324809665</v>
+        <v>1.8470341198826548</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2004952911126283</v>
+        <v>1.2005721779237255</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0158037078645317</v>
+        <v>1.0158687659354602</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.69259343718036237</v>
+        <v>0.69263779495599553</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12891,28 +12891,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2771512311.0145688</v>
+        <v>2771689815.0373573</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2771512311.0145688</v>
+        <v>2771689815.0373573</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2519556646.3768806</v>
+        <v>2519718013.6703243</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1637711820.1449726</v>
+        <v>1637816708.885711</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1385756155.5072844</v>
+        <v>1385844907.5186787</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>944833742.39133012</v>
+        <v>944894255.12637174</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12946,28 +12946,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.96284614526670265</v>
+        <v>0.96290755699399044</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.87846624588633559</v>
+        <v>0.87852222544838388</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82038562909406632</v>
+        <v>0.82043794884461563</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.63618147781694978</v>
+        <v>0.63622203570379376</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.81439098216394301</v>
+        <v>0.81444289197050368</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.65945542844319049</v>
+        <v>0.65949726695174526</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13001,28 +13001,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7448984621733884E-2</v>
+        <v>3.7451383075961665E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7448984621733884E-2</v>
+        <v>3.7451383075961665E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.404453147430353E-2</v>
+        <v>3.4046711887237874E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.2128945458297297E-2</v>
+        <v>2.2130362726704617E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.8724492310866942E-2</v>
+        <v>1.8725691537980833E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2766699302863822E-2</v>
+        <v>1.2767516957714203E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13138,26 +13138,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14025434978253615</v>
+        <v>-0.14025431944154265</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1147279233665337E-2</v>
+        <v>3.1147313455763159E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17570558866527541</v>
+        <v>0.17570557418637223</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27922703669499116</v>
+        <v>0.27922706708844958</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.22425619183356593</v>
+        <v>0.22425597480842696</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13749,23 +13749,23 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6338357204650518</v>
+        <v>1.6338351948866581</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90439568754155231</v>
+        <v>0.90439544217107859</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8951954253381176</v>
+        <v>1.8951948684953424</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5514584969402678</v>
+        <v>3.5514574128807714</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.457286842577485</v>
+        <v>3.4572847618379856</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13857,28 +13857,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12564041318404878</v>
+        <v>0.12564044479757369</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14597916829585497</v>
+        <v>0.14597919987529603</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13406622923464612</v>
+        <v>0.13406625378753953</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12028624191848471</v>
+        <v>0.12028626542904527</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10027927874405212</v>
+        <v>0.10027929596158995</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.9012966444274394E-2</v>
+        <v>8.9012997506857455E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -14143,30 +14143,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.284892566496814</v>
+        <v>2.2847468420208177</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.5043648635358693</v>
+        <v>2.5042052850480303</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.4378779065261731</v>
+        <v>2.43772244179649</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0434420764039483</v>
+        <v>2.0433118110439699</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3507025790943274</v>
+        <v>1.3506164899279867</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.137302033847174</v>
+        <v>1.1372298834028023</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14200,30 +14200,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.2117835327130211E-2</v>
+        <v>4.2115149161674061E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.6163407622781004E-2</v>
+        <v>4.6160466083834659E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.4937841594952496E-2</v>
+        <v>4.4934975885649583E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.7667135048920705E-2</v>
+        <v>3.7664733844128474E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.4897743393443823E-2</v>
+        <v>2.4896156496368418E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.0964092789809659E-2</v>
+        <v>2.0962762827701424E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878458126.0870876</v>
+        <v>2878458887.258121</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35980726576.088593</v>
+        <v>35980736090.726509</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12812668695.34053</v>
+        <v>12812639111.336733</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51263410463.929123</v>
+        <v>51263390394.56324</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0828863799999999</v>
+        <v>1.08281703</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15169,7 +15169,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>40.692405576707991</v>
+        <v>40.689783631693679</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>67.936981760311028</v>
+        <v>67.932622227435317</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3054521458.6312323</v>
+        <v>3054522266.3599377</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2828260609.8437333</v>
+        <v>2828261357.7406826</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3241353854.2323022</v>
+        <v>3241354711.3664188</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2778938489.5681601</v>
+        <v>2778939224.4225125</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3439614011.7655716</v>
+        <v>3439614921.3270235</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2730476499.2042398</v>
+        <v>2730477221.2434454</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3650000919.9816751</v>
+        <v>3650001885.1772246</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2682859638.9210496</v>
+        <v>2682860348.3685923</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3873256321.8710008</v>
+        <v>3873257346.1035547</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2636073170.470161</v>
+        <v>2636073867.5456271</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4110167329.7630272</v>
+        <v>4110168416.6436338</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2590102612.6238928</v>
+        <v>2590103297.5430393</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4361569200.3804255</v>
+        <v>4361570353.7410069</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2544933736.6931238</v>
+        <v>2544934409.6679449</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4628348279.6317053</v>
+        <v>4628349503.5385647</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2500552562.12326</v>
+        <v>2500553223.3620534</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15433,7 +15433,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4911445127.5245914</v>
+        <v>4911446426.2927513</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2456945352.1670141</v>
+        <v>2456946001.8744445</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5211857834.2173834</v>
+        <v>5211859212.4257994</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2414098609.632638</v>
+        <v>2414099248.0098014</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>5530645538.8994055</v>
+        <v>5530647001.4071083</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2371999072.7063093</v>
+        <v>2371999699.9507947</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5868932163.9067745</v>
+        <v>5868933715.8700018</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2330633710.8473701</v>
+        <v>2330634327.1533203</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15521,7 +15521,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>6227910377.2385054</v>
+        <v>6227912024.1288795</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2289989720.7551446</v>
+        <v>2289990326.3133173</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>6608845797.4432945</v>
+        <v>6608847545.0671148</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2250054522.4060955</v>
+        <v>2250055117.4039211</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>7013081455.7017555</v>
+        <v>7013083310.2204685</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2210815755.1600866</v>
+        <v>2210816339.7817278</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>7442042530.8357115</v>
+        <v>7442044498.7876348</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2172261273.9345522</v>
+        <v>2172261848.3609595</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7897241373.9383392</v>
+        <v>7897243462.2617111</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2134379145.4453785</v>
+        <v>2134379709.8543468</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>8380282840.3400707</v>
+        <v>8380285056.3975124</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15643,7 +15643,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2097157644.5133445</v>
+        <v>2097158199.0795679</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8892869947.7087269</v>
+        <v>8892872299.3132</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2060585250.4349785</v>
+        <v>2060585795.3301046</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>9436809880.2321358</v>
+        <v>9436812375.6744919</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15687,7 +15687,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2024650643.4166942</v>
+        <v>2024651178.8093784</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>10014020360.051676</v>
+        <v>10014023008.129881</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
@@ -15709,7 +15709,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>1989342701.0711219</v>
+        <v>1989343227.1270776</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>10626536408.409946</v>
+        <v>10626539218.4601</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>1954650494.9745324</v>
+        <v>1954651011.8565826</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>11276517520.349781</v>
+        <v>11276520502.279036</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>1920563287.2843013</v>
+        <v>1920563795.1524301</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15763,7 +15763,7 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>11966255278.259811</v>
+        <v>11966258442.581299</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>1887070527.4153578</v>
+        <v>1887071026.4267595</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>12698181431.108994</v>
+        <v>12698184788.978888</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>1854161848.7745969</v>
+        <v>1854162339.0837238</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>13474876467.854366</v>
+        <v>13474880031.111221</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>1821827065.5522358</v>
+        <v>1821827547.3108475</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>14299078715.248579</v>
+        <v>14299082496.455061</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
@@ -15841,7 +15841,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>1790056169.5691292</v>
+        <v>1790056642.9263382</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>15173693992.12252</v>
+        <v>15173698004.609705</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>1758839327.179064</v>
+        <v>1758839792.2813828</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>16101805854.180344</v>
+        <v>16101810112.094709</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>1728166876.2250738</v>
+        <v>1728167333.2164595</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>17086686465.426048</v>
+        <v>17086690983.779356</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
@@ -15907,7 +15907,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>1698029323.0488322</v>
+        <v>1698029772.0707314</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15917,7 +15917,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38181518232.890404</v>
+        <v>38181528329.499222</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3794377434.6862488</v>
+        <v>3794378438.0603008</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>70302853076.647736</v>
+        <v>70302871667.328201</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15961,7 +15961,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>70302853076.647736</v>
+        <v>70302871667.328201</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15991,19 +15991,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37141653164.887383</v>
+        <v>37141662986.517326</v>
       </c>
       <c r="C56" s="124">
-        <v>38337348998.412666</v>
+        <v>38337359136.228912</v>
       </c>
       <c r="D56" s="124">
-        <v>39569339863.444107</v>
+        <v>39569350327.044403</v>
       </c>
       <c r="E56" s="124">
-        <v>40839198789.167274</v>
+        <v>40839209588.565346</v>
       </c>
       <c r="F56" s="124">
-        <v>42148546799.441254</v>
+        <v>42148557945.079483</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16012,19 +16012,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>38303648783.619156</v>
+        <v>38303658912.523819</v>
       </c>
       <c r="C57" s="124">
-        <v>40859390691.867523</v>
+        <v>40859401496.605087</v>
       </c>
       <c r="D57" s="124">
-        <v>43675815717.277733</v>
+        <v>43675827266.782471</v>
       </c>
       <c r="E57" s="124">
-        <v>46783902567.198624</v>
+        <v>46783914938.596756</v>
       </c>
       <c r="F57" s="124">
-        <v>50218053720.638153</v>
+        <v>50218067000.153137</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16033,19 +16033,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>39741940552.993446</v>
+        <v>39741951062.235771</v>
       </c>
       <c r="C58" s="124">
-        <v>44147191872.357376</v>
+        <v>44147203546.511444</v>
       </c>
       <c r="D58" s="124">
-        <v>49324431686.757011</v>
+        <v>49324444729.965202</v>
       </c>
       <c r="E58" s="124">
-        <v>55426907530.40461</v>
+        <v>55426922187.333626</v>
       </c>
       <c r="F58" s="124">
-        <v>62637923970.106033</v>
+        <v>62637940533.895126</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16054,19 +16054,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>41207329210.667908</v>
+        <v>41207340107.413315</v>
       </c>
       <c r="C59" s="124">
-        <v>47685937946.358307</v>
+        <v>47685950556.288025</v>
       </c>
       <c r="D59" s="124">
-        <v>55767967134.743988</v>
+        <v>55767981881.861824</v>
       </c>
       <c r="E59" s="124">
-        <v>65906330940.776695</v>
+        <v>65906348368.853714</v>
       </c>
       <c r="F59" s="124">
-        <v>78684252855.835342</v>
+        <v>78684273662.868652</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16075,19 +16075,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>42570221976.735863</v>
+        <v>42570233233.880638</v>
       </c>
       <c r="C60" s="124">
-        <v>51171723214.848076</v>
+        <v>51171736746.548637</v>
       </c>
       <c r="D60" s="124">
-        <v>62520596369.197105</v>
+        <v>62520612901.960419</v>
       </c>
       <c r="E60" s="124">
-        <v>77635589889.012833</v>
+        <v>77635610418.740707</v>
       </c>
       <c r="F60" s="124">
-        <v>97928325033.507767</v>
+        <v>97928350929.387115</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16096,19 +16096,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>43772482985.939247</v>
+        <v>43772494561.006393</v>
       </c>
       <c r="C61" s="124">
-        <v>54436192010.601006</v>
+        <v>54436206405.548111</v>
       </c>
       <c r="D61" s="124">
-        <v>69272367476.651108</v>
+        <v>69272385794.832993</v>
       </c>
       <c r="E61" s="124">
-        <v>90215465903.374878</v>
+        <v>90215489759.688324</v>
       </c>
       <c r="F61" s="124">
-        <v>120148471926.80779</v>
+        <v>120148503698.51767</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16158,23 +16158,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>40.692405576707991</v>
+        <v>40.689783631693679</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>40.692405576707991</v>
+        <v>40.689783631693679</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>40.692405576707991</v>
+        <v>40.689783631693679</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>40.692405576707991</v>
+        <v>40.689783631693679</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>40.692405576707991</v>
+        <v>40.689783631693679</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16185,23 +16185,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>41.613938014145504</v>
+        <v>41.611257296200897</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>42.56306994594366</v>
+        <v>42.560328694845133</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>43.541012527074386</v>
+        <v>43.538208905354018</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>44.549014413080187</v>
+        <v>44.546146503634091</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>45.588362357216958</v>
+        <v>45.58542816087548</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16212,23 +16212,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>42.536319037332831</v>
+        <v>42.533579492337346</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>44.565042552577879</v>
+        <v>44.562173620898953</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>46.800693836275137</v>
+        <v>46.797682320600522</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>49.267863490420694</v>
+        <v>49.264694625113847</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>51.993859874251022</v>
+        <v>51.990517152019592</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16239,23 +16239,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>43.678021305819279</v>
+        <v>43.675208946037102</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>47.174867725762788</v>
+        <v>47.171832346255449</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>51.284511239310696</v>
+        <v>51.281213757481204</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>56.128598275355671</v>
+        <v>56.12499185031573</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>61.852634248169259</v>
+        <v>61.848662759075594</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16266,23 +16266,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>44.841232825418722</v>
+        <v>44.83834627904605</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>49.983890558481903</v>
+        <v>49.980676026840086</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>56.399328131602253</v>
+        <v>56.395704440119694</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>64.447064482846159</v>
+        <v>64.442927527773023</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>74.590056848930331</v>
+        <v>74.585273000314274</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16293,23 +16293,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.923084085264612</v>
+        <v>45.920128541246157</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>52.750873609648714</v>
+        <v>52.747482607059816</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>61.759500719238567</v>
+        <v>61.755535169957945</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>73.757638202316045</v>
+        <v>73.752907443185592</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>89.865817531148267</v>
+        <v>89.860059434441283</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16319,23 +16319,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>46.877427390807853</v>
+        <v>46.874410981267687</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>55.342177758691939</v>
+        <v>55.338621489497143</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>67.118992133859507</v>
+        <v>67.114684770224258</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>83.74342362409007</v>
+        <v>83.738055997664702</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>107.50395789624191</v>
+        <v>107.49707488504225</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>107.50395789624191</v>
+        <v>107.49707488504225</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>83.74342362409007</v>
+        <v>83.738055997664702</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16415,7 +16415,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>67.118992133859507</v>
+        <v>67.114684770224258</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>55.342177758691939</v>
+        <v>55.338621489497143</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>46.877427390807853</v>
+        <v>46.874410981267687</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16582,7 +16582,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0316074157290633</v>
+        <v>2.0317375318709203</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0316074157290633</v>
+        <v>2.0317375318709203</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>69.970427387501374</v>
+        <v>69.966197853531199</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3154944568.4372644</v>
+        <v>3154945583.3319759</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878458126.0870876</v>
+        <v>2878458887.258121</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.22851168306080338</v>
+        <v>0.2285116897931645</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>40.692405576707991</v>
+        <v>40.689783631693679</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>67.118992133859507</v>
+        <v>67.114684770224258</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>55.342177758691939</v>
+        <v>55.338621489497143</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16980,7 +16980,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>83.74342362409007</v>
+        <v>83.738055997664702</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>66.910834119355357</v>
+        <v>66.906540031494217</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>46.877427390807853</v>
+        <v>46.874410981267687</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>107.50395789624191</v>
+        <v>107.49707488504225</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>67.938819971772304</v>
+        <v>67.934460321660282</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>67.936981760311028</v>
+        <v>67.932622227435317</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.17856136595451899</v>
+        <v>0.17856104323192476</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0316074157290633</v>
+        <v>2.0317375318709203</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.2280642611438459</v>
+        <v>3.2282710054508783</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17362,7 +17362,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>24.759045179217317</v>
+        <v>24.757456385444716</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>27.987109440361163</v>
+        <v>27.985727390895594</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.58805423096854725</v>
+        <v>0.58804813847954274</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11274933088119332</v>
+        <v>0.11272920573653655</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.279543398873721</v>
+        <v>4.2798174861169844</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>39.316446742923787</v>
+        <v>39.313923797257111</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>43.595990141797508</v>
+        <v>43.593741283374094</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.35830516102706711</v>
+        <v>0.35829708402828619</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>5.2356493503458212</v>
+        <v>5.235984672262993</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17511,7 +17511,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>53.932025710457864</v>
+        <v>53.928564879639374</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17523,7 +17523,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>59.167675060803688</v>
+        <v>59.164549551902368</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.12910358046567361</v>
+        <v>0.1290936989597562</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF73A8F0-C669-4AB4-8DE2-5321E113DCAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF47A6F-09E0-46DF-8D93-22824D3ED030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2377,6 +2377,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -4094,7 +4106,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4116,7 +4128,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4159,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4194,10 +4206,10 @@
         <v>427</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4206,7 +4218,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>54.25</v>
+        <v>55.3</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4227,7 +4239,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>74007.675749000002</v>
+        <v>75440.082376399994</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4254,7 +4266,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.08281703</v>
+        <v>1.0845693200000002</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4310,7 +4322,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4335,7 +4347,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>27.985727390895594</v>
+        <v>28.02065621001972</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,10 +4362,14 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11272920573653655</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+        <v>0.1059109318546132</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4494,7 +4510,7 @@
       </c>
       <c r="C45" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>177226919.33197579</v>
+        <v>177201315.4343105</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4524,7 +4540,7 @@
       </c>
       <c r="C47" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>155389865.33197579</v>
+        <v>155364261.4343105</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4564,7 +4580,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-1008364483.9099326</v>
+        <v>-1008358082.9355162</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4617,7 +4633,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>3154945583.3319759</v>
+        <v>3154919979.4343109</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4630,7 +4646,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2878458887.258121</v>
+        <v>2878439684.3348718</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4643,7 +4659,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.2115149161674061E-2</v>
+        <v>4.1382077971811766E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4668,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7451383075961665E-2</v>
+        <v>3.6680921241915881E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4709,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4721,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4774,7 +4790,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>28.559335525260224</v>
+        <v>28.605361398014882</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4841,7 +4857,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.22653041447624528</v>
+        <v>0.22689700178415143</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4899,7 +4915,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>12812639111.336733</v>
+        <v>12813385460.487564</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4912,7 +4928,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>10.16989920445369</v>
+        <v>10.186950209839438</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4943,7 +4959,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1870793164560149</v>
+        <v>2.1906186006649389</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4965,7 +4981,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>40.689783631693679</v>
+        <v>40.756033206735104</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4978,7 +4994,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>1.3458341465203663</v>
+        <v>1.3480120691529707</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5036,7 +5052,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>107.5 HKD</v>
+        <v>107.67 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5058,7 +5074,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>83.74 HKD</v>
+        <v>83.87 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5080,7 +5096,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>67.11 HKD</v>
+        <v>67.22 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5102,7 +5118,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>55.34 HKD</v>
+        <v>55.43 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5124,7 +5140,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>46.87 HKD</v>
+        <v>46.95 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5137,7 +5153,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>67.934460321660282</v>
+        <v>68.044617081498245</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5210,7 +5226,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>2.0317375318709203</v>
+        <v>2.0284549446779483</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5246,7 +5262,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>3.2282710054508783</v>
+        <v>3.2230552327973219</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5272,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>24.757456385444716</v>
+        <v>24.797600977222398</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5281,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>27.985727390895594</v>
+        <v>28.02065621001972</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5307,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.58804813847954274</v>
+        <v>0.58820172099052481</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5308,40 +5324,40 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>4.2798174861169844</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
+        <v>4.2729027769836412</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>39.313923797257111</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+        <v>39.377671922163337</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>43.593741283374094</v>
+        <v>43.650574699146979</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>426</v>
       </c>
@@ -5354,21 +5370,21 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35829708402828619</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+        <v>0.35850069305458931</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5377,40 +5393,40 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>5.235984672262993</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
+        <v>5.2275251266976062</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>53.928564879639374</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+        <v>54.016010867165065</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>59.164549551902368</v>
+        <v>59.243535993862672</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>426</v>
       </c>
@@ -5423,127 +5439,196 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>0.1290936989597562</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+        <v>0.12934279690477735</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>4.8938567403557274</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>48.771686481876429</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>53.665543222232159</v>
+      </c>
+      <c r="D163" s="342" t="str">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.21129697585389229</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="344"/>
+      <c r="D178" s="344"/>
+      <c r="E178" s="344"/>
+      <c r="F178" s="344"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="349"/>
+      <c r="D181" s="349"/>
+      <c r="E181" s="349"/>
+      <c r="F181" s="349"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="349"/>
+      <c r="D182" s="349"/>
+      <c r="E182" s="349"/>
+      <c r="F182" s="349"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B78:F78"/>
@@ -6166,23 +6251,23 @@
       </c>
       <c r="C25" s="39">
         <f>2.2/Exchange_Rate</f>
-        <v>2.0317375318709203</v>
+        <v>2.0284549446779483</v>
       </c>
       <c r="D25" s="39">
         <f>2/Exchange_Rate</f>
-        <v>1.8470341198826548</v>
+        <v>1.8440499497072254</v>
       </c>
       <c r="E25" s="39">
         <f>1.3/Exchange_Rate</f>
-        <v>1.2005721779237255</v>
+        <v>1.1986324673096966</v>
       </c>
       <c r="F25" s="39">
         <f>1.1/Exchange_Rate</f>
-        <v>1.0158687659354602</v>
+        <v>1.0142274723389741</v>
       </c>
       <c r="G25" s="39">
         <f>0.75/Exchange_Rate</f>
-        <v>0.69263779495599553</v>
+        <v>0.69151873114020956</v>
       </c>
       <c r="H25" s="39"/>
       <c r="I25" s="39"/>
@@ -6196,7 +6281,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7504,23 +7589,23 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>2.0317375318709203</v>
+        <v>2.0284549446779483</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.8470341198826548</v>
+        <v>1.8440499497072254</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.2005721779237255</v>
+        <v>1.1986324673096966</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0158687659354602</v>
+        <v>1.0142274723389741</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
-        <v>0.69263779495599553</v>
+        <v>0.69151873114020956</v>
       </c>
       <c r="H65" s="73" t="str">
         <f t="shared" si="33"/>
@@ -8857,11 +8942,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>23.066378356099818</v>
+        <v>23.103705977489014</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.3458341465203663</v>
+        <v>1.3480120691529707</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9052,7 +9137,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>12812639111.336733</v>
+        <v>12813385460.487564</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9119,11 +9204,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2535143945.7531133</v>
+        <v>-2534770771.1776977</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2583066892.3316336</v>
+        <v>-2582693717.7562184</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9135,11 +9220,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>7.0918154080040061</v>
+        <v>7.0928594807990297</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>6.9602428606760798</v>
+        <v>6.9612485492935345</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9152,7 +9237,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>5166133784.6632671</v>
+        <v>5165387435.5124369</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9267,11 +9352,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-309032063.81280249</v>
+        <v>-309532161.04076964</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.22653041447624528</v>
+        <v>-0.22689700178415143</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9284,11 +9369,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>13873743828.999479</v>
+        <v>13897004755.778887</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>10.16989920445369</v>
+        <v>10.186950209839438</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9301,11 +9386,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>2983606578.6105309</v>
+        <v>2988434858.7601643</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.1870793164560149</v>
+        <v>2.1906186006649389</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9318,11 +9403,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>16548318343.797207</v>
+        <v>16575907453.498281</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>12.130448106433459</v>
+        <v>12.150671808720226</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9902,28 +9987,28 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>155389865.33197579</v>
+        <v>155364261.4343105</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>155389865.33197579</v>
+        <v>155364261.4343105</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>129074678.46151268</v>
+        <v>129053657.37725815</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>122844273.91641244</v>
+        <v>122825192.07536528</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>68015004.615866184</v>
+        <v>68001901.171751663</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>136915207.44712156</v>
+        <v>136893453.52347052</v>
       </c>
       <c r="L12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -9957,28 +10042,28 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>4033457935.6397305</v>
+        <v>4033432331.742065</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>4691454725.3319759</v>
+        <v>4691429121.4343109</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>4549742470.4615126</v>
+        <v>4549721449.3772583</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3869797481.9164124</v>
+        <v>3869778400.0753651</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3025106004.6158662</v>
+        <v>3025092901.1717515</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2470975079.4471216</v>
+        <v>2470953325.5234704</v>
       </c>
       <c r="L13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -10012,7 +10097,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-1008364483.9099326</v>
+        <v>-1008358082.9355162</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10124,30 +10209,30 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2878458887.258121</v>
+        <v>2878439684.3348718</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>3154945583.3319759</v>
+        <v>3154919979.4343109</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3071186574.4615126</v>
+        <v>3071165553.3772583</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2574284788.9164124</v>
+        <v>2574265707.0753651</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>1701586349.6158662</v>
+        <v>1701573246.1717515</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1432749311.4471216</v>
+        <v>1432727557.5234704</v>
       </c>
       <c r="L16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -10232,30 +10317,30 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2878458887.258121</v>
+        <v>2878439684.3348718</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>3154945583.3319759</v>
+        <v>3154919979.4343109</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3071186574.4615126</v>
+        <v>3071165553.3772583</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2574284788.9164124</v>
+        <v>2574265707.0753651</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>1701586349.6158662</v>
+        <v>1701573246.1717515</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1432749311.4471216</v>
+        <v>1432727557.5234704</v>
       </c>
       <c r="L19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -11093,23 +11178,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.29622289787772832</v>
+        <v>0.29622451454091708</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.30731593866634166</v>
+        <v>0.30731735855859471</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31046064131630718</v>
+        <v>0.31046217219482181</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.4041946276045506</v>
+        <v>0.40419637840754652</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36932000107592711</v>
+        <v>0.36932325251698966</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -11231,28 +11316,28 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>177226919.33197579</v>
+        <v>177201315.4343105</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>177226919.33197579</v>
+        <v>177201315.4343105</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>145505268.46151268</v>
+        <v>145484247.37725815</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>132082073.91641244</v>
+        <v>132062992.07536528</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>90700371.615866184</v>
+        <v>90687268.171751663</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
-        <v>150577889.44712156</v>
+        <v>150556135.52347052</v>
       </c>
       <c r="L48" s="328" t="str">
         <f t="shared" si="19"/>
@@ -11343,28 +11428,28 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>155389865.33197579</v>
+        <v>155364261.4343105</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>155389865.33197579</v>
+        <v>155364261.4343105</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>129074678.46151268</v>
+        <v>129053657.37725815</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>122844273.91641244</v>
+        <v>122825192.07536528</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>68015004.615866184</v>
+        <v>68001901.171751663</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>136915207.44712156</v>
+        <v>136893453.52347052</v>
       </c>
       <c r="L50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -11986,7 +12071,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12318,7 +12403,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12430,30 +12515,30 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>4.8403261193916509E-3</v>
+        <v>4.8395285692144708E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8351075600088387E-3</v>
+        <v>4.8343108697040836E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8034149652454718E-3</v>
+        <v>3.8027955416110896E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8184114305202035E-3</v>
+        <v>3.8178183029966574E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.2546306698992625E-3</v>
+        <v>2.2541963035833477E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.9321553748200428E-3</v>
+        <v>4.9313717238768096E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12487,30 +12572,30 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12564044479757369</v>
+        <v>0.12563964724739651</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.14597919987529603</v>
+        <v>0.14597840318499128</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.13406625378753953</v>
+        <v>0.13406563436390515</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12028626542904527</v>
+        <v>0.12028567230152172</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10027929596158995</v>
+        <v>0.10027886159527404</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>8.9012997506857455E-2</v>
+        <v>8.9012213855914207E-2</v>
       </c>
       <c r="L81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12544,7 +12629,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.1410111199393423E-2</v>
+        <v>3.1409911811849128E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12659,30 +12744,30 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>8.966273125872562E-2</v>
+        <v>8.9662133096092722E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.816921591890905E-2</v>
+        <v>9.8168419228604309E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>9.0497974642260434E-2</v>
+        <v>9.0497355218626063E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>8.0017392345866897E-2</v>
+        <v>8.0016799218343357E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>5.64059179734425E-2</v>
+        <v>5.6405483607126584E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1612544354890794E-2</v>
+        <v>5.1611760703947553E-2</v>
       </c>
       <c r="L84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -12766,30 +12851,30 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>8.966273125872562E-2</v>
+        <v>8.9662133096092722E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.816921591890905E-2</v>
+        <v>9.8168419228604309E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>9.0497974642260434E-2</v>
+        <v>9.0497355218626063E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>8.0017392345866897E-2</v>
+        <v>8.0016799218343357E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>5.64059179734425E-2</v>
+        <v>5.6405483607126584E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1612544354890794E-2</v>
+        <v>5.1611760703947553E-2</v>
       </c>
       <c r="L87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -12835,28 +12920,28 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>2.0317375318709203</v>
+        <v>2.0284549446779483</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>2.0317375318709203</v>
+        <v>2.0284549446779483</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>1.8470341198826548</v>
+        <v>1.8440499497072254</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
-        <v>1.2005721779237255</v>
+        <v>1.1986324673096966</v>
       </c>
       <c r="J90" s="113">
         <f>Data!F65</f>
-        <v>1.0158687659354602</v>
+        <v>1.0142274723389741</v>
       </c>
       <c r="K90" s="113">
         <f>Data!G65</f>
-        <v>0.69263779495599553</v>
+        <v>0.69151873114020956</v>
       </c>
       <c r="L90" s="113" t="str">
         <f>Data!H65</f>
@@ -12891,28 +12976,28 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2771689815.0373573</v>
+        <v>2767211720.1323748</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2771689815.0373573</v>
+        <v>2767211720.1323748</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2519718013.6703243</v>
+        <v>2515647018.3021584</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>1637816708.885711</v>
+        <v>1635170561.8964031</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1385844907.5186787</v>
+        <v>1383605860.0661874</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
-        <v>944894255.12637174</v>
+        <v>943367631.8633095</v>
       </c>
       <c r="L91" s="74" t="str">
         <f t="shared" si="37"/>
@@ -12946,28 +13031,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.96290755699399044</v>
+        <v>0.96135824390977331</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.87852222544838388</v>
+        <v>0.87710995466469688</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0.82043794884461563</v>
+        <v>0.81911801059887035</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
-        <v>0.63622203570379376</v>
+        <v>0.63519882869982669</v>
       </c>
       <c r="J92" s="171">
         <f t="shared" si="38"/>
-        <v>0.81444289197050368</v>
+        <v>0.81313329483703611</v>
       </c>
       <c r="K92" s="171">
         <f t="shared" si="38"/>
-        <v>0.65949726695174526</v>
+        <v>0.65844174414705881</v>
       </c>
       <c r="L92" s="171" t="str">
         <f t="shared" si="38"/>
@@ -13001,28 +13086,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7451383075961665E-2</v>
+        <v>3.6680921241915881E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7451383075961665E-2</v>
+        <v>3.6680921241915881E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.4046711887237874E-2</v>
+        <v>3.3346292038105345E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.2130362726704617E-2</v>
+        <v>2.1675089824768477E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>1.8725691537980833E-2</v>
+        <v>1.8340460620957941E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.2767516957714203E-2</v>
+        <v>1.2504859514289505E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13138,26 +13223,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.14025431944154265</v>
+        <v>-0.140255084892144</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>3.1147313455763159E-2</v>
+        <v>3.114645009233441E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17570557418637223</v>
+        <v>0.1757059394637821</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.27922706708844958</v>
+        <v>0.27922630031508455</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.22425597480842696</v>
+        <v>0.22426144999355135</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13749,23 +13834,23 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.6338351948866581</v>
+        <v>1.6338484543510514</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.90439544217107859</v>
+        <v>0.90440163245045579</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.8951948684953424</v>
+        <v>1.8952089166983443</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>3.5514574128807714</v>
+        <v>3.5514847618790237</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>3.4572847618379856</v>
+        <v>3.4573372557740134</v>
       </c>
       <c r="L114" s="334" t="str">
         <f>IF(L$4="","",Data!H$22/L19)</f>
@@ -13857,28 +13942,28 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12564044479757369</v>
+        <v>0.12563964724739651</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.14597919987529603</v>
+        <v>0.14597840318499128</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.13406625378753953</v>
+        <v>0.13406563436390515</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12028626542904527</v>
+        <v>0.12028567230152172</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10027929596158995</v>
+        <v>0.10027886159527404</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>8.9012997506857455E-2</v>
+        <v>8.9012213855914207E-2</v>
       </c>
       <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -14143,30 +14228,30 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.2847468420208177</v>
+        <v>2.2884289118411902</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.5042052850480303</v>
+        <v>2.5082374088902228</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>2.43772244179649</v>
+        <v>2.4416506219143783</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0433118110439699</v>
+        <v>2.0466032701302974</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3506164899279867</v>
+        <v>1.3527917341282358</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1372298834028023</v>
+        <v>1.1390529331817276</v>
       </c>
       <c r="L124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14200,30 +14285,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.2115149161674061E-2</v>
+        <v>4.1382077971811766E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.6160466083834659E-2</v>
+        <v>4.5356915169805119E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.4934975885649583E-2</v>
+        <v>4.4152814139500514E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>3.7664733844128474E-2</v>
+        <v>3.7009100725683503E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.4896156496368418E-2</v>
+        <v>2.4462780002318912E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>2.0962762827701424E-2</v>
+        <v>2.0597702227517681E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -14257,23 +14342,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0693389442928063E-2</v>
+        <v>5.9540983314264877E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8753350649020396E-2</v>
+        <v>5.7637780699988365E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1409822555485533E-2</v>
+        <v>5.0433686684178851E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3998731713230418E-2</v>
+        <v>4.3163312756650099E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1442263001097454E-2</v>
+        <v>3.0845258007405733E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15043,7 +15128,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2878458887.258121</v>
+        <v>2878439684.3348718</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15075,7 +15160,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35980736090.726509</v>
+        <v>35980496054.185898</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15109,7 +15194,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>12812639111.336733</v>
+        <v>12813385460.487564</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15141,7 +15226,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>51263390394.56324</v>
+        <v>51263896707.173462</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15155,7 +15240,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.08281703</v>
+        <v>1.0845693200000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15169,7 +15254,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>40.689783631693679</v>
+        <v>40.756033206735104</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15222,7 +15307,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>67.932622227435317</v>
+        <v>68.042776025023315</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15257,7 +15342,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>3054522266.3599377</v>
+        <v>3054501888.8736014</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15269,7 +15354,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2828261357.7406826</v>
+        <v>2828242489.6977787</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15279,7 +15364,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3241354711.3664188</v>
+        <v>3241333087.4738483</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15291,7 +15376,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2778939224.4225125</v>
+        <v>2778920685.4199657</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15301,7 +15386,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3439614921.3270235</v>
+        <v>3439591974.7907248</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15313,7 +15398,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2730477221.2434454</v>
+        <v>2730459005.5431118</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15323,7 +15408,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3650001885.1772246</v>
+        <v>3649977535.0965714</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15335,7 +15420,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2682860348.3685923</v>
+        <v>2682842450.3323941</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15345,7 +15430,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3873257346.1035547</v>
+        <v>3873231506.6295671</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15357,7 +15442,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2636073867.5456271</v>
+        <v>2636056281.633811</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15367,7 +15452,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>4110168416.6436338</v>
+        <v>4110140996.6763048</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15379,7 +15464,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2590103297.5430393</v>
+        <v>2590086018.3124585</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15389,7 +15474,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4361570353.7410069</v>
+        <v>4361541256.6081209</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15401,7 +15486,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2544934409.6679449</v>
+        <v>2544917431.7703767</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15411,7 +15496,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4628349503.5385647</v>
+        <v>4628318626.6548681</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15423,7 +15508,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2500553223.3620534</v>
+        <v>2500536541.542542</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15433,7 +15518,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4911446426.2927513</v>
+        <v>4911413660.7982769</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15445,7 +15530,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2456946001.8744445</v>
+        <v>2456929610.969676</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15455,7 +15540,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>5211859212.4257994</v>
+        <v>5211824442.8020649</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15467,7 +15552,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2414099248.0098014</v>
+        <v>2414083142.9465046</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15477,7 +15562,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>5530647001.4071083</v>
+        <v>5530610105.0698509</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15489,7 +15574,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2371999699.9507947</v>
+        <v>2371983875.7441726</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15499,7 +15584,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5868933715.8700018</v>
+        <v>5868894562.7369823</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15511,7 +15596,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2330634327.1533203</v>
+        <v>2330618778.9055042</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15521,7 +15606,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>6227912024.1288795</v>
+        <v>6227870476.161273</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15533,7 +15618,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2289990326.3133173</v>
+        <v>2289975049.211854</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15543,7 +15628,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>6608847545.0671148</v>
+        <v>6608803455.7828331</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15555,7 +15640,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2250055117.4039211</v>
+        <v>2250040106.7202816</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15565,7 +15650,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>7013083310.2204685</v>
+        <v>7013036524.177721</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15577,7 +15662,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2210816339.7817278</v>
+        <v>2210801590.8698435</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15587,7 +15672,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>7442044498.7876348</v>
+        <v>7441994851.0369024</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15599,7 +15684,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>2172261848.3609595</v>
+        <v>2172247356.6557846</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15609,7 +15694,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7897243462.2617111</v>
+        <v>7897190777.7641983</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15621,7 +15706,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>2134379709.8543468</v>
+        <v>2134365470.8704464</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15631,7 +15716,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>8380285056.3975124</v>
+        <v>8380229149.4080267</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15643,7 +15728,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>2097158199.0795679</v>
+        <v>2097144208.4097283</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15653,7 +15738,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8892872299.3132</v>
+        <v>8892812972.7252865</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15665,7 +15750,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>2060585795.3301046</v>
+        <v>2060572048.6439693</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15675,7 +15760,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>9436812375.6744919</v>
+        <v>9436749420.3255138</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15687,7 +15772,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>2024651178.8093784</v>
+        <v>2024637671.8521085</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15697,7 +15782,7 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>10014023008.129881</v>
+        <v>10013956202.063589</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
@@ -15709,7 +15794,7 @@
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>1989343227.1270776</v>
+        <v>1989329955.7180343</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -15719,7 +15804,7 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>10626539218.4601</v>
+        <v>10626468326.144104</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
@@ -15731,7 +15816,7 @@
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>1954651011.8565826</v>
+        <v>1954637971.8880334</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -15741,7 +15826,7 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>11276520502.279036</v>
+        <v>11276445273.774406</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
@@ -15753,7 +15838,7 @@
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>1920563795.1524301</v>
+        <v>1920550982.5882773</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -15763,7 +15848,7 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>11966258442.581299</v>
+        <v>11966178612.661381</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
@@ -15775,7 +15860,7 @@
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>1887071026.4267595</v>
+        <v>1887058437.3012912</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -15785,7 +15870,7 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>12698184788.978888</v>
+        <v>12698100076.194214</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
@@ -15797,7 +15882,7 @@
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>1854162339.0837238</v>
+        <v>1854149969.5003865</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -15807,7 +15892,7 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>13474880031.111221</v>
+        <v>13474790136.797226</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
@@ -15819,7 +15904,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>1821827547.3108475</v>
+        <v>1821815393.4410391</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -15829,7 +15914,7 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>14299082496.455061</v>
+        <v>14298987103.67911</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
@@ -15841,7 +15926,7 @@
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>1790056642.9263382</v>
+        <v>1790044701.0082242</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -15851,7 +15936,7 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>15173698004.609705</v>
+        <v>15173596777.053707</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
@@ -15863,7 +15948,7 @@
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>1758839792.2813828</v>
+        <v>1758828058.618731</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -15873,7 +15958,7 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>16101810112.094709</v>
+        <v>16101702692.869398</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
@@ -15885,7 +15970,7 @@
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>1728167333.2164595</v>
+        <v>1728155804.1774974</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -15895,7 +15980,7 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>17086690983.779356</v>
+        <v>17086576994.166025</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
@@ -15907,7 +15992,7 @@
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>1698029772.0707314</v>
+        <v>1698018444.0870202</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -15917,7 +16002,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38181528329.499222</v>
+        <v>38181273610.920013</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15929,7 +16014,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>3794378438.0603008</v>
+        <v>3794353124.8073483</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15940,7 +16025,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>70302871667.328201</v>
+        <v>70302402659.188187</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15961,7 +16046,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>70302871667.328201</v>
+        <v>70302402659.188187</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15991,19 +16076,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37141662986.517326</v>
+        <v>37141415205.141388</v>
       </c>
       <c r="C56" s="124">
-        <v>38337359136.228912</v>
+        <v>38337103378.063202</v>
       </c>
       <c r="D56" s="124">
-        <v>39569350327.044403</v>
+        <v>39569086349.955582</v>
       </c>
       <c r="E56" s="124">
-        <v>40839209588.565346</v>
+        <v>40838937139.92598</v>
       </c>
       <c r="F56" s="124">
-        <v>42148557945.079483</v>
+        <v>42148276761.447906</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16012,19 +16097,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>38303658912.523819</v>
+        <v>38303403379.180771</v>
       </c>
       <c r="C57" s="124">
-        <v>40859401496.605087</v>
+        <v>40859128913.260422</v>
       </c>
       <c r="D57" s="124">
-        <v>43675827266.782471</v>
+        <v>43675535894.353088</v>
       </c>
       <c r="E57" s="124">
-        <v>46783914938.596756</v>
+        <v>46783602831.332756</v>
       </c>
       <c r="F57" s="124">
-        <v>50218067000.153137</v>
+        <v>50217731982.796951</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16033,19 +16118,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>39741951062.235771</v>
+        <v>39741685933.684021</v>
       </c>
       <c r="C58" s="124">
-        <v>44147203546.511444</v>
+        <v>44146909029.412331</v>
       </c>
       <c r="D58" s="124">
-        <v>49324444729.965202</v>
+        <v>49324115674.187943</v>
       </c>
       <c r="E58" s="124">
-        <v>55426922187.333626</v>
+        <v>55426552420.394318</v>
       </c>
       <c r="F58" s="124">
-        <v>62637940533.895126</v>
+        <v>62637522660.438644</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16054,19 +16139,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>41207340107.413315</v>
+        <v>41207065202.882668</v>
       </c>
       <c r="C59" s="124">
-        <v>47685950556.288025</v>
+        <v>47685632431.317505</v>
       </c>
       <c r="D59" s="124">
-        <v>55767981881.861824</v>
+        <v>55767609839.627487</v>
       </c>
       <c r="E59" s="124">
-        <v>65906348368.853714</v>
+        <v>65905908691.026482</v>
       </c>
       <c r="F59" s="124">
-        <v>78684273662.868652</v>
+        <v>78683748740.287766</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16075,19 +16160,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>42570233233.880638</v>
+        <v>42569949237.147141</v>
       </c>
       <c r="C60" s="124">
-        <v>51171736746.548637</v>
+        <v>51171395367.021667</v>
       </c>
       <c r="D60" s="124">
-        <v>62520612901.960419</v>
+        <v>62520195811.226089</v>
       </c>
       <c r="E60" s="124">
-        <v>77635610418.740707</v>
+        <v>77635092492.056122</v>
       </c>
       <c r="F60" s="124">
-        <v>97928350929.387115</v>
+        <v>97927697624.726395</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16096,19 +16181,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>43772494561.006393</v>
+        <v>43772202543.685188</v>
       </c>
       <c r="C61" s="124">
-        <v>54436206405.548111</v>
+        <v>54435843247.922966</v>
       </c>
       <c r="D61" s="124">
-        <v>69272385794.832993</v>
+        <v>69271923661.323425</v>
       </c>
       <c r="E61" s="124">
-        <v>90215489759.688324</v>
+        <v>90214887909.464462</v>
       </c>
       <c r="F61" s="124">
-        <v>120148503698.51767</v>
+        <v>120147702157.62885</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16158,23 +16243,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>40.689783631693679</v>
+        <v>40.756033206735104</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>40.689783631693679</v>
+        <v>40.756033206735104</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>40.689783631693679</v>
+        <v>40.756033206735104</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>40.689783631693679</v>
+        <v>40.756033206735104</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>40.689783631693679</v>
+        <v>40.756033206735104</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16185,23 +16270,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>41.611257296200897</v>
+        <v>41.67899190683049</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>42.560328694845133</v>
+        <v>42.629592817230701</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>43.538208905354018</v>
+        <v>43.60904896742133</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>44.546146503634091</v>
+        <v>44.618610945498389</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>45.58542816087548</v>
+        <v>45.659567496235482</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16212,23 +16297,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>42.533579492337346</v>
+        <v>42.602800506038193</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>44.562173620898953</v>
+        <v>44.634663891867696</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>46.797682320600522</v>
+        <v>46.873775309807002</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>49.264694625113847</v>
+        <v>49.344763420911185</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>51.990517152019592</v>
+        <v>52.074978849768875</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16239,23 +16324,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>43.675208946037102</v>
+        <v>43.746269795679609</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>47.171832346255449</v>
+        <v>47.248528311026838</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>51.281213757481204</v>
+        <v>51.364532350631549</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>56.12499185031573</v>
+        <v>56.216116616475794</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>61.848662759075594</v>
+        <v>61.949011722650987</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16266,23 +16351,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>44.83834627904605</v>
+        <v>44.911281626463122</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>49.980676026840086</v>
+        <v>50.061898689430322</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>56.395704440119694</v>
+        <v>56.487265483349304</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>64.442927527773023</v>
+        <v>64.547457376440448</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>74.585273000314274</v>
+        <v>74.706148127804454</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16293,23 +16378,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>45.920128541246157</v>
+        <v>45.994807275609482</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>52.747482607059816</v>
+        <v>52.833164220996629</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>61.755535169957945</v>
+        <v>61.855734050259784</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>73.752907443185592</v>
+        <v>73.872441140614015</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>89.860059434441283</v>
+        <v>90.005551219281585</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16319,23 +16404,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>46.874410981267687</v>
+        <v>46.950627625436979</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>55.338621489497143</v>
+        <v>55.428478950886287</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>67.114684770224258</v>
+        <v>67.223520389898283</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>83.738055997664702</v>
+        <v>83.873681637302312</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>107.49707488504225</v>
+        <v>107.67099026636936</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16370,7 +16455,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>107.49707488504225</v>
+        <v>107.67099026636936</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16392,7 +16477,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>83.738055997664702</v>
+        <v>83.873681637302312</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16415,7 +16500,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>67.114684770224258</v>
+        <v>67.223520389898283</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16438,7 +16523,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>55.338621489497143</v>
+        <v>55.428478950886287</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16461,7 +16546,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>46.874410981267687</v>
+        <v>46.950627625436979</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16529,7 +16614,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16562,7 +16647,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-54.25</v>
+        <v>-55.3</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16582,7 +16667,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>2.0317375318709203</v>
+        <v>2.0284549446779483</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16591,7 +16676,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>2.0317375318709203</v>
+        <v>2.0284549446779483</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16611,7 +16696,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>69.966197853531199</v>
+        <v>70.073072026176192</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16645,7 +16730,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>3154945583.3319759</v>
+        <v>3154919979.4343109</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16667,7 +16752,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2878458887.258121</v>
+        <v>2878439684.3348718</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16751,7 +16836,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.2285116897931645</v>
+        <v>0.22851151994699426</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16802,7 +16887,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>54.25</v>
+        <v>55.3</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16817,7 +16902,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>40.689783631693679</v>
+        <v>40.756033206735104</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16864,7 +16949,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>67.114684770224258</v>
+        <v>67.223520389898283</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16922,7 +17007,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>55.338621489497143</v>
+        <v>55.428478950886287</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16980,7 +17065,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>83.738055997664702</v>
+        <v>83.873681637302312</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17007,7 +17092,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>66.906540031494217</v>
+        <v>67.015040207675483</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17081,7 +17166,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>46.874410981267687</v>
+        <v>46.950627625436979</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17139,7 +17224,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>107.49707488504225</v>
+        <v>107.67099026636936</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17165,7 +17250,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>67.934460321660282</v>
+        <v>68.044617081498245</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17227,7 +17312,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>67.932622227435317</v>
+        <v>68.042776025023315</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17375,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.17856104323192476</v>
+        <v>0.178569184894775</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17323,7 +17408,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>2.0317375318709203</v>
+        <v>2.0284549446779483</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17350,7 +17435,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.2282710054508783</v>
+        <v>3.2230552327973219</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17362,7 +17447,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>24.757456385444716</v>
+        <v>24.797600977222398</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17372,7 +17457,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>27.985727390895594</v>
+        <v>28.02065621001972</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17383,7 +17468,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.58804813847954274</v>
+        <v>0.58820172099052481</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17400,7 +17485,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>54.25</v>
+        <v>55.3</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17498,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11272920573653655</v>
+        <v>0.1059109318546132</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17439,7 +17524,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.2798174861169844</v>
+        <v>4.2729027769836412</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17451,7 +17536,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>39.313923797257111</v>
+        <v>39.377671922163337</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17461,7 +17546,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>43.593741283374094</v>
+        <v>43.650574699146979</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17472,7 +17557,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.35829708402828619</v>
+        <v>0.35850069305458931</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17499,7 +17584,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>5.235984672262993</v>
+        <v>5.2275251266976062</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17511,7 +17596,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>53.928564879639374</v>
+        <v>54.016010867165065</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17523,7 +17608,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>59.164549551902368</v>
+        <v>59.243535993862672</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17533,39 +17618,95 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.1290936989597562</v>
+        <v>0.12934279690477735</v>
       </c>
     </row>
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>431</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>4.8938567403557274</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>48.771686481876429</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>53.665543222232159</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.21129697585389229</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/0168.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0168.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF47A6F-09E0-46DF-8D93-22824D3ED030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F98115-3D7B-4112-9CF7-FE5566C99369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2382,13 +2359,61 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
   </si>
   <si>
     <t>N</t>
@@ -3086,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3600,14 +3625,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3665,9 +3684,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3675,7 +3691,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3767,9 +3782,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3784,9 +3796,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3794,6 +3803,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4106,10 +4142,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4124,11 +4160,11 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>435</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4183,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4156,10 +4192,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>436</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4173,9 +4209,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4196,20 +4232,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4225,17 +4261,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4249,14 +4285,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>CNY/HKD</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v/>
       </c>
       <c r="E15" s="5"/>
@@ -4266,34 +4302,34 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0845693200000002</v>
+        <v>1.0845693199999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4301,286 +4337,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>424</v>
-      </c>
-      <c r="D22" s="32" t="str">
+        <v>449</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C23" s="291" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C24" s="291" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>418</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E22" s="341" t="str">
+      <c r="E25" s="335" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>439</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (HKD):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>28.02065621001972</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (HKD) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>68.044617081498231</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>0.1059109318546132</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>437</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>0168.HK (HKD)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>433</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>28.020656210019716</v>
+      </c>
+      <c r="D29" s="339" t="str">
+        <f>D144</f>
+        <v/>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>428</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>43.650574699146972</v>
+      </c>
+      <c r="D30" s="148" t="str">
+        <f>D152</f>
+        <v/>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>59.243535993862658</v>
+      </c>
+      <c r="D31" s="148" t="str">
+        <f>D160</f>
+        <v/>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>440</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>53.665543222232152</v>
+      </c>
+      <c r="D32" s="148" t="str">
+        <f>D168</f>
+        <v/>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>442</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>3878068070.3077545</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>1191305772</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-1191305772</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>177201315.4343105</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>177201315.4343105</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-21837054</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>155364261.4343105</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-146634564.47167698</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-1008358082.9355162</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4588,1080 +4676,1109 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-146634564.47167698</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>3154919979.4343109</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-1008358082.9355162</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>2878439684.3348718</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>3154919979.4343109</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>2878439684.3348718</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.1382077971811766E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+        <v>4.1382077971811752E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.6680921241915881E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+        <v>3.6680921241915895E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D73" s="286" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
+        <v>248</v>
+      </c>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c